--- a/docs/feature-list.xlsx
+++ b/docs/feature-list.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="367">
   <si>
     <t>端</t>
   </si>
@@ -1045,6 +1045,96 @@
   </si>
   <si>
     <t>收银台标题区改白底（与下方区域一致）；AI 问书 logo 由微信绿换成会话同款电光靛紫色动画球；支付成功对勾由珊瑚色改为绿色 / 主题色（含同心圆光环），避免被误解为未支付成功。（0609 调整）</t>
+  </si>
+  <si>
+    <t>前台精修(0610)</t>
+  </si>
+  <si>
+    <t>后台精修(0610)</t>
+  </si>
+  <si>
+    <t>平台精修(0610)</t>
+  </si>
+  <si>
+    <t>机构后台 / 平台后台</t>
+  </si>
+  <si>
+    <t>登录落地页 扫码入口移除</t>
+  </si>
+  <si>
+    <t>落地页移除「在浏览器中打开？扫码登录」入口（不在原型上绘制），外部浏览器扫码授权场景仅在本清单保留说明。（0610）</t>
+  </si>
+  <si>
+    <t>AI 答案 点赞/反馈 icon 样式</t>
+  </si>
+  <si>
+    <t>点赞 / 反馈 icon 改灰色系描边填充样式（选中态为灰色填充、非主题色），参考图 1。（0610）</t>
+  </si>
+  <si>
+    <t>输入框 语音输入（会话页底部浮层）</t>
+  </si>
+  <si>
+    <t>麦克风按钮单击 / 长按进入语音输入态——在当前会话页底部弹出音浪动画浮层（非全屏新页；浮层背底渐变与会话背景自然过渡）；点击音浪外任意位置即关闭并发送本次语音问题、触发 AI 回答。（0610 新增）</t>
+  </si>
+  <si>
+    <t>我的永享 放大预览定位</t>
+  </si>
+  <si>
+    <t>放大预览内容垂直方向调整为水平居中、略偏上（不再贴顶过高）。（0610）</t>
+  </si>
+  <si>
+    <t>知识 KP 关联 Agent 下拉宽度</t>
+  </si>
+  <si>
+    <t>「关联 Agent」下拉框宽度收敛为与表单其他控件一致（详见全局「后台下拉选择器」规范）。（0610）</t>
+  </si>
+  <si>
+    <t>知识库 下载按钮/切片对齐/PDF icon</t>
+  </si>
+  <si>
+    <t>列表操作列最前增加「下载」按钮，可下载已上传的知识文件内容；上传弹窗切片方式字段与下方上传区域左对齐、上传拖拽区降高更紧凑；文件列表 PDF 文件 icon 中「PDF」三字母缩小并与边框留间距。（0610）</t>
+  </si>
+  <si>
+    <t>知识库 向量化失败检索状态</t>
+  </si>
+  <si>
+    <t>向量化失败的文件检索状态直接显示「下架」（而非空）；失败原因悬浮提示统一为指标同款问号 icon。（0610）</t>
+  </si>
+  <si>
+    <t>兑换码详情 右侧抽屉化</t>
+  </si>
+  <si>
+    <t>兑换码点「详情」改为当前页右侧抽屉展示（交互对齐二维码码包）：支持状态单选筛选、兑换用户 / 手机号模糊匹配、导出；明细列「状态」「权益」支持排序。（0610）</t>
+  </si>
+  <si>
+    <t>数据看板 总览两段式</t>
+  </si>
+  <si>
+    <t>「总览 Tab」区分「实时总览」（累计注册 / 当前会员 / 累计 GMV / 当日 DAU 等存量·累计指标，不随时间筛选）与「经营分析」（随时间区间联动的趋势指标），复用主控台两段式。（0610）</t>
+  </si>
+  <si>
+    <t>机构账户列表 三列排序</t>
+  </si>
+  <si>
+    <t>机构账户列表「上级机构」「角色」「状态」三列支持点击表头排序。（0610）</t>
+  </si>
+  <si>
+    <t>模型用量 两段式</t>
+  </si>
+  <si>
+    <t>模型用量区分「实时总览」（平台开通至今累计 tokens / 累计调用次数）与「经营分析」（随时间区间的 tokens、调用次数、平均响应、各机构趋势），复用主控台两段式。（0610）</t>
+  </si>
+  <si>
+    <t>后台下拉选择器（两端通用）</t>
+  </si>
+  <si>
+    <t>统一下拉框宽度为与同表单其他控件一致（通查机构后台 / 平台超管所有下拉，不符的统一整改）；选中后回显文字不使用主题色、与普通 UI 文本色一致（仅反映数据变化）。（0610）</t>
+  </si>
+  <si>
+    <t>后台侧栏收起态（两端通用）</t>
+  </si>
+  <si>
+    <t>左侧菜单收起后，鼠标悬浮浮出的菜单名小面板层级修正，不再被右侧表单内容遮盖。（0610）</t>
   </si>
 </sst>
 </file>
@@ -2265,7 +2355,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D111"/>
+  <dimension ref="A1:D124"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -3828,8 +3918,190 @@
         <v>336</v>
       </c>
     </row>
+    <row r="112" spans="1:4">
+      <c r="A112" t="s">
+        <v>194</v>
+      </c>
+      <c r="B112" t="s">
+        <v>337</v>
+      </c>
+      <c r="C112" t="s">
+        <v>341</v>
+      </c>
+      <c r="D112" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" t="s">
+        <v>194</v>
+      </c>
+      <c r="B113" t="s">
+        <v>337</v>
+      </c>
+      <c r="C113" t="s">
+        <v>343</v>
+      </c>
+      <c r="D113" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4">
+      <c r="A114" t="s">
+        <v>194</v>
+      </c>
+      <c r="B114" t="s">
+        <v>337</v>
+      </c>
+      <c r="C114" t="s">
+        <v>345</v>
+      </c>
+      <c r="D114" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4">
+      <c r="A115" t="s">
+        <v>194</v>
+      </c>
+      <c r="B115" t="s">
+        <v>337</v>
+      </c>
+      <c r="C115" t="s">
+        <v>347</v>
+      </c>
+      <c r="D115" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4">
+      <c r="A116" t="s">
+        <v>223</v>
+      </c>
+      <c r="B116" t="s">
+        <v>338</v>
+      </c>
+      <c r="C116" t="s">
+        <v>349</v>
+      </c>
+      <c r="D116" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4">
+      <c r="A117" t="s">
+        <v>223</v>
+      </c>
+      <c r="B117" t="s">
+        <v>338</v>
+      </c>
+      <c r="C117" t="s">
+        <v>351</v>
+      </c>
+      <c r="D117" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4">
+      <c r="A118" t="s">
+        <v>223</v>
+      </c>
+      <c r="B118" t="s">
+        <v>338</v>
+      </c>
+      <c r="C118" t="s">
+        <v>353</v>
+      </c>
+      <c r="D118" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4">
+      <c r="A119" t="s">
+        <v>223</v>
+      </c>
+      <c r="B119" t="s">
+        <v>338</v>
+      </c>
+      <c r="C119" t="s">
+        <v>355</v>
+      </c>
+      <c r="D119" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4">
+      <c r="A120" t="s">
+        <v>223</v>
+      </c>
+      <c r="B120" t="s">
+        <v>338</v>
+      </c>
+      <c r="C120" t="s">
+        <v>357</v>
+      </c>
+      <c r="D120" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4">
+      <c r="A121" t="s">
+        <v>218</v>
+      </c>
+      <c r="B121" t="s">
+        <v>339</v>
+      </c>
+      <c r="C121" t="s">
+        <v>359</v>
+      </c>
+      <c r="D121" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4">
+      <c r="A122" t="s">
+        <v>218</v>
+      </c>
+      <c r="B122" t="s">
+        <v>339</v>
+      </c>
+      <c r="C122" t="s">
+        <v>361</v>
+      </c>
+      <c r="D122" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4">
+      <c r="A123" t="s">
+        <v>340</v>
+      </c>
+      <c r="B123" t="s">
+        <v>338</v>
+      </c>
+      <c r="C123" t="s">
+        <v>363</v>
+      </c>
+      <c r="D123" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4">
+      <c r="A124" t="s">
+        <v>340</v>
+      </c>
+      <c r="B124" t="s">
+        <v>338</v>
+      </c>
+      <c r="C124" t="s">
+        <v>365</v>
+      </c>
+      <c r="D124" t="s">
+        <v>366</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D111" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D124" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/feature-list.xlsx
+++ b/docs/feature-list.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="472">
   <si>
     <t>端</t>
   </si>
@@ -1135,6 +1135,321 @@
   </si>
   <si>
     <t>左侧菜单收起后，鼠标悬浮浮出的菜单名小面板层级修正，不再被右侧表单内容遮盖。（0610）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">前台精修(0613)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">登录与绑定按 H5 能力重构</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H5 网页授权可取 openid/昵称/头像/性别/地区但无法取手机号，手机号统一用「手机号+验证码」绑定、不分浏览器环境；删除账号合并逻辑，手机号被占用直接提示更换或联系客服；手机号验证码登录用户不绑定微信信息。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">微信两种环境授权流程上线</t>
+  </si>
+  <si>
+    <t xml:space="preserve">微信内→官方授权弹窗（昵称/头像/性别/地区），浏览器→open.weixin.qq.com 扫码授权；落地页可切换演示环境；授权回调自动带回头像/昵称/性别/地区。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">敏感操作手机号绑定门槛（合规）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">支付下单、兑换码核销、开通/充值会员三类操作前置校验是否已绑手机号，未绑引导前往「我的-绑定手机号」绑定后继续，不强制所有用户绑定。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">个人资料（头像/昵称/性别/地区）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">微信环境头像/昵称/性别/地区由授权自动带回（头像用微信头像）；非微信环境用户可上传头像、填写性别与地区。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我的纸书（扫码解锁的知识 KP）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">展示用户扫线下纸书二维码绑定、获权益的知识 KP，卡片布局（封面+名称+扫码时间），支持按名称模糊搜索；免费用户亦可畅享该 KP 全部文/图/音/视，永享标内容仍需单独购买。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我的永享搜索与筛选</t>
+  </si>
+  <si>
+    <t xml:space="preserve">列表顶部新增搜索（按文件名模糊匹配）+ 文件类型筛选（全部/图片/音频/视频）。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">会员中心免费 vs 会员对比表</t>
+  </si>
+  <si>
+    <t xml:space="preserve">非会员页改为「免费/会员」权益对比表（逐项✅/✗，永享为单独购买），强化付费价值感。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">自动续费提前 3 天短信通知</t>
+  </si>
+  <si>
+    <t xml:space="preserve">开启自动续费后弹 3 秒消失 tips「将于到期前 3 天短信提醒」，权益说明标注「提前 3 天短信通知续费」。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">答案溯源第三方跳转倒计时</t>
+  </si>
+  <si>
+    <t xml:space="preserve">web 类型来源跳转第三方前增加 3 秒倒计时过渡浮层「即将跳转至第三方页面…」，倒计时结束再打开来源网页。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">换绑手机号仅新号+验证码</t>
+  </si>
+  <si>
+    <t xml:space="preserve">确认换绑仅需「新手机号+验证码」，不要求旧手机号双重校验；异常场景留待生产期风控/客服申诉。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">微信内浏览器登录流程</t>
+  </si>
+  <si>
+    <t xml:space="preserve">点「微信授权登录」→官方授权弹窗(授权昵称/头像/性别/地区)→允许携code回调进首页(手机号空、后续按需绑定)；拒绝留登录页；不出二维码、不弹手机号授权窗。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">非微信浏览器扫码登录流程</t>
+  </si>
+  <si>
+    <t xml:space="preserve">点「微信授权登录」→open.weixin.qq.com动态二维码→微信扫码、手机端确认→允许携code回调进首页，流程同微信内。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">手机号验证码登录</t>
+  </si>
+  <si>
+    <t xml:space="preserve">两环境一致，手机号+短信验证码校验通过即登录；该方式不获取、不绑定任何微信信息。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">微信网页授权可获取字段</t>
+  </si>
+  <si>
+    <t xml:space="preserve">snsapi_userinfo 可取 openid/unionid/昵称/头像/性别/地区(国家省市)，不含手机号(H5公众号无手机号能力，一键授权手机号为小程序专属)。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">手机号绑定与冲突(不合并)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">绑定/换绑统一手机号+验证码、不要旧号双重校验；待绑号已被占用→提示更换或联系客服、不合并不顶替；A/B两微信绑同号后者同样提示占用。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">后台精修(0613)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">订单退款全链路</t>
+  </si>
+  <si>
+    <t xml:space="preserve">订单列表操作列加「退款」(危险色)→金额弹窗(显示实付/支持部分退款)→二次确认→原路退回；状态扩展退款中/已退款/部分退款；订单详情退款时间线；GMV扣减已退；主控台+看板加退款指标。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">知识库去切片方式</t>
+  </si>
+  <si>
+    <t xml:space="preserve">上传弹窗去掉「切片方式」选择，直接上传、系统默认处理。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">知识文件格式/大小/时长上限</t>
+  </si>
+  <si>
+    <t xml:space="preserve">文档PDF/DOC/DOCX/PPT/PPTX/TXT/MD≤100MB；图片JPG/PNG≤20MB；音频MP3/WAV/M4A≤300MB≤120分钟；视频MP4/MOV≤1GB≤90分钟(更长分段)。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">分享时效改名</t>
+  </si>
+  <si>
+    <t xml:space="preserve">已分享列表「时效」改为「链接分享有效期」，新建弹窗有效期字段同步该叫法。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agent编辑瘦身</t>
+  </si>
+  <si>
+    <t xml:space="preserve">移除「形象图」上传(头像保留)；移除「AI会话引导问题示例」区块。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C端用户地区性别+导出</t>
+  </si>
+  <si>
+    <t xml:space="preserve">用户列表/详情展示地区、性别(无则空)；用户列表新增「导出」(当前筛选结果)。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">看板转化漏斗改百分比</t>
+  </si>
+  <si>
+    <t xml:space="preserve">会员漏斗、永享转化漏斗由数量改为百分比呈现(各环节相对转化%)。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">被提问数Top10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">热门KP「提问数Top10」改名为「被提问数Top10 KP」，语义更清晰。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">看板用户/提问领域统计</t>
+  </si>
+  <si>
+    <t xml:space="preserve">用户分析加地区分布、性别分布；提问分析加提问领域分布(脑科学/心理/卒中/超声…)。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">答案反馈Tab(新增)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">汇总前台点赞/点踩/反馈(前台已埋点、后台原未呈现)：点赞率/点踩率+反馈明细(问题/标签/时间/关联Agent·KP)，供运营迭代知识库。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">回答策略3条明确</t>
+  </si>
+  <si>
+    <t xml:space="preserve">保留3条并明确语义：严谨模式/透明兜底(默认)/流畅模式；想加的「直接回答不告知」即策略①、不新增第4条。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">机构配额+套餐预设</t>
+  </si>
+  <si>
+    <t xml:space="preserve">创建机构加KP数/存储/月度Token三限额+4档套餐(基础10·20GB·5千万/专业50·100GB·2亿/旗舰200·500GB·10亿/定制)；token按月重置、机构可设服务有效期；用量看板已用·上限进度预警。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">微信配置整合(公众号+支付)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">机构「微信支付配置」升级「微信配置」：①公众号AppID/AppSecret/网页授权回调域名②微信支付MchID/APIv3/证书；标注公众号AppID需与商户号绑定。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">机构品牌外观(多租户色系)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Organization加logo+主视觉色+辅助视觉色(主→辅渐变)；创建/详情品牌外观配置(传logo智能取色+渐变预览)；前台品牌球+主强调色读取该机构配色。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">多机构Token图表优化</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「全部机构」视图改总量趋势(单线/面积)+Top机构token排行榜(条形)、弃多折线；选中单机构看该机构趋势；主控台/看板加全部·指定机构筛选。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全域KP视图(新增)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">跨机构KP聚合只读视图(机构/名称/状态/文件数/提问数+按机构·状态·名称筛选)，供平台监管统计；Agent/反馈/兑换码不建全域、从机构详情下钻。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBAC权限三态</t>
+  </si>
+  <si>
+    <t xml:space="preserve">角色对每个功能点设「无/只读/可操作」三态，替代角色级只读；编辑网格用三态选择器，按功能粒度控制读写。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">后台列表操作列固定右侧</t>
+  </si>
+  <si>
+    <t xml:space="preserve">两后台所有列表(含详情内嵌)的「操作」列sticky固定右侧、中间字段横向滚动；通查全部含操作列列表统一生效。（0613）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">实测精修(0613-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">扫码登录页美化+去Logo+演示开关标识</t>
+  </si>
+  <si>
+    <t xml:space="preserve">非微信扫码登录用内嵌二维码(WxLogin)整页可美化、二维码中央不放Logo;演示环境切换移到协议下方+加「仅演示·环境切换」标识。（0613-2）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我的纸书扫一扫+卡片重排</t>
+  </si>
+  <si>
+    <t xml:space="preserve">文案改「微信扫码解锁纸书全部数字内容，永享内容另购」;右上角扫一扫调相机扫码进KP会话(新需求);去永享标;点卡片进KP会话;名称两行高+扫码时间钉底对齐。（0613-2）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">个人资料重做</t>
+  </si>
+  <si>
+    <t xml:space="preserve">删独立菜单(顶部头像箭头进入);头像调相册+圆形裁剪页;昵称行内改;性别仅男/女(去保密);地区改省/市/区级联真实数据、居中弹窗、不手填。（0613-2）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">占用提示复用客服弹窗</t>
+  </si>
+  <si>
+    <t xml:space="preserve">手机号占用页「联系平台客服」复用「我的-联系客服」同款弹窗(含二维码/电话/邮箱)，不另绘。（0613-2）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">会员文案+门槛弹窗居中</t>
+  </si>
+  <si>
+    <t xml:space="preserve">会员对比「基础图文问答」→「基础知识问答」;手机号门槛拦截弹窗文案两行、整体垂直居中。（0613-2）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">溯源全链路跳转倒计时</t>
+  </si>
+  <si>
+    <t xml:space="preserve">跳出AI问书的链接(web互联网+KP纸书/运营填写链接)都先弹3秒过渡浮层;浮层去掉URL地址展示。（0613-2）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">订单退款精修</t>
+  </si>
+  <si>
+    <t xml:space="preserve">退款状态独立成列(未退款/退款中/部分退款/全额退款)与订单状态解耦;金额仅数字不超实付;二次确认加账户信息;时间线降序(最新在上);发起人=登录账户名+真实姓名(括号);提示珊瑚红+黄色警告icon。（0613-2）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">数据看板退款指标+时间联动</t>
+  </si>
+  <si>
+    <t xml:space="preserve">数据看板补退款指标(主控台已加、看板漏了);非实时指标随今日/7日/30日做假数据联动。（0613-2）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">提问分析并列+关键词云</t>
+  </si>
+  <si>
+    <t xml:space="preserve">按Agent提问分布与提问领域分布改左右并列;新增关键词云(高频提问词,词频越高字越大)。（0613-2）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">答案反馈独立工作台</t>
+  </si>
+  <si>
+    <t xml:space="preserve">提为数据中心独立菜单(与数据看板同级);去待处理指标;明细分页+按标签/时间区间/问题搜索;去关联Agent/KP列、加反馈人(标会员);详情看问题+AI答案含多模态;导出仅问答文本(不含媒体/溯源)。（0613-2）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">知识库上传居中+规格告知</t>
+  </si>
+  <si>
+    <t xml:space="preserve">上传弹窗拖拽区居中;上传区显示支持格式/大小/时长清晰告知。（0613-2）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">文件规格修订</t>
+  </si>
+  <si>
+    <t xml:space="preserve">文档收敛为PDF/DOC/DOCX/TXT/MD(去PPT);视频时长上限改≤60分钟。（0613-2）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C端列表/订单排序</t>
+  </si>
+  <si>
+    <t xml:space="preserve">用户列表支持按地区/性别排序;用户详情全部订单支持按类型/状态/支付方式排序。（0613-2）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">配额套餐移位+平铺</t>
+  </si>
+  <si>
+    <t xml:space="preserve">配额/套餐从创建机构移到机构详情独立「套餐/配额」Tab;套餐平铺卡片(基础/专业/旗舰)点选自动填充;单位KP=个、存储=GB、月度Token=百万(M)/亿。（0613-2）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">微信配置美化+限制提示</t>
+  </si>
+  <si>
+    <t xml:space="preserve">公众号/支付两块分区卡片强区分;提示改后台标准字号色;加结构化限制提示(网页授权需认证服务号、JSAPI支付需服务号+商户号且AppID与商户号绑定)。（0613-2）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">用量看板重排+品牌取色+经营分析重排</t>
+  </si>
+  <si>
+    <t xml:space="preserve">用量看板重排(配额进度重点+2×2);品牌外观真实canvas智能取色+删「全量主题化后续」句;经营分析版式重排;Token单位用M/亿。（0613-2）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">角色权限图例</t>
+  </si>
+  <si>
+    <t xml:space="preserve">角色权限页加「无/只读/可操作」含义说明(无=看不见菜单/只读=可看不可操作/可操作=全部可操作)。（0613-2）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">指标tooltip压盖修复+必填红星+操作列加深+保存按钮</t>
+  </si>
+  <si>
+    <t xml:space="preserve">修指标问号悬浮被左侧菜单压盖bug(通查);必填项补红星(通查);固定操作列底色加深;保存按钮按交互就近+兜底默认、消除忽左忽右。（0613-2）</t>
   </si>
 </sst>
 </file>
@@ -2355,7 +2670,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D124"/>
+  <dimension ref="A1:D175"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -4100,8 +4415,722 @@
         <v>366</v>
       </c>
     </row>
+    <row r="125" spans="1:4">
+      <c r="A125" t="s">
+        <v>194</v>
+      </c>
+      <c r="B125" t="s">
+        <v>367</v>
+      </c>
+      <c r="C125" t="s">
+        <v>368</v>
+      </c>
+      <c r="D125" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4">
+      <c r="A126" t="s">
+        <v>194</v>
+      </c>
+      <c r="B126" t="s">
+        <v>367</v>
+      </c>
+      <c r="C126" t="s">
+        <v>370</v>
+      </c>
+      <c r="D126" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4">
+      <c r="A127" t="s">
+        <v>194</v>
+      </c>
+      <c r="B127" t="s">
+        <v>367</v>
+      </c>
+      <c r="C127" t="s">
+        <v>372</v>
+      </c>
+      <c r="D127" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4">
+      <c r="A128" t="s">
+        <v>194</v>
+      </c>
+      <c r="B128" t="s">
+        <v>367</v>
+      </c>
+      <c r="C128" t="s">
+        <v>374</v>
+      </c>
+      <c r="D128" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4">
+      <c r="A129" t="s">
+        <v>194</v>
+      </c>
+      <c r="B129" t="s">
+        <v>367</v>
+      </c>
+      <c r="C129" t="s">
+        <v>376</v>
+      </c>
+      <c r="D129" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4">
+      <c r="A130" t="s">
+        <v>194</v>
+      </c>
+      <c r="B130" t="s">
+        <v>367</v>
+      </c>
+      <c r="C130" t="s">
+        <v>378</v>
+      </c>
+      <c r="D130" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4">
+      <c r="A131" t="s">
+        <v>194</v>
+      </c>
+      <c r="B131" t="s">
+        <v>367</v>
+      </c>
+      <c r="C131" t="s">
+        <v>380</v>
+      </c>
+      <c r="D131" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4">
+      <c r="A132" t="s">
+        <v>194</v>
+      </c>
+      <c r="B132" t="s">
+        <v>367</v>
+      </c>
+      <c r="C132" t="s">
+        <v>382</v>
+      </c>
+      <c r="D132" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4">
+      <c r="A133" t="s">
+        <v>194</v>
+      </c>
+      <c r="B133" t="s">
+        <v>367</v>
+      </c>
+      <c r="C133" t="s">
+        <v>384</v>
+      </c>
+      <c r="D133" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4">
+      <c r="A134" t="s">
+        <v>194</v>
+      </c>
+      <c r="B134" t="s">
+        <v>367</v>
+      </c>
+      <c r="C134" t="s">
+        <v>386</v>
+      </c>
+      <c r="D134" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4">
+      <c r="A135" t="s">
+        <v>194</v>
+      </c>
+      <c r="B135" t="s">
+        <v>367</v>
+      </c>
+      <c r="C135" t="s">
+        <v>388</v>
+      </c>
+      <c r="D135" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4">
+      <c r="A136" t="s">
+        <v>194</v>
+      </c>
+      <c r="B136" t="s">
+        <v>367</v>
+      </c>
+      <c r="C136" t="s">
+        <v>390</v>
+      </c>
+      <c r="D136" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4">
+      <c r="A137" t="s">
+        <v>194</v>
+      </c>
+      <c r="B137" t="s">
+        <v>367</v>
+      </c>
+      <c r="C137" t="s">
+        <v>392</v>
+      </c>
+      <c r="D137" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4">
+      <c r="A138" t="s">
+        <v>194</v>
+      </c>
+      <c r="B138" t="s">
+        <v>367</v>
+      </c>
+      <c r="C138" t="s">
+        <v>394</v>
+      </c>
+      <c r="D138" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4">
+      <c r="A139" t="s">
+        <v>194</v>
+      </c>
+      <c r="B139" t="s">
+        <v>367</v>
+      </c>
+      <c r="C139" t="s">
+        <v>396</v>
+      </c>
+      <c r="D139" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4">
+      <c r="A140" t="s">
+        <v>223</v>
+      </c>
+      <c r="B140" t="s">
+        <v>398</v>
+      </c>
+      <c r="C140" t="s">
+        <v>399</v>
+      </c>
+      <c r="D140" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4">
+      <c r="A141" t="s">
+        <v>223</v>
+      </c>
+      <c r="B141" t="s">
+        <v>398</v>
+      </c>
+      <c r="C141" t="s">
+        <v>401</v>
+      </c>
+      <c r="D141" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" t="s">
+        <v>223</v>
+      </c>
+      <c r="B142" t="s">
+        <v>398</v>
+      </c>
+      <c r="C142" t="s">
+        <v>403</v>
+      </c>
+      <c r="D142" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4">
+      <c r="A143" t="s">
+        <v>223</v>
+      </c>
+      <c r="B143" t="s">
+        <v>398</v>
+      </c>
+      <c r="C143" t="s">
+        <v>405</v>
+      </c>
+      <c r="D143" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4">
+      <c r="A144" t="s">
+        <v>223</v>
+      </c>
+      <c r="B144" t="s">
+        <v>398</v>
+      </c>
+      <c r="C144" t="s">
+        <v>407</v>
+      </c>
+      <c r="D144" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4">
+      <c r="A145" t="s">
+        <v>223</v>
+      </c>
+      <c r="B145" t="s">
+        <v>398</v>
+      </c>
+      <c r="C145" t="s">
+        <v>409</v>
+      </c>
+      <c r="D145" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4">
+      <c r="A146" t="s">
+        <v>223</v>
+      </c>
+      <c r="B146" t="s">
+        <v>398</v>
+      </c>
+      <c r="C146" t="s">
+        <v>411</v>
+      </c>
+      <c r="D146" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4">
+      <c r="A147" t="s">
+        <v>223</v>
+      </c>
+      <c r="B147" t="s">
+        <v>398</v>
+      </c>
+      <c r="C147" t="s">
+        <v>413</v>
+      </c>
+      <c r="D147" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4">
+      <c r="A148" t="s">
+        <v>223</v>
+      </c>
+      <c r="B148" t="s">
+        <v>398</v>
+      </c>
+      <c r="C148" t="s">
+        <v>415</v>
+      </c>
+      <c r="D148" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4">
+      <c r="A149" t="s">
+        <v>223</v>
+      </c>
+      <c r="B149" t="s">
+        <v>398</v>
+      </c>
+      <c r="C149" t="s">
+        <v>417</v>
+      </c>
+      <c r="D149" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4">
+      <c r="A150" t="s">
+        <v>223</v>
+      </c>
+      <c r="B150" t="s">
+        <v>398</v>
+      </c>
+      <c r="C150" t="s">
+        <v>419</v>
+      </c>
+      <c r="D150" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4">
+      <c r="A151" t="s">
+        <v>218</v>
+      </c>
+      <c r="B151" t="s">
+        <v>398</v>
+      </c>
+      <c r="C151" t="s">
+        <v>421</v>
+      </c>
+      <c r="D151" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4">
+      <c r="A152" t="s">
+        <v>218</v>
+      </c>
+      <c r="B152" t="s">
+        <v>398</v>
+      </c>
+      <c r="C152" t="s">
+        <v>423</v>
+      </c>
+      <c r="D152" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4">
+      <c r="A153" t="s">
+        <v>218</v>
+      </c>
+      <c r="B153" t="s">
+        <v>398</v>
+      </c>
+      <c r="C153" t="s">
+        <v>425</v>
+      </c>
+      <c r="D153" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4">
+      <c r="A154" t="s">
+        <v>218</v>
+      </c>
+      <c r="B154" t="s">
+        <v>398</v>
+      </c>
+      <c r="C154" t="s">
+        <v>427</v>
+      </c>
+      <c r="D154" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4">
+      <c r="A155" t="s">
+        <v>218</v>
+      </c>
+      <c r="B155" t="s">
+        <v>398</v>
+      </c>
+      <c r="C155" t="s">
+        <v>429</v>
+      </c>
+      <c r="D155" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4">
+      <c r="A156" t="s">
+        <v>218</v>
+      </c>
+      <c r="B156" t="s">
+        <v>398</v>
+      </c>
+      <c r="C156" t="s">
+        <v>431</v>
+      </c>
+      <c r="D156" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4">
+      <c r="A157" t="s">
+        <v>229</v>
+      </c>
+      <c r="B157" t="s">
+        <v>398</v>
+      </c>
+      <c r="C157" t="s">
+        <v>433</v>
+      </c>
+      <c r="D157" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4">
+      <c r="A158" t="s">
+        <v>194</v>
+      </c>
+      <c r="B158" t="s">
+        <v>435</v>
+      </c>
+      <c r="C158" t="s">
+        <v>436</v>
+      </c>
+      <c r="D158" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4">
+      <c r="A159" t="s">
+        <v>194</v>
+      </c>
+      <c r="B159" t="s">
+        <v>435</v>
+      </c>
+      <c r="C159" t="s">
+        <v>438</v>
+      </c>
+      <c r="D159" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4">
+      <c r="A160" t="s">
+        <v>194</v>
+      </c>
+      <c r="B160" t="s">
+        <v>435</v>
+      </c>
+      <c r="C160" t="s">
+        <v>440</v>
+      </c>
+      <c r="D160" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4">
+      <c r="A161" t="s">
+        <v>194</v>
+      </c>
+      <c r="B161" t="s">
+        <v>435</v>
+      </c>
+      <c r="C161" t="s">
+        <v>442</v>
+      </c>
+      <c r="D161" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4">
+      <c r="A162" t="s">
+        <v>194</v>
+      </c>
+      <c r="B162" t="s">
+        <v>435</v>
+      </c>
+      <c r="C162" t="s">
+        <v>444</v>
+      </c>
+      <c r="D162" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4">
+      <c r="A163" t="s">
+        <v>194</v>
+      </c>
+      <c r="B163" t="s">
+        <v>435</v>
+      </c>
+      <c r="C163" t="s">
+        <v>446</v>
+      </c>
+      <c r="D163" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4">
+      <c r="A164" t="s">
+        <v>223</v>
+      </c>
+      <c r="B164" t="s">
+        <v>435</v>
+      </c>
+      <c r="C164" t="s">
+        <v>448</v>
+      </c>
+      <c r="D164" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4">
+      <c r="A165" t="s">
+        <v>223</v>
+      </c>
+      <c r="B165" t="s">
+        <v>435</v>
+      </c>
+      <c r="C165" t="s">
+        <v>450</v>
+      </c>
+      <c r="D165" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4">
+      <c r="A166" t="s">
+        <v>223</v>
+      </c>
+      <c r="B166" t="s">
+        <v>435</v>
+      </c>
+      <c r="C166" t="s">
+        <v>452</v>
+      </c>
+      <c r="D166" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4">
+      <c r="A167" t="s">
+        <v>223</v>
+      </c>
+      <c r="B167" t="s">
+        <v>435</v>
+      </c>
+      <c r="C167" t="s">
+        <v>454</v>
+      </c>
+      <c r="D167" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4">
+      <c r="A168" t="s">
+        <v>223</v>
+      </c>
+      <c r="B168" t="s">
+        <v>435</v>
+      </c>
+      <c r="C168" t="s">
+        <v>456</v>
+      </c>
+      <c r="D168" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4">
+      <c r="A169" t="s">
+        <v>223</v>
+      </c>
+      <c r="B169" t="s">
+        <v>435</v>
+      </c>
+      <c r="C169" t="s">
+        <v>458</v>
+      </c>
+      <c r="D169" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4">
+      <c r="A170" t="s">
+        <v>223</v>
+      </c>
+      <c r="B170" t="s">
+        <v>435</v>
+      </c>
+      <c r="C170" t="s">
+        <v>460</v>
+      </c>
+      <c r="D170" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4">
+      <c r="A171" t="s">
+        <v>218</v>
+      </c>
+      <c r="B171" t="s">
+        <v>435</v>
+      </c>
+      <c r="C171" t="s">
+        <v>462</v>
+      </c>
+      <c r="D171" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4">
+      <c r="A172" t="s">
+        <v>218</v>
+      </c>
+      <c r="B172" t="s">
+        <v>435</v>
+      </c>
+      <c r="C172" t="s">
+        <v>464</v>
+      </c>
+      <c r="D172" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4">
+      <c r="A173" t="s">
+        <v>218</v>
+      </c>
+      <c r="B173" t="s">
+        <v>435</v>
+      </c>
+      <c r="C173" t="s">
+        <v>466</v>
+      </c>
+      <c r="D173" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4">
+      <c r="A174" t="s">
+        <v>218</v>
+      </c>
+      <c r="B174" t="s">
+        <v>435</v>
+      </c>
+      <c r="C174" t="s">
+        <v>468</v>
+      </c>
+      <c r="D174" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4">
+      <c r="A175" t="s">
+        <v>229</v>
+      </c>
+      <c r="B175" t="s">
+        <v>435</v>
+      </c>
+      <c r="C175" t="s">
+        <v>470</v>
+      </c>
+      <c r="D175" t="s">
+        <v>471</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D124" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D175" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/feature-list.xlsx
+++ b/docs/feature-list.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18740" windowHeight="16660"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="功能清单" sheetId="1" r:id="rId1"/>
@@ -12,8 +12,8 @@
     <sheet name="用量看板指标" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">功能清单!$A$1:$D$111</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">数据看板指标!$A$1:$D$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">功能清单!$A$1:$D$238</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">数据看板指标!$A$1:$D$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">用量看板指标!$A$1:$B$5</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1278" uniqueCount="737">
   <si>
     <t>端</t>
   </si>
@@ -738,234 +738,1176 @@
     <t>后台 KPI / 用量指标名称紧随其后置浅灰小问号,悬浮展示统计规则与统计区间、移开即消失;tooltip 自适应位置,行内最后一张卡片改为向左展开,避免被页面右缘遮挡。</t>
   </si>
   <si>
-    <t>看板 Tab</t>
+    <t>前台精修(0609)</t>
+  </si>
+  <si>
+    <t>微信授权登录（两种场景）</t>
+  </si>
+  <si>
+    <t>①微信 App 内打开 H5 → 专属授权弹窗：点击「微信授权登录」不出二维码，直接唤起微信官方授权弹窗（询问授予昵称、头像权限）；「允许」携 code 走回调——新用户引导绑定手机号、已绑手机号用户直接进入 AI 会话页，「拒绝」留在登录页。②外部浏览器打开 H5 → 微信扫码授权页：由 open.weixin.qq.com 渲染动态二维码，用户微信扫码后手机端弹出授权确认（允许/拒绝）；「允许」携 code 跳转回调页继续①的绑定/进入流程，「拒绝」退回登录页。（0609 新增）</t>
+  </si>
+  <si>
+    <t>后台精修(0609)</t>
+  </si>
+  <si>
+    <t>知识库 纯音频/纯视频 去确认</t>
+  </si>
+  <si>
+    <t>纯音频/纯视频上传后，系统自动提取字幕 → 提取完成后直接向量化，去掉原「用户确认」步骤（无需二次确认）。（0609 调整，替代原「知识库—纯音频 / 纯视频」中的确认环节）</t>
+  </si>
+  <si>
+    <t>知识库文件 上架/下架 + 检索可见性</t>
+  </si>
+  <si>
+    <t>已向量化成功的文件提供「上架/下架」切换并展示状态；仅「上架」文件参与用户问答检索，「下架」不参与（与 KP 发布状态叠加生效）。「重试」仅对向量化失败的文件提供，已向量化成功的不再提供重试。（0609 新增/调整）</t>
+  </si>
+  <si>
+    <t>知识文件名重复规则</t>
+  </si>
+  <si>
+    <t>同一 KP 内上传的知识文件文件名允许重复、不做唯一性限制。（0609 新增）</t>
+  </si>
+  <si>
+    <t>上传知识文件弹窗</t>
+  </si>
+  <si>
+    <t>知识库顶部入口改为「上传知识文件」按钮，点击居中弹出上传表单：设置切片方式 + 点击/拖拽多文件上传（支持文件与多媒体混传、不支持文件夹嵌套），每个文件实时显示上传进度，全部完成后点「进入知识库」进入解析、向量化处理；上传多个则在知识库列表展示多条。（0609 新增）</t>
+  </si>
+  <si>
+    <t>二维码包 列表字段与查看详情</t>
+  </si>
+  <si>
+    <t>列表数量字段调整为：生成的二维码数量、扫描总量、首扫数量、后扫数量（均支持排序，无值以 - 表示）；点击「查看」在右侧抽屉/详情按列表展示该包全部二维码（分页每页 10），字段含 二维码 ID、缩略图、首扫状态、首扫时间、首扫账户名称、首扫手机号、后扫数量，支持按首扫账户名称、首扫手机号模糊筛选；下载 zip 每张图片以二维码 ID 命名，二维码 ID 全平台唯一且具可读性。（0609 新增/调整）</t>
+  </si>
+  <si>
+    <t>平台精修(0609)</t>
+  </si>
+  <si>
+    <t>默认 LLM 模型名称唯一</t>
+  </si>
+  <si>
+    <t>默认 LLM 模型名称全平台唯一，新建/编辑时校验重名并阻断保存。（0609 新增）</t>
+  </si>
+  <si>
+    <t>微信支付页视觉精修</t>
+  </si>
+  <si>
+    <t>收银台标题区改白底（与下方区域一致）；AI 问书 logo 由微信绿换成会话同款电光靛紫色动画球；支付成功对勾由珊瑚色改为绿色 / 主题色（含同心圆光环），避免被误解为未支付成功。（0609 调整）</t>
+  </si>
+  <si>
+    <t>前台精修(0610)</t>
+  </si>
+  <si>
+    <t>登录落地页 扫码入口移除</t>
+  </si>
+  <si>
+    <t>落地页移除「在浏览器中打开？扫码登录」入口（不在原型上绘制），外部浏览器扫码授权场景仅在本清单保留说明。（0610）</t>
+  </si>
+  <si>
+    <t>AI 答案 点赞/反馈 icon 样式</t>
+  </si>
+  <si>
+    <t>点赞 / 反馈 icon 改灰色系描边填充样式（选中态为灰色填充、非主题色），参考图 1。（0610）</t>
+  </si>
+  <si>
+    <t>输入框 语音输入（会话页底部浮层）</t>
+  </si>
+  <si>
+    <t>麦克风按钮单击 / 长按进入语音输入态——在当前会话页底部弹出音浪动画浮层（非全屏新页；浮层背底渐变与会话背景自然过渡）；点击音浪外任意位置即关闭并发送本次语音问题、触发 AI 回答。（0610 新增）</t>
+  </si>
+  <si>
+    <t>我的永享 放大预览定位</t>
+  </si>
+  <si>
+    <t>放大预览内容垂直方向调整为水平居中、略偏上（不再贴顶过高）。（0610）</t>
+  </si>
+  <si>
+    <t>后台精修(0610)</t>
+  </si>
+  <si>
+    <t>知识 KP 关联 Agent 下拉宽度</t>
+  </si>
+  <si>
+    <t>「关联 Agent」下拉框宽度收敛为与表单其他控件一致（详见全局「后台下拉选择器」规范）。（0610）</t>
+  </si>
+  <si>
+    <t>知识库 下载按钮/切片对齐/PDF icon</t>
+  </si>
+  <si>
+    <t>列表操作列最前增加「下载」按钮，可下载已上传的知识文件内容；上传弹窗切片方式字段与下方上传区域左对齐、上传拖拽区降高更紧凑；文件列表 PDF 文件 icon 中「PDF」三字母缩小并与边框留间距。（0610）</t>
+  </si>
+  <si>
+    <t>知识库 向量化失败检索状态</t>
+  </si>
+  <si>
+    <t>向量化失败的文件检索状态直接显示「下架」（而非空）；失败原因悬浮提示统一为指标同款问号 icon。（0610）</t>
+  </si>
+  <si>
+    <t>兑换码详情 右侧抽屉化</t>
+  </si>
+  <si>
+    <t>兑换码点「详情」改为当前页右侧抽屉展示（交互对齐二维码码包）：支持状态单选筛选、兑换用户 / 手机号模糊匹配、导出；明细列「状态」「权益」支持排序。（0610）</t>
+  </si>
+  <si>
+    <t>数据看板 总览两段式</t>
+  </si>
+  <si>
+    <t>「总览 Tab」区分「实时总览」（累计注册 / 当前会员 / 累计 GMV / 当日 DAU 等存量·累计指标，不随时间筛选）与「经营分析」（随时间区间联动的趋势指标），复用主控台两段式。（0610）</t>
+  </si>
+  <si>
+    <t>平台精修(0610)</t>
+  </si>
+  <si>
+    <t>机构账户列表 三列排序</t>
+  </si>
+  <si>
+    <t>机构账户列表「上级机构」「角色」「状态」三列支持点击表头排序。（0610）</t>
+  </si>
+  <si>
+    <t>模型用量 两段式</t>
+  </si>
+  <si>
+    <t>模型用量区分「实时总览」（平台开通至今累计 tokens / 累计调用次数）与「经营分析」（随时间区间的 tokens、调用次数、平均响应、各机构趋势），复用主控台两段式。（0610）</t>
+  </si>
+  <si>
+    <t>后台下拉选择器（两端通用）</t>
+  </si>
+  <si>
+    <t>统一下拉框宽度为与同表单其他控件一致（通查机构后台 / 平台超管所有下拉，不符的统一整改）；选中后回显文字不使用主题色、与普通 UI 文本色一致（仅反映数据变化）。（0610）</t>
+  </si>
+  <si>
+    <t>后台侧栏收起态（两端通用）</t>
+  </si>
+  <si>
+    <t>左侧菜单收起后，鼠标悬浮浮出的菜单名小面板层级修正，不再被右侧表单内容遮盖。（0610）</t>
+  </si>
+  <si>
+    <t>前台精修(0613)</t>
+  </si>
+  <si>
+    <t>登录与绑定按 H5 能力重构</t>
+  </si>
+  <si>
+    <t>H5 网页授权可取 openid/昵称/头像/性别/地区但无法取手机号，手机号统一用「手机号+验证码」绑定、不分浏览器环境；删除账号合并逻辑，手机号被占用直接提示更换或联系客服；手机号验证码登录用户不绑定微信信息。（0613）</t>
+  </si>
+  <si>
+    <t>微信两种环境授权流程上线</t>
+  </si>
+  <si>
+    <t>微信内→官方授权弹窗（昵称/头像/性别/地区），浏览器→open.weixin.qq.com 扫码授权；落地页可切换演示环境；授权回调自动带回头像/昵称/性别/地区。（0613）</t>
+  </si>
+  <si>
+    <t>敏感操作手机号绑定门槛（合规）</t>
+  </si>
+  <si>
+    <t>支付下单、兑换码核销、开通/充值会员三类操作前置校验是否已绑手机号，未绑引导前往「我的-绑定手机号」绑定后继续，不强制所有用户绑定。（0613）</t>
+  </si>
+  <si>
+    <t>个人资料（头像/昵称/性别/地区）</t>
+  </si>
+  <si>
+    <t>微信环境头像/昵称/性别/地区由授权自动带回（头像用微信头像）；非微信环境用户可上传头像、填写性别与地区。（0613）</t>
+  </si>
+  <si>
+    <t>我的纸书（扫码解锁的知识 KP）</t>
+  </si>
+  <si>
+    <t>展示用户扫线下纸书二维码绑定、获权益的知识 KP，卡片布局（封面+名称+扫码时间），支持按名称模糊搜索；免费用户亦可畅享该 KP 全部文/图/音/视，永享标内容仍需单独购买。（0613）</t>
+  </si>
+  <si>
+    <t>我的永享搜索与筛选</t>
+  </si>
+  <si>
+    <t>列表顶部新增搜索（按文件名模糊匹配）+ 文件类型筛选（全部/图片/音频/视频）。（0613）</t>
+  </si>
+  <si>
+    <t>会员中心免费 vs 会员对比表</t>
+  </si>
+  <si>
+    <t>非会员页改为「免费/会员」权益对比表（逐项✅/✗，永享为单独购买），强化付费价值感。（0613）</t>
+  </si>
+  <si>
+    <t>自动续费提前 3 天短信通知</t>
+  </si>
+  <si>
+    <t>开启自动续费后弹 3 秒消失 tips「将于到期前 3 天短信提醒」，权益说明标注「提前 3 天短信通知续费」。（0613）</t>
+  </si>
+  <si>
+    <t>答案溯源第三方跳转倒计时</t>
+  </si>
+  <si>
+    <t>web 类型来源跳转第三方前增加 3 秒倒计时过渡浮层「即将跳转至第三方页面…」，倒计时结束再打开来源网页。（0613）</t>
+  </si>
+  <si>
+    <t>换绑手机号仅新号+验证码</t>
+  </si>
+  <si>
+    <t>确认换绑仅需「新手机号+验证码」，不要求旧手机号双重校验；异常场景留待生产期风控/客服申诉。（0613）</t>
+  </si>
+  <si>
+    <t>微信内浏览器登录流程</t>
+  </si>
+  <si>
+    <t>点「微信授权登录」→官方授权弹窗(授权昵称/头像/性别/地区)→允许携code回调进首页(手机号空、后续按需绑定)；拒绝留登录页；不出二维码、不弹手机号授权窗。（0613）</t>
+  </si>
+  <si>
+    <t>非微信浏览器扫码登录流程</t>
+  </si>
+  <si>
+    <t>点「微信授权登录」→open.weixin.qq.com动态二维码→微信扫码、手机端确认→允许携code回调进首页，流程同微信内。（0613）</t>
+  </si>
+  <si>
+    <t>手机号验证码登录</t>
+  </si>
+  <si>
+    <t>两环境一致，手机号+短信验证码校验通过即登录；该方式不获取、不绑定任何微信信息。（0613）</t>
+  </si>
+  <si>
+    <t>微信网页授权可获取字段</t>
+  </si>
+  <si>
+    <t>snsapi_userinfo 可取 openid/unionid/昵称/头像/性别/地区(国家省市)，不含手机号(H5公众号无手机号能力，一键授权手机号为小程序专属)。（0613）</t>
+  </si>
+  <si>
+    <t>手机号绑定与冲突(不合并)</t>
+  </si>
+  <si>
+    <t>绑定/换绑统一手机号+验证码、不要旧号双重校验；待绑号已被占用→提示更换或联系客服、不合并不顶替；A/B两微信绑同号后者同样提示占用。（0613）</t>
+  </si>
+  <si>
+    <t>后台精修(0613)</t>
+  </si>
+  <si>
+    <t>订单退款全链路</t>
+  </si>
+  <si>
+    <t>订单列表操作列加「退款」(危险色)→金额弹窗(显示实付/支持部分退款)→二次确认→原路退回；状态扩展退款中/已退款/部分退款；订单详情退款时间线；GMV扣减已退；主控台+看板加退款指标。（0613）</t>
+  </si>
+  <si>
+    <t>知识库去切片方式</t>
+  </si>
+  <si>
+    <t>上传弹窗去掉「切片方式」选择，直接上传、系统默认处理。（0613）</t>
+  </si>
+  <si>
+    <t>知识文件格式/大小/时长上限</t>
+  </si>
+  <si>
+    <t>文档PDF/DOC/DOCX/PPT/PPTX/TXT/MD≤100MB；图片JPG/PNG≤20MB；音频MP3/WAV/M4A≤300MB≤120分钟；视频MP4/MOV≤1GB≤90分钟(更长分段)。（0613）</t>
+  </si>
+  <si>
+    <t>分享时效改名</t>
+  </si>
+  <si>
+    <t>已分享列表「时效」改为「链接分享有效期」，新建弹窗有效期字段同步该叫法。（0613）</t>
+  </si>
+  <si>
+    <t>Agent编辑瘦身</t>
+  </si>
+  <si>
+    <t>移除「形象图」上传(头像保留)；移除「AI会话引导问题示例」区块。（0613）</t>
+  </si>
+  <si>
+    <t>C端用户地区性别+导出</t>
+  </si>
+  <si>
+    <t>用户列表/详情展示地区、性别(无则空)；用户列表新增「导出」(当前筛选结果)。（0613）</t>
+  </si>
+  <si>
+    <t>看板转化漏斗改百分比</t>
+  </si>
+  <si>
+    <t>会员漏斗、永享转化漏斗由数量改为百分比呈现(各环节相对转化%)。（0613）</t>
+  </si>
+  <si>
+    <t>被提问数Top10</t>
+  </si>
+  <si>
+    <t>热门KP「提问数Top10」改名为「被提问数Top10 KP」，语义更清晰。（0613）</t>
+  </si>
+  <si>
+    <t>看板用户/提问领域统计</t>
+  </si>
+  <si>
+    <t>用户分析加地区分布、性别分布；提问分析加提问领域分布(脑科学/心理/卒中/超声…)。（0613）</t>
+  </si>
+  <si>
+    <t>答案反馈Tab(新增)</t>
+  </si>
+  <si>
+    <t>汇总前台点赞/点踩/反馈(前台已埋点、后台原未呈现)：点赞率/点踩率+反馈明细(问题/标签/时间/关联Agent·KP)，供运营迭代知识库。（0613）</t>
+  </si>
+  <si>
+    <t>回答策略3条明确</t>
+  </si>
+  <si>
+    <t>保留3条并明确语义：严谨模式/透明兜底(默认)/流畅模式；想加的「直接回答不告知」即策略①、不新增第4条。（0613）</t>
+  </si>
+  <si>
+    <t>机构配额+套餐预设</t>
+  </si>
+  <si>
+    <t>创建机构加KP数/存储/月度Token三限额+4档套餐(基础10·20GB·5千万/专业50·100GB·2亿/旗舰200·500GB·10亿/定制)；token按月重置、机构可设服务有效期；用量看板已用·上限进度预警。（0613）</t>
+  </si>
+  <si>
+    <t>微信配置整合(公众号+支付)</t>
+  </si>
+  <si>
+    <t>机构「微信支付配置」升级「微信配置」：①公众号AppID/AppSecret/网页授权回调域名②微信支付MchID/APIv3/证书；标注公众号AppID需与商户号绑定。（0613）</t>
+  </si>
+  <si>
+    <t>机构品牌外观(多租户色系)</t>
+  </si>
+  <si>
+    <t>Organization加logo+主视觉色+辅助视觉色(主→辅渐变)；创建/详情品牌外观配置(传logo智能取色+渐变预览)；前台品牌球+主强调色读取该机构配色。（0613）</t>
+  </si>
+  <si>
+    <t>多机构Token图表优化</t>
+  </si>
+  <si>
+    <t>「全部机构」视图改总量趋势(单线/面积)+Top机构token排行榜(条形)、弃多折线；选中单机构看该机构趋势；主控台/看板加全部·指定机构筛选。（0613）</t>
+  </si>
+  <si>
+    <t>全域KP视图(新增)</t>
+  </si>
+  <si>
+    <t>跨机构KP聚合只读视图(机构/名称/状态/文件数/提问数+按机构·状态·名称筛选)，供平台监管统计；Agent/反馈/兑换码不建全域、从机构详情下钻。（0613）</t>
+  </si>
+  <si>
+    <t>RBAC权限三态</t>
+  </si>
+  <si>
+    <t>角色对每个功能点设「无/只读/可操作」三态，替代角色级只读；编辑网格用三态选择器，按功能粒度控制读写。（0613）</t>
+  </si>
+  <si>
+    <t>后台列表操作列固定右侧</t>
+  </si>
+  <si>
+    <t>两后台所有列表(含详情内嵌)的「操作」列sticky固定右侧、中间字段横向滚动；通查全部含操作列列表统一生效。（0613）</t>
+  </si>
+  <si>
+    <t>实测精修(0613-2)</t>
+  </si>
+  <si>
+    <t>扫码登录页美化+去Logo+演示开关标识</t>
+  </si>
+  <si>
+    <t>非微信扫码登录用内嵌二维码(WxLogin)整页可美化、二维码中央不放Logo;演示环境切换移到协议下方+加「仅演示·环境切换」标识。（0613-2）</t>
+  </si>
+  <si>
+    <t>我的纸书扫一扫+卡片重排</t>
+  </si>
+  <si>
+    <t>文案改「微信扫码解锁纸书全部数字内容，永享内容另购」;右上角扫一扫调相机扫码进KP会话(新需求);去永享标;点卡片进KP会话;名称两行高+扫码时间钉底对齐。（0613-2）</t>
+  </si>
+  <si>
+    <t>个人资料重做</t>
+  </si>
+  <si>
+    <t>删独立菜单(顶部头像箭头进入);头像调相册+圆形裁剪页;昵称行内改;性别仅男/女(去保密);地区改省/市/区级联真实数据、居中弹窗、不手填。（0613-2）</t>
+  </si>
+  <si>
+    <t>占用提示复用客服弹窗</t>
+  </si>
+  <si>
+    <t>手机号占用页「联系平台客服」复用「我的-联系客服」同款弹窗(含二维码/电话/邮箱)，不另绘。（0613-2）</t>
+  </si>
+  <si>
+    <t>会员文案+门槛弹窗居中</t>
+  </si>
+  <si>
+    <t>会员对比「基础图文问答」→「基础知识问答」;手机号门槛拦截弹窗文案两行、整体垂直居中。（0613-2）</t>
+  </si>
+  <si>
+    <t>溯源全链路跳转倒计时</t>
+  </si>
+  <si>
+    <t>跳出AI问书的链接(web互联网+KP纸书/运营填写链接)都先弹3秒过渡浮层;浮层去掉URL地址展示。（0613-2）</t>
+  </si>
+  <si>
+    <t>订单退款精修</t>
+  </si>
+  <si>
+    <t>退款状态独立成列(未退款/退款中/部分退款/全额退款)与订单状态解耦;金额仅数字不超实付;二次确认加账户信息;时间线降序(最新在上);发起人=登录账户名+真实姓名(括号);提示珊瑚红+黄色警告icon。（0613-2）</t>
+  </si>
+  <si>
+    <t>数据看板退款指标+时间联动</t>
+  </si>
+  <si>
+    <t>数据看板补退款指标(主控台已加、看板漏了);非实时指标随今日/7日/30日做假数据联动。（0613-2）</t>
+  </si>
+  <si>
+    <t>提问分析并列+关键词云</t>
+  </si>
+  <si>
+    <t>按Agent提问分布与提问领域分布改左右并列;新增关键词云(高频提问词,词频越高字越大)。（0613-2）</t>
+  </si>
+  <si>
+    <t>答案反馈独立工作台</t>
+  </si>
+  <si>
+    <t>提为数据中心独立菜单(与数据看板同级);去待处理指标;明细分页+按标签/时间区间/问题搜索;去关联Agent/KP列、加反馈人(标会员);详情看问题+AI答案含多模态;导出仅问答文本(不含媒体/溯源)。（0613-2）</t>
+  </si>
+  <si>
+    <t>知识库上传居中+规格告知</t>
+  </si>
+  <si>
+    <t>上传弹窗拖拽区居中;上传区显示支持格式/大小/时长清晰告知。（0613-2）</t>
+  </si>
+  <si>
+    <t>文件规格修订</t>
+  </si>
+  <si>
+    <t>文档收敛为PDF/DOC/DOCX/TXT/MD(去PPT);视频时长上限改≤60分钟。（0613-2）</t>
+  </si>
+  <si>
+    <t>C端列表/订单排序</t>
+  </si>
+  <si>
+    <t>用户列表支持按地区/性别排序;用户详情全部订单支持按类型/状态/支付方式排序。（0613-2）</t>
+  </si>
+  <si>
+    <t>配额套餐移位+平铺</t>
+  </si>
+  <si>
+    <t>配额/套餐从创建机构移到机构详情独立「套餐/配额」Tab;套餐平铺卡片(基础/专业/旗舰)点选自动填充;单位KP=个、存储=GB、月度Token=百万(M)/亿。（0613-2）</t>
+  </si>
+  <si>
+    <t>微信配置美化+限制提示</t>
+  </si>
+  <si>
+    <t>公众号/支付两块分区卡片强区分;提示改后台标准字号色;加结构化限制提示(网页授权需认证服务号、JSAPI支付需服务号+商户号且AppID与商户号绑定)。（0613-2）</t>
+  </si>
+  <si>
+    <t>用量看板重排+品牌取色+经营分析重排</t>
+  </si>
+  <si>
+    <t>用量看板重排(配额进度重点+2×2);品牌外观真实canvas智能取色+删「全量主题化后续」句;经营分析版式重排;Token单位用M/亿。（0613-2）</t>
+  </si>
+  <si>
+    <t>角色权限图例</t>
+  </si>
+  <si>
+    <t>角色权限页加「无/只读/可操作」含义说明(无=看不见菜单/只读=可看不可操作/可操作=全部可操作)。（0613-2）</t>
+  </si>
+  <si>
+    <t>指标tooltip压盖修复+必填红星+操作列加深+保存按钮</t>
+  </si>
+  <si>
+    <t>修指标问号悬浮被左侧菜单压盖bug(通查);必填项补红星(通查);固定操作列底色加深;保存按钮按交互就近+兜底默认、消除忽左忽右。（0613-2）</t>
+  </si>
+  <si>
+    <t>前台精修(0614)</t>
+  </si>
+  <si>
+    <t>参考来源跳转浮层</t>
+  </si>
+  <si>
+    <t>即将跳转外部的弹窗改为黑底白字「倒计时条」（3·2·1 倒计时 + 即将跳转到外部 + 右侧"取消跳转"按钮），不再用大弹窗。（0614）</t>
+  </si>
+  <si>
+    <t>手机号占用文案</t>
+  </si>
+  <si>
+    <t>手机号被占用提示「联系平台客服」统一改为「联系客服」。（0614）</t>
+  </si>
+  <si>
+    <t>会员权益名称统一</t>
+  </si>
+  <si>
+    <t>会员权益统一为五项：基础文字知识问答 / 图音视频深度知识精讲 / VIP 极速优先通道 / 实时电话即时问答 / 永享名家典藏知识（会员中心与对比表同步）。（0614）</t>
+  </si>
+  <si>
+    <t>续费前手机号门槛</t>
+  </si>
+  <si>
+    <t>会员续费 / 开通前先校验手机号绑定，未绑先引导绑定（自动续费前需短信通知）；拦截文案改为「支付、开会员等操作需绑定手机号，来保障账户安全」。（0614）</t>
+  </si>
+  <si>
+    <t>我的纸书续修</t>
+  </si>
+  <si>
+    <t>说明文案「永享内容另购」→「需另购」；右上角入口 icon 改"扫一扫"；扫码 / 点击纸书进入对应 KP 的全新会话（非已有会话）；卡片 hover 放大 / 高亮提示可跳转。（0614）</t>
+  </si>
+  <si>
+    <t>个人资料续修</t>
+  </si>
+  <si>
+    <t>头像裁剪去掉拖拽缩放条；标题与取消 / 确定按钮套用前台 AI 主视觉重做；点确定直接提示上传成功并回显；点取消回个人资料页（非"我的"页）。（0614）</t>
+  </si>
+  <si>
+    <t>后台精修(0614)</t>
+  </si>
+  <si>
+    <t>主控台指标重划</t>
+  </si>
+  <si>
+    <t>定位关键指标驾驶舱：实时总览 = 累计 GMV / 累计退款·退款率 / 净 GMV(新增) / 当前会员数 / 累计注册用户；经营分析 = 活跃用户 / 新增会员 / 区间 GMV / 区间提问数 + 趋势；移除累计提问卡。（0614）</t>
+  </si>
+  <si>
+    <t>数据看板去总览Tab</t>
+  </si>
+  <si>
+    <t>去掉总览 Tab（职责交主控台），重组为用户分析 / 提问分析 / 营收分析 / 热门 KP 四个主题域；所有非实时指标按今日 / 7 日 / 30 日真联动。（0614）</t>
+  </si>
+  <si>
+    <t>营收分析 Tab</t>
+  </si>
+  <si>
+    <t>原"转化分析"改名"营收分析"，重排三小节：①收入与转化（区间 GMV / 付费用户 / 付费转化率 / ARPPU / 续费率，改区间联动）②退款 ③转化漏斗（受限触发率 → 会员漏斗·永享转化，独立小节标题）。（0614）</t>
+  </si>
+  <si>
+    <t>新增答案点赞率 / 反馈率摘要；受限内容触发率移至营收 Tab；提问量趋势图自总览移入；关键词云升级 UI 并支持 hover 显示当前区间该词提问数。（0614）</t>
+  </si>
+  <si>
+    <t>热门 KP 联动</t>
+  </si>
+  <si>
+    <t>被提问数 / 付费转化贡献 / 永享购买 三个 TOP10 榜单改为随今日 / 7 日 / 30 日区间联动。（0614）</t>
+  </si>
+  <si>
+    <t>退款二次确认 / 提示</t>
+  </si>
+  <si>
+    <t>二次确认弹窗字段垂直并列：发起人 admin（张三）/ 退款对象 昵称（手机号，空则不显）/ 订单号 / 退款金额 / 资金路径 / 备注。退款提示框改浅灰圆角引用块 + 珊瑚字 + 无序圆点垂直展开。（0614）</t>
+  </si>
+  <si>
+    <t>订单列表排序</t>
+  </si>
+  <si>
+    <t>订单状态 / 退款状态 / 支付方式 / 类型 四字段支持表头排序。（0614）</t>
+  </si>
+  <si>
+    <t>答案反馈精修</t>
+  </si>
+  <si>
+    <t>反馈标签列可排序；反馈人直接显昵称 + 是否会员（去"微信用户"）；删列表与详情的关联 Agent / KP；详情用户问题 / AI 答案改左右气泡布局。（0614）</t>
+  </si>
+  <si>
+    <t>上传知识弹窗</t>
+  </si>
+  <si>
+    <t>改左右布局（左上按钮 + 左下文图音视单文件限制、右侧批量进度）；明确为单文件上限；加"支持批量上传"说明；删知识库列表"切片方式"列；向量化失败问号间距缩窄。（0614）</t>
+  </si>
+  <si>
+    <t>C 端用户订单复用</t>
+  </si>
+  <si>
+    <t>用户详情"全部订单"加退款状态列、规范订单状态字段，与订单管理列表对齐复用。（0614）</t>
+  </si>
+  <si>
+    <t>KP 定价权益文案</t>
+  </si>
+  <si>
+    <t>免费 / 会员 / 永享说明详化：免费 = 所有用户(含会员)可看非影响内容(文图音视)；会员 = 仅会员可看图音视媒体、文字不限；永享需单独计价。（0614）</t>
+  </si>
+  <si>
+    <t>操作列视觉柔化</t>
+  </si>
+  <si>
+    <t>固定操作列的视觉区分由"加深底色块"改为柔和过渡——左侧发丝线 + 极淡渐隐 / 磨砂底，圆润自然、不与左侧割裂。（0614）</t>
+  </si>
+  <si>
+    <t>指标 tooltip 遮挡修复</t>
+  </si>
+  <si>
+    <t>按实测截图复查并彻底修掉「累计退款」等指标 tooltip 仍被左侧菜单压盖的问题（定位 .kpi/.dash-section 的 overflow 与侧栏 z 层级）。（0614）</t>
+  </si>
+  <si>
+    <t>平台精修(0614)</t>
+  </si>
+  <si>
+    <t>主控台净 GMV</t>
+  </si>
+  <si>
+    <t>实时总览增加"净 GMV(扣退款)"关键指标(tooltip 注明退款额·率)；主控台保持精简，用户画像走全域用户。（0614）</t>
+  </si>
+  <si>
+    <t>创建机构文案 + 联系人</t>
+  </si>
+  <si>
+    <t>说明文案精简为「仅顶级机构可被选为上级」；创建机构弹窗与基本资料增加"联系人手机号 + 联系姓名"(手机号可重复)。（0614）</t>
+  </si>
+  <si>
+    <t>套餐配额歧义</t>
+  </si>
+  <si>
+    <t>保留套餐标签；选套餐填充后一旦手动改任一配额值，标签自动变"自定义套餐"并 badge 明示，消除歧义。（0614）</t>
+  </si>
+  <si>
+    <t>Token 单位统一亿</t>
+  </si>
+  <si>
+    <t>Token 额度统一「亿」(基础 0.5 亿 / 专业 2 亿 / 旗舰 10 亿)，套餐卡 / 配额表单 / 用量看板全统一，不再中英混用(M)。（0614）</t>
+  </si>
+  <si>
+    <t>微信配置文案 + 必填</t>
+  </si>
+  <si>
+    <t>公众号 / 支付用途说明改行内灰色小号字；公众号、支付均为必填加红星，两处「选填」改「必填」。（0614）</t>
+  </si>
+  <si>
+    <t>配额闭环</t>
+  </si>
+  <si>
+    <t>用量看板加退款金额 / 率；KP 数 / 存储超限提示并阻断、前台 Token 超限友好提示联系客服；达 70 / 80 / 90 / 95% 向联系人发预警短信(可视化演示)。（0614）</t>
+  </si>
+  <si>
+    <t>品牌外观</t>
+  </si>
+  <si>
+    <t>主 / 辅视觉色块矩形改圆角；渐变预览整体缩小(球 / 条 / 矩形收紧)。（0614）</t>
+  </si>
+  <si>
+    <t>模型用量联动 + 当期</t>
+  </si>
+  <si>
+    <t>经营分析全部指标 + 总量趋势 + Top 机构排行按今日 / 近 7 天 / 30 天真联动；删「当期」硬编码改按所选时间显示；通查两后台「当期」字样统一改。（0614）</t>
+  </si>
+  <si>
+    <t>后台精修(0614b)</t>
+  </si>
+  <si>
+    <t>操作列样式终版</t>
+  </si>
+  <si>
+    <t>固定操作列按截图改：底色与表格一致（白底 / hover 暖底，不再用色块），仅左侧 1px 细线 + 柔和左阴影区分，横滚时数据从其下方滑过。（0614b）</t>
+  </si>
+  <si>
+    <t>指标单位规范（万进制）</t>
+  </si>
+  <si>
+    <t>全后台指标统一中文万进制（个 / 万 / 亿）：&lt;1万显原值千分位，≥1万缩“X.X万”，≥1亿缩“X.XX亿”；金额¥前缀；每 KPI 显单位（个 / 条 / 次 / 单 / 人）；大数自动缩写避免撑爆卡片（提问总量 320万）；Token 也用万 / 亿；规则上界面 + 详见清单「指标数值单位规范」。（0614b）</t>
+  </si>
+  <si>
+    <t>平台精修(0614b)</t>
+  </si>
+  <si>
+    <t>全域知识 KP（改名 + 卡片）</t>
+  </si>
+  <si>
+    <t>「全域 KP」改名「全域知识 KP」；列表 → 卡片布局（复用机构后台 KP 列表视觉），每卡标注归属机构；保留机构 / 状态 / 名称筛选；平台只读。（0614b）</t>
+  </si>
+  <si>
+    <t>全域 Agent 人设（新增）</t>
+  </si>
+  <si>
+    <t>新增（与全域知识 KP 同级）：跨机构 Agent 人设卡片聚合（只读），每卡显归属机构 + Agent 名 + 关联 KP 数 + 音色；支持机构 / 名称筛选。（0614b）</t>
+  </si>
+  <si>
+    <t>全域答案反馈（新增）</t>
+  </si>
+  <si>
+    <t>新增（与全域 Agent 同级）：汇总全平台各机构 C 端答案反馈，复用机构后台答案反馈工作台（分页 + 左右气泡详情 + 导出）；列表 / 详情多显归属机构，顶部支持机构筛选。（0614b）</t>
+  </si>
+  <si>
+    <t>全域页通用约束</t>
+  </si>
+  <si>
+    <t>凡平台后台全域页（用户 / 订单 / 知识 KP / Agent 人设 / 答案反馈）：每行（卡）显示归属机构、详情显示归属机构、顶部支持按机构筛选。（0614b）</t>
+  </si>
+  <si>
+    <t>前台精修(0614c)</t>
+  </si>
+  <si>
+    <t>即将跳转弹窗位置</t>
+  </si>
+  <si>
+    <t>跳出外部来源的倒计时提示条移到屏幕中上方（与 3 秒 toast 同位）；触发时不再关闭右侧「参考来源」抽屉，直接在当前页提示。（0614c）</t>
+  </si>
+  <si>
+    <t>手机号门槛文案一行</t>
+  </si>
+  <si>
+    <t>「支付、开会员等操作需绑定手机号，来保障账户安全」改为一行显示，去掉强制换行。（0614c）</t>
+  </si>
+  <si>
+    <t>个人资料头像裁剪修复</t>
+  </si>
+  <si>
+    <t>修复「确定」无效（原把整张原图 base64 写入 localStorage 撑爆配额导致保存失败）：改为 canvas 将裁剪圈渲染为 256px 方图再存，真裁剪且可持久化；修复「调整头像」标题被页面标题层级穿透遮挡（裁剪层 z-index 提至页面标题之上）。（0614c）</t>
+  </si>
+  <si>
+    <t>裁剪页取消返回</t>
+  </si>
+  <si>
+    <t>头像裁剪页点「取消」停留在个人资料页，不再退回「我的」列表页。（0614c）</t>
+  </si>
+  <si>
+    <t>Token 超额提问拦截</t>
+  </si>
+  <si>
+    <t>机构本月 Token 超额时，前台任何提问 / 语音 / 实时会话入口都被拦截、问题不发出；不再弹 3 秒 toast，改为让顶部已有的珊瑚红提示条「当前机构 Token 已达上限，请联系客服」放大抖动 + 跳亮一下，引导用户看已有提示。（0614c）</t>
+  </si>
+  <si>
+    <t>后台精修(0614c)</t>
+  </si>
+  <si>
+    <t>列表操作列分隔线</t>
+  </si>
+  <si>
+    <t>两后台所有列表固定的「操作」列：左侧分隔灰线加深、常驻可见，未横向滚动到最后一列时也能与其他列做视觉区分。（0614c）</t>
+  </si>
+  <si>
+    <t>答案反馈详情对齐前台</t>
+  </si>
+  <si>
+    <t>机构 / 平台后台答案反馈详情抽为共用组件并对齐前台 AI 会话：用户问题=主题色渐变气泡、AI 答案=白底+边框气泡；「当时推送的多模态知识」改名「相关媒体资源」并改横向缩略图条（左右滑动、点击放大）；反馈标签 / 反馈人 / 日期 与问答气泡间加浅灰分隔线；弹窗增加底部留白。（0614c）</t>
+  </si>
+  <si>
+    <t>上传弹窗文案与音频格式</t>
+  </si>
+  <si>
+    <t>知识文件上传弹窗说明文案从「支持批量上传」处换行、两行居中；音频支持格式去掉 M4A，仅保留 MP3、WAV。（0614c）</t>
+  </si>
+  <si>
+    <t>上传弹窗右侧标题</t>
+  </si>
+  <si>
+    <t>批量上传区无文件时只显示「批量上传」，不再显示「（0 个文件）」。（0614c）</t>
+  </si>
+  <si>
+    <t>主控台当前机构配额</t>
+  </si>
+  <si>
+    <t>机构主控台「实时总览」下方新增「当前机构配额（已用 / 上限）」进度卡（KP 数 / 存储 / 本月 Token），复用平台机构详情用量进度卡，便于机构自查用量。（0614c）</t>
+  </si>
+  <si>
+    <t>受限触发率 tooltip 遮挡修复</t>
+  </si>
+  <si>
+    <t>数据看板·营收分析·转化漏斗「受限内容触发率」指标问号悬浮面板不再被左侧菜单压盖（改为向右展开）。（0614c）</t>
+  </si>
+  <si>
+    <t>受限触发率排版</t>
+  </si>
+  <si>
+    <t>「受限内容触发率」不再单独占一行，与「会员漏斗」「永享转化」并排为同一行三列，视觉更均衡。（0614c）</t>
+  </si>
+  <si>
+    <t>热门 KP 被提问数单位</t>
+  </si>
+  <si>
+    <t>数据看板·热门 KP「被提问数 TOP10」数值补上单位「条」。（0614c）</t>
+  </si>
+  <si>
+    <t>平台精修(0614c)</t>
+  </si>
+  <si>
+    <t>联系人手机号明文</t>
+  </si>
+  <si>
+    <t>机构详情·基本资料的联系人手机号直接明文展示，不再加密打码。（0614c）</t>
+  </si>
+  <si>
+    <t>品牌视觉色块改圆形</t>
+  </si>
+  <si>
+    <t>机构详情·品牌外观的主视觉色 / 辅助视觉色取色块由矩形直接改为圆形。（0614c）</t>
+  </si>
+  <si>
+    <t>Token 预警短信出现时机（清单）</t>
+  </si>
+  <si>
+    <t>明确用量看板「本月 Token 已用 XX%」预警条出现时机：非常驻，仅本计费周期 Token 已用率 ≥70% 时出现；短信按阈值 70/80/90/95% 首次达到各推一次、同周期不重复、下周期重置归零。（0614c）</t>
+  </si>
+  <si>
+    <t>服务有效期时间选择</t>
+  </si>
+  <si>
+    <t>机构详情·套餐配额的「服务有效期」改为「开始 ~ 截止」双时间选择控件（精确到时分秒），不再手填文本。（0614c）</t>
+  </si>
+  <si>
+    <t>自定义套餐提示与徽标</t>
+  </si>
+  <si>
+    <t>「已手动调整配额，当前为自定义套餐…」文案移到「配额」标题右侧并改小灰字；「自定义套餐」徽标改浅橙底 + 深橙字（原同色系导致文字看不清）。（0614c）</t>
+  </si>
+  <si>
+    <t>手机号唯一性规则（清单+问号）</t>
+  </si>
+  <si>
+    <t>明确：C 端用户手机号「机构内唯一、全平台可重复」——同一手机号在同一机构内唯一、不可重复，但可在不同机构各注册一个账户（如张三在 A、B 机构各有账户用同一号，允许）；机构联系人 / 机构账户联系人手机号均可重复（均为必填）。相关字段旁加问号悬浮面板（无序点）说明此差异。（0614c 更正：此前误写「全平台唯一」）</t>
+  </si>
+  <si>
+    <t>全域用户详情订单复用</t>
+  </si>
+  <si>
+    <t>全域用户详情「全部订单」复用全域订单同一份数据（按当前用户过滤），含退款状态列，不再单写一套。（0614c）</t>
+  </si>
+  <si>
+    <t>全域订单复用+归属机构+退款状态</t>
+  </si>
+  <si>
+    <t>全域订单列表 / 详情字段完全复用机构后台订单（同一份数据与退款状态 store），仅多一列「归属机构」+ 机构筛选；补齐此前缺失的「退款状态」列，详情含退款信息与退款时间线。（0614c）</t>
+  </si>
+  <si>
+    <t>删除全域 KP 聚合说明文案</t>
+  </si>
+  <si>
+    <t>删除全域知识 KP 列表上方「平台视角跨机构知识产品聚合（只读，供监管 / 统计）…」说明文案。（0614c）</t>
+  </si>
+  <si>
+    <t>全域 KP 卡片精简 + 进详情</t>
+  </si>
+  <si>
+    <t>全域知识 KP 卡片删去书籍/系列/专家库粒度标、免费/会员、创建时间（只留名称/机构/状态/永享）；点击卡片进入 KP 详情，直接复用机构后台 KP 详情页。（0614c）</t>
+  </si>
+  <si>
+    <t>全域 Agent 进详情 + Prompt 超管可编辑</t>
+  </si>
+  <si>
+    <t>全域 Agent 人设点击卡片进入 Agent 详情（复用机构后台）；其中「回答 Prompt」对平台超管开放编辑（不受角色权限限制，可对任意机构任意 Agent 修改并保存、即时生效），机构侧仍只读。（0614c）</t>
+  </si>
+  <si>
+    <t>角色三态说明排版</t>
+  </si>
+  <si>
+    <t>角色权限「无 / 只读 / 可操作」说明改为「状态：说明」（用冒号，不用点）、保留无序圆点排列；加宽悬浮面板使「只读」一行不换行。（0614c）</t>
+  </si>
+  <si>
+    <t>时间面板统一 + 选年月</t>
+  </si>
+  <si>
+    <t>两个后台所有时间面板统一为主控台日历样式（白底 + 主视觉，替换原生 datetime-local）；并支持点中间「2026 年 6 月」标题下钻：日→点标题进月选择→再点进年选择，可灵活跳任意年 / 月再选日，不再只能逐月翻。（0614c）</t>
+  </si>
+  <si>
+    <t>服务有效期日历选择</t>
+  </si>
+  <si>
+    <t>机构详情·套餐配额「服务有效期」改用与主控台一致的日历面板选「开始 ~ 截止」（仅到年月日，不需时分秒），替换原生 datetime-local。（0614c）</t>
+  </si>
+  <si>
+    <t>平台后台菜单重组</t>
+  </si>
+  <si>
+    <t>侧边栏按机构后台四大板块镜像重排（平台↔机构对称）：机构管理（机构管理 / 机构账户 / 角色权限——角色权限从原「全局策略」移入、与机构账户同级）、产品中心（全域知识产品 KP / 全域 Agent 人设）、运营中心（全域用户 / 全域订单）、数据中心（全域答案反馈 / 全域模型用量——原「模型用量」更名）、系统设置（默认 LLM）。组名沿用机构后台同名，靠「全域」前缀标明跨机构只读范围。原「平台数据中心」一坨 6 项拆开。（0614c）</t>
+  </si>
+  <si>
+    <t>菜单 / 页面更名</t>
+  </si>
+  <si>
+    <t>平台后台菜单 / 页面更名：「机构列表」→「机构管理」、「全域知识 KP」→「全域知识产品 KP」（与机构后台「知识产品 KP」对齐）、「模型用量」→「全域模型用量」（统一全域前缀）；菜单 / 页头 / 路由标题 / 原型清单四处同步。（0614c）</t>
+  </si>
+  <si>
+    <t>答案反馈缩略图悬浮裁剪修复</t>
+  </si>
+  <si>
+    <t>机构 / 平台后台答案反馈详情「相关媒体资源」缩略图鼠标悬浮放大时，顶角被横向滚动容器裁剪（overflow-x:auto 令 overflow-y 计算为 auto）；改为缩略图条上下留白 + 悬浮用 scale + 抬层级，放大后完整可见、不再被裁顶角。（0614c）</t>
+  </si>
+  <si>
+    <t>看板 / 段</t>
+  </si>
+  <si>
+    <t>指标（实时 / 区间）</t>
+  </si>
+  <si>
+    <t>公式 / 取数</t>
+  </si>
+  <si>
+    <t>业务意义</t>
+  </si>
+  <si>
+    <t>主控台·实时总览</t>
+  </si>
+  <si>
+    <t>累计 GMV（实时）</t>
+  </si>
+  <si>
+    <t>SUM(已支付订单金额)</t>
+  </si>
+  <si>
+    <t>总营收</t>
+  </si>
+  <si>
+    <t>累计退款 / 退款率（实时）</t>
+  </si>
+  <si>
+    <t>SUM(退款成功额)；退款率 = 退款额 ÷ GMV</t>
+  </si>
+  <si>
+    <t>售后与资金健康度</t>
+  </si>
+  <si>
+    <t>净 GMV 累计扣退款（实时，0614 新增）</t>
+  </si>
+  <si>
+    <t>累计 GMV − 累计退款</t>
+  </si>
+  <si>
+    <t>实际到账净收入</t>
+  </si>
+  <si>
+    <t>当前会员数（实时）</t>
+  </si>
+  <si>
+    <t>会员未到期的去重用户数</t>
+  </si>
+  <si>
+    <t>商业化基本盘</t>
+  </si>
+  <si>
+    <t>累计注册用户（实时）</t>
+  </si>
+  <si>
+    <t>COUNT(DISTINCT user_id)</t>
+  </si>
+  <si>
+    <t>用户规模</t>
+  </si>
+  <si>
+    <t>主控台·经营分析</t>
+  </si>
+  <si>
+    <t>活跃用户 / 新增会员 / 区间 GMV / 区间提问数（区间）+ 趋势图</t>
+  </si>
+  <si>
+    <t>区间聚合</t>
+  </si>
+  <si>
+    <t>经营动态</t>
+  </si>
+  <si>
+    <t>用户分析</t>
+  </si>
+  <si>
+    <t>DAU / WAU / MAU（实时·固定窗口）</t>
+  </si>
+  <si>
+    <t>周期内有效行为去重用户数</t>
+  </si>
+  <si>
+    <t>粘性分层</t>
+  </si>
+  <si>
+    <t>新增用户数（区间）</t>
+  </si>
+  <si>
+    <t>区间内首次注册数</t>
+  </si>
+  <si>
+    <t>拉新效果</t>
+  </si>
+  <si>
+    <t>次日 / 7 日 / 30 日留存率（区间）</t>
+  </si>
+  <si>
+    <t>新增用户 N 日后仍活跃占比</t>
+  </si>
+  <si>
+    <t>产品价值是否站得住</t>
+  </si>
+  <si>
+    <t>来源分布（区间）</t>
+  </si>
+  <si>
+    <t>扫码进入 vs 直接访问</t>
+  </si>
+  <si>
+    <t>渠道效果</t>
+  </si>
+  <si>
+    <t>地区分布 / 性别分布（区间）</t>
+  </si>
+  <si>
+    <t>按地区·性别分组占比</t>
+  </si>
+  <si>
+    <t>用户画像与精细化运营</t>
+  </si>
+  <si>
+    <t>提问分析</t>
+  </si>
+  <si>
+    <t>总提问数（区间）</t>
+  </si>
+  <si>
+    <t>COUNT(提问)</t>
+  </si>
+  <si>
+    <t>使用强度</t>
+  </si>
+  <si>
+    <t>人均提问数（区间）</t>
+  </si>
+  <si>
+    <t>总提问数 / 活跃用户</t>
+  </si>
+  <si>
+    <t>单用户深度</t>
+  </si>
+  <si>
+    <t>平均会话轮次（区间）</t>
+  </si>
+  <si>
+    <t>总提问数 / 总会话数</t>
+  </si>
+  <si>
+    <t>对话沉浸度</t>
+  </si>
+  <si>
+    <t>答案点赞率 / 答案反馈率（区间，0614 移入）</t>
+  </si>
+  <si>
+    <t>点赞数 ÷ 答案数；反馈数 ÷ 答案数</t>
+  </si>
+  <si>
+    <t>答案质量摘要（明细在答案反馈菜单）</t>
+  </si>
+  <si>
+    <t>提问量趋势（区间，0614 自总览移入）</t>
+  </si>
+  <si>
+    <t>每日提问条数</t>
+  </si>
+  <si>
+    <t>提问走势</t>
+  </si>
+  <si>
+    <t>按 Agent 提问分布（区间）</t>
+  </si>
+  <si>
+    <t>各 Agent 接收提问占比</t>
+  </si>
+  <si>
+    <t>Agent 配置 / 路由质量</t>
+  </si>
+  <si>
+    <t>提问领域分布（区间）</t>
+  </si>
+  <si>
+    <t>按 KP / 领域聚合占比</t>
+  </si>
+  <si>
+    <t>用户最关心的领域</t>
+  </si>
+  <si>
+    <t>提问关键词云（区间）</t>
+  </si>
+  <si>
+    <t>高频关键词，hover 显示该词区间提问数</t>
+  </si>
+  <si>
+    <t>运营 / 商业化分析</t>
+  </si>
+  <si>
+    <t>营收分析·收入与转化</t>
+  </si>
+  <si>
+    <t>区间 GMV（区间）</t>
+  </si>
+  <si>
+    <t>SUM(区间已支付金额)</t>
+  </si>
+  <si>
+    <t>区间营收</t>
+  </si>
+  <si>
+    <t>付费用户数 / 付费转化率（区间，0614 改联动）</t>
+  </si>
+  <si>
+    <t>区间付费用户 / 区间活跃用户</t>
+  </si>
+  <si>
+    <t>商业化核心</t>
+  </si>
+  <si>
+    <t>ARPPU（区间）</t>
+  </si>
+  <si>
+    <t>区间收入 / 区间付费用户数</t>
+  </si>
+  <si>
+    <t>单付费用户产值</t>
+  </si>
+  <si>
+    <t>续费率（区间）</t>
+  </si>
+  <si>
+    <t>到期续费数 / 到期会员数</t>
+  </si>
+  <si>
+    <t>长期价值</t>
+  </si>
+  <si>
+    <t>营收分析·退款</t>
+  </si>
+  <si>
+    <t>退款金额 / 退款率 / 退款订单数 / 净 GMV（区间）</t>
+  </si>
+  <si>
+    <t>见各指标</t>
+  </si>
+  <si>
+    <t>售后与净收入</t>
+  </si>
+  <si>
+    <t>营收分析·转化漏斗</t>
+  </si>
+  <si>
+    <t>受限内容触发率（区间，0614 移入）</t>
+  </si>
+  <si>
+    <t>触发付费墙次数 / 总提问数</t>
+  </si>
+  <si>
+    <t>付费墙强度（漏斗入口）</t>
+  </si>
+  <si>
+    <t>会员漏斗（区间）</t>
+  </si>
+  <si>
+    <t>看到会员页 → 点击购买 → 完成支付（%）</t>
+  </si>
+  <si>
+    <t>找漏斗瓶颈</t>
+  </si>
+  <si>
+    <t>永享转化（区间）</t>
+  </si>
+  <si>
+    <t>触发永享墙 → 完成购买（%）</t>
+  </si>
+  <si>
+    <t>永享定价是否合理</t>
+  </si>
+  <si>
+    <t>热门 KP</t>
+  </si>
+  <si>
+    <t>被提问数 TOP 10 KP（区间，0614 联动）</t>
+  </si>
+  <si>
+    <t>按 KP 维度统计提问</t>
+  </si>
+  <si>
+    <t>真正被使用的内容</t>
+  </si>
+  <si>
+    <t>付费转化贡献 TOP 10 KP（区间，0614 联动）</t>
+  </si>
+  <si>
+    <t>通过该 KP 触发的会员 / 永享订单数</t>
+  </si>
+  <si>
+    <t>营销价值高的内容</t>
+  </si>
+  <si>
+    <t>永享购买 TOP 10 KP（区间，0614 联动）</t>
+  </si>
+  <si>
+    <t>按 KP 永享订单数</t>
+  </si>
+  <si>
+    <t>永享潜力</t>
+  </si>
+  <si>
+    <t>维度</t>
   </si>
   <si>
     <t>指标</t>
   </si>
   <si>
-    <t>公式 / 取数</t>
-  </si>
-  <si>
-    <t>业务意义</t>
-  </si>
-  <si>
-    <t>总览</t>
-  </si>
-  <si>
-    <t>累计注册用户</t>
-  </si>
-  <si>
-    <t>COUNT(DISTINCT user_id)</t>
-  </si>
-  <si>
-    <t>规模</t>
-  </si>
-  <si>
-    <t>当前会员数</t>
-  </si>
-  <si>
-    <t>会员未到期的去重用户数</t>
-  </si>
-  <si>
-    <t>商业化基本盘</t>
-  </si>
-  <si>
-    <t>累计 GMV</t>
-  </si>
-  <si>
-    <t>SUM(订单金额 WHERE 状态=已支付)</t>
-  </si>
-  <si>
-    <t>总营收</t>
-  </si>
-  <si>
-    <t>当日 DAU</t>
-  </si>
-  <si>
-    <t>COUNT(DISTINCT user_id WHERE 当日有登录或发问)</t>
-  </si>
-  <si>
-    <t>即时活跃度</t>
-  </si>
-  <si>
-    <t>用户分析</t>
-  </si>
-  <si>
-    <t>DAU / WAU / MAU</t>
-  </si>
-  <si>
-    <t>周期内有效行为去重用户数</t>
-  </si>
-  <si>
-    <t>粘性分层</t>
-  </si>
-  <si>
-    <t>新增用户数</t>
-  </si>
-  <si>
-    <t>当日首次注册数</t>
-  </si>
-  <si>
-    <t>拉新效果</t>
-  </si>
-  <si>
-    <t>次日 / 7 日 / 30 日留存率</t>
-  </si>
-  <si>
-    <t>新增用户在 N 日后仍活跃占比</t>
-  </si>
-  <si>
-    <t>产品价值是否站得住</t>
-  </si>
-  <si>
-    <t>来源分布</t>
-  </si>
-  <si>
-    <t>扫码进入 vs 直接访问</t>
-  </si>
-  <si>
-    <t>渠道效果</t>
-  </si>
-  <si>
-    <t>活跃时段分布</t>
-  </si>
-  <si>
-    <t>按小时统计提问数</t>
-  </si>
-  <si>
-    <t>运营 / 推送时点参考</t>
-  </si>
-  <si>
-    <t>提问分析</t>
-  </si>
-  <si>
-    <t>总提问数</t>
-  </si>
-  <si>
-    <t>COUNT(提问)</t>
-  </si>
-  <si>
-    <t>使用强度</t>
-  </si>
-  <si>
-    <t>人均提问数</t>
-  </si>
-  <si>
-    <t>总提问数 / DAU</t>
-  </si>
-  <si>
-    <t>单用户深度</t>
-  </si>
-  <si>
-    <t>平均会话轮次</t>
-  </si>
-  <si>
-    <t>总提问数 / 总会话数</t>
-  </si>
-  <si>
-    <t>对话沉浸度</t>
-  </si>
-  <si>
-    <t>受限内容触发率</t>
-  </si>
-  <si>
-    <t>触发付费墙次数 / 总提问数</t>
-  </si>
-  <si>
-    <t>付费墙强度是否合理</t>
-  </si>
-  <si>
-    <t>按 Agent 提问分布</t>
-  </si>
-  <si>
-    <t>每个 Agent 接收提问占比</t>
-  </si>
-  <si>
-    <t>Agent 配置 / 路由质量</t>
-  </si>
-  <si>
-    <t>转化分析</t>
-  </si>
-  <si>
-    <t>付费用户数 / 付费转化率</t>
-  </si>
-  <si>
-    <t>付费用户 / 累计用户</t>
-  </si>
-  <si>
-    <t>商业化核心</t>
-  </si>
-  <si>
-    <t>会员漏斗</t>
-  </si>
-  <si>
-    <t>看到会员页 → 点击购买 → 完成支付 三步转化</t>
-  </si>
-  <si>
-    <t>找漏斗瓶颈</t>
-  </si>
-  <si>
-    <t>永享转化率</t>
-  </si>
-  <si>
-    <t>购买永享数 / 触发永享付费墙数</t>
-  </si>
-  <si>
-    <t>永享定价是否合理</t>
-  </si>
-  <si>
-    <t>ARPPU</t>
-  </si>
-  <si>
-    <t>总收入 / 付费用户数</t>
-  </si>
-  <si>
-    <t>单付费用户产值</t>
-  </si>
-  <si>
-    <t>续费率</t>
-  </si>
-  <si>
-    <t>到期续费数 / 到期会员数</t>
-  </si>
-  <si>
-    <t>长期价值</t>
-  </si>
-  <si>
-    <t>热门 KP</t>
-  </si>
-  <si>
-    <t>提问数 TOP 10 KP</t>
-  </si>
-  <si>
-    <t>按 KP 维度统计提问</t>
-  </si>
-  <si>
-    <t>真正被使用的内容</t>
-  </si>
-  <si>
-    <t>付费转化贡献 TOP 10 KP</t>
-  </si>
-  <si>
-    <t>通过该 KP 触发的会员 / 永享订单数</t>
-  </si>
-  <si>
-    <t>营销价值高的内容</t>
-  </si>
-  <si>
-    <t>永享购买 TOP 10 KP</t>
-  </si>
-  <si>
-    <t>按 KP 永享订单数</t>
-  </si>
-  <si>
-    <t>永享潜力</t>
-  </si>
-  <si>
-    <t>维度</t>
-  </si>
-  <si>
     <t>活跃度</t>
   </si>
   <si>
@@ -990,466 +1932,319 @@
     <t>tokens 用量、调用次数、平均响应时长</t>
   </si>
   <si>
-    <t>前台精修(0609)</t>
-  </si>
-  <si>
-    <t>后台精修(0609)</t>
-  </si>
-  <si>
-    <t>平台精修(0609)</t>
-  </si>
-  <si>
-    <t>微信授权登录（两种场景）</t>
-  </si>
-  <si>
-    <t>①微信 App 内打开 H5 → 专属授权弹窗：点击「微信授权登录」不出二维码，直接唤起微信官方授权弹窗（询问授予昵称、头像权限）；「允许」携 code 走回调——新用户引导绑定手机号、已绑手机号用户直接进入 AI 会话页，「拒绝」留在登录页。②外部浏览器打开 H5 → 微信扫码授权页：由 open.weixin.qq.com 渲染动态二维码，用户微信扫码后手机端弹出授权确认（允许/拒绝）；「允许」携 code 跳转回调页继续①的绑定/进入流程，「拒绝」退回登录页。（0609 新增）</t>
-  </si>
-  <si>
-    <t>知识库 纯音频/纯视频 去确认</t>
-  </si>
-  <si>
-    <t>纯音频/纯视频上传后，系统自动提取字幕 → 提取完成后直接向量化，去掉原「用户确认」步骤（无需二次确认）。（0609 调整，替代原「知识库—纯音频 / 纯视频」中的确认环节）</t>
-  </si>
-  <si>
-    <t>知识库文件 上架/下架 + 检索可见性</t>
-  </si>
-  <si>
-    <t>已向量化成功的文件提供「上架/下架」切换并展示状态；仅「上架」文件参与用户问答检索，「下架」不参与（与 KP 发布状态叠加生效）。「重试」仅对向量化失败的文件提供，已向量化成功的不再提供重试。（0609 新增/调整）</t>
-  </si>
-  <si>
-    <t>知识文件名重复规则</t>
-  </si>
-  <si>
-    <t>同一 KP 内上传的知识文件文件名允许重复、不做唯一性限制。（0609 新增）</t>
-  </si>
-  <si>
-    <t>上传知识文件弹窗</t>
-  </si>
-  <si>
-    <t>知识库顶部入口改为「上传知识文件」按钮，点击居中弹出上传表单：设置切片方式 + 点击/拖拽多文件上传（支持文件与多媒体混传、不支持文件夹嵌套），每个文件实时显示上传进度，全部完成后点「进入知识库」进入解析、向量化处理；上传多个则在知识库列表展示多条。（0609 新增）</t>
-  </si>
-  <si>
-    <t>二维码包 列表字段与查看详情</t>
-  </si>
-  <si>
-    <t>列表数量字段调整为：生成的二维码数量、扫描总量、首扫数量、后扫数量（均支持排序，无值以 - 表示）；点击「查看」在右侧抽屉/详情按列表展示该包全部二维码（分页每页 10），字段含 二维码 ID、缩略图、首扫状态、首扫时间、首扫账户名称、首扫手机号、后扫数量，支持按首扫账户名称、首扫手机号模糊筛选；下载 zip 每张图片以二维码 ID 命名，二维码 ID 全平台唯一且具可读性。（0609 新增/调整）</t>
-  </si>
-  <si>
-    <t>默认 LLM 模型名称唯一</t>
-  </si>
-  <si>
-    <t>默认 LLM 模型名称全平台唯一，新建/编辑时校验重名并阻断保存。（0609 新增）</t>
-  </si>
-  <si>
-    <t>微信支付页视觉精修</t>
-  </si>
-  <si>
-    <t>收银台标题区改白底（与下方区域一致）；AI 问书 logo 由微信绿换成会话同款电光靛紫色动画球；支付成功对勾由珊瑚色改为绿色 / 主题色（含同心圆光环），避免被误解为未支付成功。（0609 调整）</t>
-  </si>
-  <si>
-    <t>前台精修(0610)</t>
-  </si>
-  <si>
-    <t>后台精修(0610)</t>
-  </si>
-  <si>
-    <t>平台精修(0610)</t>
-  </si>
-  <si>
-    <t>机构后台 / 平台后台</t>
-  </si>
-  <si>
-    <t>登录落地页 扫码入口移除</t>
-  </si>
-  <si>
-    <t>落地页移除「在浏览器中打开？扫码登录」入口（不在原型上绘制），外部浏览器扫码授权场景仅在本清单保留说明。（0610）</t>
-  </si>
-  <si>
-    <t>AI 答案 点赞/反馈 icon 样式</t>
-  </si>
-  <si>
-    <t>点赞 / 反馈 icon 改灰色系描边填充样式（选中态为灰色填充、非主题色），参考图 1。（0610）</t>
-  </si>
-  <si>
-    <t>输入框 语音输入（会话页底部浮层）</t>
-  </si>
-  <si>
-    <t>麦克风按钮单击 / 长按进入语音输入态——在当前会话页底部弹出音浪动画浮层（非全屏新页；浮层背底渐变与会话背景自然过渡）；点击音浪外任意位置即关闭并发送本次语音问题、触发 AI 回答。（0610 新增）</t>
-  </si>
-  <si>
-    <t>我的永享 放大预览定位</t>
-  </si>
-  <si>
-    <t>放大预览内容垂直方向调整为水平居中、略偏上（不再贴顶过高）。（0610）</t>
-  </si>
-  <si>
-    <t>知识 KP 关联 Agent 下拉宽度</t>
-  </si>
-  <si>
-    <t>「关联 Agent」下拉框宽度收敛为与表单其他控件一致（详见全局「后台下拉选择器」规范）。（0610）</t>
-  </si>
-  <si>
-    <t>知识库 下载按钮/切片对齐/PDF icon</t>
-  </si>
-  <si>
-    <t>列表操作列最前增加「下载」按钮，可下载已上传的知识文件内容；上传弹窗切片方式字段与下方上传区域左对齐、上传拖拽区降高更紧凑；文件列表 PDF 文件 icon 中「PDF」三字母缩小并与边框留间距。（0610）</t>
-  </si>
-  <si>
-    <t>知识库 向量化失败检索状态</t>
-  </si>
-  <si>
-    <t>向量化失败的文件检索状态直接显示「下架」（而非空）；失败原因悬浮提示统一为指标同款问号 icon。（0610）</t>
-  </si>
-  <si>
-    <t>兑换码详情 右侧抽屉化</t>
-  </si>
-  <si>
-    <t>兑换码点「详情」改为当前页右侧抽屉展示（交互对齐二维码码包）：支持状态单选筛选、兑换用户 / 手机号模糊匹配、导出；明细列「状态」「权益」支持排序。（0610）</t>
-  </si>
-  <si>
-    <t>数据看板 总览两段式</t>
-  </si>
-  <si>
-    <t>「总览 Tab」区分「实时总览」（累计注册 / 当前会员 / 累计 GMV / 当日 DAU 等存量·累计指标，不随时间筛选）与「经营分析」（随时间区间联动的趋势指标），复用主控台两段式。（0610）</t>
-  </si>
-  <si>
-    <t>机构账户列表 三列排序</t>
-  </si>
-  <si>
-    <t>机构账户列表「上级机构」「角色」「状态」三列支持点击表头排序。（0610）</t>
-  </si>
-  <si>
-    <t>模型用量 两段式</t>
-  </si>
-  <si>
-    <t>模型用量区分「实时总览」（平台开通至今累计 tokens / 累计调用次数）与「经营分析」（随时间区间的 tokens、调用次数、平均响应、各机构趋势），复用主控台两段式。（0610）</t>
-  </si>
-  <si>
-    <t>后台下拉选择器（两端通用）</t>
-  </si>
-  <si>
-    <t>统一下拉框宽度为与同表单其他控件一致（通查机构后台 / 平台超管所有下拉，不符的统一整改）；选中后回显文字不使用主题色、与普通 UI 文本色一致（仅反映数据变化）。（0610）</t>
-  </si>
-  <si>
-    <t>后台侧栏收起态（两端通用）</t>
-  </si>
-  <si>
-    <t>左侧菜单收起后，鼠标悬浮浮出的菜单名小面板层级修正，不再被右侧表单内容遮盖。（0610）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">前台精修(0613)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">登录与绑定按 H5 能力重构</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H5 网页授权可取 openid/昵称/头像/性别/地区但无法取手机号，手机号统一用「手机号+验证码」绑定、不分浏览器环境；删除账号合并逻辑，手机号被占用直接提示更换或联系客服；手机号验证码登录用户不绑定微信信息。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">微信两种环境授权流程上线</t>
-  </si>
-  <si>
-    <t xml:space="preserve">微信内→官方授权弹窗（昵称/头像/性别/地区），浏览器→open.weixin.qq.com 扫码授权；落地页可切换演示环境；授权回调自动带回头像/昵称/性别/地区。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">敏感操作手机号绑定门槛（合规）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">支付下单、兑换码核销、开通/充值会员三类操作前置校验是否已绑手机号，未绑引导前往「我的-绑定手机号」绑定后继续，不强制所有用户绑定。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">个人资料（头像/昵称/性别/地区）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">微信环境头像/昵称/性别/地区由授权自动带回（头像用微信头像）；非微信环境用户可上传头像、填写性别与地区。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我的纸书（扫码解锁的知识 KP）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">展示用户扫线下纸书二维码绑定、获权益的知识 KP，卡片布局（封面+名称+扫码时间），支持按名称模糊搜索；免费用户亦可畅享该 KP 全部文/图/音/视，永享标内容仍需单独购买。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我的永享搜索与筛选</t>
-  </si>
-  <si>
-    <t xml:space="preserve">列表顶部新增搜索（按文件名模糊匹配）+ 文件类型筛选（全部/图片/音频/视频）。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">会员中心免费 vs 会员对比表</t>
-  </si>
-  <si>
-    <t xml:space="preserve">非会员页改为「免费/会员」权益对比表（逐项✅/✗，永享为单独购买），强化付费价值感。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">自动续费提前 3 天短信通知</t>
-  </si>
-  <si>
-    <t xml:space="preserve">开启自动续费后弹 3 秒消失 tips「将于到期前 3 天短信提醒」，权益说明标注「提前 3 天短信通知续费」。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">答案溯源第三方跳转倒计时</t>
-  </si>
-  <si>
-    <t xml:space="preserve">web 类型来源跳转第三方前增加 3 秒倒计时过渡浮层「即将跳转至第三方页面…」，倒计时结束再打开来源网页。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">换绑手机号仅新号+验证码</t>
-  </si>
-  <si>
-    <t xml:space="preserve">确认换绑仅需「新手机号+验证码」，不要求旧手机号双重校验；异常场景留待生产期风控/客服申诉。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">微信内浏览器登录流程</t>
-  </si>
-  <si>
-    <t xml:space="preserve">点「微信授权登录」→官方授权弹窗(授权昵称/头像/性别/地区)→允许携code回调进首页(手机号空、后续按需绑定)；拒绝留登录页；不出二维码、不弹手机号授权窗。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">非微信浏览器扫码登录流程</t>
-  </si>
-  <si>
-    <t xml:space="preserve">点「微信授权登录」→open.weixin.qq.com动态二维码→微信扫码、手机端确认→允许携code回调进首页，流程同微信内。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">手机号验证码登录</t>
-  </si>
-  <si>
-    <t xml:space="preserve">两环境一致，手机号+短信验证码校验通过即登录；该方式不获取、不绑定任何微信信息。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">微信网页授权可获取字段</t>
-  </si>
-  <si>
-    <t xml:space="preserve">snsapi_userinfo 可取 openid/unionid/昵称/头像/性别/地区(国家省市)，不含手机号(H5公众号无手机号能力，一键授权手机号为小程序专属)。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">手机号绑定与冲突(不合并)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">绑定/换绑统一手机号+验证码、不要旧号双重校验；待绑号已被占用→提示更换或联系客服、不合并不顶替；A/B两微信绑同号后者同样提示占用。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">后台精修(0613)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">订单退款全链路</t>
-  </si>
-  <si>
-    <t xml:space="preserve">订单列表操作列加「退款」(危险色)→金额弹窗(显示实付/支持部分退款)→二次确认→原路退回；状态扩展退款中/已退款/部分退款；订单详情退款时间线；GMV扣减已退；主控台+看板加退款指标。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">知识库去切片方式</t>
-  </si>
-  <si>
-    <t xml:space="preserve">上传弹窗去掉「切片方式」选择，直接上传、系统默认处理。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">知识文件格式/大小/时长上限</t>
-  </si>
-  <si>
-    <t xml:space="preserve">文档PDF/DOC/DOCX/PPT/PPTX/TXT/MD≤100MB；图片JPG/PNG≤20MB；音频MP3/WAV/M4A≤300MB≤120分钟；视频MP4/MOV≤1GB≤90分钟(更长分段)。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">分享时效改名</t>
-  </si>
-  <si>
-    <t xml:space="preserve">已分享列表「时效」改为「链接分享有效期」，新建弹窗有效期字段同步该叫法。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agent编辑瘦身</t>
-  </si>
-  <si>
-    <t xml:space="preserve">移除「形象图」上传(头像保留)；移除「AI会话引导问题示例」区块。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C端用户地区性别+导出</t>
-  </si>
-  <si>
-    <t xml:space="preserve">用户列表/详情展示地区、性别(无则空)；用户列表新增「导出」(当前筛选结果)。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">看板转化漏斗改百分比</t>
-  </si>
-  <si>
-    <t xml:space="preserve">会员漏斗、永享转化漏斗由数量改为百分比呈现(各环节相对转化%)。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">被提问数Top10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">热门KP「提问数Top10」改名为「被提问数Top10 KP」，语义更清晰。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">看板用户/提问领域统计</t>
-  </si>
-  <si>
-    <t xml:space="preserve">用户分析加地区分布、性别分布；提问分析加提问领域分布(脑科学/心理/卒中/超声…)。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">答案反馈Tab(新增)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">汇总前台点赞/点踩/反馈(前台已埋点、后台原未呈现)：点赞率/点踩率+反馈明细(问题/标签/时间/关联Agent·KP)，供运营迭代知识库。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">回答策略3条明确</t>
-  </si>
-  <si>
-    <t xml:space="preserve">保留3条并明确语义：严谨模式/透明兜底(默认)/流畅模式；想加的「直接回答不告知」即策略①、不新增第4条。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">机构配额+套餐预设</t>
-  </si>
-  <si>
-    <t xml:space="preserve">创建机构加KP数/存储/月度Token三限额+4档套餐(基础10·20GB·5千万/专业50·100GB·2亿/旗舰200·500GB·10亿/定制)；token按月重置、机构可设服务有效期；用量看板已用·上限进度预警。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">微信配置整合(公众号+支付)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">机构「微信支付配置」升级「微信配置」：①公众号AppID/AppSecret/网页授权回调域名②微信支付MchID/APIv3/证书；标注公众号AppID需与商户号绑定。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">机构品牌外观(多租户色系)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Organization加logo+主视觉色+辅助视觉色(主→辅渐变)；创建/详情品牌外观配置(传logo智能取色+渐变预览)；前台品牌球+主强调色读取该机构配色。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">多机构Token图表优化</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「全部机构」视图改总量趋势(单线/面积)+Top机构token排行榜(条形)、弃多折线；选中单机构看该机构趋势；主控台/看板加全部·指定机构筛选。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">全域KP视图(新增)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">跨机构KP聚合只读视图(机构/名称/状态/文件数/提问数+按机构·状态·名称筛选)，供平台监管统计；Agent/反馈/兑换码不建全域、从机构详情下钻。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RBAC权限三态</t>
-  </si>
-  <si>
-    <t xml:space="preserve">角色对每个功能点设「无/只读/可操作」三态，替代角色级只读；编辑网格用三态选择器，按功能粒度控制读写。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">后台列表操作列固定右侧</t>
-  </si>
-  <si>
-    <t xml:space="preserve">两后台所有列表(含详情内嵌)的「操作」列sticky固定右侧、中间字段横向滚动；通查全部含操作列列表统一生效。（0613）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">实测精修(0613-2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">扫码登录页美化+去Logo+演示开关标识</t>
-  </si>
-  <si>
-    <t xml:space="preserve">非微信扫码登录用内嵌二维码(WxLogin)整页可美化、二维码中央不放Logo;演示环境切换移到协议下方+加「仅演示·环境切换」标识。（0613-2）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">我的纸书扫一扫+卡片重排</t>
-  </si>
-  <si>
-    <t xml:space="preserve">文案改「微信扫码解锁纸书全部数字内容，永享内容另购」;右上角扫一扫调相机扫码进KP会话(新需求);去永享标;点卡片进KP会话;名称两行高+扫码时间钉底对齐。（0613-2）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">个人资料重做</t>
-  </si>
-  <si>
-    <t xml:space="preserve">删独立菜单(顶部头像箭头进入);头像调相册+圆形裁剪页;昵称行内改;性别仅男/女(去保密);地区改省/市/区级联真实数据、居中弹窗、不手填。（0613-2）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">占用提示复用客服弹窗</t>
-  </si>
-  <si>
-    <t xml:space="preserve">手机号占用页「联系平台客服」复用「我的-联系客服」同款弹窗(含二维码/电话/邮箱)，不另绘。（0613-2）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">会员文案+门槛弹窗居中</t>
-  </si>
-  <si>
-    <t xml:space="preserve">会员对比「基础图文问答」→「基础知识问答」;手机号门槛拦截弹窗文案两行、整体垂直居中。（0613-2）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">溯源全链路跳转倒计时</t>
-  </si>
-  <si>
-    <t xml:space="preserve">跳出AI问书的链接(web互联网+KP纸书/运营填写链接)都先弹3秒过渡浮层;浮层去掉URL地址展示。（0613-2）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">订单退款精修</t>
-  </si>
-  <si>
-    <t xml:space="preserve">退款状态独立成列(未退款/退款中/部分退款/全额退款)与订单状态解耦;金额仅数字不超实付;二次确认加账户信息;时间线降序(最新在上);发起人=登录账户名+真实姓名(括号);提示珊瑚红+黄色警告icon。（0613-2）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">数据看板退款指标+时间联动</t>
-  </si>
-  <si>
-    <t xml:space="preserve">数据看板补退款指标(主控台已加、看板漏了);非实时指标随今日/7日/30日做假数据联动。（0613-2）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">提问分析并列+关键词云</t>
-  </si>
-  <si>
-    <t xml:space="preserve">按Agent提问分布与提问领域分布改左右并列;新增关键词云(高频提问词,词频越高字越大)。（0613-2）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">答案反馈独立工作台</t>
-  </si>
-  <si>
-    <t xml:space="preserve">提为数据中心独立菜单(与数据看板同级);去待处理指标;明细分页+按标签/时间区间/问题搜索;去关联Agent/KP列、加反馈人(标会员);详情看问题+AI答案含多模态;导出仅问答文本(不含媒体/溯源)。（0613-2）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">知识库上传居中+规格告知</t>
-  </si>
-  <si>
-    <t xml:space="preserve">上传弹窗拖拽区居中;上传区显示支持格式/大小/时长清晰告知。（0613-2）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">文件规格修订</t>
-  </si>
-  <si>
-    <t xml:space="preserve">文档收敛为PDF/DOC/DOCX/TXT/MD(去PPT);视频时长上限改≤60分钟。（0613-2）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C端列表/订单排序</t>
-  </si>
-  <si>
-    <t xml:space="preserve">用户列表支持按地区/性别排序;用户详情全部订单支持按类型/状态/支付方式排序。（0613-2）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">配额套餐移位+平铺</t>
-  </si>
-  <si>
-    <t xml:space="preserve">配额/套餐从创建机构移到机构详情独立「套餐/配额」Tab;套餐平铺卡片(基础/专业/旗舰)点选自动填充;单位KP=个、存储=GB、月度Token=百万(M)/亿。（0613-2）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">微信配置美化+限制提示</t>
-  </si>
-  <si>
-    <t xml:space="preserve">公众号/支付两块分区卡片强区分;提示改后台标准字号色;加结构化限制提示(网页授权需认证服务号、JSAPI支付需服务号+商户号且AppID与商户号绑定)。（0613-2）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">用量看板重排+品牌取色+经营分析重排</t>
-  </si>
-  <si>
-    <t xml:space="preserve">用量看板重排(配额进度重点+2×2);品牌外观真实canvas智能取色+删「全量主题化后续」句;经营分析版式重排;Token单位用M/亿。（0613-2）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">角色权限图例</t>
-  </si>
-  <si>
-    <t xml:space="preserve">角色权限页加「无/只读/可操作」含义说明(无=看不见菜单/只读=可看不可操作/可操作=全部可操作)。（0613-2）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">指标tooltip压盖修复+必填红星+操作列加深+保存按钮</t>
-  </si>
-  <si>
-    <t xml:space="preserve">修指标问号悬浮被左侧菜单压盖bug(通查);必填项补红星(通查);固定操作列底色加深;保存按钮按交互就近+兜底默认、消除忽左忽右。（0613-2）</t>
+    <t>月度 Token 额度输入只填数字</t>
+  </si>
+  <si>
+    <t>套餐 / 配额「月度 Token 额度」输入框只填数字（如 2），单位「亿」作后缀 / 单位标，与 KP「个」、存储「GB」一致，不再把「亿」塞进输入值；套餐卡同步显示「月度 Token 2 亿」。（0614c）</t>
+  </si>
+  <si>
+    <t>机构管理列表新增套餐 + 配额列</t>
+  </si>
+  <si>
+    <t>机构管理（原机构列表）新增「套餐」列（基础/专业/旗舰/定制，可按档位排序 + 按套餐筛选）+ KP 用量 / Token 额度 / 存储空间 三列，均以「已用 / 上限」展示（接近上限标色），上限由套餐推断、定制版单列。（0614c）</t>
+  </si>
+  <si>
+    <t>配额口径明确：服务有效期内</t>
+  </si>
+  <si>
+    <t>KP 数量、存储空间、月度 Token 额度三项配额均为机构「服务有效期内」的额度上限；机构详情「月度 Token 额度」后文案由「按计费周期·月重置」改为「单位：亿（服务有效期内）」。（0614c）</t>
+  </si>
+  <si>
+    <t>机构管理列表删去序号列 + 配额已用/上限颜色规则</t>
+  </si>
+  <si>
+    <t>机构管理列表删去「序号」列（机构 ID 已可定位）。配额「已用 / 上限」颜色：用量看板进度条始终着色（&lt;70% 青/70~90% 橙/≥90% 珊瑚红）；机构管理列表已用值正常态(&lt;70%)黑字、仅预警时变色并加粗（70~90% 橙、≥90% 珊瑚红），避免整列花。（0614c）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">前台精修(0615)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我的纸书 · 去 hover + 进会话提示</t>
+  </si>
+  <si>
+    <t xml:space="preserve">去掉纸书卡片 hover 放大 / 高亮交互（仅保留可点击、无视觉强调）；点击纸书后在屏幕中上方弹 3 秒黑底 toast「即将进入「{KP 名称}」AI 会话」（与其他 3 秒提示同位），随后进入该 KP 全新会话。（0615）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">后台精修(0615)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">后台登录验证码刷新</t>
+  </si>
+  <si>
+    <t xml:space="preserve">后台登录图形验证码由硬编码固定值改为随机生成 4 位字符（排除 0/O/1/I 等易混字符），并支持点击「换一张」刷新（点验证码本身或刷新按钮均可）。两端登录页共用同一组件。（0615）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">个人中心页（顶栏入口 → 落地页）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">顶栏右上原「姓名 · 角色」下拉项改为「个人中心」入口（保留退出登录），点击进入个人中心落地页。展示头像、账户名称、姓名、所属机构、上级机构（仅当所属机构有上级时显示）、角色、联系方式（手机 / 邮箱）、账户状态；平台超管账户无所属 / 上级机构故不展示该两项。仅头像可上传更新（相册选图 + 圆形裁剪、canvas 真裁剪输出小图，上传后顶栏头像同步回显），其余字段只读不可编辑，表单底部灰色小字「若需更改账户信息，请联系平台管理员」。（0615）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">配额用量百分比</t>
+  </si>
+  <si>
+    <t xml:space="preserve">两后台配额进度卡（机构后台主控台「当前机构配额」+ 平台后台机构详情「用量看板」）在「已用 / 上限」数字基础上，于进度条右侧补显百分比，色调与进度条联动（&lt; 70% 中性 / 70~90% 橙 / ≥ 90% 珊瑚红），便于一眼判断紧张程度。（0615）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">主控台配额条前置</t>
+  </si>
+  <si>
+    <t xml:space="preserve">机构后台主控台「当前机构配额」进度卡从「实时总览 / 经营分析之间」上移到页面顶部（实时总览之上），机构进后台先看额度是否吃紧、再看经营数据。（0615）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">平台精修(0615)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">机构订阅订单 · 订阅闭环</t>
+  </si>
+  <si>
+    <t xml:space="preserve">机构详情「套餐 / 配额」Tab 改造为订阅闭环：当前生效订阅只读卡 + 订阅记录列表 + 「新建续签 / 升级」弹窗；选套餐带出额度（保留商务手动微调）、有效期必填、商务负责人选填、不填合同金额（平台不经手资金）；机构当前额度 = 当前生效订阅快照，不再独立手填覆盖（保留历史可追溯）。（0615）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">订阅订单（全域菜单）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">机构管理组新增「订阅订单」全域页(/subscriptions)：跨机构汇总所有订阅，列含 机构 / 操作类型（新签·续签·升级）/ 套餐 / 额度 / 有效期 / 商务负责人 / 状态（待生效·生效中·已到期）/ 创建时间，支持按机构 / 套餐 / 状态 / 操作类型筛选 + 即将到期汇总；B 端订阅订单与 C 端全域订单两套体系、互不混淆。（0615）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">支付收银台双场景</t>
+  </si>
+  <si>
+    <t xml:space="preserve">支付收银台补「微信内 JSAPI / 微信外 H5(MWEB)」两套支付引导，随落地页环境开关联动：微信内直接调起、微信外提示唤起微信并模拟跳转回跳，完整演示微信外支付路径。（0615）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我的纸书 toast 限宽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">我的纸书「即将进入「KP 名」AI 会话」toast 增加最大宽度 + 自动换行，长 KP 名不再超出屏幕。（0615）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">知识库文件类型 icon 统一</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KP 详情知识库列表文件类型小 icon 由彩色（PDF 红 / Word 蓝 / 图音视珊瑚）改为统一淡灰（--ink-3）线性风格，与平台其他图标一致；按 文档 / PDF / 图片 / 音频 / 视频 分别绘制，PDF 去红字、视频补线性图标。（0615）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">个人中心提示 + 净 GMV 文案</t>
+  </si>
+  <si>
+    <t xml:space="preserve">平台超管个人中心不展示「若需更改账户信息，请联系平台管理员」灰字（机构后台保留）；平台主控台「净 GMV」tooltip 由「反映平台净流水」改为「全平台各机构净收入合计（平台不参与分账）」去歧义。（0615）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">订阅模型重做</t>
+  </si>
+  <si>
+    <t xml:space="preserve">订阅类型简化为 订阅（常规·定套餐+有效期）/ 加油包（期中加量·即时生效·额度累加·不改套餐），去掉新签/续签/升级三选与待生效；每笔加生效/未生效状态开关（默认生效），机构当前可用额度 = 生效订阅 + 生效加油包累加。（0615）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">订阅记录增强 + 详情/复制</t>
+  </si>
+  <si>
+    <t xml:space="preserve">订阅记录列增 订阅号（自动）/ 创建人 / 创建时间到时分秒 / 额度（已用 / 上限）；支持按 类型 / 套餐 / 商务负责人 / 状态筛选；操作加「详情」（弹窗含备注）+「复制」（带数据进新建表单）；当前生效订阅卡重做带已用进度条；新建弹窗套餐改竖排左对齐。（0615）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全域订阅订单美化</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全域订阅订单顶部汇总改 KPI 卡（与主控台风格一致）；搜索仅按机构 / 商务负责人；额度列展示已用 / 上限。（0615）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">平台账户菜单</t>
+  </si>
+  <si>
+    <t xml:space="preserve">新增独立「平台账户」菜单（系统设置组，/platform-accounts），平台级角色（平台超管 / 运营 / 财务）、无所属机构，与机构账户明显区分；列表 + 新建弹窗（账户名称 / 姓名 / 角色 / 手机号，密码系统生成、不在界面设置）。（0615）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">知识库文件 icon 换彩色品牌图</t>
+  </si>
+  <si>
+    <t xml:space="preserve">知识库文件类型小 icon 改用上传的彩色品牌图标（Word / PDF / 图片 / 音频 / 视频），两后台共用 FileTypeIcon 组件；icon 与文件名间距加大。（0615）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">支付文案一行 + 纸书 toast 加宽</t>
+  </si>
+  <si>
+    <t xml:space="preserve">微信外支付提示改一行「跳转微信支付，付款成功自动返回当前页面」不换行；我的纸书 toast 加宽到 330px（10 字内 KP 名一行、超出换行）。（0615）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">入驻清单 Word 精简 + 顶栏下载</t>
+  </si>
+  <si>
+    <t xml:space="preserve">顶栏（角色旁）新增「AI问书·新机构入驻微信对接清单」下载按钮；Word 按机构客户视角重写：删空目录 / AI 文风 / 平台不进钱话术，合并「平台做什么+需提供数据」「前置条件+注意事项」，删「与现有原型的关系」，表格内多项用无序列表；资金说明仅留 C 端资金进机构商户号 + 退款机构原路退回 + 平台仅记录订单与退款状态。（0615）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">订阅记录按订阅维度 + 加油包抽屉</t>
+  </si>
+  <si>
+    <t xml:space="preserve">订阅记录改按订阅维度（同一机构同时一个生效订阅、可预建未生效下一期）；每行显示加油包数，操作列「加油包」按钮 → 右抽屉展示该订阅的加油包列表 + 新建加油包（即时生效、额度累加、跟随订阅到期日，加油包通过 parentId 挂到订阅）。（0615）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">加油包额度去「加量」显已用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">加油包额度展示去掉「加量」字样、改显已用 / 上限（只显非零维度）；机构详情订阅记录 + 全域订阅订单同步。新建订阅弹窗说明改无序列表换行，状态开关去「（默认生效）」。（0615）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">账户密码体系</t>
+  </si>
+  <si>
+    <t xml:space="preserve">密码规则：8–16 位，至少同时含字母和数字，区分大小写，可含特殊字符，不含空格。机构 / 平台账户操作列加「重置密码」；创建账户 + 重置密码后弹账户凭证弹窗（账号 / 密码 / 姓名 / 机构 / 角色 + 一键复制，密码仅此一次明文）；个人中心支持修改登录密码（旧 1 次 + 新 2 次，旧密码项问号「忘记旧密码联系平台管理员」）；平台账户停用 / 启用弹 3 秒提示。（0615）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">角色权限重构（机构 / 平台双类型）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「角色权限」从机构管理移到系统设置组；按角色类型机构 / 平台分别管理，两者权限点不同；顶部切换 + 新建角色选类型；机构账户选机构角色、平台账户选平台角色。（0615）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">顶栏下载按钮文案</t>
+  </si>
+  <si>
+    <t xml:space="preserve">平台顶栏下载按钮文字「AI问书·新机构入驻微信对接清单」改为「新机构入驻微信对接清单」。（0615）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">平台精修(0615-5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">新建订阅说明块左对齐</t>
+  </si>
+  <si>
+    <t xml:space="preserve">新建订阅弹窗底部说明块与上方「状态开关 / 输入框」左对齐（缩进至控件列）。（0615-5）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">订阅记录总额度列</t>
+  </si>
+  <si>
+    <t xml:space="preserve">订阅记录「额度（已用 / 上限）」列改为「总额度（已用 / 上限，含加油包）」= 该订阅基础额度 + 其名下生效加油包累加（与当前生效订阅卡口径一致）；列表默认按创建时间倒序。（0615-5）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">加油包右抽屉重构</t>
+  </si>
+  <si>
+    <t xml:space="preserve">加油包右抽屉：「新建加油包」按钮移到抽屉上方；加油包改列表展示（创建时间 / 创建人 / 加油包额度 / 备注 / 状态，去掉商务负责人，参考兑换码详情页）；空数据走标准空态；新建表单 KP / 存储 / Token 三项同一行，三项全为 0 不可创建并提示「请至少为一项加量额度填写大于 0 的值」；整体按设计规范重做美化。（0615-5）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">订阅订单只显订阅+加油包列</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全域订阅订单列表只展示「订阅」、去掉类型列与类型筛选；额度列改「总额度（已用 / 上限，含加油包）」；新增「加油包」数量列。（0615-5）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">订阅订单加油包抽屉</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全域订阅订单操作列新增「加油包」按钮 → 右抽屉展示该订阅订单的加油包列表，并支持在抽屉内直接为其新建加油包（与机构详情订阅记录同一组件、同一交互）。（0615-5）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">订阅订单指标说明</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全域订阅订单顶部 KPI 每个指标名称后加说明 icon，鼠标悬浮显示计算规则面板（同主控台交互）；订阅总数 / 生效 / 未生效仅计「订阅」，加油包单列计数。（0615-5）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">后台精修(0615-5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">操作列固定标准通查整改</t>
+  </si>
+  <si>
+    <t xml:space="preserve">两后台所有含「操作」列的列表（含详情内嵌、订阅记录、加油包抽屉）统一走共享 .dg-op 固定标准：无横滚也常驻左侧 1px 浅灰边框线 + 左阴影；横向滚动时为不透明白底、下方数据列文字不透出；左阴影适度加重。以机构管理为达标基准对齐订阅记录等全部列表。（0615-5）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">角色权限位置复核</t>
+  </si>
+  <si>
+    <t xml:space="preserve">复核确认「角色权限」已位于「系统设置」组（线上旧版仍显示在「机构管理」组，将随本批部署一并更正）。（0615-5）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">角色权限点分组对齐菜单</t>
+  </si>
+  <si>
+    <t xml:space="preserve">平台角色权限矩阵里的「角色权限」权限点（p.role）从「机构管理」分组移到「系统设置」分组（置于 平台账户 与 默认 LLM 之间），与菜单分组一致（菜单一致性）。（0615-5）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">操作列未溢出也常驻可见</t>
+  </si>
+  <si>
+    <t xml:space="preserve">修正：表格未横向溢出（无需滚动）时固定操作列的浅灰线+阴影几乎看不见；改为 1px 浅灰线(.2)+贴边硬阴影线+外扩柔光，无论是否左右滑动都常驻清晰可见；两后台全部非卡片列表（订单管理/机构管理/订阅订单/全域订单/全域用户等）一并生效。（0615-5b）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">操作列灰线根因订正(box-shadow→伪元素)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">根因订正：5b 的 box-shadow 方案不生效——.tbl 为 border-collapse:collapse，collapse 模型下单元格 box-shadow 在 Chrome 不渲染（订阅订单/订单管理操作列没有灰线的真因）。改为 border-left 1px 浅灰线(.22)+伪元素::before 渐变向左投 12px 柔光，不受 collapse 影响，是否横滚都常驻清晰可见。两后台全部非卡片列表生效。（0615-5c）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">操作列定稿:去硬线+轻阴影+修右侧露数据</t>
+  </si>
+  <si>
+    <t xml:space="preserve">定稿：① 去掉固定操作列硬边框线、只留很轻的柔和左阴影(::before 渐变, 看出层次即可); ② 修横滚时操作列右侧露出被滑动数据的 BUG——根因 .tbl-wrap 右内边距 10px 留缝, 用 ::after 同底色盖板(宽度=内边距、不越界, 免凭空加横向滚动条)盖住; 一处共享样式覆盖两后台全部非卡片列表。（0615-5d）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">平台精修(0615-6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">机构管理列表去配额变色</t>
+  </si>
+  <si>
+    <t xml:space="preserve">机构管理列表的 KP用量 / Token额度 / 存储空间「已用」值去掉按使用率变色（原 70%橙 / 90%珊瑚红+加粗），整列太花，统一普通文字（已用黑、上限灰）；用量预警仍在机构详情用量看板进度条体现。（0615-6）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">新建订阅生效规则定稿(A+C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">新建订阅生效规则：① 同一时段只能一个生效订阅；② 有生效订阅时最多再预建 1 期未生效订阅；③ 新建有效期不可与已有订阅重叠(重叠拦截);④ 未生效到生效日期自动转生效。去掉状态手动开关、状态按有效期自动判定;有效期默认从最晚订阅到期次日衔接。规则以无序列表写进新建订阅说明块、不换行依次展示。（0615-6）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">加油包额度列只显额度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">加油包列表「加油包额度」列只显该加油包的额度(如 0.5 亿 Token)，不再显已用/上限。（0615-6）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">加油包空态插画美化</t>
+  </si>
+  <si>
+    <t xml:space="preserve">加油包列表空态插画换为更贴合 AI 问书品牌的图形(去掉星星圆圈, 奶白底+电光靛/朝霞橙)。（0615-6）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">后台精修(0615-6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">当前生效订阅卡抽共享件并同步三处</t>
+  </si>
+  <si>
+    <t xml:space="preserve">当前生效订阅卡(套餐/状态/加油包数/有效期/剩余+三项已用上限含加油包进度条)抽为共享组件 CurrentSubCard；机构详情订阅Tab(含商务负责人+新建按钮) / 机构详情用量看板 + 机构后台主控台(均不含商务负责人和新建按钮)三处复用。（0615-6）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">平台精修(0615-7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">订阅状态三态(已过期)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">订阅状态改三态、由有效期自动判定：未生效(今天&lt;生效日)/生效(生效日≤今天≤到期日)/已过期(今天&gt;到期日)；去掉手动状态；机构详情订阅订单与全域订阅订单状态列/筛选/KPI均按此口径。（0615-7）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">订阅订单误建删除</t>
+  </si>
+  <si>
+    <t xml:space="preserve">订阅订单操作列对"零用量+无加油包+非已过期"的订单显删除(危险色+二次确认、不可恢复)；生效中有消耗/已过期不可删,保留服务与计费历史；覆盖"机构第一笔生效订阅建错了,刚建未消耗即可删"。（0615-7）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">订阅改名(订阅订单/订阅订单ID)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「订阅记录」改名「订阅订单」；列表字段「订阅号」改名「订阅订单 ID」(机构详情与全域订阅订单同步)。（0615-7）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">后台精修(0615-7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">列表导出统一标准</t>
+  </si>
+  <si>
+    <t xml:space="preserve">两后台所有导出统一：Excel(.xlsx)；范围=当前筛选+排序后全部结果(非仅当前页/非全量)；字段=可见列+完整字段(不脱敏);单次≤1万条,超出提示缩小筛选/分批;文件名=模块+筛选摘要+时间戳;前端即时生成不经审批。各模块字段见PRD。（0615-7）</t>
   </si>
 </sst>
 </file>
@@ -2102,13 +2897,16 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -2670,13 +3468,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D175"/>
+  <dimension ref="A1:D286"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="26" customWidth="1"/>
-    <col min="4" max="4" width="95" customWidth="1"/>
+    <col min="4" max="4" width="95" style="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:4">
@@ -3883,7 +4681,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="87" spans="1:4">
+    <row r="87" ht="34" spans="1:4">
       <c r="A87" t="s">
         <v>194</v>
       </c>
@@ -3893,11 +4691,11 @@
       <c r="C87" t="s">
         <v>196</v>
       </c>
-      <c r="D87" t="s">
+      <c r="D87" s="3" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
+    <row r="88" ht="34" spans="1:4">
       <c r="A88" t="s">
         <v>194</v>
       </c>
@@ -3907,11 +4705,11 @@
       <c r="C88" t="s">
         <v>198</v>
       </c>
-      <c r="D88" t="s">
+      <c r="D88" s="3" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
+    <row r="89" ht="17" spans="1:4">
       <c r="A89" t="s">
         <v>194</v>
       </c>
@@ -3921,11 +4719,11 @@
       <c r="C89" t="s">
         <v>200</v>
       </c>
-      <c r="D89" t="s">
+      <c r="D89" s="3" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="90" spans="1:4">
+    <row r="90" ht="68" spans="1:4">
       <c r="A90" t="s">
         <v>194</v>
       </c>
@@ -3935,11 +4733,11 @@
       <c r="C90" t="s">
         <v>202</v>
       </c>
-      <c r="D90" t="s">
+      <c r="D90" s="3" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
+    <row r="91" ht="34" spans="1:4">
       <c r="A91" t="s">
         <v>194</v>
       </c>
@@ -3949,11 +4747,11 @@
       <c r="C91" t="s">
         <v>204</v>
       </c>
-      <c r="D91" t="s">
+      <c r="D91" s="3" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
+    <row r="92" ht="17" spans="1:4">
       <c r="A92" t="s">
         <v>194</v>
       </c>
@@ -3963,11 +4761,11 @@
       <c r="C92" t="s">
         <v>206</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D92" s="3" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" ht="17" spans="1:4">
       <c r="A93" t="s">
         <v>194</v>
       </c>
@@ -3977,11 +4775,11 @@
       <c r="C93" t="s">
         <v>208</v>
       </c>
-      <c r="D93" t="s">
+      <c r="D93" s="3" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
+    <row r="94" ht="34" spans="1:4">
       <c r="A94" t="s">
         <v>194</v>
       </c>
@@ -3991,11 +4789,11 @@
       <c r="C94" t="s">
         <v>210</v>
       </c>
-      <c r="D94" t="s">
+      <c r="D94" s="3" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="95" spans="1:4">
+    <row r="95" ht="34" spans="1:4">
       <c r="A95" t="s">
         <v>194</v>
       </c>
@@ -4005,11 +4803,11 @@
       <c r="C95" t="s">
         <v>212</v>
       </c>
-      <c r="D95" t="s">
+      <c r="D95" s="3" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="96" spans="1:4">
+    <row r="96" ht="51" spans="1:4">
       <c r="A96" t="s">
         <v>214</v>
       </c>
@@ -4019,11 +4817,11 @@
       <c r="C96" t="s">
         <v>216</v>
       </c>
-      <c r="D96" t="s">
+      <c r="D96" s="3" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
+    <row r="97" ht="34" spans="1:4">
       <c r="A97" t="s">
         <v>218</v>
       </c>
@@ -4033,11 +4831,11 @@
       <c r="C97" t="s">
         <v>219</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D97" s="3" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
+    <row r="98" ht="17" spans="1:4">
       <c r="A98" t="s">
         <v>218</v>
       </c>
@@ -4047,11 +4845,11 @@
       <c r="C98" t="s">
         <v>221</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D98" s="3" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
+    <row r="99" ht="17" spans="1:4">
       <c r="A99" t="s">
         <v>223</v>
       </c>
@@ -4061,11 +4859,11 @@
       <c r="C99" t="s">
         <v>224</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D99" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
+    <row r="100" ht="34" spans="1:4">
       <c r="A100" t="s">
         <v>223</v>
       </c>
@@ -4075,11 +4873,11 @@
       <c r="C100" t="s">
         <v>212</v>
       </c>
-      <c r="D100" t="s">
+      <c r="D100" s="3" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
+    <row r="101" ht="17" spans="1:4">
       <c r="A101" t="s">
         <v>223</v>
       </c>
@@ -4089,11 +4887,11 @@
       <c r="C101" t="s">
         <v>227</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D101" s="3" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
+    <row r="102" ht="51" spans="1:4">
       <c r="A102" t="s">
         <v>229</v>
       </c>
@@ -4103,11 +4901,11 @@
       <c r="C102" t="s">
         <v>230</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D102" s="3" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
+    <row r="103" ht="34" spans="1:4">
       <c r="A103" t="s">
         <v>229</v>
       </c>
@@ -4117,1020 +4915,2574 @@
       <c r="C103" t="s">
         <v>232</v>
       </c>
-      <c r="D103" t="s">
+      <c r="D103" s="3" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
+    <row r="104" ht="68" spans="1:4">
       <c r="A104" t="s">
         <v>194</v>
       </c>
       <c r="B104" t="s">
-        <v>318</v>
+        <v>234</v>
       </c>
       <c r="C104" t="s">
-        <v>321</v>
-      </c>
-      <c r="D104" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4">
+        <v>235</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="105" ht="34" spans="1:4">
       <c r="A105" t="s">
         <v>223</v>
       </c>
       <c r="B105" t="s">
-        <v>319</v>
+        <v>237</v>
       </c>
       <c r="C105" t="s">
-        <v>323</v>
-      </c>
-      <c r="D105" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4">
+        <v>238</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="106" ht="34" spans="1:4">
       <c r="A106" t="s">
         <v>223</v>
       </c>
       <c r="B106" t="s">
-        <v>319</v>
+        <v>237</v>
       </c>
       <c r="C106" t="s">
-        <v>325</v>
-      </c>
-      <c r="D106" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4">
+        <v>240</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="107" ht="17" spans="1:4">
       <c r="A107" t="s">
         <v>223</v>
       </c>
       <c r="B107" t="s">
-        <v>319</v>
+        <v>237</v>
       </c>
       <c r="C107" t="s">
-        <v>327</v>
-      </c>
-      <c r="D107" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4">
+        <v>242</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="108" ht="51" spans="1:4">
       <c r="A108" t="s">
         <v>223</v>
       </c>
       <c r="B108" t="s">
-        <v>319</v>
+        <v>237</v>
       </c>
       <c r="C108" t="s">
-        <v>329</v>
-      </c>
-      <c r="D108" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4">
+        <v>244</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="109" ht="68" spans="1:4">
       <c r="A109" t="s">
         <v>223</v>
       </c>
       <c r="B109" t="s">
-        <v>319</v>
+        <v>237</v>
       </c>
       <c r="C109" t="s">
-        <v>331</v>
-      </c>
-      <c r="D109" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4">
+        <v>246</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="110" ht="17" spans="1:4">
       <c r="A110" t="s">
         <v>218</v>
       </c>
       <c r="B110" t="s">
-        <v>320</v>
+        <v>248</v>
       </c>
       <c r="C110" t="s">
-        <v>333</v>
-      </c>
-      <c r="D110" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4">
+        <v>249</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="111" ht="34" spans="1:4">
       <c r="A111" t="s">
         <v>194</v>
       </c>
       <c r="B111" t="s">
-        <v>318</v>
+        <v>234</v>
       </c>
       <c r="C111" t="s">
-        <v>335</v>
-      </c>
-      <c r="D111" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4">
+        <v>251</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="112" ht="17" spans="1:4">
       <c r="A112" t="s">
         <v>194</v>
       </c>
       <c r="B112" t="s">
-        <v>337</v>
+        <v>253</v>
       </c>
       <c r="C112" t="s">
-        <v>341</v>
-      </c>
-      <c r="D112" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4">
+        <v>254</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="113" ht="17" spans="1:4">
       <c r="A113" t="s">
         <v>194</v>
       </c>
       <c r="B113" t="s">
-        <v>337</v>
+        <v>253</v>
       </c>
       <c r="C113" t="s">
-        <v>343</v>
-      </c>
-      <c r="D113" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4">
+        <v>256</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="114" ht="34" spans="1:4">
       <c r="A114" t="s">
         <v>194</v>
       </c>
       <c r="B114" t="s">
-        <v>337</v>
+        <v>253</v>
       </c>
       <c r="C114" t="s">
-        <v>345</v>
-      </c>
-      <c r="D114" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4">
+        <v>258</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="115" ht="17" spans="1:4">
       <c r="A115" t="s">
         <v>194</v>
       </c>
       <c r="B115" t="s">
-        <v>337</v>
+        <v>253</v>
       </c>
       <c r="C115" t="s">
-        <v>347</v>
-      </c>
-      <c r="D115" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4">
+        <v>260</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="116" ht="17" spans="1:4">
       <c r="A116" t="s">
         <v>223</v>
       </c>
       <c r="B116" t="s">
-        <v>338</v>
+        <v>262</v>
       </c>
       <c r="C116" t="s">
-        <v>349</v>
-      </c>
-      <c r="D116" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4">
+        <v>263</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="117" ht="34" spans="1:4">
       <c r="A117" t="s">
         <v>223</v>
       </c>
       <c r="B117" t="s">
-        <v>338</v>
+        <v>262</v>
       </c>
       <c r="C117" t="s">
-        <v>351</v>
-      </c>
-      <c r="D117" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4">
+        <v>265</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="118" ht="17" spans="1:4">
       <c r="A118" t="s">
         <v>223</v>
       </c>
       <c r="B118" t="s">
-        <v>338</v>
+        <v>262</v>
       </c>
       <c r="C118" t="s">
-        <v>353</v>
-      </c>
-      <c r="D118" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4">
+        <v>267</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="119" ht="34" spans="1:4">
       <c r="A119" t="s">
         <v>223</v>
       </c>
       <c r="B119" t="s">
-        <v>338</v>
+        <v>262</v>
       </c>
       <c r="C119" t="s">
-        <v>355</v>
-      </c>
-      <c r="D119" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4">
+        <v>269</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="120" ht="34" spans="1:4">
       <c r="A120" t="s">
         <v>223</v>
       </c>
       <c r="B120" t="s">
-        <v>338</v>
+        <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>357</v>
-      </c>
-      <c r="D120" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4">
+        <v>271</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="121" ht="17" spans="1:4">
       <c r="A121" t="s">
         <v>218</v>
       </c>
       <c r="B121" t="s">
-        <v>339</v>
+        <v>273</v>
       </c>
       <c r="C121" t="s">
-        <v>359</v>
-      </c>
-      <c r="D121" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4">
+        <v>274</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="122" ht="34" spans="1:4">
       <c r="A122" t="s">
         <v>218</v>
       </c>
       <c r="B122" t="s">
-        <v>339</v>
+        <v>273</v>
       </c>
       <c r="C122" t="s">
-        <v>361</v>
-      </c>
-      <c r="D122" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4">
+        <v>276</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="123" ht="34" spans="1:4">
       <c r="A123" t="s">
-        <v>340</v>
+        <v>229</v>
       </c>
       <c r="B123" t="s">
-        <v>338</v>
+        <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>363</v>
-      </c>
-      <c r="D123" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4">
+        <v>278</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="124" ht="17" spans="1:4">
       <c r="A124" t="s">
-        <v>340</v>
+        <v>229</v>
       </c>
       <c r="B124" t="s">
-        <v>338</v>
+        <v>262</v>
       </c>
       <c r="C124" t="s">
-        <v>365</v>
-      </c>
-      <c r="D124" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4">
+        <v>280</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="125" ht="34" spans="1:4">
       <c r="A125" t="s">
         <v>194</v>
       </c>
       <c r="B125" t="s">
-        <v>367</v>
+        <v>282</v>
       </c>
       <c r="C125" t="s">
-        <v>368</v>
-      </c>
-      <c r="D125" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4">
+        <v>283</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="126" ht="34" spans="1:4">
       <c r="A126" t="s">
         <v>194</v>
       </c>
       <c r="B126" t="s">
-        <v>367</v>
+        <v>282</v>
       </c>
       <c r="C126" t="s">
-        <v>370</v>
-      </c>
-      <c r="D126" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4">
+        <v>285</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="127" ht="34" spans="1:4">
       <c r="A127" t="s">
         <v>194</v>
       </c>
       <c r="B127" t="s">
-        <v>367</v>
+        <v>282</v>
       </c>
       <c r="C127" t="s">
-        <v>372</v>
-      </c>
-      <c r="D127" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4">
+        <v>287</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="128" ht="17" spans="1:4">
       <c r="A128" t="s">
         <v>194</v>
       </c>
       <c r="B128" t="s">
-        <v>367</v>
+        <v>282</v>
       </c>
       <c r="C128" t="s">
-        <v>374</v>
-      </c>
-      <c r="D128" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4">
+        <v>289</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="129" ht="34" spans="1:4">
       <c r="A129" t="s">
         <v>194</v>
       </c>
       <c r="B129" t="s">
-        <v>367</v>
+        <v>282</v>
       </c>
       <c r="C129" t="s">
-        <v>376</v>
-      </c>
-      <c r="D129" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4">
+        <v>291</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="130" ht="17" spans="1:4">
       <c r="A130" t="s">
         <v>194</v>
       </c>
       <c r="B130" t="s">
-        <v>367</v>
+        <v>282</v>
       </c>
       <c r="C130" t="s">
-        <v>378</v>
-      </c>
-      <c r="D130" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4">
+        <v>293</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="131" ht="17" spans="1:4">
       <c r="A131" t="s">
         <v>194</v>
       </c>
       <c r="B131" t="s">
-        <v>367</v>
+        <v>282</v>
       </c>
       <c r="C131" t="s">
-        <v>380</v>
-      </c>
-      <c r="D131" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4">
+        <v>295</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="132" ht="17" spans="1:4">
       <c r="A132" t="s">
         <v>194</v>
       </c>
       <c r="B132" t="s">
-        <v>367</v>
+        <v>282</v>
       </c>
       <c r="C132" t="s">
-        <v>382</v>
-      </c>
-      <c r="D132" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4">
+        <v>297</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="133" ht="17" spans="1:4">
       <c r="A133" t="s">
         <v>194</v>
       </c>
       <c r="B133" t="s">
-        <v>367</v>
+        <v>282</v>
       </c>
       <c r="C133" t="s">
-        <v>384</v>
-      </c>
-      <c r="D133" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4">
+        <v>299</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="134" ht="17" spans="1:4">
       <c r="A134" t="s">
         <v>194</v>
       </c>
       <c r="B134" t="s">
-        <v>367</v>
+        <v>282</v>
       </c>
       <c r="C134" t="s">
-        <v>386</v>
-      </c>
-      <c r="D134" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4">
+        <v>301</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="135" ht="34" spans="1:4">
       <c r="A135" t="s">
         <v>194</v>
       </c>
       <c r="B135" t="s">
-        <v>367</v>
+        <v>282</v>
       </c>
       <c r="C135" t="s">
-        <v>388</v>
-      </c>
-      <c r="D135" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4">
+        <v>303</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="136" ht="34" spans="1:4">
       <c r="A136" t="s">
         <v>194</v>
       </c>
       <c r="B136" t="s">
-        <v>367</v>
+        <v>282</v>
       </c>
       <c r="C136" t="s">
-        <v>390</v>
-      </c>
-      <c r="D136" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4">
+        <v>305</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="137" ht="17" spans="1:4">
       <c r="A137" t="s">
         <v>194</v>
       </c>
       <c r="B137" t="s">
-        <v>367</v>
+        <v>282</v>
       </c>
       <c r="C137" t="s">
-        <v>392</v>
-      </c>
-      <c r="D137" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4">
+        <v>307</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="138" ht="34" spans="1:4">
       <c r="A138" t="s">
         <v>194</v>
       </c>
       <c r="B138" t="s">
-        <v>367</v>
+        <v>282</v>
       </c>
       <c r="C138" t="s">
-        <v>394</v>
-      </c>
-      <c r="D138" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4">
+        <v>309</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="139" ht="34" spans="1:4">
       <c r="A139" t="s">
         <v>194</v>
       </c>
       <c r="B139" t="s">
-        <v>367</v>
+        <v>282</v>
       </c>
       <c r="C139" t="s">
-        <v>396</v>
-      </c>
-      <c r="D139" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4">
+        <v>311</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="140" ht="34" spans="1:4">
       <c r="A140" t="s">
         <v>223</v>
       </c>
       <c r="B140" t="s">
-        <v>398</v>
+        <v>313</v>
       </c>
       <c r="C140" t="s">
-        <v>399</v>
-      </c>
-      <c r="D140" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4">
+        <v>314</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="141" ht="17" spans="1:4">
       <c r="A141" t="s">
         <v>223</v>
       </c>
       <c r="B141" t="s">
-        <v>398</v>
+        <v>313</v>
       </c>
       <c r="C141" t="s">
-        <v>401</v>
-      </c>
-      <c r="D141" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4">
+        <v>316</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="142" ht="34" spans="1:4">
       <c r="A142" t="s">
         <v>223</v>
       </c>
       <c r="B142" t="s">
-        <v>398</v>
+        <v>313</v>
       </c>
       <c r="C142" t="s">
-        <v>403</v>
-      </c>
-      <c r="D142" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4">
+        <v>318</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="143" ht="17" spans="1:4">
       <c r="A143" t="s">
         <v>223</v>
       </c>
       <c r="B143" t="s">
-        <v>398</v>
+        <v>313</v>
       </c>
       <c r="C143" t="s">
-        <v>405</v>
-      </c>
-      <c r="D143" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4">
+        <v>320</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="144" ht="17" spans="1:4">
       <c r="A144" t="s">
         <v>223</v>
       </c>
       <c r="B144" t="s">
-        <v>398</v>
+        <v>313</v>
       </c>
       <c r="C144" t="s">
-        <v>407</v>
-      </c>
-      <c r="D144" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4">
+        <v>322</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="145" ht="17" spans="1:4">
       <c r="A145" t="s">
         <v>223</v>
       </c>
       <c r="B145" t="s">
-        <v>398</v>
+        <v>313</v>
       </c>
       <c r="C145" t="s">
-        <v>409</v>
-      </c>
-      <c r="D145" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4">
+        <v>324</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="146" ht="17" spans="1:4">
       <c r="A146" t="s">
         <v>223</v>
       </c>
       <c r="B146" t="s">
-        <v>398</v>
+        <v>313</v>
       </c>
       <c r="C146" t="s">
-        <v>411</v>
-      </c>
-      <c r="D146" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4">
+        <v>326</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="147" ht="17" spans="1:4">
       <c r="A147" t="s">
         <v>223</v>
       </c>
       <c r="B147" t="s">
-        <v>398</v>
+        <v>313</v>
       </c>
       <c r="C147" t="s">
-        <v>413</v>
-      </c>
-      <c r="D147" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4">
+        <v>328</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="148" ht="17" spans="1:4">
       <c r="A148" t="s">
         <v>223</v>
       </c>
       <c r="B148" t="s">
-        <v>398</v>
+        <v>313</v>
       </c>
       <c r="C148" t="s">
-        <v>415</v>
-      </c>
-      <c r="D148" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4">
+        <v>330</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="149" ht="34" spans="1:4">
       <c r="A149" t="s">
         <v>223</v>
       </c>
       <c r="B149" t="s">
-        <v>398</v>
+        <v>313</v>
       </c>
       <c r="C149" t="s">
-        <v>417</v>
-      </c>
-      <c r="D149" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4">
+        <v>332</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="150" ht="17" spans="1:4">
       <c r="A150" t="s">
         <v>223</v>
       </c>
       <c r="B150" t="s">
-        <v>398</v>
+        <v>313</v>
       </c>
       <c r="C150" t="s">
-        <v>419</v>
-      </c>
-      <c r="D150" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4">
+        <v>334</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="151" ht="34" spans="1:4">
       <c r="A151" t="s">
         <v>218</v>
       </c>
       <c r="B151" t="s">
-        <v>398</v>
+        <v>313</v>
       </c>
       <c r="C151" t="s">
-        <v>421</v>
-      </c>
-      <c r="D151" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4">
+        <v>336</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="152" ht="34" spans="1:4">
       <c r="A152" t="s">
         <v>218</v>
       </c>
       <c r="B152" t="s">
-        <v>398</v>
+        <v>313</v>
       </c>
       <c r="C152" t="s">
-        <v>423</v>
-      </c>
-      <c r="D152" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4">
+        <v>338</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="153" ht="34" spans="1:4">
       <c r="A153" t="s">
         <v>218</v>
       </c>
       <c r="B153" t="s">
-        <v>398</v>
+        <v>313</v>
       </c>
       <c r="C153" t="s">
-        <v>425</v>
-      </c>
-      <c r="D153" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4">
+        <v>340</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="154" ht="34" spans="1:4">
       <c r="A154" t="s">
         <v>218</v>
       </c>
       <c r="B154" t="s">
-        <v>398</v>
+        <v>313</v>
       </c>
       <c r="C154" t="s">
-        <v>427</v>
-      </c>
-      <c r="D154" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4">
+        <v>342</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="155" ht="34" spans="1:4">
       <c r="A155" t="s">
         <v>218</v>
       </c>
       <c r="B155" t="s">
-        <v>398</v>
+        <v>313</v>
       </c>
       <c r="C155" t="s">
-        <v>429</v>
-      </c>
-      <c r="D155" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4">
+        <v>344</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="156" ht="17" spans="1:4">
       <c r="A156" t="s">
         <v>218</v>
       </c>
       <c r="B156" t="s">
-        <v>398</v>
+        <v>313</v>
       </c>
       <c r="C156" t="s">
-        <v>431</v>
-      </c>
-      <c r="D156" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4">
+        <v>346</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="157" ht="17" spans="1:4">
       <c r="A157" t="s">
         <v>229</v>
       </c>
       <c r="B157" t="s">
-        <v>398</v>
+        <v>313</v>
       </c>
       <c r="C157" t="s">
-        <v>433</v>
-      </c>
-      <c r="D157" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4">
+        <v>348</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="158" ht="34" spans="1:4">
       <c r="A158" t="s">
         <v>194</v>
       </c>
       <c r="B158" t="s">
-        <v>435</v>
+        <v>350</v>
       </c>
       <c r="C158" t="s">
-        <v>436</v>
-      </c>
-      <c r="D158" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4">
+        <v>351</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="159" ht="34" spans="1:4">
       <c r="A159" t="s">
         <v>194</v>
       </c>
       <c r="B159" t="s">
-        <v>435</v>
+        <v>350</v>
       </c>
       <c r="C159" t="s">
-        <v>438</v>
-      </c>
-      <c r="D159" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4">
+        <v>353</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="160" ht="34" spans="1:4">
       <c r="A160" t="s">
         <v>194</v>
       </c>
       <c r="B160" t="s">
-        <v>435</v>
+        <v>350</v>
       </c>
       <c r="C160" t="s">
-        <v>440</v>
-      </c>
-      <c r="D160" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4">
+        <v>355</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="161" ht="17" spans="1:4">
       <c r="A161" t="s">
         <v>194</v>
       </c>
       <c r="B161" t="s">
-        <v>435</v>
+        <v>350</v>
       </c>
       <c r="C161" t="s">
-        <v>442</v>
-      </c>
-      <c r="D161" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4">
+        <v>357</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="162" ht="17" spans="1:4">
       <c r="A162" t="s">
         <v>194</v>
       </c>
       <c r="B162" t="s">
-        <v>435</v>
+        <v>350</v>
       </c>
       <c r="C162" t="s">
-        <v>444</v>
-      </c>
-      <c r="D162" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4">
+        <v>359</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="163" ht="17" spans="1:4">
       <c r="A163" t="s">
         <v>194</v>
       </c>
       <c r="B163" t="s">
-        <v>435</v>
+        <v>350</v>
       </c>
       <c r="C163" t="s">
-        <v>446</v>
-      </c>
-      <c r="D163" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4">
+        <v>361</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="164" ht="34" spans="1:4">
       <c r="A164" t="s">
         <v>223</v>
       </c>
       <c r="B164" t="s">
-        <v>435</v>
+        <v>350</v>
       </c>
       <c r="C164" t="s">
-        <v>448</v>
-      </c>
-      <c r="D164" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4">
+        <v>363</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="165" ht="17" spans="1:4">
       <c r="A165" t="s">
         <v>223</v>
       </c>
       <c r="B165" t="s">
-        <v>435</v>
+        <v>350</v>
       </c>
       <c r="C165" t="s">
-        <v>450</v>
-      </c>
-      <c r="D165" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4">
+        <v>365</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="166" ht="17" spans="1:4">
       <c r="A166" t="s">
         <v>223</v>
       </c>
       <c r="B166" t="s">
-        <v>435</v>
+        <v>350</v>
       </c>
       <c r="C166" t="s">
-        <v>452</v>
-      </c>
-      <c r="D166" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4">
+        <v>367</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="167" ht="34" spans="1:4">
       <c r="A167" t="s">
         <v>223</v>
       </c>
       <c r="B167" t="s">
-        <v>435</v>
+        <v>350</v>
       </c>
       <c r="C167" t="s">
-        <v>454</v>
-      </c>
-      <c r="D167" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4">
+        <v>369</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="168" ht="17" spans="1:4">
       <c r="A168" t="s">
         <v>223</v>
       </c>
       <c r="B168" t="s">
-        <v>435</v>
+        <v>350</v>
       </c>
       <c r="C168" t="s">
-        <v>456</v>
-      </c>
-      <c r="D168" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4">
+        <v>371</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="169" ht="17" spans="1:4">
       <c r="A169" t="s">
         <v>223</v>
       </c>
       <c r="B169" t="s">
-        <v>435</v>
+        <v>350</v>
       </c>
       <c r="C169" t="s">
-        <v>458</v>
-      </c>
-      <c r="D169" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4">
+        <v>373</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="170" ht="17" spans="1:4">
       <c r="A170" t="s">
         <v>223</v>
       </c>
       <c r="B170" t="s">
-        <v>435</v>
+        <v>350</v>
       </c>
       <c r="C170" t="s">
-        <v>460</v>
-      </c>
-      <c r="D170" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4">
+        <v>375</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="171" ht="34" spans="1:4">
       <c r="A171" t="s">
         <v>218</v>
       </c>
       <c r="B171" t="s">
-        <v>435</v>
+        <v>350</v>
       </c>
       <c r="C171" t="s">
-        <v>462</v>
-      </c>
-      <c r="D171" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4">
+        <v>377</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="172" ht="34" spans="1:4">
       <c r="A172" t="s">
         <v>218</v>
       </c>
       <c r="B172" t="s">
-        <v>435</v>
+        <v>350</v>
       </c>
       <c r="C172" t="s">
-        <v>464</v>
-      </c>
-      <c r="D172" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4">
+        <v>379</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="173" ht="34" spans="1:4">
       <c r="A173" t="s">
         <v>218</v>
       </c>
       <c r="B173" t="s">
-        <v>435</v>
+        <v>350</v>
       </c>
       <c r="C173" t="s">
-        <v>466</v>
-      </c>
-      <c r="D173" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4">
+        <v>381</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="174" ht="17" spans="1:4">
       <c r="A174" t="s">
         <v>218</v>
       </c>
       <c r="B174" t="s">
-        <v>435</v>
+        <v>350</v>
       </c>
       <c r="C174" t="s">
-        <v>468</v>
-      </c>
-      <c r="D174" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4">
+        <v>383</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="175" ht="34" spans="1:4">
       <c r="A175" t="s">
         <v>229</v>
       </c>
       <c r="B175" t="s">
+        <v>350</v>
+      </c>
+      <c r="C175" t="s">
+        <v>385</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="176" ht="34" spans="1:4">
+      <c r="A176" t="s">
+        <v>194</v>
+      </c>
+      <c r="B176" t="s">
+        <v>387</v>
+      </c>
+      <c r="C176" t="s">
+        <v>388</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="177" ht="17" spans="1:4">
+      <c r="A177" t="s">
+        <v>194</v>
+      </c>
+      <c r="B177" t="s">
+        <v>387</v>
+      </c>
+      <c r="C177" t="s">
+        <v>390</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="178" ht="34" spans="1:4">
+      <c r="A178" t="s">
+        <v>194</v>
+      </c>
+      <c r="B178" t="s">
+        <v>387</v>
+      </c>
+      <c r="C178" t="s">
+        <v>392</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="179" ht="34" spans="1:4">
+      <c r="A179" t="s">
+        <v>194</v>
+      </c>
+      <c r="B179" t="s">
+        <v>387</v>
+      </c>
+      <c r="C179" t="s">
+        <v>394</v>
+      </c>
+      <c r="D179" s="3" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="180" ht="34" spans="1:4">
+      <c r="A180" t="s">
+        <v>194</v>
+      </c>
+      <c r="B180" t="s">
+        <v>387</v>
+      </c>
+      <c r="C180" t="s">
+        <v>396</v>
+      </c>
+      <c r="D180" s="3" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="181" ht="34" spans="1:4">
+      <c r="A181" t="s">
+        <v>194</v>
+      </c>
+      <c r="B181" t="s">
+        <v>387</v>
+      </c>
+      <c r="C181" t="s">
+        <v>398</v>
+      </c>
+      <c r="D181" s="3" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="182" ht="34" spans="1:4">
+      <c r="A182" t="s">
+        <v>223</v>
+      </c>
+      <c r="B182" t="s">
+        <v>400</v>
+      </c>
+      <c r="C182" t="s">
+        <v>401</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="183" ht="34" spans="1:4">
+      <c r="A183" t="s">
+        <v>223</v>
+      </c>
+      <c r="B183" t="s">
+        <v>400</v>
+      </c>
+      <c r="C183" t="s">
+        <v>403</v>
+      </c>
+      <c r="D183" s="3" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="184" ht="34" spans="1:4">
+      <c r="A184" t="s">
+        <v>223</v>
+      </c>
+      <c r="B184" t="s">
+        <v>400</v>
+      </c>
+      <c r="C184" t="s">
+        <v>405</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="185" ht="34" spans="1:4">
+      <c r="A185" t="s">
+        <v>223</v>
+      </c>
+      <c r="B185" t="s">
+        <v>400</v>
+      </c>
+      <c r="C185" t="s">
+        <v>118</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="186" ht="17" spans="1:4">
+      <c r="A186" t="s">
+        <v>223</v>
+      </c>
+      <c r="B186" t="s">
+        <v>400</v>
+      </c>
+      <c r="C186" t="s">
+        <v>408</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="187" ht="34" spans="1:4">
+      <c r="A187" t="s">
+        <v>223</v>
+      </c>
+      <c r="B187" t="s">
+        <v>400</v>
+      </c>
+      <c r="C187" t="s">
+        <v>410</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="188" ht="17" spans="1:4">
+      <c r="A188" t="s">
+        <v>223</v>
+      </c>
+      <c r="B188" t="s">
+        <v>400</v>
+      </c>
+      <c r="C188" t="s">
+        <v>412</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="189" ht="34" spans="1:4">
+      <c r="A189" t="s">
+        <v>223</v>
+      </c>
+      <c r="B189" t="s">
+        <v>400</v>
+      </c>
+      <c r="C189" t="s">
+        <v>414</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="190" ht="34" spans="1:4">
+      <c r="A190" t="s">
+        <v>223</v>
+      </c>
+      <c r="B190" t="s">
+        <v>400</v>
+      </c>
+      <c r="C190" t="s">
+        <v>416</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="191" ht="17" spans="1:4">
+      <c r="A191" t="s">
+        <v>223</v>
+      </c>
+      <c r="B191" t="s">
+        <v>400</v>
+      </c>
+      <c r="C191" t="s">
+        <v>418</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="192" ht="34" spans="1:4">
+      <c r="A192" t="s">
+        <v>223</v>
+      </c>
+      <c r="B192" t="s">
+        <v>400</v>
+      </c>
+      <c r="C192" t="s">
+        <v>420</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="193" ht="17" spans="1:4">
+      <c r="A193" t="s">
+        <v>229</v>
+      </c>
+      <c r="B193" t="s">
+        <v>400</v>
+      </c>
+      <c r="C193" t="s">
+        <v>422</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="194" ht="34" spans="1:4">
+      <c r="A194" t="s">
+        <v>229</v>
+      </c>
+      <c r="B194" t="s">
+        <v>400</v>
+      </c>
+      <c r="C194" t="s">
+        <v>424</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="195" ht="17" spans="1:4">
+      <c r="A195" t="s">
+        <v>218</v>
+      </c>
+      <c r="B195" t="s">
+        <v>426</v>
+      </c>
+      <c r="C195" t="s">
+        <v>427</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="196" ht="34" spans="1:4">
+      <c r="A196" t="s">
+        <v>218</v>
+      </c>
+      <c r="B196" t="s">
+        <v>426</v>
+      </c>
+      <c r="C196" t="s">
+        <v>429</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="197" ht="17" spans="1:4">
+      <c r="A197" t="s">
+        <v>218</v>
+      </c>
+      <c r="B197" t="s">
+        <v>426</v>
+      </c>
+      <c r="C197" t="s">
+        <v>431</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="198" ht="34" spans="1:4">
+      <c r="A198" t="s">
+        <v>218</v>
+      </c>
+      <c r="B198" t="s">
+        <v>426</v>
+      </c>
+      <c r="C198" t="s">
+        <v>433</v>
+      </c>
+      <c r="D198" s="3" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="199" ht="17" spans="1:4">
+      <c r="A199" t="s">
+        <v>218</v>
+      </c>
+      <c r="B199" t="s">
+        <v>426</v>
+      </c>
+      <c r="C199" t="s">
         <v>435</v>
       </c>
-      <c r="C175" t="s">
+      <c r="D199" s="3" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="200" ht="34" spans="1:4">
+      <c r="A200" t="s">
+        <v>218</v>
+      </c>
+      <c r="B200" t="s">
+        <v>426</v>
+      </c>
+      <c r="C200" t="s">
+        <v>437</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="201" ht="17" spans="1:4">
+      <c r="A201" t="s">
+        <v>218</v>
+      </c>
+      <c r="B201" t="s">
+        <v>426</v>
+      </c>
+      <c r="C201" t="s">
+        <v>439</v>
+      </c>
+      <c r="D201" s="3" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="202" ht="34" spans="1:4">
+      <c r="A202" t="s">
+        <v>218</v>
+      </c>
+      <c r="B202" t="s">
+        <v>426</v>
+      </c>
+      <c r="C202" t="s">
+        <v>441</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="203" ht="34" spans="1:4">
+      <c r="A203" t="s">
+        <v>229</v>
+      </c>
+      <c r="B203" t="s">
+        <v>443</v>
+      </c>
+      <c r="C203" t="s">
+        <v>444</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="204" ht="51" spans="1:4">
+      <c r="A204" t="s">
+        <v>229</v>
+      </c>
+      <c r="B204" t="s">
+        <v>443</v>
+      </c>
+      <c r="C204" t="s">
+        <v>446</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="205" ht="34" spans="1:4">
+      <c r="A205" t="s">
+        <v>218</v>
+      </c>
+      <c r="B205" t="s">
+        <v>448</v>
+      </c>
+      <c r="C205" t="s">
+        <v>449</v>
+      </c>
+      <c r="D205" s="3" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="206" ht="34" spans="1:4">
+      <c r="A206" t="s">
+        <v>218</v>
+      </c>
+      <c r="B206" t="s">
+        <v>448</v>
+      </c>
+      <c r="C206" t="s">
+        <v>451</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="207" ht="34" spans="1:4">
+      <c r="A207" t="s">
+        <v>218</v>
+      </c>
+      <c r="B207" t="s">
+        <v>448</v>
+      </c>
+      <c r="C207" t="s">
+        <v>453</v>
+      </c>
+      <c r="D207" s="3" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="208" ht="34" spans="1:4">
+      <c r="A208" t="s">
+        <v>218</v>
+      </c>
+      <c r="B208" t="s">
+        <v>448</v>
+      </c>
+      <c r="C208" t="s">
+        <v>455</v>
+      </c>
+      <c r="D208" s="3" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="209" ht="34" spans="1:4">
+      <c r="A209" t="s">
+        <v>194</v>
+      </c>
+      <c r="B209" t="s">
+        <v>457</v>
+      </c>
+      <c r="C209" t="s">
+        <v>458</v>
+      </c>
+      <c r="D209" s="3" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="210" ht="17" spans="1:4">
+      <c r="A210" t="s">
+        <v>194</v>
+      </c>
+      <c r="B210" t="s">
+        <v>457</v>
+      </c>
+      <c r="C210" t="s">
+        <v>460</v>
+      </c>
+      <c r="D210" s="3" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="211" ht="34" spans="1:4">
+      <c r="A211" t="s">
+        <v>194</v>
+      </c>
+      <c r="B211" t="s">
+        <v>457</v>
+      </c>
+      <c r="C211" t="s">
+        <v>462</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="212" ht="17" spans="1:4">
+      <c r="A212" t="s">
+        <v>194</v>
+      </c>
+      <c r="B212" t="s">
+        <v>457</v>
+      </c>
+      <c r="C212" t="s">
+        <v>464</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="213" ht="34" spans="1:4">
+      <c r="A213" t="s">
+        <v>194</v>
+      </c>
+      <c r="B213" t="s">
+        <v>457</v>
+      </c>
+      <c r="C213" t="s">
+        <v>466</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="214" ht="34" spans="1:4">
+      <c r="A214" t="s">
+        <v>229</v>
+      </c>
+      <c r="B214" t="s">
+        <v>468</v>
+      </c>
+      <c r="C214" t="s">
+        <v>469</v>
+      </c>
+      <c r="D214" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="D175" t="s">
+    </row>
+    <row r="215" ht="51" spans="1:4">
+      <c r="A215" t="s">
+        <v>229</v>
+      </c>
+      <c r="B215" t="s">
+        <v>468</v>
+      </c>
+      <c r="C215" t="s">
         <v>471</v>
       </c>
+      <c r="D215" s="3" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="216" ht="17" spans="1:4">
+      <c r="A216" t="s">
+        <v>223</v>
+      </c>
+      <c r="B216" t="s">
+        <v>468</v>
+      </c>
+      <c r="C216" t="s">
+        <v>473</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="217" ht="17" spans="1:4">
+      <c r="A217" t="s">
+        <v>223</v>
+      </c>
+      <c r="B217" t="s">
+        <v>468</v>
+      </c>
+      <c r="C217" t="s">
+        <v>475</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="218" ht="34" spans="1:4">
+      <c r="A218" t="s">
+        <v>223</v>
+      </c>
+      <c r="B218" t="s">
+        <v>468</v>
+      </c>
+      <c r="C218" t="s">
+        <v>477</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="219" ht="17" spans="1:4">
+      <c r="A219" t="s">
+        <v>223</v>
+      </c>
+      <c r="B219" t="s">
+        <v>468</v>
+      </c>
+      <c r="C219" t="s">
+        <v>479</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="220" ht="17" spans="1:4">
+      <c r="A220" t="s">
+        <v>223</v>
+      </c>
+      <c r="B220" t="s">
+        <v>468</v>
+      </c>
+      <c r="C220" t="s">
+        <v>481</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="221" ht="17" spans="1:4">
+      <c r="A221" t="s">
+        <v>223</v>
+      </c>
+      <c r="B221" t="s">
+        <v>468</v>
+      </c>
+      <c r="C221" t="s">
+        <v>483</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="222" ht="17" spans="1:4">
+      <c r="A222" t="s">
+        <v>218</v>
+      </c>
+      <c r="B222" t="s">
+        <v>485</v>
+      </c>
+      <c r="C222" t="s">
+        <v>486</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="223" ht="17" spans="1:4">
+      <c r="A223" t="s">
+        <v>218</v>
+      </c>
+      <c r="B223" t="s">
+        <v>485</v>
+      </c>
+      <c r="C223" t="s">
+        <v>488</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="224" ht="34" spans="1:4">
+      <c r="A224" t="s">
+        <v>218</v>
+      </c>
+      <c r="B224" t="s">
+        <v>485</v>
+      </c>
+      <c r="C224" t="s">
+        <v>490</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="225" ht="17" spans="1:4">
+      <c r="A225" t="s">
+        <v>218</v>
+      </c>
+      <c r="B225" t="s">
+        <v>485</v>
+      </c>
+      <c r="C225" t="s">
+        <v>492</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="226" ht="34" spans="1:4">
+      <c r="A226" t="s">
+        <v>218</v>
+      </c>
+      <c r="B226" t="s">
+        <v>485</v>
+      </c>
+      <c r="C226" t="s">
+        <v>494</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="227" ht="51" spans="1:4">
+      <c r="A227" t="s">
+        <v>218</v>
+      </c>
+      <c r="B227" t="s">
+        <v>485</v>
+      </c>
+      <c r="C227" t="s">
+        <v>496</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="228" ht="17" spans="1:4">
+      <c r="A228" t="s">
+        <v>218</v>
+      </c>
+      <c r="B228" t="s">
+        <v>485</v>
+      </c>
+      <c r="C228" t="s">
+        <v>498</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="229" ht="34" spans="1:4">
+      <c r="A229" t="s">
+        <v>218</v>
+      </c>
+      <c r="B229" t="s">
+        <v>485</v>
+      </c>
+      <c r="C229" t="s">
+        <v>500</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="230" ht="17" spans="1:4">
+      <c r="A230" t="s">
+        <v>218</v>
+      </c>
+      <c r="B230" t="s">
+        <v>485</v>
+      </c>
+      <c r="C230" t="s">
+        <v>502</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="231" ht="34" spans="1:4">
+      <c r="A231" t="s">
+        <v>218</v>
+      </c>
+      <c r="B231" t="s">
+        <v>485</v>
+      </c>
+      <c r="C231" t="s">
+        <v>504</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="232" ht="34" spans="1:4">
+      <c r="A232" t="s">
+        <v>218</v>
+      </c>
+      <c r="B232" t="s">
+        <v>485</v>
+      </c>
+      <c r="C232" t="s">
+        <v>506</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="233" ht="34" spans="1:4">
+      <c r="A233" t="s">
+        <v>218</v>
+      </c>
+      <c r="B233" t="s">
+        <v>485</v>
+      </c>
+      <c r="C233" t="s">
+        <v>508</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="234" ht="34" spans="1:4">
+      <c r="A234" t="s">
+        <v>229</v>
+      </c>
+      <c r="B234" t="s">
+        <v>468</v>
+      </c>
+      <c r="C234" t="s">
+        <v>510</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="235" ht="34" spans="1:4">
+      <c r="A235" t="s">
+        <v>218</v>
+      </c>
+      <c r="B235" t="s">
+        <v>485</v>
+      </c>
+      <c r="C235" t="s">
+        <v>512</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="236" ht="68" spans="1:4">
+      <c r="A236" t="s">
+        <v>218</v>
+      </c>
+      <c r="B236" t="s">
+        <v>485</v>
+      </c>
+      <c r="C236" t="s">
+        <v>514</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="237" ht="34" spans="1:4">
+      <c r="A237" t="s">
+        <v>218</v>
+      </c>
+      <c r="B237" t="s">
+        <v>485</v>
+      </c>
+      <c r="C237" t="s">
+        <v>516</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="238" ht="34" spans="1:4">
+      <c r="A238" t="s">
+        <v>229</v>
+      </c>
+      <c r="B238" t="s">
+        <v>468</v>
+      </c>
+      <c r="C238" t="s">
+        <v>518</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4">
+      <c r="A239" t="s">
+        <v>218</v>
+      </c>
+      <c r="B239" t="s">
+        <v>612</v>
+      </c>
+      <c r="C239" t="s">
+        <v>632</v>
+      </c>
+      <c r="D239" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4">
+      <c r="A240" t="s">
+        <v>218</v>
+      </c>
+      <c r="B240" t="s">
+        <v>485</v>
+      </c>
+      <c r="C240" t="s">
+        <v>634</v>
+      </c>
+      <c r="D240" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4">
+      <c r="A241" t="s">
+        <v>218</v>
+      </c>
+      <c r="B241" t="s">
+        <v>485</v>
+      </c>
+      <c r="C241" t="s">
+        <v>636</v>
+      </c>
+      <c r="D241" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4">
+      <c r="A242" t="s">
+        <v>218</v>
+      </c>
+      <c r="B242" t="s">
+        <v>485</v>
+      </c>
+      <c r="C242" t="s">
+        <v>638</v>
+      </c>
+      <c r="D242" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s">
+        <v>194</v>
+      </c>
+      <c r="B243" t="s">
+        <v>640</v>
+      </c>
+      <c r="C243" t="s">
+        <v>641</v>
+      </c>
+      <c r="D243" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s">
+        <v>229</v>
+      </c>
+      <c r="B244" t="s">
+        <v>643</v>
+      </c>
+      <c r="C244" t="s">
+        <v>644</v>
+      </c>
+      <c r="D244" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s">
+        <v>229</v>
+      </c>
+      <c r="B245" t="s">
+        <v>643</v>
+      </c>
+      <c r="C245" t="s">
+        <v>646</v>
+      </c>
+      <c r="D245" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s">
+        <v>229</v>
+      </c>
+      <c r="B246" t="s">
+        <v>643</v>
+      </c>
+      <c r="C246" t="s">
+        <v>648</v>
+      </c>
+      <c r="D246" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s">
+        <v>223</v>
+      </c>
+      <c r="B247" t="s">
+        <v>643</v>
+      </c>
+      <c r="C247" t="s">
+        <v>650</v>
+      </c>
+      <c r="D247" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s">
+        <v>218</v>
+      </c>
+      <c r="B248" t="s">
+        <v>652</v>
+      </c>
+      <c r="C248" t="s">
+        <v>653</v>
+      </c>
+      <c r="D248" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s">
+        <v>218</v>
+      </c>
+      <c r="B249" t="s">
+        <v>652</v>
+      </c>
+      <c r="C249" t="s">
+        <v>655</v>
+      </c>
+      <c r="D249" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s">
+        <v>194</v>
+      </c>
+      <c r="B250" t="s">
+        <v>640</v>
+      </c>
+      <c r="C250" t="s">
+        <v>657</v>
+      </c>
+      <c r="D250" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s">
+        <v>194</v>
+      </c>
+      <c r="B251" t="s">
+        <v>640</v>
+      </c>
+      <c r="C251" t="s">
+        <v>659</v>
+      </c>
+      <c r="D251" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="s">
+        <v>229</v>
+      </c>
+      <c r="B252" t="s">
+        <v>643</v>
+      </c>
+      <c r="C252" t="s">
+        <v>661</v>
+      </c>
+      <c r="D252" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="s">
+        <v>218</v>
+      </c>
+      <c r="B253" t="s">
+        <v>652</v>
+      </c>
+      <c r="C253" t="s">
+        <v>663</v>
+      </c>
+      <c r="D253" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="s">
+        <v>218</v>
+      </c>
+      <c r="B254" t="s">
+        <v>652</v>
+      </c>
+      <c r="C254" t="s">
+        <v>665</v>
+      </c>
+      <c r="D254" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="s">
+        <v>218</v>
+      </c>
+      <c r="B255" t="s">
+        <v>652</v>
+      </c>
+      <c r="C255" t="s">
+        <v>667</v>
+      </c>
+      <c r="D255" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="s">
+        <v>218</v>
+      </c>
+      <c r="B256" t="s">
+        <v>652</v>
+      </c>
+      <c r="C256" t="s">
+        <v>669</v>
+      </c>
+      <c r="D256" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="s">
+        <v>218</v>
+      </c>
+      <c r="B257" t="s">
+        <v>652</v>
+      </c>
+      <c r="C257" t="s">
+        <v>671</v>
+      </c>
+      <c r="D257" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="s">
+        <v>229</v>
+      </c>
+      <c r="B258" t="s">
+        <v>643</v>
+      </c>
+      <c r="C258" t="s">
+        <v>673</v>
+      </c>
+      <c r="D258" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="s">
+        <v>194</v>
+      </c>
+      <c r="B259" t="s">
+        <v>640</v>
+      </c>
+      <c r="C259" t="s">
+        <v>675</v>
+      </c>
+      <c r="D259" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="s">
+        <v>218</v>
+      </c>
+      <c r="B260" t="s">
+        <v>652</v>
+      </c>
+      <c r="C260" t="s">
+        <v>677</v>
+      </c>
+      <c r="D260" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="s">
+        <v>218</v>
+      </c>
+      <c r="B261" t="s">
+        <v>652</v>
+      </c>
+      <c r="C261" t="s">
+        <v>679</v>
+      </c>
+      <c r="D261" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="s">
+        <v>218</v>
+      </c>
+      <c r="B262" t="s">
+        <v>652</v>
+      </c>
+      <c r="C262" t="s">
+        <v>681</v>
+      </c>
+      <c r="D262" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="s">
+        <v>229</v>
+      </c>
+      <c r="B263" t="s">
+        <v>643</v>
+      </c>
+      <c r="C263" t="s">
+        <v>683</v>
+      </c>
+      <c r="D263" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="s">
+        <v>218</v>
+      </c>
+      <c r="B264" t="s">
+        <v>652</v>
+      </c>
+      <c r="C264" t="s">
+        <v>685</v>
+      </c>
+      <c r="D264" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="s">
+        <v>218</v>
+      </c>
+      <c r="B265" t="s">
+        <v>652</v>
+      </c>
+      <c r="C265" t="s">
+        <v>687</v>
+      </c>
+      <c r="D265" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="s">
+        <v>218</v>
+      </c>
+      <c r="B266" t="s">
+        <v>689</v>
+      </c>
+      <c r="C266" t="s">
+        <v>690</v>
+      </c>
+      <c r="D266" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="s">
+        <v>218</v>
+      </c>
+      <c r="B267" t="s">
+        <v>689</v>
+      </c>
+      <c r="C267" t="s">
+        <v>692</v>
+      </c>
+      <c r="D267" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="s">
+        <v>218</v>
+      </c>
+      <c r="B268" t="s">
+        <v>689</v>
+      </c>
+      <c r="C268" t="s">
+        <v>694</v>
+      </c>
+      <c r="D268" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="s">
+        <v>218</v>
+      </c>
+      <c r="B269" t="s">
+        <v>689</v>
+      </c>
+      <c r="C269" t="s">
+        <v>696</v>
+      </c>
+      <c r="D269" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="s">
+        <v>218</v>
+      </c>
+      <c r="B270" t="s">
+        <v>689</v>
+      </c>
+      <c r="C270" t="s">
+        <v>698</v>
+      </c>
+      <c r="D270" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="s">
+        <v>218</v>
+      </c>
+      <c r="B271" t="s">
+        <v>689</v>
+      </c>
+      <c r="C271" t="s">
+        <v>700</v>
+      </c>
+      <c r="D271" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="s">
+        <v>229</v>
+      </c>
+      <c r="B272" t="s">
+        <v>702</v>
+      </c>
+      <c r="C272" t="s">
+        <v>703</v>
+      </c>
+      <c r="D272" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="s">
+        <v>218</v>
+      </c>
+      <c r="B273" t="s">
+        <v>689</v>
+      </c>
+      <c r="C273" t="s">
+        <v>705</v>
+      </c>
+      <c r="D273" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="s">
+        <v>218</v>
+      </c>
+      <c r="B274" t="s">
+        <v>689</v>
+      </c>
+      <c r="C274" t="s">
+        <v>707</v>
+      </c>
+      <c r="D274" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="s">
+        <v>229</v>
+      </c>
+      <c r="B275" t="s">
+        <v>702</v>
+      </c>
+      <c r="C275" t="s">
+        <v>709</v>
+      </c>
+      <c r="D275" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="s">
+        <v>229</v>
+      </c>
+      <c r="B276" t="s">
+        <v>702</v>
+      </c>
+      <c r="C276" t="s">
+        <v>711</v>
+      </c>
+      <c r="D276" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="s">
+        <v>229</v>
+      </c>
+      <c r="B277" t="s">
+        <v>702</v>
+      </c>
+      <c r="C277" t="s">
+        <v>713</v>
+      </c>
+      <c r="D277" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="s">
+        <v>218</v>
+      </c>
+      <c r="B278" t="s">
+        <v>715</v>
+      </c>
+      <c r="C278" t="s">
+        <v>716</v>
+      </c>
+      <c r="D278" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="s">
+        <v>218</v>
+      </c>
+      <c r="B279" t="s">
+        <v>715</v>
+      </c>
+      <c r="C279" t="s">
+        <v>718</v>
+      </c>
+      <c r="D279" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="s">
+        <v>218</v>
+      </c>
+      <c r="B280" t="s">
+        <v>715</v>
+      </c>
+      <c r="C280" t="s">
+        <v>720</v>
+      </c>
+      <c r="D280" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="s">
+        <v>218</v>
+      </c>
+      <c r="B281" t="s">
+        <v>715</v>
+      </c>
+      <c r="C281" t="s">
+        <v>722</v>
+      </c>
+      <c r="D281" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="s">
+        <v>229</v>
+      </c>
+      <c r="B282" t="s">
+        <v>724</v>
+      </c>
+      <c r="C282" t="s">
+        <v>725</v>
+      </c>
+      <c r="D282" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="s">
+        <v>218</v>
+      </c>
+      <c r="B283" t="s">
+        <v>727</v>
+      </c>
+      <c r="C283" t="s">
+        <v>728</v>
+      </c>
+      <c r="D283" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="s">
+        <v>218</v>
+      </c>
+      <c r="B284" t="s">
+        <v>727</v>
+      </c>
+      <c r="C284" t="s">
+        <v>730</v>
+      </c>
+      <c r="D284" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="s">
+        <v>218</v>
+      </c>
+      <c r="B285" t="s">
+        <v>727</v>
+      </c>
+      <c r="C285" t="s">
+        <v>732</v>
+      </c>
+      <c r="D285" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="s">
+        <v>229</v>
+      </c>
+      <c r="B286" t="s">
+        <v>734</v>
+      </c>
+      <c r="C286" t="s">
+        <v>735</v>
+      </c>
+      <c r="D286" t="s">
+        <v>736</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D175" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D286" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5141,7 +7493,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -5150,330 +7502,442 @@
     <col min="4" max="4" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" spans="1:4">
+    <row r="1" ht="17" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>234</v>
+        <v>520</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>235</v>
+        <v>521</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>522</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="2" ht="19" customHeight="1" spans="1:4">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="2" ht="17" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>238</v>
+        <v>524</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>239</v>
+        <v>525</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>240</v>
+        <v>526</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="3" ht="19" customHeight="1" spans="1:4">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="3" ht="17" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>238</v>
+        <v>524</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>242</v>
+        <v>528</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>243</v>
+        <v>529</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="4" ht="19" customHeight="1" spans="1:4">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="4" ht="34" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>238</v>
+        <v>524</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>245</v>
+        <v>531</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>246</v>
+        <v>532</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="5" ht="19" customHeight="1" spans="1:4">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="5" ht="17" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>238</v>
+        <v>524</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>248</v>
+        <v>534</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>249</v>
+        <v>535</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="6" ht="19" customHeight="1" spans="1:4">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="6" ht="17" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>251</v>
+        <v>524</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>252</v>
+        <v>537</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>253</v>
+        <v>538</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="7" ht="19" customHeight="1" spans="1:4">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="7" ht="34" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>251</v>
+        <v>540</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>255</v>
+        <v>541</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>256</v>
+        <v>542</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="8" ht="19" customHeight="1" spans="1:4">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="8" ht="34" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>251</v>
+        <v>544</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>258</v>
+        <v>545</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>259</v>
+        <v>546</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="9" ht="19" customHeight="1" spans="1:4">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="9" ht="17" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>251</v>
+        <v>544</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>261</v>
+        <v>548</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>262</v>
+        <v>549</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="10" ht="19" customHeight="1" spans="1:4">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="10" ht="17" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>251</v>
+        <v>544</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>264</v>
+        <v>551</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>265</v>
+        <v>552</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="11" ht="19" customHeight="1" spans="1:4">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="11" ht="17" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>267</v>
+        <v>544</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>268</v>
+        <v>554</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>269</v>
+        <v>555</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="12" ht="19" customHeight="1" spans="1:4">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="12" ht="17" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>267</v>
+        <v>544</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>271</v>
+        <v>557</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>272</v>
+        <v>558</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="13" ht="19" customHeight="1" spans="1:4">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="13" ht="17" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>267</v>
+        <v>560</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>274</v>
+        <v>561</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>275</v>
+        <v>562</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="14" ht="19" customHeight="1" spans="1:4">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="14" ht="17" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>267</v>
+        <v>560</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>277</v>
+        <v>564</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>278</v>
+        <v>565</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="15" ht="19" customHeight="1" spans="1:4">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="15" ht="17" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>267</v>
+        <v>560</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>280</v>
+        <v>567</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>281</v>
+        <v>568</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="16" ht="19" customHeight="1" spans="1:4">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="16" ht="34" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>283</v>
+        <v>560</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>284</v>
+        <v>570</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>285</v>
+        <v>571</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="17" ht="19" customHeight="1" spans="1:4">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="17" ht="34" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>283</v>
+        <v>560</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>287</v>
+        <v>573</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>288</v>
+        <v>574</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="18" ht="19" customHeight="1" spans="1:4">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="18" ht="17" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>283</v>
+        <v>560</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>290</v>
+        <v>576</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>291</v>
+        <v>577</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="19" ht="19" customHeight="1" spans="1:4">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="19" ht="17" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>283</v>
+        <v>560</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>293</v>
+        <v>579</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>294</v>
+        <v>580</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="20" ht="19" customHeight="1" spans="1:4">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="20" ht="17" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>283</v>
+        <v>560</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>296</v>
+        <v>582</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>297</v>
+        <v>583</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="21" ht="19" customHeight="1" spans="1:4">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="21" ht="34" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>299</v>
+        <v>585</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>300</v>
+        <v>586</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>301</v>
+        <v>587</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="22" ht="19" customHeight="1" spans="1:4">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="22" ht="34" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>299</v>
+        <v>585</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>303</v>
+        <v>589</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>304</v>
+        <v>590</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="23" ht="19" customHeight="1" spans="1:4">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="23" ht="34" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>299</v>
+        <v>585</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>306</v>
+        <v>592</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>307</v>
+        <v>593</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>308</v>
+        <v>594</v>
+      </c>
+    </row>
+    <row r="24" ht="34" spans="1:4">
+      <c r="A24" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="25" ht="34" spans="1:4">
+      <c r="A25" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="26" ht="34" spans="1:4">
+      <c r="A26" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="27" ht="34" spans="1:4">
+      <c r="A27" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="28" ht="34" spans="1:4">
+      <c r="A28" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="29" ht="34" spans="1:4">
+      <c r="A29" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="30" ht="34" spans="1:4">
+      <c r="A30" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="31" ht="34" spans="1:4">
+      <c r="A31" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>621</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D23" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:D31" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5493,42 +7957,42 @@
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>309</v>
+        <v>622</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>235</v>
+        <v>623</v>
       </c>
     </row>
     <row r="2" ht="19" customHeight="1" spans="1:2">
       <c r="A2" s="2" t="s">
-        <v>310</v>
+        <v>624</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>311</v>
+        <v>625</v>
       </c>
     </row>
     <row r="3" ht="19" customHeight="1" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>312</v>
+        <v>626</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>313</v>
+        <v>627</v>
       </c>
     </row>
     <row r="4" ht="19" customHeight="1" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>314</v>
+        <v>628</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>315</v>
+        <v>629</v>
       </c>
     </row>
     <row r="5" ht="19" customHeight="1" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>316</v>
+        <v>630</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>317</v>
+        <v>631</v>
       </c>
     </row>
   </sheetData>

--- a/docs/feature-list.xlsx
+++ b/docs/feature-list.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>1. 登录与授权</t>
+          <t>登录与授权</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>1. 登录与授权</t>
+          <t>登录与授权</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>1. 登录与授权</t>
+          <t>登录与授权</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>1. 登录与授权</t>
+          <t>登录与授权</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1. 登录与授权</t>
+          <t>登录与授权</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>1. 登录与授权</t>
+          <t>登录与授权</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2. AI 会话</t>
+          <t>AI 会话</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>2. AI 会话</t>
+          <t>AI 会话</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2. AI 会话</t>
+          <t>AI 会话</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>2. AI 会话</t>
+          <t>AI 会话</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>2. AI 会话</t>
+          <t>AI 会话</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2. AI 会话</t>
+          <t>AI 会话</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -868,7 +868,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>2. AI 会话</t>
+          <t>AI 会话</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2. AI 会话</t>
+          <t>AI 会话</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>2. AI 会话</t>
+          <t>AI 会话</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>2. AI 会话</t>
+          <t>AI 会话</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>2. AI 会话</t>
+          <t>AI 会话</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>2. AI 会话</t>
+          <t>AI 会话</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>2. AI 会话</t>
+          <t>AI 会话</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>3. 付费墙与权益</t>
+          <t>付费墙与权益</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>3. 付费墙与权益</t>
+          <t>付费墙与权益</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>3. 付费墙与权益</t>
+          <t>付费墙与权益</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>3. 付费墙与权益</t>
+          <t>付费墙与权益</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>3. 付费墙与权益</t>
+          <t>付费墙与权益</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>4. 我的</t>
+          <t>我的</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>4. 我的</t>
+          <t>我的</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>4. 我的</t>
+          <t>我的</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>4. 我的</t>
+          <t>我的</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>4. 我的</t>
+          <t>我的</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>4. 我的</t>
+          <t>我的</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>4. 我的</t>
+          <t>我的</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>4. 我的</t>
+          <t>我的</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>4. 我的</t>
+          <t>我的</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>4. 我的</t>
+          <t>我的</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>4. 我的</t>
+          <t>我的</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>5. 支付</t>
+          <t>支付</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>5. 支付</t>
+          <t>支付</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>5. 支付</t>
+          <t>支付</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>6. 协议与辅助页</t>
+          <t>协议与辅助页</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>6. 协议与辅助页</t>
+          <t>协议与辅助页</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>6. 协议与辅助页</t>
+          <t>协议与辅助页</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>6. 协议与辅助页</t>
+          <t>协议与辅助页</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>1. 登录与主控台</t>
+          <t>登录与主控台</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>1. 登录与主控台</t>
+          <t>登录与主控台</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>2. 知识产品 KP</t>
+          <t>知识产品 KP</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>2. 知识产品 KP</t>
+          <t>知识产品 KP</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>2. 知识产品 KP</t>
+          <t>知识产品 KP</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>2. 知识产品 KP</t>
+          <t>知识产品 KP</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>2. 知识产品 KP</t>
+          <t>知识产品 KP</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>2. 知识产品 KP</t>
+          <t>知识产品 KP</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>2. 知识产品 KP</t>
+          <t>知识产品 KP</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>2. 知识产品 KP</t>
+          <t>知识产品 KP</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>2. 知识产品 KP</t>
+          <t>知识产品 KP</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>2. 知识产品 KP</t>
+          <t>知识产品 KP</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>2. 知识产品 KP</t>
+          <t>知识产品 KP</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>2. 知识产品 KP</t>
+          <t>知识产品 KP</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>2. 知识产品 KP</t>
+          <t>知识产品 KP</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>2. 知识产品 KP</t>
+          <t>知识产品 KP</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>3. Agent 人设</t>
+          <t>Agent 人设</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>3. Agent 人设</t>
+          <t>Agent 人设</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>4. C 端用户</t>
+          <t>C 端用户</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -2317,7 +2317,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>4. C 端用户</t>
+          <t>C 端用户</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>5. 订单管理</t>
+          <t>订单管理</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>5. 订单管理</t>
+          <t>订单管理</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>5. 订单管理</t>
+          <t>订单管理</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>6. 兑换码</t>
+          <t>兑换码</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>6. 兑换码</t>
+          <t>兑换码</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>6. 兑换码</t>
+          <t>兑换码</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>7. 数据看板</t>
+          <t>数据看板</t>
         </is>
       </c>
       <c r="C70" s="3" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>7. 数据看板</t>
+          <t>数据看板</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>7. 数据看板</t>
+          <t>数据看板</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>7. 数据看板</t>
+          <t>数据看板</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>8. 答案反馈</t>
+          <t>答案反馈</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>8. 答案反馈</t>
+          <t>答案反馈</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>9. 客服配置</t>
+          <t>客服配置</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>10. 系统配置</t>
+          <t>系统配置</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>10. 系统配置</t>
+          <t>系统配置</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>11. 个人中心</t>
+          <t>个人中心</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>11. 个人中心</t>
+          <t>个人中心</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>11. 个人中心</t>
+          <t>个人中心</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>12. 评审工具</t>
+          <t>评审工具</t>
         </is>
       </c>
       <c r="C82" s="3" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>1. 登录与主控台</t>
+          <t>登录与主控台</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>1. 登录与主控台</t>
+          <t>登录与主控台</t>
         </is>
       </c>
       <c r="C84" s="3" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>2. 机构管理</t>
+          <t>机构管理</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>2. 机构管理</t>
+          <t>机构管理</t>
         </is>
       </c>
       <c r="C86" s="3" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>2. 机构管理</t>
+          <t>机构管理</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>2. 机构管理</t>
+          <t>机构管理</t>
         </is>
       </c>
       <c r="C88" s="3" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>2. 机构管理</t>
+          <t>机构管理</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>2. 机构管理</t>
+          <t>机构管理</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>2. 机构管理</t>
+          <t>机构管理</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>2. 机构管理</t>
+          <t>机构管理</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>2. 机构管理</t>
+          <t>机构管理</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="B94" s="3" t="inlineStr">
         <is>
-          <t>2. 机构管理</t>
+          <t>机构管理</t>
         </is>
       </c>
       <c r="C94" s="3" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>2. 机构管理</t>
+          <t>机构管理</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>2. 机构管理</t>
+          <t>机构管理</t>
         </is>
       </c>
       <c r="C96" s="3" t="inlineStr">
@@ -3308,7 +3308,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>2. 机构管理</t>
+          <t>机构管理</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="B98" s="3" t="inlineStr">
         <is>
-          <t>3. 机构账户</t>
+          <t>机构账户</t>
         </is>
       </c>
       <c r="C98" s="3" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>3. 机构账户</t>
+          <t>机构账户</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="B100" s="3" t="inlineStr">
         <is>
-          <t>3. 机构账户</t>
+          <t>机构账户</t>
         </is>
       </c>
       <c r="C100" s="3" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>4. 订阅订单（全域 B 端）</t>
+          <t>订阅订单（全域 B 端）</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="B102" s="3" t="inlineStr">
         <is>
-          <t>4. 订阅订单（全域 B 端）</t>
+          <t>订阅订单（全域 B 端）</t>
         </is>
       </c>
       <c r="C102" s="3" t="inlineStr">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>5. 全域知识产品 KP</t>
+          <t>全域知识产品 KP</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>5. 全域知识产品 KP</t>
+          <t>全域知识产品 KP</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>5. 全域知识产品 KP</t>
+          <t>全域知识产品 KP</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>5. 全域知识产品 KP</t>
+          <t>全域知识产品 KP</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>5. 全域知识产品 KP</t>
+          <t>全域知识产品 KP</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>5. 全域知识产品 KP</t>
+          <t>全域知识产品 KP</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>6. 全域 Agent 人设</t>
+          <t>全域 Agent 人设</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>6. 全域 Agent 人设</t>
+          <t>全域 Agent 人设</t>
         </is>
       </c>
       <c r="C110" s="3" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>7. 全域用户</t>
+          <t>全域用户</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>7. 全域用户</t>
+          <t>全域用户</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>8. 全域订单</t>
+          <t>全域订单</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>8. 全域订单</t>
+          <t>全域订单</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>9. 全域答案反馈</t>
+          <t>全域答案反馈</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -3855,7 +3855,7 @@
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>10. 全域模型用量</t>
+          <t>全域模型用量</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>11. 平台账户</t>
+          <t>平台账户</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="B118" s="3" t="inlineStr">
         <is>
-          <t>11. 平台账户</t>
+          <t>平台账户</t>
         </is>
       </c>
       <c r="C118" s="3" t="inlineStr">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>12. 角色权限</t>
+          <t>角色权限</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="B120" s="3" t="inlineStr">
         <is>
-          <t>12. 角色权限</t>
+          <t>角色权限</t>
         </is>
       </c>
       <c r="C120" s="3" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>13. 默认 LLM</t>
+          <t>默认 LLM</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>13. 默认 LLM</t>
+          <t>默认 LLM</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>14. 个人中心</t>
+          <t>个人中心</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="B124" s="3" t="inlineStr">
         <is>
-          <t>14. 个人中心</t>
+          <t>个人中心</t>
         </is>
       </c>
       <c r="C124" s="3" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>14. 个人中心</t>
+          <t>个人中心</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>15. 评审工具</t>
+          <t>评审工具</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>1. 通用状态规范</t>
+          <t>通用状态规范</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>1. 通用状态规范</t>
+          <t>通用状态规范</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>1. 通用状态规范</t>
+          <t>通用状态规范</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="B130" s="3" t="inlineStr">
         <is>
-          <t>1. 通用状态规范</t>
+          <t>通用状态规范</t>
         </is>
       </c>
       <c r="C130" s="3" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>1. 通用状态规范</t>
+          <t>通用状态规范</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>1. 通用状态规范</t>
+          <t>通用状态规范</t>
         </is>
       </c>
       <c r="C132" s="3" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>1. 通用状态规范</t>
+          <t>通用状态规范</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="B134" s="3" t="inlineStr">
         <is>
-          <t>1. 通用状态规范</t>
+          <t>通用状态规范</t>
         </is>
       </c>
       <c r="C134" s="3" t="inlineStr">
@@ -4378,8 +4378,7 @@
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>（1）移动端登录态有效期 30 天，每次操作自动重置有效期
-（2）游客模式：未登录可浏览只读内容，创建会话/发送问题等需授权操作时引导登录，登录后自动补发游客态已输入问题</t>
+          <t>（1）移动端登录态有效期 30 天，每次操作自动重置有效期</t>
         </is>
       </c>
     </row>

--- a/docs/feature-list.xlsx
+++ b/docs/feature-list.xlsx
@@ -33,7 +33,7 @@
       <sz val="11"/>
     </font>
     <font>
-      <color rgb="002563EB"/>
+      <color rgb="00DC2626"/>
     </font>
   </fonts>
   <fills count="4">
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E137"/>
+  <dimension ref="A1:E138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -510,7 +510,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>1. 登录与授权</t>
+          <t>登录与授权</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>1. 登录与授权</t>
+          <t>登录与授权</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>1. 登录与授权</t>
+          <t>登录与授权</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>1. 登录与授权</t>
+          <t>登录与授权</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1. 登录与授权</t>
+          <t>登录与授权</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>1. 登录与授权</t>
+          <t>登录与授权</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2. AI 会话</t>
+          <t>AI 会话</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>2. AI 会话</t>
+          <t>AI 会话</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -760,51 +760,83 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2. AI 会话</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
+          <t>AI 会话</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>KP 前台入口（状态判活）</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>0718周六新增
+（1）0717 #1.3/#1.6：新增统一入口 /kp/:kpId——KP 前台地址直达与知识 KP 二维码扫码（含首扫权益绑定核销）共用，进入时先判 KP 状态
+（2）已发布：过渡提示后进入该 KP 的全新 AI 会话
+（3）草稿（未发布）：与「已删除」同等处理——整屏提示「该知识 KP 已失效，若有问题请联系客服」，停留 3 秒后按跳转规则①处理（草稿未对外发布，前台不区分「未发布」与「已删除」，避免暴露机构未上线内容）
+（4）已下架：整屏提示「该知识 KP 已下架，若有问题请联系客服」，停留 3 秒后按跳转规则①处理
+（5）已删除（逻辑删除）/ 不存在：整屏提示「该知识 KP 已失效，若有问题请联系客服」，停留 3 秒后按跳转规则①处理
+（6）跳转规则①：目标＝本 KP 同机构下「最新创建且已发布」KP 的会话；用户未登录则先进登录界面（仅当存在目标时）；本机构无满足条件的 KP 则不跳转、也不进登录界面，停留提示页并显示「本机构暂无可进入的知识 KP」</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>移动端 H5（C 端用户）</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>AI 会话</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>流式问答（打字机）</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>（1）AI 答案文字打字机式流式输出，未输出完时显示光标
 （2）仅新生成的回答展示打字机动效；切换历史会话、电话挂断返回等场景下已生成回答直接整段展示、不重复动效</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>移动端 H5（C 端用户）</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>2. AI 会话</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>AI 会话</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>相关媒体资源（多模态卡片）</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>0716周四更新
-（1）答案卡片内「相关媒体资源」作为加粗小标题贴在卡片上；文字区在上、媒体区在下，两区做明显视觉区分
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>（1）答案卡片内「相关媒体资源」作为加粗小标题贴在卡片上；文字区在上、媒体区在下，两区做明显视觉区分
 （2）媒体并列排布支持左右滑动，顺序按后台返回的相关度从左到右排列（非图→音→视固定序），不展示相关度数值
 （3）受限内容在封面上展示权益标签 + 类型角标（图片/音频/视频）：会员内容标「会员」、永享内容标「永享」，便于用户一眼区分付费类型
 （4）一个资源若既是会员又设了永享价，按权益边界归永享池——只标「永享」、只走永享购买
@@ -813,56 +845,56 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>移动端 H5（C 端用户）</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>2. AI 会话</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>AI 会话</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>答案操作与反馈</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>（1）每条 AI 答案下方、「参考 N 篇知识」入口左侧并排三个 icon：复制（toast「已复制答案」）、点赞、点踩
 （2）点赞/点踩互斥，可再次点击取消；icon 为灰色系描边填充样式（选中态灰填充、非主题色）</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>移动端 H5（C 端用户）</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>2. AI 会话</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>AI 会话</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>答案操作与反馈</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>点踩反馈弹层</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>（1）点踩 → 弹底部反馈 sheet，标题「反馈」
 （2）4 个互选标签：有害/不安全、虚假信息、没有帮助、其他
@@ -871,56 +903,56 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>移动端 H5（C 端用户）</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>2. AI 会话</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>AI 会话</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>推荐追问</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>（1）展示在多模态卡片下方，2–3 个追问上下纵向堆叠（非左右并列）
 （2）点击任一即作为新问题发送</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>移动端 H5（C 端用户）</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>2. AI 会话</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>AI 会话</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>语音输入（短语音）</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>（1）点输入框右侧麦克风 → 在当前会话页底部弹音浪动画浮层（非全屏新页），浮层背底与会话背景自然过渡
 （2）提示「松手发送，上滑取消」
@@ -928,28 +960,28 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>移动端 H5（C 端用户）</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>2. AI 会话</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>AI 会话</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>历史会话抽屉</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>（1）左上角菜单开抽屉；顶部「新建会话」
 （2）历史按时间分组（今天/昨天/某年某月）列出，点任一条载入该会话
@@ -957,31 +989,30 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>移动端 H5（C 端用户）</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>2. AI 会话</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>AI 会话</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>答案溯源抽屉</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>0716周四更新
-（1）答案下「参考 N 篇知识」入口，点击从右侧抽屉拉出溯源列表，仅按相关度从高到低排序、不显数值
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>（1）答案下「参考 N 篇知识」入口，点击从右侧抽屉拉出溯源列表，仅按相关度从高到低排序、不显数值
 （2）分两块、中间浅灰横线分隔：上块知识 KP（KP 封面 + KP 名 + 文件名 + 章节页码；同 KP 多命中文件归并最多 2 个、其余「…等 N 个文件」），下块互联网检索（站点用小圆形图标）
 （3）字段过长尾部省略号截断
 （4）条目点击：book 类型跳该 KP 纸书购买链接，链接为空提示「暂不可查看详情」；web 类型打开来源网页
@@ -989,28 +1020,28 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>移动端 H5（C 端用户）</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>2. AI 会话</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>AI 会话</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>外部来源跳转倒计时</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>（1）所有「跳出 AI 问书」的链接（web 互联网来源 + 知识 KP 的纸书/运营填写链接）均先弹过渡提示
 （2）样式为屏幕中上方黑底白字倒计时条：左侧 3·2·1 倒计时 + 「即将跳转到外部」+ 右侧「取消跳转」
@@ -1019,28 +1050,28 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>移动端 H5（C 端用户）</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>2. AI 会话</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>AI 会话</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>机构 Token 超限拦截</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>（1）〔演示〕由落地页演示开关触发；生产由机构实际 Token 用量判定
 （2）超限时会话顶部常驻珊瑚红提示条「当前机构 Token 已达上限，请联系客服」
@@ -1048,28 +1079,28 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>移动端 H5（C 端用户）</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>2. AI 会话</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>AI 会话</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>实时电话式语音</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>（1）会员专属：未开通会员点电话入口时引导开通；开通后方可进入
 （2）独立电话页：中央 Agent 形象 + 实时语音状态文案与动画（如「正在听…」「正在回答…」）
@@ -1079,28 +1110,28 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>移动端 H5（C 端用户）</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>3. 付费墙与权益</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>付费墙与权益</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>多模态付费墙</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>（1）受限媒体触发，按资源所属权益池动态呈现按钮（不再固定两按钮）：
 （2）会员资源：标题「{资源名} · 会员内容」+ 单按钮「开通会员 · 畅享全部会员内容」（进会员页）
@@ -1109,28 +1140,28 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>移动端 H5（C 端用户）</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>3. 付费墙与权益</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>付费墙与权益</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>多模态 lightbox 预览</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>（1）放大预览顶部固定「因版权限制，暂不支持保存下载」+ 关闭✕
 （2）支持左右翻页（循环）+ 底部缩略点/缩略图条切换，主预览区可左右滑动浏览同卡片其他媒体
@@ -1138,35 +1169,6 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>移动端 H5（C 端用户）</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>3. 付费墙与权益</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>开通会员</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>（1）仅展示首月折扣价、月度价两档，无年付；首月特惠默认选中
-（2）含自动续费协议入口与「可随时退订 · 会员到期后 72 小时为服务缓冲期」说明；缓冲期不计入已付费会员时长
-（3）「立即开通」前校验手机号绑定（未绑先引导绑定再继续），通过后按所选档进微信支付收银台</t>
-        </is>
-      </c>
-    </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
@@ -1175,20 +1177,53 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>3. 付费墙与权益</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
+          <t>付费墙与权益</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>开通会员</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>0718周六更新
+（1）0717 二批 #9：两档改为「购买方式即续费语义」，消除「按月自动续费」歧义——① 连续包月（默认选中，角标「首月特惠」）：首月 ¥9.9、次月起 ¥19.9/月 自动续费，卡内说明「自动续费，可随时退订」② 单月（¥19.9 / 1 个月）：一次性购买，卡内说明「到期自动失效，不自动续费不扣款」；选中即表达是否自动续费，不再靠一个含糊的全局勾选
+（2）协议、按钮与底部说明随所选方式联动：连续包月→勾选《自动续费协议》+ 按钮「¥9.9 开通连续包月」+ 底部说明「次月起 ¥19.9/月 自动扣费 · 支持随时退订，到期赠 72 小时会员缓冲使用期」；单月→协议行换成《会员服务协议》（无自动续费协议）+ 按钮「¥19.9 购买单月会员」+ 底部说明「到期自动失效，不会自动扣费」；缓冲期不计入已付费会员时长
+（3）「立即开通」前校验手机号绑定（未绑先引导绑定再继续），通过后按所选方式进微信支付收银台
+（4）「0718 修订」开通会员页按「先权益、再套餐、后协议」重构交互：① 标题下新增三枚权益速览 chip（受限内容全解锁 / 图音视频精讲 / 电话问答·VIP 优先）；② 套餐卡信息层级重排——卡名 + 续费语义 pill（连续包月＝「自动续费 · 可随时取消」琥珀标；单月＝「一次性购买 · 不自动续费」灰标）+ 一行说明 + 右侧大价签；选中态改左侧对勾圆点（琥珀填充）+ 琥珀描边淡底，「首月特惠」角标改琥珀渐变；③ 协议勾选改为真实可点交互（未勾选点按钮 toast 引导先同意协议），连续包月需同意《会员服务协议》《自动续费协议》两份，单月仅《会员服务协议》；④ 按钮与底部说明随所选方式联动（语义与 0717 二批 #9 不变：连续包月＝首月 ¥9.9、次月起 ¥19.9/月 自动续费可退订；单月＝¥19.9 一次性、到期自动失效）
+（5）「0718 修订」删除开通按钮下方的补充说明文案（原「次月起 ¥19.9/月 自动扣费 · 支持随时退订，到期赠 72 小时会员缓冲使用期」/「一次性购买 · 到期自动失效，不会自动扣费」），续费规则由套餐卡内的续费语义 pill 与说明承载，不再页底重复
+（6）「0719 修订」协议勾选框改为**默认未勾选**，须用户主动勾选后方可开通（原默认已勾选）——连续包月场景含《自动续费协议》，默认代勾在国内合规口径下通常不被接受；同时与登录落地页「协议默认未勾选」的口径保持一致。未勾选时开通按钮呈置灰视觉，点击 toast「请先阅读并同意相关协议」并阻断，不进收银台</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>移动端 H5（C 端用户）</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>付费墙与权益</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>会员中心</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>（1）会员卡：会员标识 + 有效期 + 续费状态（自动续费 / 到期不再续费）
 （2）「免费 vs 会员」权益对比表（逐项 ✅/✗）：基础文字知识问答、图音视频深度知识精讲、VIP 极速优先通道、实时电话即时问答、永享名家典藏知识（永享标注为「单独购买」）
@@ -1196,28 +1231,28 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>移动端 H5（C 端用户）</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>3. 付费墙与权益</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>付费墙与权益</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>会员中心</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>取消/开启自动续费</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>（1）自动续费开启时显示「取消自动续费」入口（无手动续费按钮）
 （2）点取消 → 二次确认 sheet（挽留设计：主按钮「暂不取消」、弱化「确认取消」）
@@ -1226,28 +1261,28 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>移动端 H5（C 端用户）</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>4. 我的</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>我的</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>我的主页</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>（1）顶部用户卡（点击进个人资料）：头像 + 昵称（无则「未设置昵称」）+ 会员标 + 手机号（未绑显「未绑定手机号」）
 （2）「会员」分组：会员中心（右值 已开通/未开通）
@@ -1258,99 +1293,74 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>移动端 H5（C 端用户）</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>4. 我的</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>我的</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>我的永享</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>0716周四更新
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>0718周六更新
 （1）已购永享列表，按文件名模糊搜索 + 类型筛选（全部/图片/音频/视频）
 （2）网格卡片：封面 + 类型角标 + 名称 +「{类型} · 永久解锁」
 （3）点卡片进多模态预览（顶部固定版权保护文案，不支持保存下载）
 （4）空态「没有匹配的永享内容」
-（5）KP 被机构删除后，已购永享条目保留但打「已失效」标，点击拦截并提示「内容已被提供方移除，如有疑问请联系客服」，不可再预览/进会话
-（6）KP 仅「下架」时已购权益不受影响，永享内容照常可看——下架只停新售，不动存量权益（买断契约）
-（7）0716 #9.2：永享购后机构端处理规则——删除资源：C 端标「已失效」、内容不可访问；调价：永享为一次性买断，不影响已购用户、仅新购按新价，不补差不重复扣费；转为非永享/停售：已购永享用户权益保留，仅停止新的永享售卖入口</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+（5）KP 被机构删除后（逻辑删除），已购永享条目保留但打「已失效」标，点击拦截并提示「该内容已失效，若有问题请联系客服」，不可再预览/进会话
+（6）0717 #1.4：KP「下架」后已购永享同样拦截——封面置灰 + 琥珀「已下架」标（区别于「已失效」的珊瑚红），点击提示「该内容已下架，若有问题请联系客服」；下架＝运营临时禁访问，已购权益不清除，重新上架后自动恢复可预览（不再按买断契约放行）
+（7）0717【永享购后机构端处理规则】（终版）：① 下架 KP → 已购永享标「已下架」、暂不可访问，权益不清除，重新上架自动恢复 ② 删除 KP / 删除永享资源（逻辑删除）→ C 端标「已失效」、内容不可访问，数据库保留购买与权益数据 ③ 调价 → 永享为一次性买断，不影响已购用户、仅新购按新价，不补差不重复扣费 ④ 转为非永享 / 停售 → 已购权益保留，仅停止新的永享售卖入口</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>移动端 H5（C 端用户）</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>4. 我的</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>我的</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>我的纸书</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>0716周四更新
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>0718周六更新
 （1）展示用户所有线下扫码对应的知识 KP（不只首扫绑定的），含已解锁与未解锁
 （2）卡片：KP 封面 + KP 名（固定两行高）+「扫码解锁 · 时间」（钉在卡片底部对齐）；按 KP 名模糊搜索
-（3）状态区分：顶部筛选 chip（全部 / 已解锁 / 未解锁，与「我的永享」同款 UI，默认「全部」）；首扫绑定的 KP 卡片显「已解锁」标，后扫未获权益不显状态标（界面保持干净）；列表说明文案「展示全部扫过纸书，首扫解锁相应权益」
+（3）状态区分：顶部筛选 chip（全部 / 已解锁 / 未解锁，与「我的永享」同款 UI，默认「全部」）；首扫绑定的 KP 卡片显「已解锁」标，后扫未获权益不显状态标（界面保持干净）；列表说明文案「首扫永久解锁该 KP 当前及未来新增的全部内容」
 （4）首扫绑定后获得该 KP 级完整阅读权益：当前及未来新增的免费、会员、永享内容均可访问，权益长期归属该用户
 （5）已解锁 KP 持续保留在「我的纸书」并直接进入会话；永享媒体不重复逐条写入「我的永享」。未解锁 KP 仍按普通会员/永享规则付费
 （6）进入会话仍弹 3 秒黑底 toast「即将进入「{KP名}」AI 会话」（文案过长自动换行）
-（7）0716 #9.1：扫码对应 KP 状态两级呈现（与我的永享 / 历史会话全端统一）——已下架标「已下架」：首扫已解锁的仍可进入会话（既有权益保留），未解锁的点击提示「当前「{KP名}」已下架，若有问题请联系客服」；已删除标「已失效」：无论是否解锁点击均提示「当前「{KP名}」已失效，若有问题请联系客服」，不可再解锁/进会话</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>移动端 H5（C 端用户）</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>4. 我的</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>我的纸书</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>扫一扫</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>（1）右上角「扫一扫」入口，点击调起手机相机扫码
-（2）扫到纸书二维码后 toast「已识别纸书二维码 · 正在进入全新会话」→ 进入对应 KP 的全新会话并绑定该 KP 权益</t>
+（7）0717 #1.1/二批 #3：KP 状态呈现（与我的永享全端统一）——已下架标「已下架」、已删除标「已失效」，若已解锁则均并列保留「已解锁」标（双标堆叠、间距加大、「已解锁」降低透明度示意此内容当前不可访问）；无论是否解锁点击均拦截，提示文案不带 KP 名：「该内容已下架，若有问题请联系客服」/「该内容已失效，若有问题请联系客服」（下架＝临时禁访问，权益保留、重新上架自动恢复）
+（8）「0718 修订」纸书状态标视觉系统统一：已下架（琥珀底琥珀字）/ 已失效（珊瑚底珊瑚字）/ 已解锁（白底玉绿字+皇冠）三标统一为封面右上纵向堆叠的圆角胶囊（同字号同字重同内边距），一张卡可同时展示「已下架/已失效」与「已解锁」双标；双标时「已解锁」降为中性灰示意当前不可访问。语义不变（下架＝临时禁访问权益保留、删除＝失效拦截）
+（9）「0718 修订」纸书状态标布局与样式再调整：① 已下架/已失效标签从封面右上角移到卡片内「KP 名称」后面，改为中性灰小胶囊（浅灰底灰字，不再用琥珀/珊瑚红），封面右上角只保留「已解锁」；② 已下架/已失效的封面降透明度+轻微去色，示意当前无法访问（「已解锁」标挂卡片层、不受封面置灰影响）；③ 双标场景（已下架/已失效 + 已解锁）依旧同时展示，点击拦截语义不变
+（10）「0718 修订」下架/失效呈现再调整：已下架/已失效标签从 KP 名称后移到「扫码时间」后面；且已下架/已失效的整卡（封面 + 名称 + 时间 + 标签）统一降低透明度、「已解锁」标同步变淡，一眼区分暂不可访问的纸书；正常纸书不受影响</t>
         </is>
       </c>
     </row>
@@ -1362,48 +1372,77 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>4. 我的</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
+          <t>我的</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>我的纸书</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>扫一扫</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>0718周六更新
+（1）右上角「扫一扫」入口，点击调起手机相机扫码
+（2）0717 #1.3：扫码统一走「KP 前台入口 /kp/:kpId」判活——toast「已识别知识 KP 二维码」后进入入口页：已发布正常进入全新会话并绑定权益；已下架 / 已删除按入口页失效流程提示并跳转（原型演示按 已发布→已下架→已失效 轮换）。注意用词：兑换码的权益是会员，与 KP 绑定的是「知识 KP 二维码」</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>移动端 H5（C 端用户）</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>我的</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>个人资料</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>（1）由「我的」顶部头像/昵称/手机号区右侧箭头进入（不再有独立「个人资料」菜单）
 （2）「资料」列表：头像、昵称、性别、地区；微信环境由授权自动带回作初始填充，全字段均可修改</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>移动端 H5（C 端用户）</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>4. 我的</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>我的</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>个人资料</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>头像上传+圆形裁剪</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>（1）点头像行调起手机相册，选图后弹全屏裁剪 overlay
 （2）可拖拽移动图片调整位置（无底部缩放条）；顶部标题与取消/确定按钮套用前台 AI 主视觉
@@ -1411,28 +1450,28 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>移动端 H5（C 端用户）</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>4. 我的</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>我的</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>个人资料</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>昵称/性别/地区编辑</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>（1）昵称：居中弹窗输入框（限 20 字）+ 保存 → toast「已更新」
 （2）性别：弹窗仅「男/女」两项（去掉「保密」），选中即保存
@@ -1440,28 +1479,28 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>移动端 H5（C 端用户）</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>4. 我的</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>我的</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>兑换码</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>（1）「兑换会员权益 / 输入兑换码,或拍照自动识别」
 （2）输入框（自动转大写）+ 相机按钮（调起相机/相册 OCR 识别）
@@ -1472,31 +1511,30 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>移动端 H5（C 端用户）</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>4. 我的</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>我的</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>我的订单</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>0716周四更新
-（1）双维度筛选并存：顶部为「订单类型」Tab（全部 / 会员 / 永享 / 兑换码），其下为「订单状态」chips（全部 / 已支付 / 退款售后）；两维度分层放置，过滤取交集。部分退款、全额退款、退款中统一归入「退款/售后」桶；已支付、兑换码已核销归「已支付」桶。0716 #4：支付成功才落库（中断不生成订单），故无「待支付」态；0716 #5：切到「兑换码」Tab 时隐藏状态 chips（能显示的兑换码必为已核销，无需状态维度）
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>（1）双维度筛选并存：顶部为「订单类型」Tab（全部 / 会员 / 永享 / 兑换码），其下为「订单状态」chips（全部 / 已支付 / 退款售后）；两维度分层放置，过滤取交集。部分退款、全额退款、退款中统一归入「退款/售后」桶；已支付、兑换码已核销归「已支付」桶。0716 #4：支付成功才落库（中断不生成订单），故无「待支付」态；0716 #5：切到「兑换码」Tab 时隐藏状态 chips（能显示的兑换码必为已核销，无需状态维度）
 （2）列表按付款时间降序
 （3）每单展示类型标签 + 标题 + 金额 + 状态 + 时间；仅「永享」订单展示关联 KP + 媒体名
 （4）存在退款时，列表以浅灰退款内容条（奶白暖灰底，弱化不抢视觉）展示逐笔退款进度、金额与时间；单笔退款进度三色语义：退款成功=青绿、退款中=靛蓝、退款失败=珊瑚红
@@ -1505,28 +1543,28 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>移动端 H5（C 端用户）</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>4. 我的</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>我的</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>订单详情</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>（1）按类型差异化呈现
 （2）会员：基础信息卡（订单编号/支付方式/续费方式 自动续费·手动支付/下单·付款时间）+ 会员权益卡（有效期）
@@ -1537,28 +1575,28 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>移动端 H5（C 端用户）</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>4. 我的</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>我的</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>换绑手机号</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
         <is>
           <t>（1）展示当前手机号（脱敏）+「换绑后用新号码登录」
 （2）新手机号 + 验证码两输入框（校验同登录）+「获取验证码」
@@ -1567,28 +1605,28 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>移动端 H5（C 端用户）</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>5. 支付</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>支付</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>微信支付收银台</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
         <is>
           <t>（1）会员开通与永享买断统一走模拟微信支付收银台：标题区白底、AI 问书 logo 用会话同款电光靛紫色动画球
 （2）展示商户「AI 问书」+ 金额 + 商品名；商户/确认支付按钮沿用微信绿 + 模拟环境提示「不会产生真实扣款」
@@ -1597,28 +1635,28 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>移动端 H5（C 端用户）</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>5. 支付</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>支付</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>支付成功</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>（1）成功对勾用绿色/主题色 + 同心圆光环（避免被误解为未支付成功）
 （2）文案「已为你解锁权益，回到刚才的对话继续探索」
@@ -1626,90 +1664,62 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>移动端 H5（C 端用户）</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>5. 支付</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>支付</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>支付失败</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
         <is>
           <t>（1）珊瑚红✕ +「支付失败」+「未扣款,可重新支付或稍后再试」
 （2）按钮：「重新支付」（重新发起微信支付）、「返回」（回会话）</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>移动端 H5（C 端用户）</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>6. 协议与辅助页</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>协议与辅助页</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
         <is>
           <t>用户协议 / 隐私政策</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>（1）两个独立入口并列，纯文本/Markdown 渲染
 （2）底部展示更新日期</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>移动端 H5（C 端用户）</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>6. 协议与辅助页</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>二维码失效落地页</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>（1）二维码作废/KP 下架时提示「二维码已失效」+「N 秒后自动跳转首页…」
-（2）3 秒倒计时自动跳首页，另提供「立即前往首页」按钮</t>
-        </is>
-      </c>
-    </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
@@ -1718,76 +1728,105 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>6. 协议与辅助页</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
+          <t>协议与辅助页</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>二维码失效落地页</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>0718周六更新
+（1）二维码本身作废时提示「二维码已失效」+「N 秒后自动跳转首页…」；KP 已下架 / 已删除的扫码改走「KP 前台入口 /kp/:kpId」判活流程（提示已下架/已失效并按跳转规则①处理），与二维码作废场景区分
+（2）3 秒倒计时自动跳首页，另提供「立即前往首页」按钮</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>移动端 H5（C 端用户）</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>协议与辅助页</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>联系客服弹窗</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>（1）展示机构后台配置的一个二维码（企微/个微）
 （2）下方电话、邮箱均非必填，有则展示无则隐藏并自动补位（不留空块）</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>移动端 H5（C 端用户）</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>6. 协议与辅助页</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>协议与辅助页</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>原型清单 / 演示环境开关</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
         <is>
           <t>（1）〔评审〕原型清单：三端站点地图，列全站页面便于评审跳转，脱手机框全宽渲染
 （2）〔演示〕落地页演示环境开关：微信内/浏览器、Token 正常/超限，仅原型演示用、标注非上线功能</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>1. 登录与主控台</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>登录与主控台</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>登录页</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>（1）左侧动态毛玻璃品牌区（浮动 blob + 旋转知识核）+ 标语「答案有出处 · 知识更可信」
 （2）右侧登录卡：账号（账号/手机号）、密码、图形验证码（4 位，字母表排除易混 0/O/1/I/L）
@@ -1796,31 +1835,30 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>1. 登录与主控台</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>登录与主控台</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>主控台</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>0716周四新增
-（1）页头标题 + 右上「导出」；文件名规范「AI问书_{机构名}_主控台数据导出.xlsx」；拆分“实时总览/经营分析”两个 Sheet——实时 Sheet 标注实时统计时间、经营分析 Sheet 标注所选区间具体起止；头部统一注明导出时间与导出时刻的全部筛选条件
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>（1）页头标题 + 右上「导出」；文件名规范「AI问书_{机构名}_主控台数据导出.xlsx」；拆分“实时总览/经营分析”两个 Sheet——实时 Sheet 标注实时统计时间、经营分析 Sheet 标注所选区间具体起止；头部统一注明导出时间与导出时刻的全部筛选条件
 （2）0716 #3【全平台导出通用规则】：单次导出统一上限 10000 条（任一业务 Sheet 数据行超限即拦截，不下载），弹窗提示「本次筛选结果约 N 条，超过单次导出上限 10000 条，请缩小筛选范围后重试，或联系平台管理员导出完整数据」。规则集中在导出底座内拦截，两后台全部导出入口一致生效；导出进行中的提示统一为「正在导出」
 （3）导出指标全量不遗漏：实时总览含 累计GMV/累计退款/退款率/净GMV/当前会员数/累计注册用户；经营分析含各 KPI 及「较上一周期」环比列与趋势数据
 （4）当前生效订阅卡（机构侧只读）：KP 数、存储明确标“占用量/当前占用”，Token 明确标“消耗量/本周期消耗”；上限＝当前订阅基础额度+该订阅有效加油包，InfoDot 写明跨订阅、重置和降配阻断规则
@@ -1830,38 +1868,6 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>机构后台 PC（机构运营）</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>2. 知识产品 KP</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>KP 列表</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>0716周四更新
-（1）卡片网格：封面色块 + KP 名 + 来源标签（自建/共享）+ 发布状态标签（已发/未发/已下架）+ Agent 名 + 文件数/提问数；已删除的 KP 不在后台列表展示（机构后台与平台后台一致，仅数据库留存）
-（2）按 KP 名称模糊搜索；筛选 状态（全部/未发/已发/已下架）、来源（全部/自建/共享）——已删除 KP 不在列表与筛选中出现
-（3）顶部右侧配额 chip：KP X/Y · 存储 X/Y GB（≥90% 红/≥70% 黄）+ 提示「达上限将无法新建/上传，请联系平台扩容」
-（4）新建阻断：KP 数达上限时点新建 → toast「已达 KP 数量上限（Y 个），请联系平台扩容」
-（5）点卡片进 KP 详情；空态「没有匹配的 KP」</t>
-        </is>
-      </c>
-    </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
@@ -1870,48 +1876,83 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>2. 知识产品 KP</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
+          <t>知识产品 KP</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>KP 列表</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>0718周六更新
+（1）卡片网格：封面色块 + KP 名 + 来源标签（自建/共享）+ 状态标签（草稿/已发布/已下架，0717 #2.4 两后台命名统一）+ 实时分享·分享方标（0717 二批 #4：接收方不再单独加标——「共享」来源标签已表达，避免标签堆叠）+ Agent 名 + 文件数/提问数；已删除（逻辑删除）的 KP 不在三端界面展示，数据库保留数据
+（2）按 KP 名称模糊搜索；筛选 状态（全部/草稿/已发布/已下架）、来源（全部/自建/共享）——已删除 KP 不在列表与筛选中出现
+（3）0717 #2.3：列表与详情同一数据源（点开哪张卡，详情即那条数据：名称/状态/导入方式/业务关系一致）；演示数据覆盖每个状态各至少一条（草稿/已发布/已下架），并含实时分享双视角各一条——分享方（本机构分享出去）与接收方（实时同步导入、只读）
+（4）顶部右侧配额 chip：KP X/Y · 存储 X/Y GB（≥90% 红/≥70% 黄）+ 提示「达上限将无法新建/上传，请联系平台扩容」
+（5）新建阻断：KP 数达上限时点新建 → toast「已达 KP 数量上限（Y 个），请联系平台扩容」
+（6）点卡片进 KP 详情；空态「没有匹配的 KP」
+（7）「0718 修订」来源标签体系三分并在两后台统一：自建＝机构自己创建；分享导入·实时＝经实时同步导入（只读）；分享导入·快照＝经独立快照导入（可编辑）。来源标签统一使用灰色（原「自建」的靛蓝色取消），仅 KP 状态标签（草稿/已发布/已下架）随状态变色；「实时分享 · 分享方」角色标同步改灰。来源筛选选项改为 全部 / 自建 / 分享导入·实时 / 分享导入·快照
+（8）「0718 修订」状态标签颜色在列表与详情间统一：已发布＝玉绿、已下架＝琥珀、草稿＝灰描边（列表原「已发布」电光靛取消，与详情头 tag-s 同色）；平台 Agent 列表的「机构」类型标改用靛蓝类保持原观感，不受 KP 状态色统一影响</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>机构后台 PC（机构运营）</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>知识产品 KP</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>KP 列表</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>新建 KP</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>（1）弹窗：KP 名称（必填）+ 简介
 （2）确定 → toast「已创建 KP」</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>2. 知识产品 KP</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>知识产品 KP</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>KP 列表</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>导入分享 KP</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>（1）弹窗：分享链接（必填）+ 密码（必填）
 （2）弹窗底部提示改为灰色内容框内三条无序结构化条目：① 导入限制：仅支持导入外部机构分享，本机构分享不可导入 ② 实时同步：不占用接收方 KP 与存储，内容只读，Token 消耗归属接收方 ③ 独立快照：占用接收方 KP 与存储，支持编辑，Token 消耗归属接收方
@@ -1920,43 +1961,6 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>机构后台 PC（机构运营）</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>2. 知识产品 KP</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>KP 详情 · 基础信息</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>0716周四更新
-（1）详情头：返回 + KP 名 + 来源标签 + 发布状态 + 右侧操作「下架」「删除」；操作真实生效——下架后状态变「已下架」、删除后回列表（原型内真实改状态，非仅提示）。0716 #1.1：状态机由四态精简为三态「草稿 / 已发布 / 已下架」，「归档」并入「删除」，不再单独设归档态
-（2）下架＝停止公开发现、新购买、新扫码及通用访问链接；已购买、纸书解锁等既有权益继续访问（C 端照常可看可问）。合规强制下架例外：保留权益与订单记录，但内容不可访问，并展示客服/退款指引
-（3）删除＝唯一终态操作（归档已并入）：无论有无业务关系均为物理删除（清除全部文件/向量/二维码/分享，删除后不可恢复）；删除后机构后台与平台后台列表均不再展示该 KP，仅数据库留存记录与 C 端历史凭证
-（4）删除确认弹窗按有无业务关系区分内容：无关系→简明确认（文案含「删除后不可恢复」）；有关系→无序列表列出影响要点 + 淡红警示引用块统计「N 位已购永享用户」与「M 位纸书扫码解锁用户」，明确告知对 C 端「我的永享 / 我的纸书 / 历史 AI 会话 / 订单记录」的影响
-（5）KP 状态对 C 端的呈现统一为两级：下架→前台各入口统一显「已下架」；删除→前台各入口统一显「已失效」（我的永享 / 我的纸书 / 历史 AI 会话 / 内容溯源全端一致），点击提示联系客服；订单记录保留可查。仅「下架」时已购权益不受影响（买断/已解锁照常）
-（6）左侧 9:16 封面区（上传/重新上传/删除，上传走「裁剪封面 9:16」弹窗、裁剪框可拖拽）
-（7）右侧表单：KP 名称（必填）、简介、纸书购买链接（填写后用户查看溯源时可跳转）、关联 Agent（必填，下拉）
-（8）前台访问地址（5.3）：只读链接 + 复制按钮，随当前环境（本地/线上）自动生成；说明移到字段名旁问号 icon 的 hover 面板、用无序列表两行不换行展示（① C 端用户访问本机构该 KP 的前台地址 ② 随当前环境自动生成），字段下方不再常驻长文案
-（9）前台访问地址由机构域名前缀与当前环境根域名动态生成：输入 test 时为 test-aba.{当前环境根域名}，KP 链接追加 /kp/{kpId}，机构后台追加 /admin/
-（10）底部「保存」→ toast「已保存」</t>
-        </is>
-      </c>
-    </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
@@ -1965,22 +1969,62 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>2. 知识产品 KP</t>
+          <t>知识产品 KP</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
+          <t>KP 详情 · 基础信息</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>0718周六更新
+（1）详情头：返回 + KP 名（与列表同源）+ 来源标签 + 状态标签（草稿/已发布/已下架，两后台命名统一）+ 右侧状态操作按钮——0717 #2.1/#2.2：草稿→「发布」、已发布→「下架」、已下架→「重新发布」；删除对草稿/已发布/已下架均可用；操作真实生效（原型内真实改状态，非仅提示）。0717 二批 #2/#4：来源标签统一「自建 / 共享」（详情不再用「共享导入」，与列表一致）；实时同步导入的详情头不再显示「实时同步 · 只读」附加标（顶部只读 banner 已说明）
+（2）「发布」同样走二次确认——弹窗说明「发布后前台立即可见：支持检索、购买、扫码与链接访问；发布需至少一份已向量化完成的知识内容」，确认后状态真实置为已发布并 toast「已发布」
+（3）0717 #1.4：下架＝运营临时禁止访问（处理完问题可随时重新发布）——停止检索、新购买、新扫码与链接访问；C 端「我的纸书」「我的永享」等入口统一显「已下架」、点击提示联系客服、暂不可进入会话/预览；已购权益不清除，重新发布后自动恢复访问
+（4）0717 #1.8：下架确认弹窗结构化——无序列表明示前台影响（我的纸书/我的永享显「已下架」、暂不可进入；已购权益保留、重新发布自动恢复）+ 琥珀提示块说明下架适用于「临时禁止访问、处理完再上架」的运营场景
+（5）0717 #1.5：删除＝逻辑删除（软删除，全平台统一口径，后端建议实现为逻辑删除）——删除后三端界面均不再展示该 KP（列表/详情/筛选均过滤），数据库保留全部数据（订单/权益/文件/向量/二维码/分享记录）与 C 端历史凭证；界面文案只说「删除」，不出现「物理删除/彻底删除/永久删除」
+（6）删除确认弹窗按有无业务关系区分内容：无关系→简明确认（明示逻辑删除口径：三端不再展示、数据库保留数据、前台提示「已失效」）；有关系→无序列表列出影响要点 + 淡红警示引用块统计「N 位已购永享用户」与「M 位纸书扫码解锁用户」，明确告知对 C 端「我的永享 / 我的纸书 / 新会话与扫码入口 / 历史 AI 会话 / 订单记录」的影响
+（7）0717【KP 状态 × 前台影响矩阵】（终版）——▸ 新 AI 会话（KP 前台地址进入）：已发布＝正常进入；已下架＝提示「已下架，若有问题请联系客服」3 秒 → 跳转规则①；已删除＝提示「已失效，若有问题请联系客服」3 秒 → 跳转规则①。▸ 知识 KP 二维码扫码（含首扫权益绑定核销）：规则与「新 AI 会话（前台地址进入）」完全相同——已下架 / 已删除提示相应文案 3 秒后跳转至当前机构最新已发布的 KP（跳转规则①）（注意用词：兑换码的权益是会员，与 KP 绑定的是「知识 KP 二维码」）。▸ 我的纸书：已下架＝标「已下架」（已解锁则并列保留「已解锁」标）、点击拦截提示联系客服；已删除＝标「已失效」拦截。▸ 我的永享：同我的纸书——已下架拦截（权益保留、重新上架自动恢复）、已删除标「已失效」拦截。▸ 草稿：新会话 / 二维码扫码均按「已失效」处理。▸ 历史会话 / 内容溯源：已下架 / 已删除分别灰标「已下架 / 已失效」。跳转规则①：目标＝本 KP 同机构下最新创建且已发布的 KP 会话；未登录先进登录界面（仅当存在目标）；机构无满足条件 KP 则不跳转、也不进登录界面。订单记录一律保留可查
+（8）左侧 9:16 封面区（上传/重新上传/删除，上传走「裁剪封面 9:16」弹窗、裁剪框可拖拽）
+（9）右侧表单：KP 名称（必填）、简介、纸书购买链接（填写后用户查看溯源时可跳转）、关联 Agent（必填，下拉）
+（10）前台访问地址（5.3）：只读链接 + 复制按钮，随当前环境（本地/线上）自动生成；说明移到字段名旁问号 icon 的 hover 面板、用无序列表两行不换行展示（① C 端用户访问本机构该 KP 的前台地址 ② 随当前环境自动生成），字段下方不再常驻长文案
+（11）前台访问地址由机构域名前缀与当前环境根域名动态生成：输入 test 时为 test-aba.{当前环境根域名}，KP 链接追加 /kp/{kpId}，机构后台追加 /admin/
+（12）底部「保存」→ toast「已保存」
+（13）「0718 修订」详情头来源标签与列表统一为三态——自建 / 分享导入·实时 / 分享导入·快照，统一灰色（原自建靛蓝取消）；旧「共享」二分法废弃</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>机构后台 PC（机构运营）</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>知识产品 KP</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
           <t>KP 详情 · 知识库</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>0716周四新增
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>0718周六更新
 （1）按文件名搜索 + 类型筛选（全部/文档/图片/音频/视频）
 （2）提示「上传即向量化，发布知识 KP 需至少一份已向量化完成的知识内容」
 （3）表格列：文件名、类型、预览（图音视缩略图、点击放大）、权益（免费/会员/永享¥X，联动定价与权益）、处理状态、检索状态、操作；操作列随按钮数自适应宽度
@@ -1989,32 +2033,32 @@
 （6）权益列（联动定价与权益）：文档(word/pdf)恒「免费」；图/音/视——设永享价显「永享 ¥X」、否则随 KP 基础权益显「免费/会员」；列表上方加 权益筛选(全部/免费/会员) + 永享筛选(全部/永享/非永享)
 （7）图/音/视文件操作列额外提供：预览（缩略图点击放大只读预览）、设置/编辑永享价；文档无此两项
 （8）权益边界：设了永享价的资源即为永享内容，无论本 KP 基础权益是免费还是会员，该资源都需单独永享付费（会员也不含）；免费用户无需先开会员即可直接购买——永享与会员是两套独立权益
-（9）0716 #8【永享购后机构端处理规则】：① 删除永享资源→C 端「我的永享」标「已失效」、内容不可访问，点击提示联系客服 ② 调价→永享为一次性买断，不影响已购用户，仅新购按新价，不补差价不重复扣费 ③ 转为非永享 / 停售→已购用户权益保留（买断契约），仅停止新的永享售卖入口。定价与权益 Tab 的权益模型说明块内常驻此三条</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+（9）0717【永享购后机构端处理规则】（终版）：① 下架 KP → 已购永享标「已下架」、暂不可访问，权益不清除，重新上架自动恢复 ② 删除 KP / 删除永享资源（逻辑删除）→ C 端标「已失效」、内容不可访问，数据库保留购买与权益数据 ③ 调价 → 永享为一次性买断，不影响已购用户、仅新购按新价，不补差不重复扣费 ④ 转为非永享 / 停售 → 已购权益保留，仅停止新的永享售卖入口。定价与权益 Tab 的权益模型说明块内常驻</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>2. 知识产品 KP</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>知识产品 KP</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>KP 详情 · 知识库</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
         <is>
           <t>上传知识文件</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>（1）弹窗左右布局：左=拖拽/点击上传区（文档/图片/音频/视频多文件混传、批量、不支持文件夹）+ 单文件上限说明（文档≤100MB、图片≤20MB、音频≤300MB·120分钟、视频≤1GB·60分钟）
 （2）右=批量上传进度列表（每文件进度条 + 百分比 + 移除）
@@ -2022,28 +2066,28 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>2. 知识产品 KP</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>知识产品 KP</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>KP 详情 · 知识库</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
         <is>
           <t>文件上下架/重试/删除</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>（1）已向量化：下载 / 上架↔下架（toast「已上架,该内容可被检索」/「已下架,该内容停止被检索」）/ 删除
 （2）失败：下载 / 重试（确认「重新执行向量化」→ toast「已重新提交向量化」）/ 删除
@@ -2051,28 +2095,28 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>2. 知识产品 KP</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>知识产品 KP</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>KP 详情 · 知识库</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>设置 / 编辑永享价（图音视）</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="E54" s="4" t="inlineStr">
         <is>
           <t>（1）在知识库列表对图/音/视文件点「设置/编辑永享价」→ 弹窗：内容名 + 永享价（必填，元）
 （2）弹窗内含说明块（淡紫 / 淡珊瑚底）：「永享内容需单独付费，无论该 KP 是免费还是会员；免费用户无需先开通会员即可直接购买——免费/会员 与 永享 是两套独立的权益模型」
@@ -2081,58 +2125,60 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>2. 知识产品 KP</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>知识产品 KP</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>KP 详情 · 定价与权益</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>（1）此处设「基础权益」，决定本 KP 非永享内容的门槛：免费 / 会员 二选一互斥单选
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>0718周六新增
+（1）此处设「基础权益」，决定本 KP 非永享内容的门槛：免费 / 会员 二选一互斥单选
 （2）免费：所有用户均可查看该 KP 全部非永享内容（文字/图片/音频/视频）
 （3）会员：仅会员可查看图/音/视媒体资源，文字内容不受会员身份限制
-（4）权益模型边界：凡在知识库设了永享价的资源都属「永享池」，无论基础权益是免费还是会员都需单独永享付费（会员也不含）；永享与会员是两套相互独立的权益，互不覆盖、各自计费</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+（4）0717 #5：免费 / 会员切换点击即生效 → 增加二次确认弹窗（说明切换后果与立即生效），确认后才生效并 toast，避免误操作；实时同步（接收方）视角下单选整体置灰不可切换
+（5）权益模型边界：凡在知识库设了永享价的资源都属「永享池」，无论基础权益是免费还是会员都需单独永享付费（会员也不含）；永享与会员是两套相互独立的权益，互不覆盖、各自计费</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>2. 知识产品 KP</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>知识产品 KP</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
         <is>
           <t>KP 详情 · 二维码</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>（1）按二维码包名称搜索 + 权益模式筛选（全部/首扫绑定后扫引导/无权益）
 （2）表格列：二维码包名称、权益模式、生成的二维码数量、扫描总量、首扫数量、后扫数量、操作（查看/下载 zip）
@@ -2141,56 +2187,56 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>2. 知识产品 KP</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>知识产品 KP</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>KP 详情 · 二维码</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
         <is>
           <t>新建二维码包</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="E57" s="4" t="inlineStr">
         <is>
           <t>（1）弹窗：包名称（必填）+ 权益模式（下拉）+ 生成数量（必填）
 （2）确定 → toast「已生成二维码包」</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>2. 知识产品 KP</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>知识产品 KP</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>KP 详情 · 二维码</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>二维码明细抽屉</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="E58" s="4" t="inlineStr">
         <is>
           <t>（1）「查看」从右侧拉出抽屉：抽屉头显包名 +「包号 X · 权益模式 Y · 共 N 个二维码」
 （2）按 首扫账户名称/首扫手机号 模糊搜索
@@ -2198,28 +2244,28 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>2. 知识产品 KP</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>知识产品 KP</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>KP 详情 · 分享</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
         <is>
           <t>（1）筛选 模式（全部/实时同步/独立快照）、状态（全部/生效中/已作废）
 （2）表格列：链接/密码（点击复制 toast「已复制分享链接」）、模式、有效期（如还剩 N 天）、消费/上限、状态、操作
@@ -2227,63 +2273,34 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>2. 知识产品 KP</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>知识产品 KP</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>KP 详情 · 分享</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
         <is>
           <t>新建分享</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>（1）弹窗：同步模式（实时同步/独立快照）+ 有效期（1天/7天/30天/永久）+ 导入次数上限
 （2）确定 → toast「已生成分享链接」</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>机构后台 PC（机构运营）</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>2. 知识产品 KP</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>共享 KP 权限矩阵</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>0716周四更新
-（1）0716 #5：实时同步——基础信息、知识库、定价与权益三 Tab 数据正常可读可查（列表/表单不整块置灰），仅操作类控件（上传/下载/上架下架/删除/编辑永享价/保存等按钮）置灰，点击提示「无权限操作」；二维码、分享两 Tab 隐藏。顶部只读说明 banner 单行呈现，来源机构为动态变量：「本 KP 由「{分享机构名}」以「实时同步」分享导入：内容随源机构自动更新、仅可查看不可编辑；不占本机构 KP 数与存储、问答消耗本机构 Token；二维码与分享不可用。」
-（2）独立快照：五个 Tab 均可编辑；基础信息、知识库、定价数据在导入时复制，二维码与分享从消费机构自己的空数据开始</t>
-        </is>
-      </c>
-    </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
@@ -2292,20 +2309,50 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>3. Agent 人设</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
+          <t>知识产品 KP</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>共享 KP 权限矩阵</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>0718周六更新
+（1）0717 #4：实时同步（接收方 / 消费者视角）只读升级——基础信息表单输入框全部禁用置灰（无光标、hover 显示 not-allowed 禁止态，样式同既有只读输入框先例）、关联 Agent 下拉禁用、定价与权益单选整体置灰不可选；仅「复制链接」可操作；其余操作按钮置灰、点击提示「无权限操作」；二维码、分享两 Tab 隐藏。顶部只读说明 banner 单行呈现，来源机构为动态变量：「本 KP 由「{分享机构名}」以「实时同步」分享导入：内容随源机构自动更新、仅可查看不可编辑；不占本机构 KP 数与存储、问答消耗本机构 Token；二维码与分享不可用。」0717 二批 #5：禁用置灰统一标准＝「前台访问地址」只读框样式（纸白底 + 实线浅边框 + 深灰文字），两后台一致，不再用虚线浅灰底
+（2）独立快照：五个 Tab 均可编辑；基础信息、知识库、定价数据在导入时复制，二维码与分享从消费机构自己的空数据开始
+（3）「0718 修订」实现对齐：实时同步只读表单的禁用输入框底色/边框/文字色已统一为「前台访问地址」只读框同款（纸白 --paper 底 + --line-2 实线浅边框 + --ink-2 深灰文字），修复此前禁用框使用另一套灰底（--surface-warm）造成的两灰并存</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>机构后台 PC（机构运营）</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>Agent 人设</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>Agent 列表</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
         <is>
           <t>（1）卡片网格：机器人封面 + 名称 + 类型标签（机构/普通）+「关联 KP · N」+ 音色（已设/默认）
 （2）按 Agent 名称模糊搜索
@@ -2314,31 +2361,30 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>3. Agent 人设</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>Agent 人设</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>Agent 详情 / 编辑</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>0716周四更新
-（1）区分新建/编辑：头部名称 + 类型标签 + 右侧「创建」/「保存」
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>（1）区分新建/编辑：头部名称 + 类型标签 + 右侧「创建」/「保存」
 （2）左侧表单：头像（必填，上传 png/gif/jpg 走圆形裁剪）、名称（必填）、类型（不可更改，注「类型不可更改」）、TTS 参考音（必填，已上传显波形条 + 播放/暂停 + 时长 + 重新上传）、回答 Prompt
 （3）0716 #11：名称校验——机构内不允许重复（重名保存拦截 toast「该 Agent 名称在机构内已存在，请更换」），字段旁提示「名称在机构内不可重复」
 （4）0716 #11：TTS 参考音校验——仅支持 MP3 / WAV 格式、时长 3~10 秒；上传时真实读取音频元数据校验，超范围拦截并提示；字段旁提示「格式 MP3 / WAV · 时长 3~10 秒」
@@ -2348,59 +2394,58 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>4. C 端用户</t>
-        </is>
-      </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>C 端用户</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>用户列表</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>0716周四更新
-（1）表格列：用户昵称、手机号、微信号、地区、性别、会员状态、已购永享、累计 GMV、最新登录时间、注册时间、操作（详情）；「注册时间」列支持升 / 降序排序
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>（1）表格列：用户昵称、手机号、微信号、地区、性别、会员状态、已购永享、累计 GMV、最新登录时间、注册时间、操作（详情）；「注册时间」列支持升 / 降序排序
 （2）按 手机号/微信号/昵称 三字段模糊搜索；筛选 会员状态（全部/会员/非会员）
 （3）筛选行右侧「导出」：生成「AI问书_{机构名}_C端用户数据导出.xlsx」，严格沿用手机号/微信号/昵称搜索和会员状态筛选；文件头部注明导出时间与筛选条件
 （4）昵称规则：微信登录取微信昵称、手机号登录取「用户+后四位」；地区/性别为微信授权带回，非微信用户显「—」</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>4. C 端用户</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>C 端用户</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>用户详情</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
         <is>
           <t>（1）用户卡：头像 + 昵称 + 会员标签 + 手机号/微信号 + 地区/性别 + 活跃度（近 30 天提问次数 · 最近活跃时间）
 （2）「已购永享」卡：媒体项列表，点击进媒体预览弹窗
@@ -2408,28 +2453,28 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>5. 订单管理</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>订单管理</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>订单列表</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
         <is>
           <t>（1）仅显本机构订单，按付款时间降序
 （2）表格列：订单号、类型、关联知识产品、金额、支付方式、订单状态、退款状态、用户、下单时间、付款时间、兑换时间、操作（操作列固定右侧）
@@ -2439,28 +2484,28 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>5. 订单管理</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>订单管理</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>订单列表</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>发起退款</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
+      <c r="E67" s="4" t="inlineStr">
         <is>
           <t>（1）退款入口仅在可退款时显示（金额&gt;0 且退款状态不在「退款中/全额退款」）
 （2）退款金额弹窗：订单号 + 订单实付（已退&gt;0 时显「已退 ¥X · 可退 ¥Y」）+ 退款金额（默认填可退余额）+ 说明「支持部分退款 / 确认后原路退回，不可撤销」
@@ -2471,28 +2516,28 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>5. 订单管理</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>订单管理</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>订单详情</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
         <is>
           <t>（1）头部标题（兑换码订单显「详情」，其余「订单详情」）+ 类型标签；订单不存在显空态
 （2）兑换码订单：基础卡（类型 兑换码核销/兑换码/兑换时间）+ 兑换权益卡（权益标题 + 会员时间区间）
@@ -2502,28 +2547,28 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>6. 兑换码</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>兑换码</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>兑换码批次列表</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
         <is>
           <t>（1）副文案「每次生成为一个批次,点击批次查看该批次全部兑换码」
 （2）按批次名称搜索
@@ -2532,28 +2577,28 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>6. 兑换码</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>兑换码</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>兑换码批次列表</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>批量生成</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
+      <c r="E70" s="4" t="inlineStr">
         <is>
           <t>（1）弹窗：批次名称（必填）+ 权益类型（固定会员）+ 会员时长（默认3个月，1–12）+ 兑换有效开始/结束时间（必填且开始≤结束）+ 生成数量（默认500）
 （2）弹窗加宽，兑换有效开始/结束时间在一行内完整展示；点击时间字段后日历面板完整弹出可直接选择，不被弹窗裁切、无需滚动
@@ -2561,28 +2606,28 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>6. 兑换码</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>兑换码</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
         <is>
           <t>兑换码批次详情抽屉</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
         <is>
           <t>（1）「详情」从右侧拉出抽屉：抽屉头显批次名 +「已兑换 X/Y · 权益 会员 · Z · 批次创建 时间」
 （2）按兑换用户/手机号搜索 + 状态筛选；「导出」生成「AI问书_{机构名}_兑换码_{批次名}数据导出.xlsx」，含批次信息与兑换码明细（有效期、兑换人、兑换时间、权益到期时间）；头部注明导出时间与筛选条件
@@ -2590,44 +2635,6 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>机构后台 PC（机构运营）</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>7. 数据看板</t>
-        </is>
-      </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>用户分析 Tab</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>0716周四更新
-（1）0716 #12：页面自上而下四段——① 实时活跃概览（DAU/WAU/MAU 一行三卡）② 用户留存（D+1/D+7/D+30 一行三卡）③ 统一区间时间选择器条（今日/7日/30日/自定义，位于四个主题 Tab 之上、驱动全部 Tab 的区间联动指标）④ 四个主题 Tab（用户分析/提问分析/营收分析/热门 KP）。实时与留存为页级常驻（不再归属用户分析 Tab），页头只保留「导出」。导出生成「AI问书_{机构名}_数据看板数据导出.xlsx」，七个 Sheet 全量覆盖页面内容——区间指标（全部 KPI）、留存率、提问趋势、分布明细（来源/地区/性别/Agent/领域）、关键词云、转化漏斗、热门KP榜单；头部注明导出时间、所选区间起止与实时/区间口径
-（2）页面按三种时间口径明确拆成三段（自上而下）：① 实时活跃概览 ② 用户留存 ③ 区间分析——三段分别对应「当前快照 / 注册时间 / 日历区间」，杜绝同屏三层时间概念混淆；区间选择器就近置于「区间分析」段头，实时概览 / 用户留存 在其之上、各自独立不受影响
-（3）① 实时活跃概览（标「实时」）：DAU / WAU / MAU，锚定当前时刻的滚动固定窗口去重快照（自然日 / 近 7 / 近 30 天），不随时间筛选变化、不展示环比
-（4）② 用户留存（标「按注册时间」，页级常驻段，位于实时概览之后）：口径即注册日，「注册批次」更名「注册时间」便于理解；口径问号 InfoDot 紧跟「用户留存」标题之后；常驻说明「观察注册用户在第 1 / 7 / 30 天是否仍然活跃，不受区间筛选影响」；右侧「注册时间：最新可统计 ▼」下拉（选项：最新可统计 / 近 7 个注册日 / 近 30 个注册日 / 自定义日期）；选「自定义日期」弹单日日历面板（视觉同区间选择器的自定义日历，但只选具体某一天，因留存按单个注册日观察）
-（5）用户留存用三张等宽指标卡（D+1 次日 / D+7 7日 / D+30 30日）替代横向进度条；每卡独立展示：留存率大数字、可统计样本数（如「样本 1,126 人」）、对应注册截止日（如「统计至 7月14日注册用户」）、数据状态——不同观察天数对应的成熟样本范围可不同，不再共用一个笼统样本数
-（6）未成熟节点不再显示易被误读为 0% 的空进度条或「—」，改为中性灰状态文案：「尚未到统计时间」+「该批用户最早于 {日期} 产生 {N}日留存」；状态用文字表达、不只依赖颜色
-（7）用户留存段底部常驻一行：「数据更新至 {时间} · 活跃口径：注册后第 N 天发生登录或提问行为」；「实时」只描述数据更新时间、不作为留存指标的分类标签
-（8）③ 区间分析（随顶部今日/7日/30日/自定义联动）：时间筛选置于本段标题右侧，仅控制新增用户、来源 / 地区 / 性别等区间指标；因留存已移出本段，删除原「留存率除外」例外说明
-（9）KPI 卡环比行呈现：方向箭头 + 百分比 +「较上一周期」为第一行，「对比 {区间}」为第二行（避免今日档长文案被卡片截断）；三端主控台 / 数据看板同源一致
-（10）来源分布环形图：扫码进入 vs 直接访问
-（11）地区分布条形图、性别分布条形图（女/男/未知，微信授权带回）</t>
-        </is>
-      </c>
-    </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
@@ -2636,20 +2643,65 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>7. 数据看板</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
+          <t>数据看板</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>用户分析 Tab</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>0718周六更新
+（1）0717 二批 #8：页面自上而下——① 用户留存（页级常驻，一行三张等宽指标卡，卡片式回归、与平台整体风格一致）② 区间分析条（轻量样式：左标题 + 右时间筛选，去掉白底 / 灰框容器）③ 四个主题 Tab（用户分析/提问分析/营收分析/热门 KP）。活跃概览移入「用户分析」Tab 并改为随区间联动的周期统计（口径修订，原「固定窗口快照」弃用）。页头只保留「导出」，导出生成「AI问书_{机构名}_数据看板数据导出.xlsx」，七个 Sheet 全量覆盖页面内容（活跃概览按当前所选区间导出）；头部注明导出时间、所选区间起止与口径
+（2）时间口径收敛为两类：用户留存＝按注册时间（独立筛选、不受区间影响，活跃口径＝注册后第 N 天发生登录或提问行为，完整公式在卡面口径问号内）；其余指标（含活跃概览）＝随「区间分析」时间筛选联动并环比。0717 二批 #8.3：删除留存段底部「数据更新至 …」脚注，界面不再显示
+（3）0717 二批 #8.2/#8.4：活跃概览（日活 / 周活 / 月活）一行三卡置于用户分析 Tab 顶部——数值随所选区间联动（区间内日均去重口径），并与上一等长周期环比（KPI 卡同款 Delta + 对比窗口）
+（4）② 用户留存（标「按注册时间」，页级常驻段，位于实时概览右侧）：口径即注册日，「注册批次」更名「注册时间」便于理解；口径问号 InfoDot 紧跟「用户留存」标题之后；常驻说明「观察注册用户在第 1 / 7 / 30 天是否仍然活跃，不受区间筛选影响」；右侧「注册时间：最新可统计 ▼」下拉（选项：最新可统计 / 近 7 个注册日 / 近 30 个注册日 / 自定义日期）；选「自定义日期」弹单日日历面板（视觉同区间选择器的自定义日历，但只选具体某一天，因留存按单个注册日观察）。0717 #8：选定具体日期后回显在下拉触发器上（如「注册时间：2026-06-30」），不再停留显示「自定义日期」字样
+（5）0717 二批 #8.1：用户留存回归一行三张等宽指标卡（D+1 次日 / D+7 7日 / D+30 30日，卡片式、平台风格统一）——标题行左＝节点名 + 口径问号，右＝状态标（已可统计 / 待成熟）；卡身留存率大数字；底部单行灰字「样本 N 人 · 统计至 {日期}注册用户」——不同观察天数对应的成熟样本范围可不同，不再共用一个笼统样本数
+（6）未成熟节点不再显示易被误读为 0% 的空进度条或「—」，改为中性灰状态文案：「尚未到统计时间」+「该批用户最早于 {日期} 产生 {N}日留存」；状态用文字表达、不只依赖颜色
+（7）③ 区间分析（随顶部今日/7日/30日/自定义联动）：时间筛选置于本段标题右侧，仅控制新增用户、来源 / 地区 / 性别等区间指标；因留存已移出本段，删除原「留存率除外」例外说明
+（8）0717 二批 #6：撤销区间分析条与主题 Tab 的吸顶固定交互（回归普通文档流）
+（9）KPI 卡环比行呈现：方向箭头 + 百分比 +「较上一周期」为第一行，「对比 {区间}」为第二行（避免今日档长文案被卡片截断）；三端主控台 / 数据看板同源一致
+（10）0717 二批 #8.4：用户分析 Tab 三行布局——第一行 日活｜周活｜月活（一行三卡，区间联动 + 环比）；第二行 新增用户与来源分布同行：新增用户卡左＝大数字 + 环比 +「对比 {区间}」，右＝随区间联动的迷你趋势折线（周期 UI 参考提问分析「总提问」）；来源分布环形图图例补充人数（如「扫码进入 · 68%（216 人）」）并展示占比环比「较上一周期」（0717 二批 #7）；第三行 地区分布与性别分布同行（女/男/未知，微信授权带回）
+（11）「0718 修订」留存「注册时间」筛选由白色下拉改为与「区间分析」同款灰底分段控件（最新可统计 / 近 7 个注册日 / 近 30 个注册日 / 自定义），自定义经单日日历选定具体注册日后以 chip 回显日期、可点 ✕ 回到「最新可统计」；两区筛选视觉统一，不再出现孤立白框
+（12）「0718 修订」留存数据改为按真实日期联动推算：选某个注册日 D 时，D+N 节点在「D+N ≤ 今天」时可统计（截止文案＝「统计 {D}注册用户」），否则为「待成熟」（预计可统计日期＝D+N）；修复此前自定义日期档写死 6月30日、与所选注册日脱节的假数据问题
+（13）「0718 修订」四个主题 Tab 切换时内容区保留历史最大高度（min-height 自适应），切回较矮 Tab 页面不再整体回缩跳动；区间切换同理
+（14）「0718 修订」来源分布环比文案与其他指标统一为「↑x.x% 较上一周期」——去掉「pp」字样与「扫码占比」前缀（口径不变，仍为占比的百分点差，见附表一）
+（15）「0718 修订」自定义注册日的日期回显 chip 移到分段控件左侧（与下方「区间分析」RangePicker 的自定义回显位置一致），不再挂在控件右侧
+（16）「0718 修订」留存卡截止文案改白话（原「统计至 {日期}注册用户」不易懂）——可统计节点显示「统计 {注册日}注册的 {样本} 人 · {次日/第 7 天/第 30 天}是否回来」，待成熟节点显示「{注册日}注册的用户 · 等满 {N} 天（{日期}）后可统计」；不懂数据的人也能一眼看懂「统计的是哪天注册的人、在看他们哪天回不回来」
+（17）「0718 修订」四个主题 Tab 支持地址栏 ?tab=N（0=用户分析 / 1=提问分析 / 2=营收分析 / 3=热门 KP）直达，便于评审与验收直接跳到指定主题；越界值回落第一个 Tab
+（18）「0718 修订」自定义单注册日批次的三个留存节点共用同一样本人数（同一批注册用户、分母相同）；样本随节点递减仅保留在「最新可统计 / 近 N 个注册日」等多天批次（不同节点的成熟截止日不同、对应不同注册人群）——修复单注册日批次节点样本不一致造成的误解</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>机构后台 PC（机构运营）</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>数据看板</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>提问分析 Tab</t>
         </is>
       </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
         <is>
           <t>（1）5 KPI：总提问、人均提问、平均会话轮次、答案点赞率、答案反馈率（InfoDot 指向答案反馈工作台）
 （2）提问量趋势面积折线图（区间联动 x 轴）
@@ -2658,28 +2710,28 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>7. 数据看板</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>数据看板</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>营收分析 Tab</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
         <is>
           <t>（1）小节① 收入与转化（5 KPI）：区间 GMV、付费用户、付费转化率、ARPPU、续费率
 （2）小节② 退款（4 KPI）：退款金额、退款率、退款订单数、净 GMV（扣退款）
@@ -2687,86 +2739,87 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>7. 数据看板</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>数据看板</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>热门 KP Tab</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
         <is>
           <t>（1）3 榜单（每榜 TOP10，数值按区间缩放、万进制）：被提问数 TOP10、付费转化贡献 TOP10、永享购买 TOP10
 （2）排名前 3 带奖牌样式；每行可点击下钻该 KP 详情</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>7. 数据看板</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>数据看板</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>数据看板 · 指标周期说明</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>（1）指标按统计口径分四类，并在界面按「实时 / 区间」分区呈现：① 实时快照——累计 / 存量，如累计 GMV、当前会员、KP 占用，截至当前的实时值、不参与环比；② 固定窗口快照——DAU / WAU / MAU，锚定当前时刻的滚动窗口（自然日 / 近 7 / 近 30 天），不随时间筛选变化、不参与环比；③ 区间统计——随今日 / 7 日 / 30 日联动并与上一等长周期环比，如新增用户、区间 GMV、区间提问、付费转化；④ 成熟 cohort——留存率，独立队列口径、不跟随全局筛选。①② 归「实时」分区、③ 归「区间 / 经营分析」分区、④ 用独立队列筛选
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>0718周六更新
+（1）指标按统计口径分三类（0717 二批 #8.2：数据看板内的日活 / 周活 / 月活由固定窗口快照改为区间联动统计）：① 实时快照——累计 / 存量，如主控台累计 GMV、当前会员、KP 占用，截至当前的实时值、不参与环比；② 区间统计——随今日 / 7 日 / 30 日联动并与上一等长周期环比，如日活 / 周活 / 月活、新增用户、区间 GMV、区间提问、付费转化；③ 成熟 cohort——留存率，独立队列口径、不跟随全局筛选。① 归「实时」分区、② 归「区间 / 经营分析」分区、③ 用独立队列筛选
 （2）每个指标悬浮面板统一写清：指标定义、分子/分母、去重主键、时区、统计周期、上一周期与差值单位；累计/快照指标明确标注“不参与环比”
 （3）今日 00:00–当前时刻对比昨日相同经过时长；近7/30天及自定义区间对比紧邻的上一等长区间；计数/金额用相对百分比，率类用百分点，时长用绝对差
 （4）上一周期为0时不计算无穷增幅，统一显示“上期为0，暂无可比增幅”；趋势按精确去重数据计算，不再使用0.62/0.42等估算系数；今日趋势按小时</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>8. 答案反馈</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>答案反馈</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>答案反馈工作台</t>
         </is>
       </c>
-      <c r="D76" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
         <is>
           <t>（1）副文案「前台答案点踩/反馈记录，供运营定位问题、迭代知识库」
 （2）表格列：问题、反馈标签、反馈人（昵称 + 会员标签）、提交时间、操作（详情）
@@ -2775,28 +2828,28 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>8. 答案反馈</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>答案反馈</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>答案反馈详情弹窗</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
         <is>
           <t>（1）顶部标签 + 反馈人（+会员标签）+ 时间，浅灰分隔线
 （2）仿前台 AI 会话气泡：用户问题（主题色气泡）+ AI 答案（白底气泡）
@@ -2804,28 +2857,28 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>9. 客服配置</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>客服配置</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>客服配置</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
         <is>
           <t>（1）客服二维码（必填，上传企微/个微二维码）
 （2）客服电话（非必填，有则展示）
@@ -2834,37 +2887,6 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>机构后台 PC（机构运营）</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>10. 系统配置</t>
-        </is>
-      </c>
-      <c r="C79" s="5" t="inlineStr">
-        <is>
-          <t>AI 会员价格</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>0716周四新增
-（1）首月折扣价、月度价两档可编辑
-（2）续费规则只读：「按月自动续费，会员到期后 72 小时为服务缓冲期 · 暂不可编辑」
-（3）0716 #10：会员价卡内加「调价须知」警示块（amber 淡底左边线）——单行文案：「会员价一经确定，非必要请勿修改；已开通自动续费的用户，下一扣费周期将按修改后的价格扣款。」
-（4）「保存」→ toast「已保存价格」</t>
-        </is>
-      </c>
-    </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
@@ -2873,106 +2895,143 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>10. 系统配置</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="inlineStr">
+          <t>系统配置</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>AI 会员价格</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>0718周六更新
+（1）「0718 修订」价格配置按两种购买方式分组展示，向运营明示每档金额——① 连续包月（自动续费）：首月价格（首月特惠，默认 ¥9.9，仅首次开通的首月扣款）+ 次月起价格（默认 ¥19.9/月，第 2 个月起每月自动扣款）；② 单月（一次性购买 · 不自动续费）：单月价格（默认 ¥19.9/1 个月，一次性扣款、到期自动失效不再扣费）；每档附前台展示位置说明，与前台「开通会员」两档一一对应
+（2）续费规则只读：「按月自动续费，会员到期后 72 小时为服务缓冲期 · 暂不可编辑」
+（3）0717 #7：「调价须知」标题与文案同一行、以「：」衔接——「调价须知：会员价一经确定，非必要请勿修改；已开通自动续费的用户，下一扣费周期将按修改后的价格扣款。」（amber 淡底左边线警示块）
+（4）「保存」→ toast「已保存价格」
+（5）「0718 修订」「调价须知」警示块移到「保存」按钮右侧（同一行，原在按钮之前独占一行），并去掉左侧 amber 色条、仅保留灰色内容块，页面动线变为：两组价格 → 续费规则 → 保存＋调价须知
+（6）「0718 修订」①「调价须知：」标题去掉加粗（与正文同字重）；②「保存」价格增加二次确认弹窗（说明影响范围：新开通按新价、已开通自动续费的用户下一扣费周期按新价扣款，确认后才生效并 toast「已保存价格」）
+（7）「0718 修订」价格配置视觉清洗：两组价格改为并排两枚子面板（连续包月＝「自动续费」琥珀语义标 / 单月＝「一次性购买 · 不自动续费」灰标，与前台「开通会员」套餐卡的续费语义标一致）；每档为「标签＋输入框＋一行说明」；续费规则由禁用输入框改为静态文本＋「暂不可编辑」小标（只读信息不再伪装成表单控件）
+（8）「0718 修订」续费规则与调价须知合并为同一灰色说明块（与上方两枚价格面板同宽、左对齐，不再缩进表单标签列；两行：续费规则 / 调价须知，纯文字呈现——去掉「暂不可编辑」小标与两行间分隔线），保存按钮单独一行、同样左对齐</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>机构后台 PC（机构运营）</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>系统配置</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
         <is>
           <t>回答策略</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>（1）副标题「知识库未检索到相关知识时」三选一
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>0718周六更新
+（1）副标题「知识库未检索到相关知识时」三选一
 （2）严谨模式：仅用知识库，未命中回「暂无相关资料」（医疗/合规场景）
 （3）透明兜底（默认）：大模型补充并标注「此为大模型生成、非知识库」
-（4）流畅模式：大模型直接补充，不标注来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+（4）流畅模式：大模型直接补充，不标注来源
+（5）「0718 修订」回答策略切换增加二次确认弹窗（展示目标模式说明、提示切换立即生效，确认后才切换并 toast；点当前已选项不触发）</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>11. 个人中心</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t>个人中心</t>
         </is>
       </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>个人中心</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
         <is>
           <t>（1）账户信息只读：账户名称、姓名、所属机构、上级机构、角色、手机号、账户状态；联系方式仅保留手机号
 （2）底部灰字「账户信息由平台统一管理，仅头像可自助更新；若需更改其他账户信息，请联系平台管理员」</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>11. 个人中心</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>个人中心</t>
         </is>
       </c>
-      <c r="D82" s="3" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>个人中心</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
         <is>
           <t>更换头像（裁剪）</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
+      <c r="E83" s="4" t="inlineStr">
         <is>
           <t>（1）相册选图 → 圆形裁剪弹层（缩放滑块 + 拖拽定位）
 （2）确定按 canvas 输出 256px 头像，顶栏头像同步回显 → toast「头像已更新」</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>11. 个人中心</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>个人中心</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>个人中心</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>修改登录密码</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
+      <c r="E84" s="4" t="inlineStr">
         <is>
           <t>（1）弹窗：旧密码（InfoDot「忘记请联系平台管理员重置」）+ 新密码 + 确认新密码
 （2）校验：旧密码非空、新密码 8~16 位且含字母+数字、两次一致
@@ -2980,55 +3039,55 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>机构后台 PC（机构运营）</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>12. 评审工具</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="inlineStr">
-        <is>
-          <t>原型清单</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>（1）〔评审〕三端通用站点地图，列全站页面便于评审跳转，同端内部导航</t>
-        </is>
-      </c>
-    </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>机构后台 PC（机构运营）</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>评审工具</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>原型清单</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>（1）〔评审〕三端通用站点地图，列全站页面便于评审跳转，同端内部导航</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>1. 登录与主控台</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>登录与主控台</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t>登录页</t>
         </is>
       </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr">
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
         <is>
           <t>（1）左侧动态毛玻璃品牌区 + 标语「答案有出处 · 知识更可信」
 （2）右侧登录卡：账号、密码、图形验证码（4 位，排除易混字符，可换一张）
@@ -3036,28 +3095,28 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>1. 登录与主控台</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>登录与主控台</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
         <is>
           <t>主控台</t>
         </is>
       </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E86" s="4" t="inlineStr">
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
         <is>
           <t>（1）页头机构筛选覆盖全部机构（来自机构主数据，非固定名单）；父机构选项带「父机构」标签；选中父机构＝自动汇总该父机构自身及其全部子机构数据，并在页头下方标注「含子机构：A、B」，让看数人明确汇总范围
 （2）右侧「导出」：生成「AI问书_全域主控台数据导出.xlsx」，沿用当前机构范围与时间筛选；实时/经营分析两 Sheet 分别标注实时统计时间与区间起止，指标全量含环比
@@ -3067,28 +3126,28 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>2. 机构管理</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>机构管理</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>机构列表</t>
         </is>
       </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E87" s="4" t="inlineStr">
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
         <is>
           <t>（1）表格列改为“二级机构域名”，仅展示 test-aba，不展示根域名；机构名称后仅父机构显示“父机构”标签（子机构的从属由「上级机构」列体现、普通机构无从属，均不加标签）。KP/存储为当前占用，Token 为当前订阅周期消耗
 （2）按 机构名称/上级机构/ID 模糊搜索；筛选 机构状态（全部/正常/停用）、套餐（基础/专业/旗舰/定制）、上级机构
@@ -3098,56 +3157,56 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>2. 机构管理</t>
-        </is>
-      </c>
-      <c r="C88" s="3" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>机构管理</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>机构从属命名规范</t>
         </is>
       </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="inlineStr">
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
         <is>
           <t>（1）「上级机构」＝关系字段（某机构的上级是谁），用于列头、详情字段与筛选；「父机构 / 子机构」＝角色标签（是否有下级 / 上级的身份），仅用于名称后标签与下拉选项后缀；两词分工不混用
 （2）数据归属列（订单 / 用户 / KP / 反馈属于哪个机构）在平台后台统一命名为「机构」，不再使用「归属机构」「所属机构」等变体</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>2. 机构管理</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>机构管理</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>机构列表</t>
         </is>
       </c>
-      <c r="D89" s="3" t="inlineStr">
+      <c r="D90" s="3" t="inlineStr">
         <is>
           <t>停用 / 恢复</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
+      <c r="E90" s="4" t="inlineStr">
         <is>
           <t>（1）操作列「停用/恢复」走二次确认
 （2）停用父机构只暂停父机构自身，不自动停用子机构，避免误伤独立经营主体；确认框列出仍在运营的子机构，如需停用须逐家确认并分别留痕
@@ -3156,28 +3215,28 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t>2. 机构管理</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>机构管理</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>机构列表</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>新建机构</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
+      <c r="E91" s="4" t="inlineStr">
         <is>
           <t>（1）弹窗加宽；域名前缀与固定后缀同框同行展示，前缀可编辑、分隔线右侧“-aba.{当前环境根域名}”置灰只读；只允许小写字母、数字与中划线且全局唯一
 （2）上级机构下拉仅列出顶级机构（含“无（顶级机构）”）；不列出已有上级的子机构，保证只有父 / 子两层。选中某顶级机构后，本机构成为其子机构、该顶级机构成为父机构
@@ -3185,28 +3244,28 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>2. 机构管理</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="inlineStr">
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>机构管理</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
         <is>
           <t>机构详情 · 基本资料</t>
         </is>
       </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E91" s="4" t="inlineStr">
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
         <is>
           <t>（1）表单含机构域名前缀：前缀与“-aba.{当前环境根域名}”同框同行、后缀置灰只读；保存前全局唯一校验，不再额外展示固定路由说明
 （2）页头状态后仅父机构显示“父机构”标签。上级机构字段按角色分三态——子机构不再只读：可直接改选其他顶级机构为新上级（二次确认后生效），并提供「取消关联，转为独立机构」操作（二次确认；解除后本机构变普通机构，原父机构若再无其他子机构则父机构身份同步解除）；父机构仍置灰并提示“已是父机构，不能再设上级机构（仅支持父 / 子两层）”；普通机构可选一个顶级机构作为上级。停用父机构默认不级联停用子机构
@@ -3215,28 +3274,28 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>2. 机构管理</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>机构管理</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
         <is>
           <t>机构详情 · 订阅配额</t>
         </is>
       </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="inlineStr">
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
         <is>
           <t>（1）KP数与存储“已用”始终取机构当前实际占用，不按订阅订单拆分；Token“已用”仅取当前订阅周期消耗，新订阅生效时清零重新累计
 （2）新订阅生效即整体替换三项基础上限，不结转旧订阅剩余额度；加油包只在所属当前订阅内累加，到期不结转
@@ -3245,31 +3304,30 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>2. 机构管理</t>
-        </is>
-      </c>
-      <c r="C93" s="5" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>机构管理</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
         <is>
           <t>机构详情 · 订阅配额</t>
         </is>
       </c>
-      <c r="D93" s="5" t="inlineStr">
+      <c r="D94" s="3" t="inlineStr">
         <is>
           <t>新建/复制订阅</t>
         </is>
       </c>
-      <c r="E93" s="6" t="inlineStr">
-        <is>
-          <t>0716周四更新
-（1）弹窗：套餐六选一（体验/基础/专业/旗舰/定制/不限，3 列网格卡片，弹窗 780 宽内容全显不滑动）→ 自动带出 KP/存储/Token 三项额度（仅填数字）；改额度后自动匹配套餐：命中某预设则选中它、否则套餐自动变「定制版」（不再额外标 badge）
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>（1）弹窗：套餐六选一（体验/基础/专业/旗舰/定制/不限，3 列网格卡片，弹窗 780 宽内容全显不滑动）→ 自动带出 KP/存储/Token 三项额度（仅填数字）；改额度后自动匹配套餐：命中某预设则选中它、否则套餐自动变「定制版」（不再额外标 badge）
 （2）有效期（必填）、商务负责人（选填）、备注（选填）
 （3）额度三项以三张横排指标卡呈现（图标 + 指标名 + 占用量/消耗量标签 + 步进器）：KP 数、存储为「占用量」型（随内容删除可释放）；Token 为「消耗量」型（只增不退、订阅周期结束清零重计）；每卡数值用「− 数字 +」步进器编辑，「不限」态禁用步进器显静态「不限」；改数值即自动匹配套餐（命中预设选中、否则转定制版）。加油包加量额度同款卡片布局。0716 #6：额度卡默认不高亮（普通描边），仅鼠标悬浮或聚焦到输入框时高亮（靛边框 + 淡靛底，与套餐卡选中态一致）；加油包新建表单底色由淡紫改为浅灰白（与下方历史列表区分）
 （4）「复制」带原订阅数据进表单，有效期取衔接默认避免重叠
@@ -3278,28 +3336,28 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>2. 机构管理</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>机构管理</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
         <is>
           <t>机构详情 · 订阅配额</t>
         </is>
       </c>
-      <c r="D94" s="3" t="inlineStr">
+      <c r="D95" s="3" t="inlineStr">
         <is>
           <t>加油包抽屉</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
+      <c r="E95" s="4" t="inlineStr">
         <is>
           <t>（1）右侧抽屉，提示“即时生效，仅在当前订阅周期累加；有效期跟随该订阅至 {endDate}，不结转下一订阅”
 （2）新建加油包：KP/存储/Token 三项额度（至少一项 &gt;0，否则 toast「请至少为一项加量额度填写大于 0 的值」）+ 备注
@@ -3308,28 +3366,28 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>2. 机构管理</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="inlineStr">
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>机构管理</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
         <is>
           <t>机构详情 · 订阅配额</t>
         </is>
       </c>
-      <c r="D95" s="3" t="inlineStr">
+      <c r="D96" s="3" t="inlineStr">
         <is>
           <t>订阅详情/删除</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
+      <c r="E96" s="4" t="inlineStr">
         <is>
           <t>（1）订阅详情弹窗：订阅 ID/套餐/额度/已用/有效期/商务负责人/状态/加油包数/创建时间/创建人/备注
 （2）删除规则（0714 与研发对齐，带护栏放开）：① 未生效订单——可直接删除，常规二次确认 ② 已生效订单——可删除，确认弹窗列明后果：连带删除其全部加油包、机构立即失去该订阅配额；若 KP/存储/Token 任一用量 &gt;0，追加红色强警告「该订阅已产生用量，删除将立即中断机构服务」 ③ 已过期订单——不可删除（商业单据审计留存，操作列不出删除入口）
@@ -3337,146 +3395,145 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>2. 机构管理</t>
-        </is>
-      </c>
-      <c r="C96" s="3" t="inlineStr">
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>机构管理</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
         <is>
           <t>机构详情 · 机构配置</t>
         </is>
       </c>
-      <c r="D96" s="3" t="inlineStr">
+      <c r="D97" s="3" t="inlineStr">
         <is>
           <t>LLM 配置</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
+      <c r="E97" s="4" t="inlineStr">
         <is>
           <t>（1）单选：平台默认（使用平台统一模型与额度，选中）/ 自配厂商（机构自有 API Key 接入，暂未开放·灰禁）
 （2）「保存」→ toast「已保存」</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>2. 机构管理</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="inlineStr">
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>机构管理</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
         <is>
           <t>机构详情 · 机构配置</t>
         </is>
       </c>
-      <c r="D97" s="3" t="inlineStr">
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t>联网配置</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
+      <c r="E98" s="4" t="inlineStr">
         <is>
           <t>（1）开关「允许联网检索」（默认开），点击 toast「已关闭/已开启联网检索」
 （2）注「开启后知识库未命中可联网补充检索（标注来源）· 开关即时生效」——此即 C 端会话「智能搜索」开关的机构级总开关</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>2. 机构管理</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>机构管理</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t>机构详情 · 机构配置</t>
         </is>
       </c>
-      <c r="D98" s="3" t="inlineStr">
+      <c r="D99" s="3" t="inlineStr">
         <is>
           <t>微信配置</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
+      <c r="E99" s="4" t="inlineStr">
         <is>
           <t>（1）微信公众号字段改为“网页授权回调地址”，微信开放平台字段改为“授权回调地址”；均填写完整 URL，并继续校验与微信后台配置一致
 （2）微信支付（必填，用于支付/退款/自动续费，未配置前台无法下单）：商户号 MchID、APIv3 密钥（掩码）、商户证书（上传 apiclient_cert.pem）；限制说明（商户号须与公众号 AppID 关联绑定/需上传证书且 APIv3 密钥在商户平台设置/退款·自动续费依赖支付能力）；保存 toast「已保存微信支付配置」</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>2. 机构管理</t>
-        </is>
-      </c>
-      <c r="C99" s="5" t="inlineStr">
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>机构管理</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>机构详情 · 用量看板</t>
         </is>
       </c>
-      <c r="D99" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E99" s="6" t="inlineStr">
-        <is>
-          <t>0716周四新增
-（1）当前生效订阅卡置于时间筛选上方，归入“实时订阅与资源占用”；KP/存储显示占用量，Token 显示当前订阅周期消耗量，不随时间筛选变化
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>（1）当前生效订阅卡置于时间筛选上方，归入“实时订阅与资源占用”；KP/存储显示占用量，Token 显示当前订阅周期消耗量，不随时间筛选变化
 （2）页面明确拆分“实时存量”和“区间运营分析”；今日/近7天/近30天/自定义仅联动活跃、新增、提问、GMV、付费用户及 LLM 区间消耗
 （3）配额阈值预警条：「Token 已用 X%，已于 日期 向机构联系人（姓名·手机号）发送 70%/80% 预警短信；达 90%/95% 将再次提醒。配额可在『订阅配额』调整」
 （4）阈值预警短信触达规则与文案模版：触发档位＝本订阅周期 Token 消耗率达 70% / 80% / 90% / 95% 四档，每档首次达到时向机构联系人手机号各发一次，同一计费周期内同档不重复、进入下一周期归零重置；四档共用一条参数化模版，签名用平台方「【AI问书】」（区别于 C 端验证码短信用机构名签名）。文案：【AI问书】您的机构「${orgName}」本订阅周期 Token 用量已达 ${pct}%，达上限后 C 端问答将被暂停，请及时登录机构后台「订阅配额」扩容或联系客服。如已处理请忽略本短信。（${orgName}=机构名，${pct}=当前消耗率）
-（5）4 维 UsageCard（每指标带 InfoDot 口径）：活跃度（DAU/WAU/MAU/累计 C 端/新增 C 端）、内容（KP 总数/已发·未发·下架/累计提问）、商业化（累计 GMV/当前会员/永享订单/付费转化/退款金额/退款率）、LLM 用量（tokens/调用次数/平均响应）
+（5）4 张 UsageCard 按两段划分（每指标带 InfoDot 口径）：【实时存量】内容存量（KP 当前占用 / 已发布·草稿·已下架 / 存储当前占用）、用户存量（累计 C 端 / 当前会员）；【区间运营分析】活跃与内容使用（活跃用户 / 新增 C 端 / 区间提问）、商业化与 LLM 消耗（区间 GMV / 付费用户 / Token 消耗量 / 调用次数 / 平均响应）
 （6）0716 #13：UsageCard 指标数值与后面的对比周期时间（如「对比 07-03~07-09」）之间增加水平间距，避免过于紧凑
 （7）「内容存量」「用户存量」卡片标题去掉括号内「实时快照」字样——实时口径已由所在「实时订阅与资源占用」分区标题统一说明，不逐卡重复</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>2. 机构管理</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>机构管理</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
         <is>
           <t>机构详情 · 品牌外观</t>
         </is>
       </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E100" s="4" t="inlineStr">
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
         <is>
           <t>（1）机构 Logo：上传 Logo 智能取色（自动读取像素主色/次色回填主辅色）→ toast「已上传 · 智能取色」
 （2）主视觉色 / 辅助视觉色取色器（含 mono 色值）
@@ -3485,28 +3542,28 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>3. 机构账户</t>
-        </is>
-      </c>
-      <c r="C101" s="3" t="inlineStr">
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>机构账户</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
         <is>
           <t>机构账户列表</t>
         </is>
       </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr">
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
         <is>
           <t>（1）表格列：账户 ID、账户名、姓名、机构、上级机构、角色（管理员/运营/只读）、状态（正常/停用）、操作（操作列固定右侧）——「所属机构」列名统一为「机构」
 （2）按 账户名/姓名 搜索；筛选 机构、上级机构、角色、状态
@@ -3514,28 +3571,28 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B102" s="3" t="inlineStr">
-        <is>
-          <t>3. 机构账户</t>
-        </is>
-      </c>
-      <c r="C102" s="3" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>机构账户</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
         <is>
           <t>机构账户列表</t>
         </is>
       </c>
-      <c r="D102" s="3" t="inlineStr">
+      <c r="D103" s="3" t="inlineStr">
         <is>
           <t>新建 / 编辑账户</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
+      <c r="E103" s="4" t="inlineStr">
         <is>
           <t>（1）新建/编辑共用弹窗：账户名称、姓名、机构、角色、联系手机号；账户名称创建后不可修改——编辑态该字段置灰并注「账户名称创建后不可修改」；平台后台列表、详情与弹窗均完整展示手机号，不脱敏
 （2）校验账户名+姓名非空（toast「请填写账户名称与姓名」）
@@ -3544,28 +3601,28 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>3. 机构账户</t>
-        </is>
-      </c>
-      <c r="C103" s="3" t="inlineStr">
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>机构账户</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
         <is>
           <t>机构账户列表</t>
         </is>
       </c>
-      <c r="D103" s="3" t="inlineStr">
+      <c r="D104" s="3" t="inlineStr">
         <is>
           <t>重置密码 / 停用恢复</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
+      <c r="E104" s="4" t="inlineStr">
         <is>
           <t>（1）重置密码 → 弹凭证弹窗（账号 + 系统生成密码）+ toast「已重置密码」
 （2）停用/恢复二次确认：停用（danger）「停用账户「X」后将无法登录机构后台，提示『账户服务已暂停』，可随时恢复」
@@ -3573,28 +3630,28 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>4. 订阅订单（全域 B 端）</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="inlineStr">
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>订阅订单（全域 B 端）</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
         <is>
           <t>全域订阅订单</t>
         </is>
       </c>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E104" s="4" t="inlineStr">
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
         <is>
           <t>（1）定位：B 端订阅（机构→平台），与 C 端「全域订单」两套体系；列表只展示「订阅」，加油包不入表
 （2）顶部 5 KPI（带 InfoDot）：订阅总数、生效、未生效、加油包、90 天内到期
@@ -3603,33 +3660,6 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>平台超管后台 PC</t>
-        </is>
-      </c>
-      <c r="B105" s="3" t="inlineStr">
-        <is>
-          <t>4. 订阅订单（全域 B 端）</t>
-        </is>
-      </c>
-      <c r="C105" s="3" t="inlineStr">
-        <is>
-          <t>全域订阅订单</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t>加油包抽屉</t>
-        </is>
-      </c>
-      <c r="E105" s="4" t="inlineStr">
-        <is>
-          <t>（1）同机构详情加油包抽屉：即时生效·额度累加·有效期跟随订阅；至少一项额度 &gt;0；列出加油包记录</t>
-        </is>
-      </c>
-    </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
@@ -3638,55 +3668,56 @@
       </c>
       <c r="B106" s="3" t="inlineStr">
         <is>
-          <t>5. 全域知识产品 KP</t>
+          <t>订阅订单（全域 B 端）</t>
         </is>
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
+          <t>全域订阅订单</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>加油包抽屉</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>（1）同机构详情加油包抽屉：即时生效·额度累加·有效期跟随订阅；至少一项额度 &gt;0；列出加油包记录</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>平台超管后台 PC</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>全域知识产品 KP</t>
+        </is>
+      </c>
+      <c r="C107" s="5" t="inlineStr">
+        <is>
           <t>全域 KP 列表</t>
         </is>
       </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E106" s="4" t="inlineStr">
-        <is>
-          <t>（1）卡片网格（复用机构后台 KP 卡视觉），平台只读监管
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>0718周六更新
+（1）卡片网格（复用机构后台 KP 卡视觉），平台只读监管
 （2）每卡：封面 + KP 名 +「机构 · {orgName}」（平台视角必显）+ 状态标签（已发布/草稿/已下架）+ 永享标
 （3）按 KP 名称搜索；筛选 机构、状态
 （4）筛选行右侧新增「导出」：生成「AI问书_全域知识产品数据导出.xlsx」，沿用 KP 名称搜索与机构、状态筛选，列含 KP ID/名称/机构/状态/永享标/权益/创建时间等；头部注明导出时间与筛选条件
-（5）点卡片进全域 KP 详情；空态「没有匹配的 KP」</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>平台超管后台 PC</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>5. 全域知识产品 KP</t>
-        </is>
-      </c>
-      <c r="C107" s="3" t="inlineStr">
-        <is>
-          <t>全域 KP 详情（5 Tab，与机构后台同构）</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>基础信息</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>（1）与机构后台 KP 详情·基础信息一致：封面（裁剪）+ KP 名称（必填）/简介/纸书购买链接/关联 Agent（必填）+ 保存
-（2）前台访问地址：只读展示 + 「复制链接」一键复制 C 端前台访问地址（随当前环境自动生成，携带机构 + KP），同机构后台
-（3）头部操作「下架」「删除」（删除后回全域 KP 列表）</t>
+（5）0717 #2.3/#2.4：点卡片进全域 KP 详情——列表与详情同一数据源（路由带 KP 真实 id，详情名称/初始状态与所点卡片一致）；状态命名与机构后台统一为「草稿 / 已发布 / 已下架」；空态「没有匹配的 KP」
+（6）「0718 修订」全域 KP 卡片补齐来源标签（自建 / 分享导入·实时 / 分享导入·快照，统一灰色），与机构后台同源同规；导出列不涉及来源变更
+（7）「0718 修订」全域 KP 卡片去掉「永享」标签（平台监管视角不再展示权益标）；平台列表/详情的标签规则与颜色与机构后台完全一致——来源标签（自建/分享导入·实时/分享导入·快照）统一灰色、状态标签（草稿灰/已发布玉绿/已下架琥珀）随状态变色，不再出现平台特有标签</t>
         </is>
       </c>
     </row>
@@ -3698,53 +3729,57 @@
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>5. 全域知识产品 KP</t>
-        </is>
-      </c>
-      <c r="C108" s="3" t="inlineStr">
+          <t>全域知识产品 KP</t>
+        </is>
+      </c>
+      <c r="C108" s="5" t="inlineStr">
         <is>
           <t>全域 KP 详情（5 Tab，与机构后台同构）</t>
         </is>
       </c>
-      <c r="D108" s="3" t="inlineStr">
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>基础信息</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>0718周六更新
+（1）与机构后台 KP 详情·基础信息一致：封面（裁剪）+ KP 名称（必填）/简介/纸书购买链接/关联 Agent（必填）+ 保存
+（2）前台访问地址：只读展示 + 「复制链接」一键复制 C 端前台访问地址（随当前环境自动生成，携带机构 + KP），同机构后台
+（3）头部状态操作与机构后台一致：草稿→「发布」、已发布→「下架」、已下架→「重新发布」+「删除」（逻辑删除，删除后回全域 KP 列表）
+（4）「0718 修订」详情头来源标签与机构后台统一三态灰色；平台超管查看「分享导入·实时」的 KP 时不套用接收方只读——保留发布/下架/删除等监管操作，仅以来源标签提示该 KP 为实时导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>平台超管后台 PC</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>全域知识产品 KP</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>全域 KP 详情（5 Tab，与机构后台同构）</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
         <is>
           <t>知识库</t>
         </is>
       </c>
-      <c r="E108" s="4" t="inlineStr">
+      <c r="E109" s="4" t="inlineStr">
         <is>
           <t>（1）与机构后台一致：上传知识文件（左右布局、向量化状态机）、文件上下架/重试/删除、类型筛选、检索状态
 （2）与机构后台一致：原『永享』Tab 取消、并入知识库——图/音/视可设永享价 + 永享/非永享标签 + 预览；设价弹窗含独立权益说明块</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>平台超管后台 PC</t>
-        </is>
-      </c>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>5. 全域知识产品 KP</t>
-        </is>
-      </c>
-      <c r="C109" s="3" t="inlineStr">
-        <is>
-          <t>全域 KP 详情（5 Tab，与机构后台同构）</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>定价与权益</t>
-        </is>
-      </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>（1）与机构后台一致：免费/会员 二选一互斥；永享与会员两套独立权益（设了永享价的资源会员也需单独购买）</t>
-        </is>
-      </c>
-    </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
@@ -3753,22 +3788,23 @@
       </c>
       <c r="B110" s="3" t="inlineStr">
         <is>
-          <t>5. 全域知识产品 KP</t>
-        </is>
-      </c>
-      <c r="C110" s="3" t="inlineStr">
+          <t>全域知识产品 KP</t>
+        </is>
+      </c>
+      <c r="C110" s="5" t="inlineStr">
         <is>
           <t>全域 KP 详情（5 Tab，与机构后台同构）</t>
         </is>
       </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>二维码</t>
-        </is>
-      </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>（1）与机构后台一致：二维码包列表 + 新建包 + 明细抽屉 + 下载 zip</t>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>定价与权益</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>0718周六更新
+（1）与机构后台一致：免费/会员 二选一互斥（0717 #5 切换前二次确认）；永享与会员两套独立权益（设了永享价的资源会员也需单独购买）</t>
         </is>
       </c>
     </row>
@@ -3780,7 +3816,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>5. 全域知识产品 KP</t>
+          <t>全域知识产品 KP</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -3790,12 +3826,12 @@
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>分享</t>
+          <t>二维码</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>（1）与机构后台一致：分享列表 + 新建分享 + 取消分享</t>
+          <t>（1）与机构后台一致：二维码包列表 + 新建包 + 明细抽屉 + 下载 zip</t>
         </is>
       </c>
     </row>
@@ -3807,20 +3843,47 @@
       </c>
       <c r="B112" s="3" t="inlineStr">
         <is>
-          <t>6. 全域 Agent 人设</t>
+          <t>全域知识产品 KP</t>
         </is>
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
+          <t>全域 KP 详情（5 Tab，与机构后台同构）</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>分享</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>（1）与机构后台一致：分享列表 + 新建分享 + 取消分享</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>平台超管后台 PC</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>全域 Agent 人设</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
           <t>全域 Agent 列表</t>
         </is>
       </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E112" s="4" t="inlineStr">
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
         <is>
           <t>（1）卡片网格：渐变封面 + Agent 名 +「机构 · {org}」+ 类型标签 +「关联 KP N 个」+ 音色（已设/默认）
 （2）按 Agent 名称搜索 + 机构筛选
@@ -3828,28 +3891,28 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t>6. 全域 Agent 人设</t>
-        </is>
-      </c>
-      <c r="C113" s="3" t="inlineStr">
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>全域 Agent 人设</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
         <is>
           <t>全域 Agent 详情（Prompt 平台可编辑）</t>
         </is>
       </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E113" s="4" t="inlineStr">
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
         <is>
           <t>（1）表单同机构后台 Agent 详情：头像（必填，圆形裁剪）、名称（必填）、类型（只读不可改）、TTS 参考音（必填）
 （2）回答 Prompt 平台超管可编辑：可编辑文本框 + 提示「平台超管可编辑全平台任意 Agent 的回答 Prompt，保存后即时生效」；保存 toast「已保存（含回答 Prompt）」
@@ -3857,59 +3920,58 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B114" s="3" t="inlineStr">
-        <is>
-          <t>7. 全域用户</t>
-        </is>
-      </c>
-      <c r="C114" s="5" t="inlineStr">
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>全域用户</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
         <is>
           <t>全域用户列表</t>
         </is>
       </c>
-      <c r="D114" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E114" s="6" t="inlineStr">
-        <is>
-          <t>0716周四更新
-（1）表格列：用户昵称、微信号、手机号、机构、会员状态、已购永享、累计 GMV、最新登录时间、注册时间、操作（详情）——「归属机构」列名统一为「机构」；「注册时间」列支持升 / 降序排序
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>（1）表格列：用户昵称、微信号、手机号、机构、会员状态、已购永享、累计 GMV、最新登录时间、注册时间、操作（详情）——「归属机构」列名统一为「机构」；「注册时间」列支持升 / 降序排序
 （2）按 账户名/微信号/手机号 搜索；筛选 会员状态、机构
 （3）点「详情」携行数据进全域用户详情
 （4）「导出」按钮位于筛选行右侧（与筛选条件同行，不在页头）：生成「AI问书_全域C端用户数据导出.xlsx」，沿用机构、会员状态和搜索条件；头部注明导出时间与筛选条件；平台侧手机号完整展示，不脱敏</t>
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B115" s="3" t="inlineStr">
-        <is>
-          <t>7. 全域用户</t>
-        </is>
-      </c>
-      <c r="C115" s="3" t="inlineStr">
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>全域用户</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
         <is>
           <t>全域用户详情</t>
         </is>
       </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E115" s="4" t="inlineStr">
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
         <is>
           <t>（1）头部卡：头像 + 昵称 + 会员/非会员标签；副行「机构 · 手机号 · 微信号」；活跃度（近 30 天提问 · 累计 GMV · 最近活跃）
 （2）已购永享卡（点击查看具体内容，进媒体预览）
@@ -3917,28 +3979,28 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>8. 全域订单</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="inlineStr">
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>全域订单</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
         <is>
           <t>全域订单列表</t>
         </is>
       </c>
-      <c r="D116" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E116" s="4" t="inlineStr">
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
         <is>
           <t>（1）C 端订单（终端用户→机构），复用订单字段，多「机构」列与筛选——「归属机构」列名统一为「机构」
 （2）表格列：订单号、机构、类型、关联知识产品、金额、支付方式、订单状态、退款状态、用户、下单时间、付款时间、兑换时间、操作（详情）
@@ -3947,28 +4009,28 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B117" s="3" t="inlineStr">
-        <is>
-          <t>8. 全域订单</t>
-        </is>
-      </c>
-      <c r="C117" s="3" t="inlineStr">
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>全域订单</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
         <is>
           <t>全域订单详情</t>
         </is>
       </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E117" s="4" t="inlineStr">
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
         <is>
           <t>（1）结构同机构后台订单详情，额外显「机构」字段（原「归属机构」统一更名）
 （2）兑换码/会员/永享三类差异化；有退款记录时显退款信息卡 + 退款时间线
@@ -3976,28 +4038,28 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B118" s="3" t="inlineStr">
-        <is>
-          <t>9. 全域答案反馈</t>
-        </is>
-      </c>
-      <c r="C118" s="3" t="inlineStr">
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>全域答案反馈</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
         <is>
           <t>全域答案反馈工作台</t>
         </is>
       </c>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E118" s="4" t="inlineStr">
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
         <is>
           <t>（1）副标题「全平台各机构 C 端答案点踩/反馈汇总，便于平台监管与质量分析」
 （2）表格列：问题、机构、反馈标签、反馈人（昵称+会员标签）、提交时间、操作（详情）——「归属机构」列名统一为「机构」
@@ -4007,31 +4069,30 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B119" s="3" t="inlineStr">
-        <is>
-          <t>10. 全域模型用量</t>
-        </is>
-      </c>
-      <c r="C119" s="5" t="inlineStr">
+      <c r="B120" s="3" t="inlineStr">
         <is>
           <t>全域模型用量</t>
         </is>
       </c>
-      <c r="D119" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E119" s="6" t="inlineStr">
-        <is>
-          <t>0716周四更新
-（1）页头机构筛选覆盖全部机构，父机构带「父机构」标签；选中父机构＝自动汇总该父机构自身及其全部子机构数据，并在页面标注「含子机构：A、B」
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>全域模型用量</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>（1）页头机构筛选覆盖全部机构，父机构带「父机构」标签；选中父机构＝自动汇总该父机构自身及其全部子机构数据，并在页面标注「含子机构：A、B」
 （2）右侧「导出」：生成「AI问书_全域模型用量数据导出.xlsx」，沿用机构范围与时间区间，实时/区间口径分别标注统计时间；头部注明导出时间与筛选条件
 （3）实时总览（累计，不随时间变）：累计 tokens、累计调用次数（各带 InfoDot）
 （4）经营分析周期与通用指标规则一致；tokens、调用次数用相对百分比，平均响应用绝对时长差，上一周期为0时显示暂无可比增幅。0716：区间 tokens / 区间调用次数 / 平均响应 的环比行去掉重复的 JSX 箭头图标，仅保留数据串内嵌的方向箭头（↑ 上升 / ↓ 缩短），避免双箭头；三张卡数值行与环比行结构一致，卡片高度对齐
@@ -4039,28 +4100,28 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>11. 平台账户</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="inlineStr">
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>平台账户</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
         <is>
           <t>平台账户列表</t>
         </is>
       </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E120" s="4" t="inlineStr">
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
         <is>
           <t>（1）副标题强调与机构账户区分：平台方人员、平台级角色、无所属机构
 （2）表格列：账户名称、姓名、角色（平台超级管理员/平台运营/平台财务）、完整手机号、状态（启用/停用）、创建时间、操作；手机号不脱敏
@@ -4069,28 +4130,28 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>11. 平台账户</t>
-        </is>
-      </c>
-      <c r="C121" s="3" t="inlineStr">
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>平台账户</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
         <is>
           <t>平台账户列表</t>
         </is>
       </c>
-      <c r="D121" s="3" t="inlineStr">
+      <c r="D122" s="3" t="inlineStr">
         <is>
           <t>新建 / 重置密码 / 启停</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
+      <c r="E122" s="4" t="inlineStr">
         <is>
           <t>（1）新建弹窗：账户名称（必填）、姓名（必填）、角色（必填，平台三角色）、联系方式（选填）；说明「平台账户无所属机构，仅用平台级角色 / 初始密码系统生成，创建后弹窗展示并支持复制」
 （2）校验账户名+姓名非空；新建成功弹凭证弹窗（机构标「平台（无所属机构）」）
@@ -4098,90 +4159,89 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t>12. 角色权限</t>
-        </is>
-      </c>
-      <c r="C122" s="5" t="inlineStr">
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>角色权限</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
         <is>
           <t>角色权限（机构/平台双类型 · 三态）</t>
         </is>
       </c>
-      <c r="D122" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E122" s="6" t="inlineStr">
-        <is>
-          <t>0716周四更新
-（1）副标题「按角色类型分别管理机构角色与平台角色（权限点不同）；机构账户选机构角色、平台账户选平台角色」
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>（1）副标题「按角色类型分别管理机构角色与平台角色（权限点不同）；机构账户选机构角色、平台账户选平台角色」
 （2）顶部切换「机构角色 / 平台角色」
 （3）机构角色权限点分组：主控台 / 产品中心（0716 #7/#8.1：知识产品 KP 与 Agent 人设同一行左右两列，KP 在左列，其三态开关与「查看主控台」垂直对齐）/ 运营中心（C 端用户、订单管理、兑换码）/ 数据中心（数据看板）/ 系统设置（客服配置、系统配置）；「Agent 回答 Prompt 编辑」为功能权限（其余为菜单权限），加「功能权限」标签区分
-（4）0716 #8：「Agent 回答 Prompt 编辑」作为「Agent 人设」的嵌套子项——仅当「Agent 人设」= 可操作时才展开显示（无 / 只读时完全不显示，而非置灰锁定）；用缩进 + 灰色虚线连接线表达从属关系（非仅背景块）；「功能权限」标签移至权限 key 行（与标题行分离，保证右侧两态开关垂直居中对齐）；子项两态（只读 / 可操作）；「Agent 人设」降级为只读 / 无时子项自动收起
+（4）0716 #8：「Agent 回答 Prompt 编辑」作为「Agent 人设」的嵌套子项——仅当「Agent 人设」= 可操作时才展开显示（无 / 只读时完全不显示，而非置灰锁定）；用缩进 + 灰色虚线连接线表达从属关系（0717 #6：去掉子项紫色背景块，仅保留缩进 + 虚线连接线）；「功能权限」标签移至权限 key 行（与标题行分离，保证右侧两态开关垂直居中对齐）；子项两态（只读 / 可操作）；「Agent 人设」降级为只读 / 无时子项自动收起
 （5）平台角色权限点分组：主控台 / 机构管理（机构管理、机构账户、订阅订单）/ 产品中心（全域 KP、全域 Agent）/ 运营中心（全域用户、全域订单）/ 数据中心（全域答案反馈、全域模型用量）/ 系统设置（平台账户、角色权限、默认 LLM）
 （6）左侧角色列表，右侧权限面板：菜单权限项 = 图标 + 名称 + 三态分段开关（无/只读/可操作）；功能权限「Agent 回答 Prompt 编辑」为两态（只读/可操作）——功能权限的「无」与「只读」语义相同（都表现为不可编辑），合并为「只读」
 （7）三态图例（InfoDot）：无＝看不见该菜单 / 只读＝可进入查看不能编辑（功能权限＝不可编辑）/ 可操作＝全部操作可用；「保存」→ toast「已保存权限」</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>12. 角色权限</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="inlineStr">
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>角色权限</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
         <is>
           <t>角色权限（机构/平台双类型 · 三态）</t>
         </is>
       </c>
-      <c r="D123" s="3" t="inlineStr">
+      <c r="D124" s="3" t="inlineStr">
         <is>
           <t>新建角色</t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr">
+      <c r="E124" s="4" t="inlineStr">
         <is>
           <t>（1）弹窗加宽，使角色类型一行完整展示不换行；角色类型继承当前“机构角色/平台角色”Tab并以置灰锁定显示，不可切换；删除解释文案「由创建入口页签决定，不可切换」（锁定态样式已自说明）；仅填写角色名称与备注
 （2）校验名称非空 + 同类型不重名；创建后入对应类型列表、空权限、自动切换选中 → toast「已创建角色，请在右侧逐项设置权限」</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B124" s="3" t="inlineStr">
-        <is>
-          <t>13. 默认 LLM</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="inlineStr">
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>默认 LLM</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
         <is>
           <t>默认 LLM 模型配置</t>
         </is>
       </c>
-      <c r="D124" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E124" s="4" t="inlineStr">
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
         <is>
           <t>（1）副标题「仅『已上架』的模型可被设为所有机构底层的默认基模」
 （2）表格：模型名称、厂商、版本号、状态（已上架/未上架 + 默认标）、操作（编辑/上架·下架/设为默认）
@@ -4190,33 +4250,6 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>平台超管后台 PC</t>
-        </is>
-      </c>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>13. 默认 LLM</t>
-        </is>
-      </c>
-      <c r="C125" s="3" t="inlineStr">
-        <is>
-          <t>默认 LLM 模型配置</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t>新建 / 编辑模型</t>
-        </is>
-      </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>（1）弹窗：模型名称（必填，唯一校验，重名实时红字 + toast「模型名称已存在」）、厂商（下拉 通义/DeepSeek/智谱/百川）、版本号（必填）、状态（编辑时只读，注「上下架请在列表操作列进行」）</t>
-        </is>
-      </c>
-    </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
@@ -4225,53 +4258,53 @@
       </c>
       <c r="B126" s="3" t="inlineStr">
         <is>
-          <t>14. 个人中心</t>
+          <t>默认 LLM</t>
         </is>
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
+          <t>默认 LLM 模型配置</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>新建 / 编辑模型</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>（1）弹窗：模型名称（必填，唯一校验，重名实时红字 + toast「模型名称已存在」）、厂商（下拉 通义/DeepSeek/智谱/百川）、版本号（必填）、状态（编辑时只读，注「上下架请在列表操作列进行」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>平台超管后台 PC</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
           <t>个人中心</t>
         </is>
       </c>
-      <c r="D126" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E126" s="4" t="inlineStr">
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>个人中心</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
         <is>
           <t>（1）账户信息只读：账户名称、姓名、角色、完整手机号、账户状态；两后台个人中心手机号均不脱敏，平台账户不显示所属机构/上级机构
 （2）平台超管不显示「账户信息由平台统一管理…」灰字提示</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>平台超管后台 PC</t>
-        </is>
-      </c>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>14. 个人中心</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="inlineStr">
-        <is>
-          <t>个人中心</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>更换头像（裁剪）</t>
-        </is>
-      </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>（1）相册选图 → 圆形裁剪（拖拽定位 + 缩放滑块）→ canvas 输出 256px 头像 → toast「头像已更新」</t>
-        </is>
-      </c>
-    </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
@@ -4280,7 +4313,7 @@
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>14. 个人中心</t>
+          <t>个人中心</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
@@ -4290,12 +4323,12 @@
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>修改登录密码</t>
+          <t>更换头像（裁剪）</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>（1）弹窗：旧密码 + 新密码 + 确认新密码；校验 旧密码非空/新密码 8~16 位含字母+数字/两次一致 → toast「登录密码已修改」</t>
+          <t>（1）相册选图 → 圆形裁剪（拖拽定位 + 缩放滑块）→ canvas 输出 256px 头像 → toast「头像已更新」</t>
         </is>
       </c>
     </row>
@@ -4307,109 +4340,109 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>15. 评审工具</t>
+          <t>个人中心</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
+          <t>个人中心</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>修改登录密码</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>（1）弹窗：旧密码 + 新密码 + 确认新密码；校验 旧密码非空/新密码 8~16 位含字母+数字/两次一致 → toast「登录密码已修改」</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>平台超管后台 PC</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>评审工具</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
           <t>原型清单 / 微信对接清单下载</t>
         </is>
       </c>
-      <c r="D129" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E129" s="4" t="inlineStr">
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
         <is>
           <t>（1）〔评审〕原型清单：三端通用站点地图，列全站页面便于评审跳转
 （2）〔评审〕顶栏固定「新机构入驻微信对接清单」下载按钮（下载对接清单 docx）</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>三端通用（全局交互）</t>
         </is>
       </c>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t>1. 通用状态规范</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="inlineStr">
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>通用状态规范</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
         <is>
           <t>Toast 轻提示</t>
         </is>
       </c>
-      <c r="D130" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E130" s="4" t="inlineStr">
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
         <is>
           <t>（1）单条、统一位置弹出（移动端底部 / 后台顶部），默认数秒自动消失
 （2）用于操作结果反馈（已保存/已删除/已复制等），文案过长自动换行不超屏</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>三端通用（全局交互）</t>
         </is>
       </c>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t>1. 通用状态规范</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="inlineStr">
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>通用状态规范</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
         <is>
           <t>二次确认弹窗（ConfirmDialog）</t>
         </is>
       </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E131" s="4" t="inlineStr">
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
         <is>
           <t>（1）危险/不可逆操作（删除/下架/停用/退款/取消分享等）统一走二次确认
 （2）危险操作主按钮为 danger 红色，文案写清后果与是否可恢复</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>三端通用（全局交互）</t>
-        </is>
-      </c>
-      <c r="B132" s="3" t="inlineStr">
-        <is>
-          <t>1. 通用状态规范</t>
-        </is>
-      </c>
-      <c r="C132" s="3" t="inlineStr">
-        <is>
-          <t>加载骨架屏</t>
-        </is>
-      </c>
-      <c r="D132" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>（1）后台列表/详情挂载先显骨架屏占位，再渲染真实数据，避免白屏跳变</t>
-        </is>
-      </c>
-    </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
@@ -4418,53 +4451,53 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>1. 通用状态规范</t>
+          <t>通用状态规范</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
+          <t>加载骨架屏</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>（1）后台列表/详情挂载先显骨架屏占位，再渲染真实数据，避免白屏跳变</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>三端通用（全局交互）</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>通用状态规范</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
           <t>空态</t>
         </is>
       </c>
-      <c r="D133" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E133" s="4" t="inlineStr">
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
         <is>
           <t>（1）列表/搜索/筛选无结果时显居中插画 + 标题 + 副文案（如「没有匹配的 X / 换个条件试试」）
 （2）部分空态内嵌主操作入口（如「新建 X」）</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>三端通用（全局交互）</t>
-        </is>
-      </c>
-      <c r="B134" s="3" t="inlineStr">
-        <is>
-          <t>1. 通用状态规范</t>
-        </is>
-      </c>
-      <c r="C134" s="3" t="inlineStr">
-        <is>
-          <t>分页</t>
-        </is>
-      </c>
-      <c r="D134" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>（1）后台列表默认每页 10 条，超过才分页；筛选/搜索变更后回到第 1 页；分页单位随实体变化（家/个/笔/条/单等）</t>
-        </is>
-      </c>
-    </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
@@ -4473,12 +4506,12 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>1. 通用状态规范</t>
+          <t>通用状态规范</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>操作列固定</t>
+          <t>分页</t>
         </is>
       </c>
       <c r="D135" s="3" t="inlineStr">
@@ -4488,7 +4521,7 @@
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>（1）后台表格「操作」列固定在右侧（白底+左侧分隔线+阴影），横向滚动时常驻可见</t>
+          <t>（1）后台列表默认每页 10 条，超过才分页；筛选/搜索变更后回到第 1 页；分页单位随实体变化（家/个/笔/条/单等）</t>
         </is>
       </c>
     </row>
@@ -4500,20 +4533,47 @@
       </c>
       <c r="B136" s="3" t="inlineStr">
         <is>
-          <t>1. 通用状态规范</t>
+          <t>通用状态规范</t>
         </is>
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
+          <t>操作列固定</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>（1）后台表格「操作」列固定在右侧（白底+左侧分隔线+阴影），横向滚动时常驻可见</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>三端通用（全局交互）</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>通用状态规范</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
           <t>数值单位规范</t>
         </is>
       </c>
-      <c r="D136" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E136" s="4" t="inlineStr">
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
         <is>
           <t>（1）两后台数值统一中文进制缩写：&lt;1 万千分位；1 万~1 亿 → X.X 万；≥1 亿 → X.XX 亿；Token 统一以「亿」为单位
 （2）各看板页脚附统一单位规范说明
@@ -4524,28 +4584,28 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>三端通用（全局交互）</t>
         </is>
       </c>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>1. 通用状态规范</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="inlineStr">
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>通用状态规范</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
         <is>
           <t>登录态有效期</t>
         </is>
       </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E137" s="4" t="inlineStr">
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
         <is>
           <t>（1）移动端采用滑动7天会话：每次经过认证的有效请求刷新最后活跃时间；连续7天无有效请求后失效并返回登录页
 （2）未登录不可进入业务内容；登录失效后的原目标地址可在重新登录成功后恢复跳转，但不自动补发任何未认证输入</t>
@@ -4563,7 +4623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4729,44 +4789,44 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>通用精确性</t>
+          <t>通用差值规则</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>去重与估算</t>
+          <t>界面环比文案（0718 新增）</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>按指标指定主键精确 DISTINCT；禁止使用 0.62/0.42 等经验系数估算</t>
+          <t>看板界面环比标签统一显示「↑x.x% 较上一周期」，不再出现「pp」字样；率类差值口径仍为百分点</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>可审计可复算</t>
+          <t>避免用户对 pp 单位困惑</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>主控台·实时总览</t>
+          <t>通用精确性</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>累计 GMV（实时）</t>
+          <t>去重与估算</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>SUM(已支付订单金额)</t>
+          <t>按指标指定主键精确 DISTINCT；禁止使用 0.62/0.42 等经验系数估算</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>总营收</t>
+          <t>可审计可复算</t>
         </is>
       </c>
     </row>
@@ -4778,17 +4838,17 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>累计退款 / 退款率（实时）</t>
+          <t>累计 GMV（实时）</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>SUM(退款成功额)；退款率 = 退款额 ÷ GMV</t>
+          <t>SUM(已支付订单金额)</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>售后与资金健康度</t>
+          <t>总营收</t>
         </is>
       </c>
     </row>
@@ -4800,17 +4860,17 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>净 GMV（累计扣退款）</t>
+          <t>累计退款 / 退款率（实时）</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>累计 GMV − 累计退款</t>
+          <t>SUM(退款成功额)；退款率 = 退款额 ÷ GMV</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>实际到账净收入</t>
+          <t>售后与资金健康度</t>
         </is>
       </c>
     </row>
@@ -4822,17 +4882,17 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>当前会员数（实时）</t>
+          <t>净 GMV（累计扣退款）</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>会员未到期的去重用户数</t>
+          <t>累计 GMV − 累计退款</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>商业化基本盘</t>
+          <t>实际到账净收入</t>
         </is>
       </c>
     </row>
@@ -4844,61 +4904,61 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>累计注册用户（实时）</t>
+          <t>当前会员数（实时）</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>COUNT(DISTINCT user_id)</t>
+          <t>会员未到期的去重用户数</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>用户规模</t>
+          <t>商业化基本盘</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>主控台·经营分析</t>
+          <t>主控台·实时总览</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>活跃用户 / 新增会员 / 区间 GMV / 区间提问数（区间）+ 趋势图</t>
+          <t>累计注册用户（实时）</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>区间聚合</t>
+          <t>COUNT(DISTINCT user_id)</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>经营动态</t>
+          <t>用户规模</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>用户分析</t>
+          <t>主控台·经营分析</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>DAU / WAU / MAU（实时·固定窗口）</t>
+          <t>活跃用户 / 新增会员 / 区间 GMV / 区间提问数（区间）+ 趋势图</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>周期内有效行为去重用户数</t>
+          <t>区间聚合</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>粘性分层</t>
+          <t>经营动态</t>
         </is>
       </c>
     </row>
@@ -4910,17 +4970,17 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>新增用户数（区间）</t>
+          <t>日活 / 周活 / 月活（区间）</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>区间内首次注册数</t>
+          <t>所选区间内日均去重活跃用户；与上一等长周期环比（KPI 卡同款 Delta）</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>拉新效果</t>
+          <t>粘性分层（0717 二批：由固定窗口快照改为区间联动）</t>
         </is>
       </c>
     </row>
@@ -4932,17 +4992,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>次日 / 7 日 / 30 日留存率（独立 cohort）</t>
+          <t>新增用户趋势（区间）</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>分母=cohort 日注册去重用户；分子=第 N 日有有效行为用户；只纳入已满 N 日的成熟 cohort，显示样本量与成熟截止日，今日显示—</t>
+          <t>区间内按日/按小时的首次注册数序列</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>产品价值是否站得住</t>
+          <t>拉新节奏（新增用户卡右侧迷你折线）</t>
         </is>
       </c>
     </row>
@@ -4954,17 +5014,17 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>来源分布（区间）</t>
+          <t>新增用户数（区间）</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>扫码进入 vs 直接访问</t>
+          <t>区间内首次注册数</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>渠道效果</t>
+          <t>拉新效果</t>
         </is>
       </c>
     </row>
@@ -4976,61 +5036,61 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>地区分布 / 性别分布（区间）</t>
+          <t>次日 / 7 日 / 30 日留存率（独立 cohort）</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>按地区·性别分组占比</t>
+          <t>分母=cohort 日注册去重用户；分子=第 N 日有有效行为用户；只纳入已满 N 日的成熟 cohort，显示样本量与成熟截止日，未成熟节点显示「尚未到统计时间」并给出预计可统计日期（注册日 + N）；单注册日批次三节点共用同一样本分母</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>用户画像与精细化运营</t>
+          <t>产品价值是否站得住</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>提问分析</t>
+          <t>用户分析</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>总提问数（区间）</t>
+          <t>来源分布（区间）</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>COUNT(提问)</t>
+          <t>扫码进入 vs 直接访问；图例含人数与占比；占比环比按百分点差计算、界面统一显示为「↑x.x% 较上一周期」</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>使用强度</t>
+          <t>渠道效果</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>提问分析</t>
+          <t>用户分析</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>人均提问数（区间）</t>
+          <t>地区分布 / 性别分布（区间）</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>总提问数 / 活跃用户</t>
+          <t>按地区·性别分组占比</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>单用户深度</t>
+          <t>用户画像与精细化运营</t>
         </is>
       </c>
     </row>
@@ -5042,17 +5102,17 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>平均会话轮次（区间）</t>
+          <t>总提问数（区间）</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>总提问数 / 总会话数</t>
+          <t>COUNT(提问)</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>对话沉浸度</t>
+          <t>使用强度</t>
         </is>
       </c>
     </row>
@@ -5064,17 +5124,17 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>答案点赞率 / 答案反馈率（区间）</t>
+          <t>人均提问数（区间）</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>点赞数 ÷ 答案数；反馈数 ÷ 答案数</t>
+          <t>总提问数 / 活跃用户</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>答案质量摘要（明细在答案反馈菜单）</t>
+          <t>单用户深度</t>
         </is>
       </c>
     </row>
@@ -5086,17 +5146,17 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>提问量趋势（区间）</t>
+          <t>平均会话轮次（区间）</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>每日提问条数</t>
+          <t>总提问数 / 总会话数</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>提问走势</t>
+          <t>对话沉浸度</t>
         </is>
       </c>
     </row>
@@ -5108,17 +5168,17 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>按 Agent 提问分布（区间）</t>
+          <t>答案点赞率 / 答案反馈率（区间）</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>各 Agent 接收提问占比</t>
+          <t>点赞数 ÷ 答案数；反馈数 ÷ 答案数</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>Agent 配置 / 路由质量</t>
+          <t>答案质量摘要（明细在答案反馈菜单）</t>
         </is>
       </c>
     </row>
@@ -5130,17 +5190,17 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>提问领域分布（区间）</t>
+          <t>提问量趋势（区间）</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>按 KP / 领域聚合占比</t>
+          <t>每日提问条数</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>用户最关心的领域</t>
+          <t>提问走势</t>
         </is>
       </c>
     </row>
@@ -5152,61 +5212,61 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>提问关键词云（区间）</t>
+          <t>按 Agent 提问分布（区间）</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>高频关键词，hover 显示该词区间提问数</t>
+          <t>各 Agent 接收提问占比</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>运营 / 商业化分析</t>
+          <t>Agent 配置 / 路由质量</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>营收分析·收入与转化</t>
+          <t>提问分析</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>区间 GMV（区间）</t>
+          <t>提问领域分布（区间）</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>SUM(区间已支付金额)</t>
+          <t>按 KP / 领域聚合占比</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>区间营收</t>
+          <t>用户最关心的领域</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>营收分析·收入与转化</t>
+          <t>提问分析</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>付费用户数 / 付费转化率（区间）</t>
+          <t>提问关键词云（区间）</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>区间付费用户 / 区间活跃用户</t>
+          <t>高频关键词，hover 显示该词区间提问数</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>商业化核心</t>
+          <t>运营 / 商业化分析</t>
         </is>
       </c>
     </row>
@@ -5218,17 +5278,17 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>ARPPU（区间）</t>
+          <t>区间 GMV（区间）</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>区间收入 / 区间付费用户数</t>
+          <t>SUM(区间已支付金额)</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>单付费用户产值</t>
+          <t>区间营收</t>
         </is>
       </c>
     </row>
@@ -5240,83 +5300,83 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>续费率（区间）</t>
+          <t>付费用户数 / 付费转化率（区间）</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>到期续费数 / 到期会员数</t>
+          <t>区间付费用户 / 区间活跃用户</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>长期价值</t>
+          <t>商业化核心</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>营收分析·退款</t>
+          <t>营收分析·收入与转化</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>退款金额 / 退款率 / 退款订单数 / 净 GMV（区间）</t>
+          <t>ARPPU（区间）</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>见各指标</t>
+          <t>区间收入 / 区间付费用户数</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>售后与净收入</t>
+          <t>单付费用户产值</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>营收分析·转化漏斗</t>
+          <t>营收分析·收入与转化</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>受限内容触发率（区间）</t>
+          <t>续费率（区间）</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>触发付费墙次数 / 总提问数</t>
+          <t>到期续费数 / 到期会员数</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>付费墙强度（漏斗入口）</t>
+          <t>长期价值</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>营收分析·转化漏斗</t>
+          <t>营收分析·退款</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>会员漏斗（区间）</t>
+          <t>退款金额 / 退款率 / 退款订单数 / 净 GMV（区间）</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>看到会员页 → 点击购买 → 完成支付（%）</t>
+          <t>见各指标</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>找漏斗瓶颈</t>
+          <t>售后与净收入</t>
         </is>
       </c>
     </row>
@@ -5328,61 +5388,61 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>永享转化（区间）</t>
+          <t>受限内容触发率（区间）</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>触发永享墙 → 完成购买（%）</t>
+          <t>触发付费墙次数 / 总提问数</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>永享定价是否合理</t>
+          <t>付费墙强度（漏斗入口）</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>热门 KP</t>
+          <t>营收分析·转化漏斗</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>被提问数 TOP 10 KP（区间）</t>
+          <t>会员漏斗（区间）</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>按 KP 维度统计提问</t>
+          <t>看到会员页 → 点击购买 → 完成支付（%）</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>真正被使用的内容</t>
+          <t>找漏斗瓶颈</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>热门 KP</t>
+          <t>营收分析·转化漏斗</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>付费转化贡献 TOP 10 KP（区间）</t>
+          <t>永享转化（区间）</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>通过该 KP 触发的会员 / 永享订单数</t>
+          <t>触发永享墙 → 完成购买（%）</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>营销价值高的内容</t>
+          <t>永享定价是否合理</t>
         </is>
       </c>
     </row>
@@ -5394,15 +5454,59 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
+          <t>被提问数 TOP 10 KP（区间）</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>按 KP 维度统计提问</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>真正被使用的内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>热门 KP</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>付费转化贡献 TOP 10 KP（区间）</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>通过该 KP 触发的会员 / 永享订单数</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>营销价值高的内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>热门 KP</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
           <t>永享购买 TOP 10 KP（区间）</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>按 KP 永享订单数</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D40" s="4" t="inlineStr">
         <is>
           <t>永享潜力</t>
         </is>
@@ -5419,20 +5523,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>分区</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>维度</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>指标</t>
         </is>
@@ -5441,48 +5551,68 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>活跃度</t>
+          <t>实时存量（不随时间筛选变化）</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>该机构 DAU / WAU / MAU、累计 C 端用户数、新增 C 端用户数</t>
+          <t>内容存量</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>KP 当前占用（自建 + 独立快照导入，实时同步不占名额）、KP 状态分布（草稿 / 已发布 / 已下架）、存储当前占用</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>内容</t>
+          <t>实时存量（不随时间筛选变化）</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>KP 总数（已发布 / 未发布 / 已下架）、累计提问数</t>
+          <t>用户存量</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>累计 C 端用户数（按用户 ID 去重）、当前会员数（含 72 小时缓冲期）</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>商业化</t>
+          <t>区间运营分析（随今日 / 近7天 / 近30天 / 自定义联动）</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>累计 GMV、当前会员数、永享订单数、付费转化率</t>
+          <t>活跃与内容使用</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>活跃用户（登录或提问，去重）、新增 C 端用户数、区间提问数（含追问）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>LLM 用量（仅平台默认 LLM）</t>
+          <t>区间运营分析（随今日 / 近7天 / 近30天 / 自定义联动）</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>tokens 用量、调用次数、平均响应时长</t>
+          <t>商业化与 LLM 消耗</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>区间 GMV、付费用户数、Token 消耗量、模型调用次数、平均响应时长</t>
         </is>
       </c>
     </row>

--- a/docs/feature-list.xlsx
+++ b/docs/feature-list.xlsx
@@ -2572,7 +2572,7 @@
         <is>
           <t>（1）副文案「每次生成为一个批次,点击批次查看该批次全部兑换码」
 （2）按批次名称搜索
-（3）表格列：批次名称、已兑换/生成、权益时长、兑换有效起止时间、批次创建时间、操作（详情）；「兑换有效起止时间」列支持升 / 降序排序（按有效开始时间）——兑换码均有明确周期，可按生效期排列
+（3）表格列：批次名称、已兑换/生成、权益时长、可兑换时间、批次创建时间、操作（详情）；「可兑换时间」列支持升 / 降序排序（按有效开始时间）——兑换码均有明确周期，可按生效期排列
 （4）空态「还没有兑换码批次」+「点击『批量生成』创建第一个批次」</t>
         </is>
       </c>
@@ -2600,8 +2600,8 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>（1）弹窗：批次名称（必填）+ 权益类型（固定会员）+ 会员时长（默认3个月，1–12）+ 兑换有效开始/结束时间（必填且开始≤结束）+ 生成数量（默认500）
-（2）弹窗加宽，兑换有效开始/结束时间在一行内完整展示；点击时间字段后日历面板完整弹出可直接选择，不被弹窗裁切、无需滚动
+          <t>（1）弹窗：批次名称（必填）+ 权益类型（固定会员）+ 会员时长（默认3个月，1–12）+ 可兑换时间（开始 / 结束）（必填且开始≤结束）+ 生成数量（默认500）
+（2）弹窗加宽，可兑换时间（开始 / 结束）在一行内完整展示；点击时间字段后日历面板完整弹出可直接选择，不被弹窗裁切、无需滚动
 （3）确定 → toast「已生成批次 · N 个兑换码」</t>
         </is>
       </c>

--- a/docs/feature-list.xlsx
+++ b/docs/feature-list.xlsx
@@ -608,22 +608,25 @@
           <t>登录与授权</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>手机号验证码登录</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>（1）手机号输入框（限 11 位数字，自动过滤非数字）+ 验证码输入框（限 6 位）+「获取验证码」（点击 toast「验证码已发送」）
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>0722周三更新
+（1）手机号输入框（限 11 位数字，自动过滤非数字）+ 验证码输入框（限 6 位）+「获取验证码」（点击 toast「验证码已发送」）
 （2）登录按钮在手机号或验证码为空时禁用
 （3）校验：手机号非 11 位 → toast「请输入正确的 11 位手机号」；验证码非 6 位 → toast「请输入 6 位验证码」
-（4）校验通过 → 登录成功进入 AI 会话页；此方式不获取、不绑定任何微信信息</t>
+（4）校验通过 → 登录成功进入 AI 会话页；此方式不获取、不绑定任何微信信息
+（5）「0722 修订」发送短信验证码后「获取验证码」进入 60 秒重发倒计时；倒计时结束仍未输入验证码 → 输入框下方出现次级入口「未收到短信验证码？接听语音电话获取」
+（6）「0722 修订」语音验证码兜底交互：点击入口即拨打（不加确认弹窗，点击即同意），入口原地变为状态行「语音电话拨打中 · 来电以 95013 开头，请留意接听」——号段提示在点击瞬间原地出现并在等待期间常驻，避免用户当骚扰电话拒接；60 秒后状态行变为「未接到电话？再次拨打」可重试；语音验证码与短信验证码共用同一校验逻辑。「95013」为原型演示号段，实际外呼号段以短信/语音供应商分配为准，上线前替换文案</t>
         </is>
       </c>
     </row>
@@ -638,24 +641,26 @@
           <t>登录与授权</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>绑定手机号</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>（1）三种来源差异化副标题：登录后引导（绑定后可跨端同步会话与权益）/ 敏感操作门槛（支付下单、兑换码与开通会员需先完成手机号绑定）/ 我的入口（绑定后可使用支付、兑换码与会员等权益）
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>0722周三更新
+（1）三种来源差异化副标题：登录后引导（绑定后可跨端同步会话与权益）/ 敏感操作门槛（支付下单、兑换码与开通会员需先完成手机号绑定）/ 我的入口（绑定后可使用支付、兑换码与会员等权益）
 （2）手机号 + 验证码两输入框（校验同手机号登录）+「获取验证码」
 （3）主按钮文案随来源变（绑定并进入 / 完成绑定）；空值禁用
 （4）绑定成功 → toast「手机号绑定成功」→ 按来源跳转（登录来源进会话页，其余返回上一页）
 （5）绑定/换绑仅需「（新）手机号 + 验证码」，不要求旧手机号双重校验（产品无密码凭证，登录态本身即归属凭证）
-（6）登录来源额外提供「暂不绑定 · 直接进入」可跳过；所有来源都有「手机号已被占用?」入口</t>
+（6）登录来源额外提供「暂不绑定 · 直接进入」可跳过；所有来源都有「手机号已被占用?」入口
+（7）「0722 修订」新增语音验证码兜底（交互同「手机号验证码登录」）：短信发送后 60 秒倒计时结束仍未输入 → 输入框下方出现「未收到短信验证码？接听语音电话获取」，点击即拨打（不加确认弹窗）并原地显示「语音电话拨打中 · 来电以 95013 开头，请留意接听」，60 秒后可「再次拨打」；语音码与短信码同一校验（95013 为演示号段，实际以供应商分配为准）</t>
         </is>
       </c>
     </row>
@@ -763,20 +768,19 @@
           <t>AI 会话</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>KP 前台入口（状态判活）</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>0718周六新增
-（1）0717 #1.3/#1.6：新增统一入口 /kp/:kpId——KP 前台地址直达与知识 KP 二维码扫码（含首扫权益绑定核销）共用，进入时先判 KP 状态
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>（1）0717 #1.3/#1.6：新增统一入口 /kp/:kpId——KP 前台地址直达与知识 KP 二维码扫码（含首扫权益绑定核销）共用，进入时先判 KP 状态
 （2）已发布：过渡提示后进入该 KP 的全新 AI 会话
 （3）草稿（未发布）：与「已删除」同等处理——整屏提示「该知识 KP 已失效，若有问题请联系客服」，停留 3 秒后按跳转规则①处理（草稿未对外发布，前台不区分「未发布」与「已删除」，避免暴露机构未上线内容）
 （4）已下架：整屏提示「该知识 KP 已下架，若有问题请联系客服」，停留 3 秒后按跳转规则①处理
@@ -1180,20 +1184,19 @@
           <t>付费墙与权益</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>开通会员</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>0718周六更新
-（1）0717 二批 #9：两档改为「购买方式即续费语义」，消除「按月自动续费」歧义——① 连续包月（默认选中，角标「首月特惠」）：首月 ¥9.9、次月起 ¥19.9/月 自动续费，卡内说明「自动续费，可随时退订」② 单月（¥19.9 / 1 个月）：一次性购买，卡内说明「到期自动失效，不自动续费不扣款」；选中即表达是否自动续费，不再靠一个含糊的全局勾选
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>（1）0717 二批 #9：两档改为「购买方式即续费语义」，消除「按月自动续费」歧义——① 连续包月（默认选中，角标「首月特惠」）：首月 ¥9.9、次月起 ¥19.9/月 自动续费，卡内说明「自动续费，可随时退订」② 单月（¥19.9 / 1 个月）：一次性购买，卡内说明「到期自动失效，不自动续费不扣款」；选中即表达是否自动续费，不再靠一个含糊的全局勾选
 （2）协议、按钮与底部说明随所选方式联动：连续包月→勾选《自动续费协议》+ 按钮「¥9.9 开通连续包月」+ 底部说明「次月起 ¥19.9/月 自动扣费 · 支持随时退订，到期赠 72 小时会员缓冲使用期」；单月→协议行换成《会员服务协议》（无自动续费协议）+ 按钮「¥19.9 购买单月会员」+ 底部说明「到期自动失效，不会自动扣费」；缓冲期不计入已付费会员时长
 （3）「立即开通」前校验手机号绑定（未绑先引导绑定再继续），通过后按所选方式进微信支付收银台
 （4）「0718 修订」开通会员页按「先权益、再套餐、后协议」重构交互：① 标题下新增三枚权益速览 chip（受限内容全解锁 / 图音视频精讲 / 电话问答·VIP 优先）；② 套餐卡信息层级重排——卡名 + 续费语义 pill（连续包月＝「自动续费 · 可随时取消」琥珀标；单月＝「一次性购买 · 不自动续费」灰标）+ 一行说明 + 右侧大价签；选中态改左侧对勾圆点（琥珀填充）+ 琥珀描边淡底，「首月特惠」角标改琥珀渐变；③ 协议勾选改为真实可点交互（未勾选点按钮 toast 引导先同意协议），连续包月需同意《会员服务协议》《自动续费协议》两份，单月仅《会员服务协议》；④ 按钮与底部说明随所选方式联动（语义与 0717 二批 #9 不变：连续包月＝首月 ¥9.9、次月起 ¥19.9/月 自动续费可退订；单月＝¥19.9 一次性、到期自动失效）
@@ -1304,20 +1307,19 @@
           <t>我的</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>我的永享</t>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>0718周六更新
-（1）已购永享列表，按文件名模糊搜索 + 类型筛选（全部/图片/音频/视频）
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>（1）已购永享列表，按文件名模糊搜索 + 类型筛选（全部/图片/音频/视频）
 （2）网格卡片：封面 + 类型角标 + 名称 +「{类型} · 永久解锁」
 （3）点卡片进多模态预览（顶部固定版权保护文案，不支持保存下载）
 （4）空态「没有匹配的永享内容」
@@ -1338,20 +1340,19 @@
           <t>我的</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
         <is>
           <t>我的纸书</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>0718周六更新
-（1）展示用户所有线下扫码对应的知识 KP（不只首扫绑定的），含已解锁与未解锁
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>（1）展示用户所有线下扫码对应的知识 KP（不只首扫绑定的），含已解锁与未解锁
 （2）卡片：KP 封面 + KP 名（固定两行高）+「扫码解锁 · 时间」（钉在卡片底部对齐）；按 KP 名模糊搜索
 （3）状态区分：顶部筛选 chip（全部 / 已解锁 / 未解锁，与「我的永享」同款 UI，默认「全部」）；首扫绑定的 KP 卡片显「已解锁」标，后扫未获权益不显状态标（界面保持干净）；列表说明文案「首扫永久解锁该 KP 当前及未来新增的全部内容」
 （4）首扫绑定后获得该 KP 级完整阅读权益：当前及未来新增的免费、会员、永享内容均可访问，权益长期归属该用户
@@ -1375,20 +1376,19 @@
           <t>我的</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>我的纸书</t>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>扫一扫</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>0718周六更新
-（1）右上角「扫一扫」入口，点击调起手机相机扫码
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>（1）右上角「扫一扫」入口，点击调起手机相机扫码
 （2）0717 #1.3：扫码统一走「KP 前台入口 /kp/:kpId」判活——toast「已识别知识 KP 二维码」后进入入口页：已发布正常进入全新会话并绑定权益；已下架 / 已删除按入口页失效流程提示并跳转（原型演示按 已发布→已下架→已失效 轮换）。注意用词：兑换码的权益是会员，与 KP 绑定的是「知识 KP 二维码」</t>
         </is>
       </c>
@@ -1522,24 +1522,29 @@
           <t>我的</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>我的订单</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>（1）双维度筛选并存：顶部为「订单类型」Tab（全部 / 会员 / 永享 / 兑换码），其下为「订单状态」chips（全部 / 已支付 / 退款售后）；两维度分层放置，过滤取交集。部分退款、全额退款、退款中统一归入「退款/售后」桶；已支付、兑换码已核销归「已支付」桶。0716 #4：支付成功才落库（中断不生成订单），故无「待支付」态；0716 #5：切到「兑换码」Tab 时隐藏状态 chips（能显示的兑换码必为已核销，无需状态维度）
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>0722周三更新
+（1）「0722 修订」双维度筛选并存：顶部为「订单类型」Tab（全部 / 会员 / 永享 / 兑换码），其下「订单状态」chips 改为 全部 / 待支付 / 已支付 / 已失效 / 退款售后，两维度分层放置、过滤取交集——推翻 0716「支付成功才落库」口径：发起支付即落库为「待支付」；部分退款、全额退款、退款中统一归入「退款/售后」桶；兑换码核销单归入「已支付」分组（行内标签仍显「已核销」；切到「兑换码」Tab 时隐藏状态 chips 的规则不变）
 （2）列表按付款时间降序
-（3）每单展示类型标签 + 标题 + 金额 + 状态 + 时间；仅「永享」订单展示关联 KP + 媒体名
-（4）存在退款时，列表以浅灰退款内容条（奶白暖灰底，弱化不抢视觉）展示逐笔退款进度、金额与时间；单笔退款进度三色语义：退款成功=青绿、退款中=靛蓝、退款失败=珊瑚红
-（5）订单整单状态（部分退款 / 全额退款 / 已核销等）统一中性墨灰呈现，不再各配彩色——状态是信息不是行动点，同屏只保留一处彩色语义（单笔退款进度）
-（6）点击进订单详情</t>
+（3）「0722 修订」待支付订单卡显示「剩余支付时间」倒计时（下单起 30 分钟支付有效期）+「去支付」按钮，可重新调起微信支付；30 分钟未支付微信自动关单转「已失效」
+（4）「0722 修订」待支付 / 已失效订单无付款时间，卡片显示下单时间（其余订单仍显付款时间）
+（5）每单展示类型标签 + 标题 + 金额 + 状态 + 时间；仅「永享」订单展示关联 KP + 媒体名
+（6）存在退款时，列表以浅灰退款内容条（奶白暖灰底，弱化不抢视觉）展示逐笔退款进度、金额与时间；单笔退款进度三色语义：退款成功=青绿、退款中=靛蓝、退款失败=珊瑚红
+（7）订单整单状态（部分退款 / 全额退款 / 已核销等）统一中性墨灰呈现，不再各配彩色——状态是信息不是行动点，同屏只保留一处彩色语义（单笔退款进度）
+（8）点击进订单详情
+（9）「0724 修订」订单状态筛选 chips 单行横向展示、不换行，超出宽度时横向滚动
+（10）「0724 修订」订单详情页待支付倒计时条 / 已失效说明条与基础信息面板同宽对齐</t>
         </is>
       </c>
     </row>
@@ -1554,24 +1559,28 @@
           <t>我的</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>订单详情</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>（1）按类型差异化呈现
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>0722周三更新
+（1）按类型差异化呈现
 （2）会员：基础信息卡（订单编号/支付方式/续费方式 自动续费·手动支付/下单·付款时间）+ 会员权益卡（有效期）
 （3）永享：基础信息卡 + 永享内容卡（整行可点直接预览，无「点击封面预览」文字）
 （4）兑换码：页面标题为「详情」（非订单详情），仅展示 类型=兑换码核销/兑换码/兑换时间 + 兑换权益（权益名 + 会员时间区间），不展示订单编号/支付方式/下单付款时间/金额
 （5）会员/永享订单存在退款时展示退款记录卡（按时间倒序）；同一订单允许多笔部分退款，逐笔展示退款单号、金额、状态、申请与完成时间；卡片标题与首条记录之间不留空白带，退款状态配色与订单列表一致（成功=青绿、退款中=靛蓝、失败=珊瑚红）
-（6）退款权益说明（全额退款仅撤销由该订单单独产生的权益 / 部分退款及其他独立赠送、兑换权益不受影响）由红色警示框改为退款记录卡内底部浅灰小字注释——C 端合规文案弱化呈现，不抢主信息视觉</t>
+（6）退款权益说明（全额退款仅撤销由该订单单独产生的权益 / 部分退款及其他独立赠送、兑换权益不受影响）由红色警示框改为退款记录卡内底部浅灰小字注释——C 端合规文案弱化呈现，不抢主信息视觉
+（7）「0722 修订」待支付订单：详情顶部显「剩余支付时间」倒计时条 +「去支付」按钮，可重新调起微信支付
+（8）「0722 修订」已失效订单：显提示「订单超 30 分钟未支付已自动失效，如需购买请重新下单」
+（9）「0722 修订」未支付订单（待支付 / 已失效）付款时间显「—」，且不渲染会员权益卡（权益未生效不展示）</t>
         </is>
       </c>
     </row>
@@ -1586,22 +1595,24 @@
           <t>我的</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>换绑手机号</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>（1）展示当前手机号（脱敏）+「换绑后用新号码登录」
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t>0722周三更新
+（1）展示当前手机号（脱敏）+「换绑后用新号码登录」
 （2）新手机号 + 验证码两输入框（校验同登录）+「获取验证码」
 （3）「确认换绑」（空值禁用）→ toast「换绑成功」→ 返回
-（4）仅需「新手机号 + 验证码」，不要求旧手机号双重校验</t>
+（4）仅需「新手机号 + 验证码」，不要求旧手机号双重校验
+（5）「0722 修订」新增语音验证码兜底（交互同「手机号验证码登录」）：短信发送后 60 秒倒计时结束仍未输入 → 输入框下方出现「未收到短信验证码？接听语音电话获取」，点击即拨打（不加确认弹窗）并原地显示「语音电话拨打中 · 来电以 95013 开头，请留意接听」，60 秒后可「再次拨打」；语音码与短信码同一校验（95013 为演示号段，实际以供应商分配为准）</t>
         </is>
       </c>
     </row>
@@ -1731,20 +1742,19 @@
           <t>协议与辅助页</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>二维码失效落地页</t>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>0718周六更新
-（1）二维码本身作废时提示「二维码已失效」+「N 秒后自动跳转首页…」；KP 已下架 / 已删除的扫码改走「KP 前台入口 /kp/:kpId」判活流程（提示已下架/已失效并按跳转规则①处理），与二维码作废场景区分
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>（1）二维码本身作废时提示「二维码已失效」+「N 秒后自动跳转首页…」；KP 已下架 / 已删除的扫码改走「KP 前台入口 /kp/:kpId」判活流程（提示已下架/已失效并按跳转规则①处理），与二维码作废场景区分
 （2）3 秒倒计时自动跳首页，另提供「立即前往首页」按钮</t>
         </is>
       </c>
@@ -1879,20 +1889,19 @@
           <t>知识产品 KP</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>KP 列表</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
-        <is>
-          <t>0718周六更新
-（1）卡片网格：封面色块 + KP 名 + 来源标签（自建/共享）+ 状态标签（草稿/已发布/已下架，0717 #2.4 两后台命名统一）+ 实时分享·分享方标（0717 二批 #4：接收方不再单独加标——「共享」来源标签已表达，避免标签堆叠）+ Agent 名 + 文件数/提问数；已删除（逻辑删除）的 KP 不在三端界面展示，数据库保留数据
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>（1）卡片网格：封面色块 + KP 名 + 来源标签（自建/共享）+ 状态标签（草稿/已发布/已下架，0717 #2.4 两后台命名统一）+ 实时分享·分享方标（0717 二批 #4：接收方不再单独加标——「共享」来源标签已表达，避免标签堆叠）+ Agent 名 + 文件数/提问数；已删除（逻辑删除）的 KP 不在三端界面展示，数据库保留数据
 （2）按 KP 名称模糊搜索；筛选 状态（全部/草稿/已发布/已下架）、来源（全部/自建/共享）——已删除 KP 不在列表与筛选中出现
 （3）0717 #2.3：列表与详情同一数据源（点开哪张卡，详情即那条数据：名称/状态/导入方式/业务关系一致）；演示数据覆盖每个状态各至少一条（草稿/已发布/已下架），并含实时分享双视角各一条——分享方（本机构分享出去）与接收方（实时同步导入、只读）
 （4）顶部右侧配额 chip：KP X/Y · 存储 X/Y GB（≥90% 红/≥70% 黄）+ 提示「达上限将无法新建/上传，请联系平台扩容」
@@ -1972,20 +1981,19 @@
           <t>知识产品 KP</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>KP 详情 · 基础信息</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>0718周六更新
-（1）详情头：返回 + KP 名（与列表同源）+ 来源标签 + 状态标签（草稿/已发布/已下架，两后台命名统一）+ 右侧状态操作按钮——0717 #2.1/#2.2：草稿→「发布」、已发布→「下架」、已下架→「重新发布」；删除对草稿/已发布/已下架均可用；操作真实生效（原型内真实改状态，非仅提示）。0717 二批 #2/#4：来源标签统一「自建 / 共享」（详情不再用「共享导入」，与列表一致）；实时同步导入的详情头不再显示「实时同步 · 只读」附加标（顶部只读 banner 已说明）
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>（1）详情头：返回 + KP 名（与列表同源）+ 来源标签 + 状态标签（草稿/已发布/已下架，两后台命名统一）+ 右侧状态操作按钮——0717 #2.1/#2.2：草稿→「发布」、已发布→「下架」、已下架→「重新发布」；删除对草稿/已发布/已下架均可用；操作真实生效（原型内真实改状态，非仅提示）。0717 二批 #2/#4：来源标签统一「自建 / 共享」（详情不再用「共享导入」，与列表一致）；实时同步导入的详情头不再显示「实时同步 · 只读」附加标（顶部只读 banner 已说明）
 （2）「发布」同样走二次确认——弹窗说明「发布后前台立即可见：支持检索、购买、扫码与链接访问；发布需至少一份已向量化完成的知识内容」，确认后状态真实置为已发布并 toast「已发布」
 （3）0717 #1.4：下架＝运营临时禁止访问（处理完问题可随时重新发布）——停止检索、新购买、新扫码与链接访问；C 端「我的纸书」「我的永享」等入口统一显「已下架」、点击提示联系客服、暂不可进入会话/预览；已购权益不清除，重新发布后自动恢复访问
 （4）0717 #1.8：下架确认弹窗结构化——无序列表明示前台影响（我的纸书/我的永享显「已下架」、暂不可进入；已购权益保留、重新发布自动恢复）+ 琥珀提示块说明下架适用于「临时禁止访问、处理完再上架」的运营场景
@@ -2012,20 +2020,19 @@
           <t>知识产品 KP</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>KP 详情 · 知识库</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>0718周六更新
-（1）按文件名搜索 + 类型筛选（全部/文档/图片/音频/视频）
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>（1）按文件名搜索 + 类型筛选（全部/文档/图片/音频/视频）
 （2）提示「上传即向量化，发布知识 KP 需至少一份已向量化完成的知识内容」
 （3）表格列：文件名、类型、预览（图音视缩略图、点击放大）、权益（免费/会员/永享¥X，联动定价与权益）、处理状态、检索状态、操作；操作列随按钮数自适应宽度
 （4）处理状态三态：已向量化 / 向量化中 N%（带进度条）/ 向量化失败（悬浮显原因，如视频超 60 分钟上限）
@@ -2136,20 +2143,19 @@
           <t>知识产品 KP</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>KP 详情 · 定价与权益</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>0718周六新增
-（1）此处设「基础权益」，决定本 KP 非永享内容的门槛：免费 / 会员 二选一互斥单选
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>（1）此处设「基础权益」，决定本 KP 非永享内容的门槛：免费 / 会员 二选一互斥单选
 （2）免费：所有用户均可查看该 KP 全部非永享内容（文字/图片/音频/视频）
 （3）会员：仅会员可查看图/音/视媒体资源，文字内容不受会员身份限制
 （4）0717 #5：免费 / 会员切换点击即生效 → 增加二次确认弹窗（说明切换后果与立即生效），确认后才生效并 toast，避免误操作；实时同步（接收方）视角下单选整体置灰不可切换
@@ -2312,20 +2318,19 @@
           <t>知识产品 KP</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>共享 KP 权限矩阵</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>0718周六更新
-（1）0717 #4：实时同步（接收方 / 消费者视角）只读升级——基础信息表单输入框全部禁用置灰（无光标、hover 显示 not-allowed 禁止态，样式同既有只读输入框先例）、关联 Agent 下拉禁用、定价与权益单选整体置灰不可选；仅「复制链接」可操作；其余操作按钮置灰、点击提示「无权限操作」；二维码、分享两 Tab 隐藏。顶部只读说明 banner 单行呈现，来源机构为动态变量：「本 KP 由「{分享机构名}」以「实时同步」分享导入：内容随源机构自动更新、仅可查看不可编辑；不占本机构 KP 数与存储、问答消耗本机构 Token；二维码与分享不可用。」0717 二批 #5：禁用置灰统一标准＝「前台访问地址」只读框样式（纸白底 + 实线浅边框 + 深灰文字），两后台一致，不再用虚线浅灰底
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>（1）0717 #4：实时同步（接收方 / 消费者视角）只读升级——基础信息表单输入框全部禁用置灰（无光标、hover 显示 not-allowed 禁止态，样式同既有只读输入框先例）、关联 Agent 下拉禁用、定价与权益单选整体置灰不可选；仅「复制链接」可操作；其余操作按钮置灰、点击提示「无权限操作」；二维码、分享两 Tab 隐藏。顶部只读说明 banner 单行呈现，来源机构为动态变量：「本 KP 由「{分享机构名}」以「实时同步」分享导入：内容随源机构自动更新、仅可查看不可编辑；不占本机构 KP 数与存储、问答消耗本机构 Token；二维码与分享不可用。」0717 二批 #5：禁用置灰统一标准＝「前台访问地址」只读框样式（纸白底 + 实线浅边框 + 深灰文字），两后台一致，不再用虚线浅灰底
 （2）独立快照：五个 Tab 均可编辑；基础信息、知识库、定价数据在导入时复制，二维码与分享从消费机构自己的空数据开始
 （3）「0718 修订」实现对齐：实时同步只读表单的禁用输入框底色/边框/文字色已统一为「前台访问地址」只读框同款（纸白 --paper 底 + --line-2 实线浅边框 + --ink-2 深灰文字），修复此前禁用框使用另一套灰底（--surface-warm）造成的两灰并存</t>
         </is>
@@ -2464,23 +2469,26 @@
           <t>订单管理</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>订单列表</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>（1）仅显本机构订单，按付款时间降序
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>0722周三更新
+（1）仅显本机构订单，按付款时间降序
 （2）表格列：订单号、类型、关联知识产品、金额、支付方式、订单状态、退款状态、用户、下单时间、付款时间、兑换时间、操作（操作列固定右侧）
 （3）按 订单号/用户 搜索；筛选 类型、订单状态、退款状态（全部/未退款/退款中/部分退款/全额退款）
 （4）三个独立时间区间筛选（下单时间、支付时间、兑换时间）真实参与列表过滤（不限/近 7 天/30 天/自定义）
-（5）筛选行右侧「导出」：生成「AI问书_{机构名}_订单管理数据导出.xlsx」，严格沿用搜索、类型、状态、退款状态及三个时间区间筛选；文件头部注明导出时间与全部筛选条件</t>
+（5）筛选行右侧「导出」：生成「AI问书_{机构名}_订单管理数据导出.xlsx」，严格沿用搜索、类型、状态、退款状态及三个时间区间筛选；文件头部注明导出时间与全部筛选条件
+（6）「0722 修订」订单状态筛选改为 全部 / 待支付 / 已支付 / 已核销 / 已失效（退款状态筛选维度不变）；状态色：待支付＝橙、已失效＝灰；付款时间为空（待支付 / 已失效）显「—」
+（7）「0722 修订」订单状态口径（三端统一，推翻 0716「支付成功才落库」）：用户发起支付即落库为「待支付」（微信 trade_state=NOTPAY），微信下单传 time_expire、30 分钟未支付微信自动关单（CLOSED）转「已失效」，无需自建定时器；网页支付（JSAPI/H5）不存在「支付失败」终态，用户余额不足、风控拦截等失败场景订单停留「待支付」可换方式重试；「已核销」为兑换码订单专属（无支付环节）；退款/售后走独立退款单与退款状态维度，与订单状态解耦；GMV、付费用户等营收指标仅计「已支付」订单（待支付 / 已失效不计入，相关指标 tooltip 注明）</t>
         </is>
       </c>
     </row>
@@ -2495,24 +2503,26 @@
           <t>订单管理</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>订单列表</t>
         </is>
       </c>
-      <c r="D67" s="3" t="inlineStr">
+      <c r="D67" s="5" t="inlineStr">
         <is>
           <t>发起退款</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>（1）退款入口仅在可退款时显示（金额&gt;0 且退款状态不在「退款中/全额退款」）
-（2）退款金额弹窗：订单号 + 订单实付（已退&gt;0 时显「已退 ¥X · 可退 ¥Y」）+ 退款金额（默认填可退余额）+ 说明「支持部分退款 / 确认后原路退回，不可撤销」
-（3）校验：金额≤0 → toast「请输入退款金额」；超可退余额 → toast「退款金额不能超过可退余额 ¥X」
-（4）二次确认：展示发起人、退款对象（昵称+手机号）、订单号、退款金额、资金路径「原路退回客户原支付账户」
-（5）全额退款仅撤销由该订单产生的会员/永享权益；部分退款不撤销。若用户还拥有兑换码、纸书、人工授予或其他订单等独立权益来源，不得连带撤销
-（6）确认 → 状态置「退款中」+ 写时间线 + toast「退款处理中 · 资金将原路退回」→ 模拟成功后按累计已退判定「全额退款/部分退款」+ 追加时间线 + toast「退款成功 · 资金已原路退回」（退款状态在订单列表/订单详情/用户详情跨页共享）</t>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>0722周三更新
+（1）退款入口仅在可退款时显示（金额&gt;0 且退款状态不在「退款中/全额退款」）
+（2）「0722 修订」退款操作仅对「已支付」订单出现：待支付、已失效、兑换码已核销订单无退款入口
+（3）退款金额弹窗：订单号 + 订单实付（已退&gt;0 时显「已退 ¥X · 可退 ¥Y」）+ 退款金额（默认填可退余额）+ 说明「支持部分退款 / 确认后原路退回，不可撤销」
+（4）校验：金额≤0 → toast「请输入退款金额」；超可退余额 → toast「退款金额不能超过可退余额 ¥X」
+（5）二次确认：展示发起人、退款对象（昵称+手机号）、订单号、退款金额、资金路径「原路退回客户原支付账户」
+（6）全额退款仅撤销由该订单产生的会员/永享权益；部分退款不撤销。若用户还拥有兑换码、纸书、人工授予或其他订单等独立权益来源，不得连带撤销
+（7）确认 → 状态置「退款中」+ 写时间线 + toast「退款处理中 · 资金将原路退回」→ 模拟成功后按累计已退判定「全额退款/部分退款」+ 追加时间线 + toast「退款成功 · 资金已原路退回」（退款状态在订单列表/订单详情/用户详情跨页共享）</t>
         </is>
       </c>
     </row>
@@ -2658,25 +2668,27 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>0718周六更新
-（1）0717 二批 #8：页面自上而下——① 用户留存（页级常驻，一行三张等宽指标卡，卡片式回归、与平台整体风格一致）② 区间分析条（轻量样式：左标题 + 右时间筛选，去掉白底 / 灰框容器）③ 四个主题 Tab（用户分析/提问分析/营收分析/热门 KP）。活跃概览移入「用户分析」Tab 并改为随区间联动的周期统计（口径修订，原「固定窗口快照」弃用）。页头只保留「导出」，导出生成「AI问书_{机构名}_数据看板数据导出.xlsx」，七个 Sheet 全量覆盖页面内容（活跃概览按当前所选区间导出）；头部注明导出时间、所选区间起止与口径
-（2）时间口径收敛为两类：用户留存＝按注册时间（独立筛选、不受区间影响，活跃口径＝注册后第 N 天发生登录或提问行为，完整公式在卡面口径问号内）；其余指标（含活跃概览）＝随「区间分析」时间筛选联动并环比。0717 二批 #8.3：删除留存段底部「数据更新至 …」脚注，界面不再显示
-（3）0717 二批 #8.2/#8.4：活跃概览（日活 / 周活 / 月活）一行三卡置于用户分析 Tab 顶部——数值随所选区间联动（区间内日均去重口径），并与上一等长周期环比（KPI 卡同款 Delta + 对比窗口）
-（4）② 用户留存（标「按注册时间」，页级常驻段，位于实时概览右侧）：口径即注册日，「注册批次」更名「注册时间」便于理解；口径问号 InfoDot 紧跟「用户留存」标题之后；常驻说明「观察注册用户在第 1 / 7 / 30 天是否仍然活跃，不受区间筛选影响」；右侧「注册时间：最新可统计 ▼」下拉（选项：最新可统计 / 近 7 个注册日 / 近 30 个注册日 / 自定义日期）；选「自定义日期」弹单日日历面板（视觉同区间选择器的自定义日历，但只选具体某一天，因留存按单个注册日观察）。0717 #8：选定具体日期后回显在下拉触发器上（如「注册时间：2026-06-30」），不再停留显示「自定义日期」字样
+          <t>0722周三更新
+（1）0717 二批 #8：页面自上而下——① 活跃概览（0724 修订：页级常驻，居用户留存上方，固定滚动窗口实时快照，见下）② 用户留存（页级常驻，一行三张等宽指标卡，卡片式回归、与平台整体风格一致）③ 区间分析条（轻量样式：左标题 + 右时间筛选，去掉白底 / 灰框容器）④ 四个主题 Tab（用户分析/提问分析/营收分析/热门 KP）。页头只保留「导出」，导出生成「AI问书_{机构名}_数据看板数据导出.xlsx」，七个 Sheet 全量覆盖页面内容（活跃概览按固定滚动窗口快照口径导出）；头部注明导出时间、所选区间起止与口径
+（2）时间口径收敛为两类：用户留存＝按注册时间（独立筛选、不受区间影响，活跃口径＝注册后第 N 天发生登录或提问行为，完整公式在卡面口径问号内）；其余指标＝随「区间分析」时间筛选联动并环比（活跃概览除外，0724 修订为固定滚动窗口实时快照）。0717 二批 #8.3：删除留存段底部「数据更新至 …」脚注，界面不再显示
+（3）0717 二批 #8.2/#8.4：活跃概览（日活 / 周活 / 月活）一行三卡，与对应对比窗口环比（KPI 卡同款 Delta + 对比窗口）；位置与统计口径按 0724 修订执行（页级常驻居用户留存上方、固定滚动窗口实时快照，见下）
+（4）② 用户留存（标「按注册时间」，页级常驻段，位于活跃概览下方）：口径即注册日，「注册批次」更名「注册时间」便于理解；口径问号 InfoDot 紧跟「用户留存」标题之后；常驻说明「观察注册用户在第 1 / 7 / 30 天是否仍然活跃，不受区间筛选影响」；右侧「注册时间：最新可统计 ▼」下拉（选项：最新可统计 / 自定义日期，0724 修订精简）；选「自定义日期」弹单日日历面板（视觉同区间选择器的自定义日历，但只选具体某一天，因留存按单个注册日观察）。0717 #8：选定具体日期后回显在下拉触发器上（如「注册时间：2026-06-30」），不再停留显示「自定义日期」字样
 （5）0717 二批 #8.1：用户留存回归一行三张等宽指标卡（D+1 次日 / D+7 7日 / D+30 30日，卡片式、平台风格统一）——标题行左＝节点名 + 口径问号，右＝状态标（已可统计 / 待成熟）；卡身留存率大数字；底部单行灰字「样本 N 人 · 统计至 {日期}注册用户」——不同观察天数对应的成熟样本范围可不同，不再共用一个笼统样本数
 （6）未成熟节点不再显示易被误读为 0% 的空进度条或「—」，改为中性灰状态文案：「尚未到统计时间」+「该批用户最早于 {日期} 产生 {N}日留存」；状态用文字表达、不只依赖颜色
 （7）③ 区间分析（随顶部今日/7日/30日/自定义联动）：时间筛选置于本段标题右侧，仅控制新增用户、来源 / 地区 / 性别等区间指标；因留存已移出本段，删除原「留存率除外」例外说明
 （8）0717 二批 #6：撤销区间分析条与主题 Tab 的吸顶固定交互（回归普通文档流）
 （9）KPI 卡环比行呈现：方向箭头 + 百分比 +「较上一周期」为第一行，「对比 {区间}」为第二行（避免今日档长文案被卡片截断）；三端主控台 / 数据看板同源一致
-（10）0717 二批 #8.4：用户分析 Tab 三行布局——第一行 日活｜周活｜月活（一行三卡，区间联动 + 环比）；第二行 新增用户与来源分布同行：新增用户卡左＝大数字 + 环比 +「对比 {区间}」，右＝随区间联动的迷你趋势折线（周期 UI 参考提问分析「总提问」）；来源分布环形图图例补充人数（如「扫码进入 · 68%（216 人）」）并展示占比环比「较上一周期」（0717 二批 #7）；第三行 地区分布与性别分布同行（女/男/未知，微信授权带回）
-（11）「0718 修订」留存「注册时间」筛选由白色下拉改为与「区间分析」同款灰底分段控件（最新可统计 / 近 7 个注册日 / 近 30 个注册日 / 自定义），自定义经单日日历选定具体注册日后以 chip 回显日期、可点 ✕ 回到「最新可统计」；两区筛选视觉统一，不再出现孤立白框
+（10）0717 二批 #8.4：用户分析 Tab 两行布局（0724 修订：活跃概览移出本 Tab）——第一行 新增用户与来源分布同行：新增用户卡左＝大数字 + 环比 +「对比 {区间}」，右＝随区间联动的迷你趋势折线（周期 UI 参考提问分析「总提问」）；来源分布环形图图例补充人数（如「扫码进入 · 68%（216 人）」）并展示占比环比「较上一周期」（0717 二批 #7）；第二行 地区分布与性别分布同行（女/男/未知，微信授权带回）
+（11）「0718 修订」留存「注册时间」筛选由白色下拉改为与「区间分析」同款灰底分段控件（最新可统计 / 自定义，0724 修订精简），自定义经单日日历选定具体注册日后以 chip 回显日期、可点 ✕ 回到「最新可统计」；两区筛选视觉统一，不再出现孤立白框
 （12）「0718 修订」留存数据改为按真实日期联动推算：选某个注册日 D 时，D+N 节点在「D+N ≤ 今天」时可统计（截止文案＝「统计 {D}注册用户」），否则为「待成熟」（预计可统计日期＝D+N）；修复此前自定义日期档写死 6月30日、与所选注册日脱节的假数据问题
 （13）「0718 修订」四个主题 Tab 切换时内容区保留历史最大高度（min-height 自适应），切回较矮 Tab 页面不再整体回缩跳动；区间切换同理
 （14）「0718 修订」来源分布环比文案与其他指标统一为「↑x.x% 较上一周期」——去掉「pp」字样与「扫码占比」前缀（口径不变，仍为占比的百分点差，见附表一）
 （15）「0718 修订」自定义注册日的日期回显 chip 移到分段控件左侧（与下方「区间分析」RangePicker 的自定义回显位置一致），不再挂在控件右侧
 （16）「0718 修订」留存卡截止文案改白话（原「统计至 {日期}注册用户」不易懂）——可统计节点显示「统计 {注册日}注册的 {样本} 人 · {次日/第 7 天/第 30 天}是否回来」，待成熟节点显示「{注册日}注册的用户 · 等满 {N} 天（{日期}）后可统计」；不懂数据的人也能一眼看懂「统计的是哪天注册的人、在看他们哪天回不回来」
 （17）「0718 修订」四个主题 Tab 支持地址栏 ?tab=N（0=用户分析 / 1=提问分析 / 2=营收分析 / 3=热门 KP）直达，便于评审与验收直接跳到指定主题；越界值回落第一个 Tab
-（18）「0718 修订」自定义单注册日批次的三个留存节点共用同一样本人数（同一批注册用户、分母相同）；样本随节点递减仅保留在「最新可统计 / 近 N 个注册日」等多天批次（不同节点的成熟截止日不同、对应不同注册人群）——修复单注册日批次节点样本不一致造成的误解</t>
+（18）「0718 修订」自定义单注册日批次的三个留存节点共用同一样本人数（同一批注册用户、分母相同）；样本随节点递减仅保留在「最新可统计」档（不同节点的成熟截止日不同、对应不同注册人群）——修复单注册日批次节点样本不一致造成的误解
+（19）「0724 修订」活跃概览（日活 / 周活 / 月活）改为固定滚动窗口实时快照、不随右侧区间筛选联动（替换 0717「随区间联动」口径）：日活＝今日 00:00 至当前时刻的去重活跃用户（实时），环比对比昨日同时段（卡片显示「对比昨日 00:00-HH:MM」）；周活＝近 7 日滚动窗口去重活跃用户，环比上一个 7 日窗口；月活＝近 30 日滚动窗口去重活跃用户，环比上一个 30 日窗口；三卡整体从「用户分析」Tab 移出，置于页面顶部、「用户留存」区块上方，与留存同为页级常驻区块，区块标题「活跃概览 · 实时滚动窗口快照 · 不随下方时间筛选联动」；用户分析 Tab 内变两行：新增用户+来源分布 / 地区+性别
+（20）「0724 修订」用户留存「注册时间」筛选精简为 最新可统计 / 自定义日期 两档，删除「近 7 个注册日 / 近 30 个注册日」两档；自定义日期仍经单日日历选定具体注册日</t>
         </is>
       </c>
     </row>
@@ -2721,21 +2733,24 @@
           <t>数据看板</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>营收分析 Tab</t>
         </is>
       </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>（1）小节① 收入与转化（5 KPI）：区间 GMV、付费用户、付费转化率、ARPPU、续费率
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>0722周三更新
+（1）小节① 收入与转化（5 KPI）：区间 GMV、付费用户、付费转化率、ARPPU、续费率
 （2）小节② 退款（4 KPI）：退款金额、退款率、退款订单数、净 GMV（扣退款）
-（3）小节③ 转化漏斗（3 卡）：受限内容触发率、会员漏斗（看到会员页→点击购买→完成支付）、永享转化（触发永享墙→完成购买）</t>
+（3）小节③ 转化漏斗（3 卡）：受限内容触发率、会员漏斗（看到会员页→点击购买→完成支付）、永享转化（触发永享墙→完成购买）
+（4）「0722 修订」小节①新增第 6 个 KPI「回流会员」（区间内开通会员、且开通时会员状态为已过期的用户数；不算新增、不算续费），KPI 行改为 3 列两行
+（5）「0722 修订」「新增会员」口径定稿＝区间内历史首次开通会员的用户数（续费、回流均不计入），两后台统一；新增 / 续费 / 回流三者互斥，任一次开通行为只落入其中一类</t>
         </is>
       </c>
     </row>
@@ -2790,11 +2805,13 @@
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>0718周六更新
-（1）指标按统计口径分三类（0717 二批 #8.2：数据看板内的日活 / 周活 / 月活由固定窗口快照改为区间联动统计）：① 实时快照——累计 / 存量，如主控台累计 GMV、当前会员、KP 占用，截至当前的实时值、不参与环比；② 区间统计——随今日 / 7 日 / 30 日联动并与上一等长周期环比，如日活 / 周活 / 月活、新增用户、区间 GMV、区间提问、付费转化；③ 成熟 cohort——留存率，独立队列口径、不跟随全局筛选。① 归「实时」分区、② 归「区间 / 经营分析」分区、③ 用独立队列筛选
+          <t>0722周三更新
+（1）指标按统计口径分三类（0724 修订：日活 / 周活 / 月活为固定滚动窗口实时快照、各自与上一等长窗口环比，不归区间统计）：① 实时快照——累计 / 存量，如主控台累计 GMV、当前会员、KP 占用，截至当前的实时值、不参与环比；② 区间统计——随今日 / 7 日 / 30 日联动并与上一等长周期环比，如新增用户、区间 GMV、区间提问、付费转化；③ 成熟 cohort——留存率，独立队列口径、不跟随全局筛选。① 归「实时」分区、② 归「区间 / 经营分析」分区、③ 用独立队列筛选
 （2）每个指标悬浮面板统一写清：指标定义、分子/分母、去重主键、时区、统计周期、上一周期与差值单位；累计/快照指标明确标注“不参与环比”
 （3）今日 00:00–当前时刻对比昨日相同经过时长；近7/30天及自定义区间对比紧邻的上一等长区间；计数/金额用相对百分比，率类用百分点，时长用绝对差
-（4）上一周期为0时不计算无穷增幅，统一显示“上期为0，暂无可比增幅”；趋势按精确去重数据计算，不再使用0.62/0.42等估算系数；今日趋势按小时</t>
+（4）上一周期为0时不计算无穷增幅，统一显示“上期为0，暂无可比增幅”；趋势按精确去重数据计算，不再使用0.62/0.42等估算系数；今日趋势按小时
+（5）「0722 修订」统一去重规则并全量落 tooltip：规模指标按用户去重——区间内按用户 ID 精确去重，同一用户跨天重复只计 1 人（活跃用户、新增 C 端、付费用户、提问用户等）；强度指标按人天——用户 × 自然日累加（日均活跃 DAU 均值、人均提问等）；两后台所有涉去重指标的悬浮口径均标注所属类别与去重口径。例：某用户 7 天区间内第 1、2 天活跃——「活跃用户」计 1 人，「日均活跃」贡献 2 个人天
+（6）「0724 修订」悬浮 tooltip 去重规则表述统一：去重规则不再混在指标定义句中，tooltip 内独立成条「· 去重：xxxx」；逐指标去重口径见附表一 / 附表二新增的「去重规则」列</t>
         </is>
       </c>
     </row>
@@ -2898,20 +2915,19 @@
           <t>系统配置</t>
         </is>
       </c>
-      <c r="C80" s="5" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>AI 会员价格</t>
         </is>
       </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="6" t="inlineStr">
-        <is>
-          <t>0718周六更新
-（1）「0718 修订」价格配置按两种购买方式分组展示，向运营明示每档金额——① 连续包月（自动续费）：首月价格（首月特惠，默认 ¥9.9，仅首次开通的首月扣款）+ 次月起价格（默认 ¥19.9/月，第 2 个月起每月自动扣款）；② 单月（一次性购买 · 不自动续费）：单月价格（默认 ¥19.9/1 个月，一次性扣款、到期自动失效不再扣费）；每档附前台展示位置说明，与前台「开通会员」两档一一对应
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>（1）「0718 修订」价格配置按两种购买方式分组展示，向运营明示每档金额——① 连续包月（自动续费）：首月价格（首月特惠，默认 ¥9.9，仅首次开通的首月扣款）+ 次月起价格（默认 ¥19.9/月，第 2 个月起每月自动扣款）；② 单月（一次性购买 · 不自动续费）：单月价格（默认 ¥19.9/1 个月，一次性扣款、到期自动失效不再扣费）；每档附前台展示位置说明，与前台「开通会员」两档一一对应
 （2）续费规则只读：「按月自动续费，会员到期后 72 小时为服务缓冲期 · 暂不可编辑」
 （3）0717 #7：「调价须知」标题与文案同一行、以「：」衔接——「调价须知：会员价一经确定，非必要请勿修改；已开通自动续费的用户，下一扣费周期将按修改后的价格扣款。」（amber 淡底左边线警示块）
 （4）「保存」→ toast「已保存价格」
@@ -2933,20 +2949,19 @@
           <t>系统配置</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>回答策略</t>
         </is>
       </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>0718周六更新
-（1）副标题「知识库未检索到相关知识时」三选一
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>（1）副标题「知识库未检索到相关知识时」三选一
 （2）严谨模式：仅用知识库，未命中回「暂无相关资料」（医疗/合规场景）
 （3）透明兜底（默认）：大模型补充并标注「此为大模型生成、非知识库」
 （4）流畅模式：大模型直接补充，不标注来源
@@ -3106,23 +3121,25 @@
           <t>登录与主控台</t>
         </is>
       </c>
-      <c r="C87" s="3" t="inlineStr">
+      <c r="C87" s="5" t="inlineStr">
         <is>
           <t>主控台</t>
         </is>
       </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>（1）页头机构筛选覆盖全部机构（来自机构主数据，非固定名单）；父机构选项带「父机构」标签；选中父机构＝自动汇总该父机构自身及其全部子机构数据，并在页头下方标注「含子机构：A、B」，让看数人明确汇总范围
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>0722周三更新
+（1）页头机构筛选覆盖全部机构（来自机构主数据，非固定名单）；父机构选项带「父机构」标签；选中父机构＝自动汇总该父机构自身及其全部子机构数据，并在页头下方标注「含子机构：A、B」，让看数人明确汇总范围
 （2）右侧「导出」：生成「AI问书_全域主控台数据导出.xlsx」，沿用当前机构范围与时间筛选；实时/经营分析两 Sheet 分别标注实时统计时间与区间起止，指标全量含环比
 （3）实时总览（标「实时」，不随时间变）：入驻机构数、累计用户、累计 GMV（资金 100% 进各机构账户）、净 GMV（扣退款，平台不参与分账）、提问总量，每卡带 InfoDot
 （4）经营分析周期与机构后台同口径；每个指标悬浮面板详细展示定义、周期、上一周期、差值单位、零基线处理和是否汇总下级机构
-（5）平台提问量趋势面积图 + 页脚单位规范</t>
+（5）平台提问量趋势面积图 + 页脚单位规范
+（6）「0722 修订」经营分析新增「续费率」（区间内到期且完成续费的会员数 ÷ 同区间到期会员数）与「回流会员」（区间内开通会员、且开通时会员状态为已过期的用户数，不算新增不算续费），KPI 行改为 3 列两行；「新增会员」口径定稿＝区间内历史首次开通会员（续费、回流均不计入），新增 / 续费 / 回流三者互斥、与机构后台统一</t>
         </is>
       </c>
     </row>
@@ -3462,20 +3479,24 @@
           <t>机构管理</t>
         </is>
       </c>
-      <c r="C99" s="3" t="inlineStr">
+      <c r="C99" s="5" t="inlineStr">
         <is>
           <t>机构详情 · 机构配置</t>
         </is>
       </c>
-      <c r="D99" s="3" t="inlineStr">
+      <c r="D99" s="5" t="inlineStr">
         <is>
           <t>微信配置</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>（1）微信公众号字段改为“网页授权回调地址”，微信开放平台字段改为“授权回调地址”；均填写完整 URL，并继续校验与微信后台配置一致
-（2）微信支付（必填，用于支付/退款/自动续费，未配置前台无法下单）：商户号 MchID、APIv3 密钥（掩码）、商户证书（上传 apiclient_cert.pem）；限制说明（商户号须与公众号 AppID 关联绑定/需上传证书且 APIv3 密钥在商户平台设置/退款·自动续费依赖支付能力）；保存 toast「已保存微信支付配置」</t>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>0722周三更新
+（1）微信公众号字段改为“网页授权回调地址”，微信开放平台字段改为“授权回调地址”；均填写完整 URL，并继续校验与微信后台配置一致
+（2）微信支付（必填，用于支付/退款/自动续费，未配置前台无法下单）：商户号 MchID、APIv3 密钥（掩码）、商户证书（上传 apiclient_cert.pem）；限制说明（商户号须与公众号 AppID 关联绑定/需上传证书且 APIv3 密钥在商户平台设置/退款·自动续费依赖支付能力）；保存 toast「已保存微信支付配置」
+（3）「0722 修订」微信公众号卡片新增「网页授权域名校验文件」上传（MP_verify_xxx.txt，公众号后台生成，需放置于网页授权域名根目录下）
+（4）「0722 修订」校验文件归属结论：域名校验文件属公众平台（公众号后台）要求，用于「网页授权域名 / JS 接口安全域名 / 业务域名」校验；微信开放平台的网站应用（扫码登录）不需要校验文件——故上传入口放「微信公众号」卡片，开放平台卡片不变
+（5）「0722 修订」微信支付卡片新增「商户 API 私钥」上传（apiclient_key.pem，与商户证书 apiclient_cert.pem 成对，调用微信支付 APIv3 接口签名必需）</t>
         </is>
       </c>
     </row>
@@ -3490,25 +3511,28 @@
           <t>机构管理</t>
         </is>
       </c>
-      <c r="C100" s="3" t="inlineStr">
+      <c r="C100" s="5" t="inlineStr">
         <is>
           <t>机构详情 · 用量看板</t>
         </is>
       </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>（1）当前生效订阅卡置于时间筛选上方，归入“实时订阅与资源占用”；KP/存储显示占用量，Token 显示当前订阅周期消耗量，不随时间筛选变化
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>0722周三更新
+（1）当前生效订阅卡置于时间筛选上方，归入“实时订阅与资源占用”；KP/存储显示占用量，Token 显示当前订阅周期消耗量，不随时间筛选变化
 （2）页面明确拆分“实时存量”和“区间运营分析”；今日/近7天/近30天/自定义仅联动活跃、新增、提问、GMV、付费用户及 LLM 区间消耗
 （3）配额阈值预警条：「Token 已用 X%，已于 日期 向机构联系人（姓名·手机号）发送 70%/80% 预警短信；达 90%/95% 将再次提醒。配额可在『订阅配额』调整」
 （4）阈值预警短信触达规则与文案模版：触发档位＝本订阅周期 Token 消耗率达 70% / 80% / 90% / 95% 四档，每档首次达到时向机构联系人手机号各发一次，同一计费周期内同档不重复、进入下一周期归零重置；四档共用一条参数化模版，签名用平台方「【AI问书】」（区别于 C 端验证码短信用机构名签名）。文案：【AI问书】您的机构「${orgName}」本订阅周期 Token 用量已达 ${pct}%，达上限后 C 端问答将被暂停，请及时登录机构后台「订阅配额」扩容或联系客服。如已处理请忽略本短信。（${orgName}=机构名，${pct}=当前消耗率）
-（5）4 张 UsageCard 按两段划分（每指标带 InfoDot 口径）：【实时存量】内容存量（KP 当前占用 / 已发布·草稿·已下架 / 存储当前占用）、用户存量（累计 C 端 / 当前会员）；【区间运营分析】活跃与内容使用（活跃用户 / 新增 C 端 / 区间提问）、商业化与 LLM 消耗（区间 GMV / 付费用户 / Token 消耗量 / 调用次数 / 平均响应）
-（6）0716 #13：UsageCard 指标数值与后面的对比周期时间（如「对比 07-03~07-09」）之间增加水平间距，避免过于紧凑
-（7）「内容存量」「用户存量」卡片标题去掉括号内「实时快照」字样——实时口径已由所在「实时订阅与资源占用」分区标题统一说明，不逐卡重复</t>
+（5）「0722 修订」UsageCard 按两段四卡划分（每指标带 InfoDot 口径）：【实时存量】用户与营收存量（原「用户存量」卡更名：累计 C 端 / 当前会员 / 累计 GMV）；【区间运营分析】活跃与内容使用（活跃用户 / 新增 C 端 / 区间提问）、商业化（区间 GMV / 净 GMV(扣退款) / 付费用户 / 付费转化率 / 永享订单 / 退款金额 / 退款率，横跨整行）、LLM 消耗（Token 消耗量 / 调用次数 / 平均响应）——原「商业化与 LLM 消耗」一张卡拆为两张
+（6）「0724 修订」内容存量板块（KP 当前占用 / KP 状态分布 已发布·草稿·已下架 / 存储当前占用）整体从用量看板移除；【实时存量】仅保留「用户与营收存量」一张卡，KP 与存储占用在页面顶部「当前生效订阅卡」查看
+（7）「0722 修订」「累计 GMV」＝机构开通至今全部已支付订单总额（含已产生退款的部分），存量口径、不随区间筛选变化，故放实时板块；放置原则：区间板块放「流量」指标（该时间段内发生的量，随时间筛选联动），实时板块放「存量」指标（当前 / 累计快照）——避免「选了近 7 天却显示累计值」的口径混乱；指标口径与机构后台数据看板、附表二三方一致
+（8）0716 #13：UsageCard 指标数值与后面的对比周期时间（如「对比 07-03~07-09」）之间增加水平间距，避免过于紧凑
+（9）「用户与营收存量」卡片标题不带括号「实时快照」字样——实时口径已由所在「实时订阅与资源占用」分区标题统一说明，不逐卡重复</t>
         </is>
       </c>
     </row>
@@ -3698,20 +3722,19 @@
           <t>全域知识产品 KP</t>
         </is>
       </c>
-      <c r="C107" s="5" t="inlineStr">
+      <c r="C107" s="3" t="inlineStr">
         <is>
           <t>全域 KP 列表</t>
         </is>
       </c>
-      <c r="D107" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E107" s="6" t="inlineStr">
-        <is>
-          <t>0718周六更新
-（1）卡片网格（复用机构后台 KP 卡视觉），平台只读监管
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>（1）卡片网格（复用机构后台 KP 卡视觉），平台只读监管
 （2）每卡：封面 + KP 名 +「机构 · {orgName}」（平台视角必显）+ 状态标签（已发布/草稿/已下架）+ 永享标
 （3）按 KP 名称搜索；筛选 机构、状态
 （4）筛选行右侧新增「导出」：生成「AI问书_全域知识产品数据导出.xlsx」，沿用 KP 名称搜索与机构、状态筛选，列含 KP ID/名称/机构/状态/永享标/权益/创建时间等；头部注明导出时间与筛选条件
@@ -3732,20 +3755,19 @@
           <t>全域知识产品 KP</t>
         </is>
       </c>
-      <c r="C108" s="5" t="inlineStr">
+      <c r="C108" s="3" t="inlineStr">
         <is>
           <t>全域 KP 详情（5 Tab，与机构后台同构）</t>
         </is>
       </c>
-      <c r="D108" s="5" t="inlineStr">
+      <c r="D108" s="3" t="inlineStr">
         <is>
           <t>基础信息</t>
         </is>
       </c>
-      <c r="E108" s="6" t="inlineStr">
-        <is>
-          <t>0718周六更新
-（1）与机构后台 KP 详情·基础信息一致：封面（裁剪）+ KP 名称（必填）/简介/纸书购买链接/关联 Agent（必填）+ 保存
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>（1）与机构后台 KP 详情·基础信息一致：封面（裁剪）+ KP 名称（必填）/简介/纸书购买链接/关联 Agent（必填）+ 保存
 （2）前台访问地址：只读展示 + 「复制链接」一键复制 C 端前台访问地址（随当前环境自动生成，携带机构 + KP），同机构后台
 （3）头部状态操作与机构后台一致：草稿→「发布」、已发布→「下架」、已下架→「重新发布」+「删除」（逻辑删除，删除后回全域 KP 列表）
 （4）「0718 修订」详情头来源标签与机构后台统一三态灰色；平台超管查看「分享导入·实时」的 KP 时不套用接收方只读——保留发布/下架/删除等监管操作，仅以来源标签提示该 KP 为实时导入</t>
@@ -3791,20 +3813,19 @@
           <t>全域知识产品 KP</t>
         </is>
       </c>
-      <c r="C110" s="5" t="inlineStr">
+      <c r="C110" s="3" t="inlineStr">
         <is>
           <t>全域 KP 详情（5 Tab，与机构后台同构）</t>
         </is>
       </c>
-      <c r="D110" s="5" t="inlineStr">
+      <c r="D110" s="3" t="inlineStr">
         <is>
           <t>定价与权益</t>
         </is>
       </c>
-      <c r="E110" s="6" t="inlineStr">
-        <is>
-          <t>0718周六更新
-（1）与机构后台一致：免费/会员 二选一互斥（0717 #5 切换前二次确认）；永享与会员两套独立权益（设了永享价的资源会员也需单独购买）</t>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>（1）与机构后台一致：免费/会员 二选一互斥（0717 #5 切换前二次确认）；永享与会员两套独立权益（设了永享价的资源会员也需单独购买）</t>
         </is>
       </c>
     </row>
@@ -3990,22 +4011,24 @@
           <t>全域订单</t>
         </is>
       </c>
-      <c r="C117" s="3" t="inlineStr">
+      <c r="C117" s="5" t="inlineStr">
         <is>
           <t>全域订单列表</t>
         </is>
       </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>（1）C 端订单（终端用户→机构），复用订单字段，多「机构」列与筛选——「归属机构」列名统一为「机构」
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>0722周三更新
+（1）C 端订单（终端用户→机构），复用订单字段，多「机构」列与筛选——「归属机构」列名统一为「机构」
 （2）表格列：订单号、机构、类型、关联知识产品、金额、支付方式、订单状态、退款状态、用户、下单时间、付款时间、兑换时间、操作（详情）
 （3）按微信号/手机号/订单号搜索；平台侧用户手机号完整展示；筛选 机构/类型/订单状态/退款状态；时间筛选与机构后台订单一致——搜索与筛选行下方三个独立时间区间（下单/支付/兑换时间），真实参与过滤
-（4）「导出」按钮位于筛选行右侧（与筛选条件同行，不在页头）：生成「AI问书_全域订单数据导出.xlsx」，沿用全部筛选与三个时间区间；头部注明导出时间与筛选条件</t>
+（4）「导出」按钮位于筛选行右侧（与筛选条件同行，不在页头）：生成「AI问书_全域订单数据导出.xlsx」，沿用全部筛选与三个时间区间；头部注明导出时间与筛选条件
+（5）「0722 修订」订单状态筛选改为 全部 / 待支付 / 已支付 / 已核销 / 已失效（与机构后台一致，退款状态筛选维度不变）；状态色 待支付＝橙、已失效＝灰；付款时间为空（待支付 / 已失效）显「—」；退款操作仅存在于「已支付」订单（平台侧仍只读、无退款入口）；GMV 等营收指标仅计「已支付」订单</t>
         </is>
       </c>
     </row>
@@ -4623,13 +4646,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4650,6 +4674,11 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>去重规则（0724 新增列）</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>业务意义</t>
         </is>
       </c>
@@ -4672,6 +4701,11 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
           <t>避免把存量规模误读为区间增长</t>
         </is>
       </c>
@@ -4694,6 +4728,11 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
           <t>保证比较窗口等长</t>
         </is>
       </c>
@@ -4716,6 +4755,11 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
           <t>统一环比边界</t>
         </is>
       </c>
@@ -4738,6 +4782,11 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
           <t>衡量相对变化</t>
         </is>
       </c>
@@ -4760,6 +4809,11 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
           <t>避免不同量纲混用</t>
         </is>
       </c>
@@ -4782,6 +4836,11 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
           <t>避免误导</t>
         </is>
       </c>
@@ -4804,6 +4863,11 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
           <t>避免用户对 pp 单位困惑</t>
         </is>
       </c>
@@ -4826,6 +4890,11 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
           <t>可审计可复算</t>
         </is>
       </c>
@@ -4833,22 +4902,27 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>主控台·实时总览</t>
+          <t>通用去重规则（0722 新增）</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>累计 GMV（实时）</t>
+          <t>规模指标 / 强度指标</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>SUM(已支付订单金额)</t>
+          <t>规模指标按用户去重：区间内按用户 ID 精确去重，同一用户跨天重复只计 1 人（活跃用户、新增 C 端、付费用户、提问用户等）；强度指标按人天：用户 × 自然日累加（日均活跃、人均提问等）；两后台涉去重指标 tooltip 全量标注所属类别</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>总营收</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>区分「多少人在用」与「用得有多勤」，口径可复算</t>
         </is>
       </c>
     </row>
@@ -4860,17 +4934,22 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>累计退款 / 退款率（实时）</t>
+          <t>累计 GMV（实时）</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>SUM(退款成功额)；退款率 = 退款额 ÷ GMV</t>
+          <t>SUM(已支付订单金额)</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>售后与资金健康度</t>
+          <t>不涉及（金额汇总）</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>总营收</t>
         </is>
       </c>
     </row>
@@ -4882,17 +4961,22 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>净 GMV（累计扣退款）</t>
+          <t>累计退款 / 退款率（实时）</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>累计 GMV − 累计退款</t>
+          <t>SUM(退款成功额)；退款率 = 退款额 ÷ GMV</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>实际到账净收入</t>
+          <t>不涉及（金额与比率）</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>售后与资金健康度</t>
         </is>
       </c>
     </row>
@@ -4904,17 +4988,22 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>当前会员数（实时）</t>
+          <t>净 GMV（累计扣退款）</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>会员未到期的去重用户数</t>
+          <t>累计 GMV − 累计退款</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>商业化基本盘</t>
+          <t>不涉及（金额汇总）</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>实际到账净收入</t>
         </is>
       </c>
     </row>
@@ -4926,105 +5015,130 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>累计注册用户（实时）</t>
+          <t>当前会员数（实时）</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>COUNT(DISTINCT user_id)</t>
+          <t>会员未到期的去重用户数</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>用户规模</t>
+          <t>按用户 ID 去重</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>商业化基本盘</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>主控台·经营分析</t>
+          <t>主控台·实时总览</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>活跃用户 / 新增会员 / 区间 GMV / 区间提问数（区间）+ 趋势图</t>
+          <t>累计注册用户（实时）</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>区间聚合</t>
+          <t>COUNT(DISTINCT user_id)</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>经营动态</t>
+          <t>按用户 ID 去重</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>用户规模</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>用户分析</t>
+          <t>主控台·经营分析</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>日活 / 周活 / 月活（区间）</t>
+          <t>活跃用户 / 新增会员 / 区间 GMV / 区间提问数（区间）+ 趋势图</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>所选区间内日均去重活跃用户；与上一等长周期环比（KPI 卡同款 Delta）</t>
+          <t>区间聚合；活跃用户＝规模指标·区间内按用户 ID 去重（0722 修订）；新增会员＝区间内历史首次开通会员的用户数，续费、回流均不计入（0722 口径定稿）；区间 GMV 仅计「已支付」订单（待支付 / 已失效不计）</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>粘性分层（0717 二批：由固定窗口快照改为区间联动）</t>
+          <t>活跃用户、新增会员＝按用户 ID 去重（跨天只计 1 人）；区间 GMV、区间提问数＝不涉及</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>经营动态</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>用户分析</t>
+          <t>主控台·经营分析（平台）</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>新增用户趋势（区间）</t>
+          <t>续费率 / 回流会员（区间）（0722 平台新增）</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>区间内按日/按小时的首次注册数序列</t>
+          <t>续费率＝区间内到期且完成续费的会员数 ÷ 同区间到期会员数；回流会员＝区间内开通会员、且开通时会员状态为已过期的用户数（不算新增、不算续费）；新增 / 续费 / 回流三者互斥，两后台统一</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>拉新节奏（新增用户卡右侧迷你折线）</t>
+          <t>续费率＝分子分母均按会员去重；回流会员＝按用户 ID 去重</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>会员经营三分：拉新 / 留存 / 召回</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>用户分析</t>
+          <t>活跃概览（页级常驻，居用户留存上方，0724 移出用户分析 Tab）</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>新增用户数（区间）</t>
+          <t>日活 / 周活 / 月活（实时滚动窗口快照）</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>区间内首次注册数</t>
+          <t>（0724 修订，替换 0717「随区间联动」口径）固定滚动窗口实时快照、不随区间筛选联动：日活＝今日 00:00 至当前时刻的去重活跃用户（实时），环比对比昨日同时段；周活＝近 7 日滚动窗口去重活跃用户，环比上一个 7 日窗口；月活＝近 30 日滚动窗口去重活跃用户，环比上一个 30 日窗口</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>拉新效果</t>
+          <t>日活＝今日 00:00 至当前时刻按用户 ID 去重；周活 / 月活＝近 7 / 30 日滚动窗口内按用户 ID 去重（窗口内跨天只计 1 人）</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>粘性分层</t>
         </is>
       </c>
     </row>
@@ -5036,17 +5150,22 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>次日 / 7 日 / 30 日留存率（独立 cohort）</t>
+          <t>新增用户趋势（区间）</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>分母=cohort 日注册去重用户；分子=第 N 日有有效行为用户；只纳入已满 N 日的成熟 cohort，显示样本量与成熟截止日，未成熟节点显示「尚未到统计时间」并给出预计可统计日期（注册日 + N）；单注册日批次三节点共用同一样本分母</t>
+          <t>区间内按日/按小时的首次注册数序列</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>产品价值是否站得住</t>
+          <t>按用户 ID 去重（注册仅计首次）</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>拉新节奏（新增用户卡右侧迷你折线）</t>
         </is>
       </c>
     </row>
@@ -5058,17 +5177,22 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>来源分布（区间）</t>
+          <t>新增用户数（区间）</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>扫码进入 vs 直接访问；图例含人数与占比；占比环比按百分点差计算、界面统一显示为「↑x.x% 较上一周期」</t>
+          <t>区间内首次注册数</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>渠道效果</t>
+          <t>按用户 ID 去重（注册仅计首次）</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>拉新效果</t>
         </is>
       </c>
     </row>
@@ -5080,61 +5204,76 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>地区分布 / 性别分布（区间）</t>
+          <t>次日 / 7 日 / 30 日留存率（独立 cohort）</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>按地区·性别分组占比</t>
+          <t>分母=cohort 日注册去重用户；分子=第 N 日有有效行为用户；只纳入已满 N 日的成熟 cohort，显示样本量与成熟截止日，未成熟节点显示「尚未到统计时间」并给出预计可统计日期（注册日 + N）；单注册日批次三节点共用同一样本分母；（0724 修订）注册批次筛选精简为「最新可统计 / 自定义日期」两档</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>用户画像与精细化运营</t>
+          <t>分子分母均按用户 ID 去重</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>产品价值是否站得住</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>提问分析</t>
+          <t>用户分析</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>总提问数（区间）</t>
+          <t>来源分布（区间）</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>COUNT(提问)</t>
+          <t>扫码进入 vs 直接访问；图例含人数与占比；占比环比按百分点差计算、界面统一显示为「↑x.x% 较上一周期」</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>使用强度</t>
+          <t>按用户 ID 去重（跨天只计 1 人）</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>渠道效果</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>提问分析</t>
+          <t>用户分析</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>人均提问数（区间）</t>
+          <t>地区分布 / 性别分布（区间）</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>总提问数 / 活跃用户</t>
+          <t>按地区·性别分组占比</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>单用户深度</t>
+          <t>按用户 ID 去重</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>用户画像与精细化运营</t>
         </is>
       </c>
     </row>
@@ -5146,17 +5285,22 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>平均会话轮次（区间）</t>
+          <t>总提问数（区间）</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>总提问数 / 总会话数</t>
+          <t>COUNT(提问)</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>对话沉浸度</t>
+          <t>不涉及（逐条计数）</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>使用强度</t>
         </is>
       </c>
     </row>
@@ -5168,17 +5312,22 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>答案点赞率 / 答案反馈率（区间）</t>
+          <t>人均提问数（区间）</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>点赞数 ÷ 答案数；反馈数 ÷ 答案数</t>
+          <t>总提问数 / 活跃用户</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>答案质量摘要（明细在答案反馈菜单）</t>
+          <t>按人天（用户×自然日）</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>单用户深度</t>
         </is>
       </c>
     </row>
@@ -5190,17 +5339,22 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>提问量趋势（区间）</t>
+          <t>平均会话轮次（区间）</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>每日提问条数</t>
+          <t>总提问数 / 总会话数</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>提问走势</t>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>对话沉浸度</t>
         </is>
       </c>
     </row>
@@ -5212,17 +5366,22 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>按 Agent 提问分布（区间）</t>
+          <t>答案点赞率 / 答案反馈率（区间）</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>各 Agent 接收提问占比</t>
+          <t>点赞数 ÷ 答案数；反馈数 ÷ 答案数</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Agent 配置 / 路由质量</t>
+          <t>不涉及（按答案条数计）</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>答案质量摘要（明细在答案反馈菜单）</t>
         </is>
       </c>
     </row>
@@ -5234,17 +5393,22 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>提问领域分布（区间）</t>
+          <t>提问量趋势（区间）</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>按 KP / 领域聚合占比</t>
+          <t>每日提问条数</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>用户最关心的领域</t>
+          <t>不涉及（逐条计数）</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>提问走势</t>
         </is>
       </c>
     </row>
@@ -5256,61 +5420,76 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>提问关键词云（区间）</t>
+          <t>按 Agent 提问分布（区间）</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>高频关键词，hover 显示该词区间提问数</t>
+          <t>各 Agent 接收提问占比</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>运营 / 商业化分析</t>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Agent 配置 / 路由质量</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>营收分析·收入与转化</t>
+          <t>提问分析</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>区间 GMV（区间）</t>
+          <t>提问领域分布（区间）</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>SUM(区间已支付金额)</t>
+          <t>按 KP / 领域聚合占比</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>区间营收</t>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>用户最关心的领域</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>营收分析·收入与转化</t>
+          <t>提问分析</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>付费用户数 / 付费转化率（区间）</t>
+          <t>提问关键词云（区间）</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>区间付费用户 / 区间活跃用户</t>
+          <t>高频关键词，hover 显示该词区间提问数</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>商业化核心</t>
+          <t>不涉及</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>运营 / 商业化分析</t>
         </is>
       </c>
     </row>
@@ -5322,17 +5501,22 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>ARPPU（区间）</t>
+          <t>区间 GMV（区间）</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>区间收入 / 区间付费用户数</t>
+          <t>SUM(区间已支付金额)</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>单付费用户产值</t>
+          <t>不涉及（金额汇总）</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>区间营收</t>
         </is>
       </c>
     </row>
@@ -5344,169 +5528,290 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>续费率（区间）</t>
+          <t>付费用户数 / 付费转化率（区间）</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>到期续费数 / 到期会员数</t>
+          <t>区间付费用户 / 区间活跃用户</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>长期价值</t>
+          <t>分子分母均按用户 ID 去重</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>商业化核心</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>营收分析·退款</t>
+          <t>营收分析·收入与转化</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>退款金额 / 退款率 / 退款订单数 / 净 GMV（区间）</t>
+          <t>ARPPU（区间）</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>见各指标</t>
+          <t>区间收入 / 区间付费用户数</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>售后与净收入</t>
+          <t>分母付费用户按用户 ID 去重</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>单付费用户产值</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>营收分析·转化漏斗</t>
+          <t>营收分析·收入与转化</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>受限内容触发率（区间）</t>
+          <t>续费率（区间）</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>触发付费墙次数 / 总提问数</t>
+          <t>到期续费数 / 到期会员数</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>付费墙强度（漏斗入口）</t>
+          <t>按会员去重</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>长期价值</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>营收分析·转化漏斗</t>
+          <t>营收分析·收入与转化</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>会员漏斗（区间）</t>
+          <t>回流会员（区间）（0722 新增）</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>看到会员页 → 点击购买 → 完成支付（%）</t>
+          <t>区间内开通会员、且开通时会员状态为已过期的用户数（按用户去重）；不算新增、不算续费，三者互斥；两后台口径一致</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>找漏斗瓶颈</t>
+          <t>按用户 ID 去重（跨天只计 1 人）</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>流失召回效果</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>营收分析·转化漏斗</t>
+          <t>营收分析·退款</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>永享转化（区间）</t>
+          <t>退款金额 / 退款率 / 退款订单数 / 净 GMV（区间）</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>触发永享墙 → 完成购买（%）</t>
+          <t>见各指标</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>永享定价是否合理</t>
+          <t>退款订单数＝按订单去重；退款金额、退款率、净 GMV＝不涉及</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>售后与净收入</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>热门 KP</t>
+          <t>营收分析·转化漏斗</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>被提问数 TOP 10 KP（区间）</t>
+          <t>受限内容触发率（区间）</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>按 KP 维度统计提问</t>
+          <t>触发付费墙次数 / 总提问数</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>真正被使用的内容</t>
+          <t>不涉及（按次计数）</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>付费墙强度（漏斗入口）</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>热门 KP</t>
+          <t>营收分析·转化漏斗</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>付费转化贡献 TOP 10 KP（区间）</t>
+          <t>会员漏斗（区间）</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>通过该 KP 触发的会员 / 永享订单数</t>
+          <t>看到会员页 → 点击购买 → 完成支付（%）</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>营销价值高的内容</t>
+          <t>各环节按用户 ID 去重</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>找漏斗瓶颈</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
+          <t>营收分析·转化漏斗</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>永享转化（区间）</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>触发永享墙 → 完成购买（%）</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>各环节按用户 ID 去重</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>永享定价是否合理</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
           <t>热门 KP</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>被提问数 TOP 10 KP（区间）</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>按 KP 维度统计提问</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>不涉及（按 KP 维度计数）</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>真正被使用的内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>热门 KP</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>付费转化贡献 TOP 10 KP（区间）</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>通过该 KP 触发的会员 / 永享订单数</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>不涉及（按 KP 维度计数）</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>营销价值高的内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>热门 KP</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>永享购买 TOP 10 KP（区间）</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>按 KP 永享订单数</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>不涉及（按 KP 维度计数）</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
         <is>
           <t>永享潜力</t>
         </is>
@@ -5523,12 +5828,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5547,6 +5853,11 @@
           <t>指标</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>去重规则（0724 新增列）</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
@@ -5556,29 +5867,39 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>内容存量</t>
+          <t>用户与营收存量（0722 由「用户存量」更名）</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>KP 当前占用（自建 + 独立快照导入，实时同步不占名额）、KP 状态分布（草稿 / 已发布 / 已下架）、存储当前占用</t>
+          <t>累计 C 端用户数（按用户 ID 去重）、当前会员数（含 72 小时缓冲期）、累计 GMV（0722 新增：机构开通至今全部已支付订单总额，含已产生退款的部分，不随区间筛选变化）</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>累计 C 端＝按用户 ID 去重；当前会员＝按用户 ID 去重；累计 GMV＝不涉及（金额汇总）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>实时存量（不随时间筛选变化）</t>
+          <t>区间运营分析（随今日 / 近7天 / 近30天 / 自定义联动）</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>用户存量</t>
+          <t>活跃与内容使用</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>累计 C 端用户数（按用户 ID 去重）、当前会员数（含 72 小时缓冲期）</t>
+          <t>活跃用户（登录或提问，区间内按用户 ID 去重）、新增 C 端用户数、区间提问数（含追问）</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>活跃用户、新增 C 端＝按用户 ID 去重（跨天只计 1 人）；区间提问数＝不涉及（逐条计数）</t>
         </is>
       </c>
     </row>
@@ -5590,12 +5911,17 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>活跃与内容使用</t>
+          <t>商业化（0722 由「商业化与 LLM 消耗」拆出，横跨整行）</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>活跃用户（登录或提问，去重）、新增 C 端用户数、区间提问数（含追问）</t>
+          <t>区间 GMV（区间内「已支付」订单金额，待支付 / 已失效不计）、净 GMV（0722 新增：区间 GMV − 区间退款金额）、付费用户数（区间内完成支付的去重用户）、付费转化率（0722 新增：付费用户 ÷ 区间活跃用户）、永享订单（0722 新增：区间内已支付永享订单数）、退款金额（0722 新增：区间内退款成功金额）、退款率（0722 新增：退款金额 ÷ 区间 GMV）</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>付费用户＝按用户 ID 去重（跨天只计 1 人）；付费转化率＝分子分母均按用户 ID 去重；永享订单＝按订单去重；区间 GMV、净 GMV、退款金额、退款率＝不涉及</t>
         </is>
       </c>
     </row>
@@ -5607,12 +5933,17 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>商业化与 LLM 消耗</t>
+          <t>LLM 消耗（0722 由「商业化与 LLM 消耗」拆出）</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>区间 GMV、付费用户数、Token 消耗量、模型调用次数、平均响应时长</t>
+          <t>Token 消耗量、模型调用次数、平均响应时长</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>不涉及（累加与均值指标）</t>
         </is>
       </c>
     </row>

--- a/docs/feature-list.xlsx
+++ b/docs/feature-list.xlsx
@@ -91,13 +91,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E138"/>
+  <dimension ref="A1:E141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -513,19 +513,20 @@
           <t>登录与授权</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>登录落地页</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>（1）页面仅展示 AI 问书 知识核动效 + 标题 + slogan「答案有出处 · 知识更可信」+ 底部「知识由 中国医学临床百家 提供」，不展示「你好我是…AI 版作者」问候语
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>0807周五更新
+（1）「0807 修订」页面仅展示 真实品牌 LOGO（上：纯图标，下：logo 文字标题图；替换原知识核动效与网页字体标题，周边彩带环动画已按反馈移除）+ slogan「答案有出处 · 知识更可信」+ 底部「知识由 中国医学临床百家 提供」，不展示「你好我是…AI 版作者」问候语
 （2）两个登录入口：「微信授权登录」（绿色）、「手机号登录」（主题色）
 （3）协议勾选区：默认未勾选，点整行切换；含《用户协议》《隐私政策》两链接（点链接不触发勾选）
 （4）校验：未勾选协议点任一登录按钮 → toast「请先阅读并同意《用户协议》与《隐私政策》」，不跳转
@@ -546,20 +547,21 @@
           <t>登录与授权</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>微信授权登录（微信内场景）</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>（1）微信 App 内打开时点「微信授权登录」不出二维码，直接唤起微信官方授权弹窗
-（2）授权弹窗：AI 问书 logo + 「申请使用」+ 权限项「获取你的昵称、头像、性别与地区」
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>0807周五更新
+（1）微信 App 内打开时点「微信授权登录」不出二维码，直接唤起微信官方授权弹窗
+（2）「0807 修订」授权弹窗：AI 问书 蓝底 app 图标（真实品牌 LOGO，贴近微信真实授权样式）+ 「申请使用」+ 权限项「获取你的昵称、头像、性别与地区」
 （3）点「允许」→ 携 code 走授权回调，自动带回 昵称/头像/性别/地区 写入账户 → 进入 AI 会话首页（手机号为空，后续按需绑定）
 （4）点「拒绝」→ 留在登录落地页
 （5）H5 网页授权（snsapi_userinfo）无法获取手机号（一键授权手机号为小程序专属），故不弹「获取手机号」授权窗，手机号统一改由用户手动「手机号+验证码」绑定</t>
@@ -587,7 +589,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>（1）非微信浏览器点「微信授权登录」→ 跳微信扫码授权页，由微信域名 open.weixin.qq.com 渲染二维码
 （2）二维码采用内嵌样式（WxLogin JS SDK，整页可美化），二维码中央不放 AI 问书 Logo（二维码属微信，避免误导）
@@ -608,20 +610,19 @@
           <t>登录与授权</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>手机号验证码登录</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>0722周三更新
-（1）手机号输入框（限 11 位数字，自动过滤非数字）+ 验证码输入框（限 6 位）+「获取验证码」（点击 toast「验证码已发送」）
+          <t>（1）手机号输入框（限 11 位数字，自动过滤非数字）+ 验证码输入框（限 6 位）+「获取验证码」（点击 toast「验证码已发送」）
 （2）登录按钮在手机号或验证码为空时禁用
 （3）校验：手机号非 11 位 → toast「请输入正确的 11 位手机号」；验证码非 6 位 → toast「请输入 6 位验证码」
 （4）校验通过 → 登录成功进入 AI 会话页；此方式不获取、不绑定任何微信信息
@@ -641,20 +642,19 @@
           <t>登录与授权</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>绑定手机号</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>0722周三更新
-（1）三种来源差异化副标题：登录后引导（绑定后可跨端同步会话与权益）/ 敏感操作门槛（支付下单、兑换码与开通会员需先完成手机号绑定）/ 我的入口（绑定后可使用支付、兑换码与会员等权益）
+          <t>（1）三种来源差异化副标题：登录后引导（绑定后可跨端同步会话与权益）/ 敏感操作门槛（支付下单、兑换码与开通会员需先完成手机号绑定）/ 我的入口（绑定后可使用支付、兑换码与会员等权益）
 （2）手机号 + 验证码两输入框（校验同手机号登录）+「获取验证码」
 （3）主按钮文案随来源变（绑定并进入 / 完成绑定）；空值禁用
 （4）绑定成功 → toast「手机号绑定成功」→ 按来源跳转（登录来源进会话页，其余返回上一页）
@@ -685,7 +685,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>（1）待绑手机号在本机构已被其他账号/微信绑定 → 提示「该手机号已绑定账号，请直接使用手机号登录；如无法登录请联系客服」
 （2）不做账号合并、不顶替、不迁移权益；A、B 两个微信身份先后绑定同一手机号时，后者必须改走手机号登录或人工客服核验
@@ -714,7 +714,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>（1）顶栏：左侧菜单（开历史会话抽屉）、中间「AI 问书 / 内容由 AI 生成」、右侧实时电话入口 + 新建会话
 （2）会话内容跨页保留（跳会员/支付/电话页再返回仍是同一会话）
@@ -747,7 +747,7 @@
           <t>能力开关（深度思考 / 智能搜索）</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>（1）输入框下方两个相互独立的能力开关，状态随会话保留
 （2）深度思考：开启后调用更强推理、给更细致的思考型回答，默认开启
@@ -778,7 +778,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>（1）0717 #1.3/#1.6：新增统一入口 /kp/:kpId——KP 前台地址直达与知识 KP 二维码扫码（含首扫权益绑定核销）共用，进入时先判 KP 状态
 （2）已发布：过渡提示后进入该 KP 的全新 AI 会话
@@ -810,7 +810,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>（1）AI 答案文字打字机式流式输出，未输出完时显示光标
 （2）仅新生成的回答展示打字机动效；切换历史会话、电话挂断返回等场景下已生成回答直接整段展示、不重复动效</t>
@@ -838,7 +838,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>（1）答案卡片内「相关媒体资源」作为加粗小标题贴在卡片上；文字区在上、媒体区在下，两区做明显视觉区分
 （2）媒体并列排布支持左右滑动，顺序按后台返回的相关度从左到右排列（非图→音→视固定序），不展示相关度数值
@@ -870,7 +870,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>（1）每条 AI 答案下方、「参考 N 篇知识」入口左侧并排三个 icon：复制（toast「已复制答案」）、点赞、点踩
 （2）点赞/点踩互斥，可再次点击取消；icon 为灰色系描边填充样式（选中态灰填充、非主题色）</t>
@@ -898,7 +898,7 @@
           <t>点踩反馈弹层</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>（1）点踩 → 弹底部反馈 sheet，标题「反馈」
 （2）4 个互选标签：有害/不安全、虚假信息、没有帮助、其他
@@ -928,7 +928,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>（1）展示在多模态卡片下方，2–3 个追问上下纵向堆叠（非左右并列）
 （2）点击任一即作为新问题发送</t>
@@ -956,7 +956,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>（1）点输入框右侧麦克风 → 在当前会话页底部弹音浪动画浮层（非全屏新页），浮层背底与会话背景自然过渡
 （2）提示「松手发送，上滑取消」
@@ -975,21 +975,23 @@
           <t>AI 会话</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>历史会话抽屉</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>（1）左上角菜单开抽屉；顶部「新建会话」
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>0807周五更新
+（1）左上角菜单开抽屉；顶部「新建会话」
 （2）历史按时间分组（今天/昨天/某年某月）列出，点任一条载入该会话
-（3）页脚用户卡（头像+昵称+会员标+手机号）点击进入「我的」</t>
+（3）页脚用户卡（头像+昵称+会员标+手机号）点击进入「我的」
+（4）「0807 修订」页脚用户卡会员标随会员状态（与「我的」页同规则、二分展示）：有效会员 / 宽限期显「会员」、已过期 / 未开通不显标；接同一数据源不再硬编码</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1016,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>（1）答案下「参考 N 篇知识」入口，点击从右侧抽屉拉出溯源列表，仅按相关度从高到低排序、不显数值
 （2）分两块、中间浅灰横线分隔：上块知识 KP（KP 封面 + KP 名 + 文件名 + 章节页码；同 KP 多命中文件归并最多 2 个、其余「…等 N 个文件」），下块互联网检索（站点用小圆形图标）
@@ -1045,7 +1047,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>（1）所有「跳出 AI 问书」的链接（web 互联网来源 + 知识 KP 的纸书/运营填写链接）均先弹过渡提示
 （2）样式为屏幕中上方黑底白字倒计时条：左侧 3·2·1 倒计时 + 「即将跳转到外部」+ 右侧「取消跳转」
@@ -1075,7 +1077,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>（1）〔演示〕由落地页演示开关触发；生产由机构实际 Token 用量判定
 （2）超限时会话顶部常驻珊瑚红提示条「当前机构 Token 已达上限，请联系客服」
@@ -1104,7 +1106,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>（1）会员专属：未开通会员点电话入口时引导开通；开通后方可进入
 （2）独立电话页：中央 Agent 形象 + 实时语音状态文案与动画（如「正在听…」「正在回答…」）
@@ -1135,7 +1137,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>（1）受限媒体触发，按资源所属权益池动态呈现按钮（不再固定两按钮）：
 （2）会员资源：标题「{资源名} · 会员内容」+ 单按钮「开通会员 · 畅享全部会员内容」（进会员页）
@@ -1165,7 +1167,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>（1）放大预览顶部固定「因版权限制，暂不支持保存下载」+ 关闭✕
 （2）支持左右翻页（循环）+ 底部缩略点/缩略图条切换，主预览区可左右滑动浏览同卡片其他媒体
@@ -1194,7 +1196,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>（1）0717 二批 #9：两档改为「购买方式即续费语义」，消除「按月自动续费」歧义——① 连续包月（默认选中，角标「首月特惠」）：首月 ¥9.9、次月起 ¥19.9/月 自动续费，卡内说明「自动续费，可随时退订」② 单月（¥19.9 / 1 个月）：一次性购买，卡内说明「到期自动失效，不自动续费不扣款」；选中即表达是否自动续费，不再靠一个含糊的全局勾选
 （2）协议、按钮与底部说明随所选方式联动：连续包月→勾选《自动续费协议》+ 按钮「¥9.9 开通连续包月」+ 底部说明「次月起 ¥19.9/月 自动扣费 · 支持随时退订，到期赠 72 小时会员缓冲使用期」；单月→协议行换成《会员服务协议》（无自动续费协议）+ 按钮「¥19.9 购买单月会员」+ 底部说明「到期自动失效，不会自动扣费」；缓冲期不计入已付费会员时长
@@ -1226,7 +1228,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>（1）会员卡：会员标识 + 有效期 + 续费状态（自动续费 / 到期不再续费）
 （2）「免费 vs 会员」权益对比表（逐项 ✅/✗）：基础文字知识问答、图音视频深度知识精讲、VIP 极速优先通道、实时电话即时问答、永享名家典藏知识（永享标注为「单独购买」）
@@ -1255,7 +1257,7 @@
           <t>取消/开启自动续费</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>（1）自动续费开启时显示「取消自动续费」入口（无手动续费按钮）
 （2）点取消 → 二次确认 sheet（挽留设计：主按钮「暂不取消」、弱化「确认取消」）
@@ -1275,24 +1277,27 @@
           <t>我的</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>我的主页</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>（1）顶部用户卡（点击进个人资料）：头像 + 昵称（无则「未设置昵称」）+ 会员标 + 手机号（未绑显「未绑定手机号」）
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>0807周五更新
+（1）顶部用户卡（点击进个人资料）：头像 + 昵称（无则「未设置昵称」）+ 会员标 + 手机号（未绑显「未绑定手机号」）
 （2）「会员」分组：会员中心（右值 已开通/未开通）
 （3）「我的」分组：我的永享、我的纸书、我的订单、兑换码
 （4）「账户与帮助」分组：换绑/绑定手机号（未绑显红字「未绑定」）、联系客服、用户协议、隐私政策
 （5）退出登录 → toast「已退出登录」→ 回落地页
-（6）〔评审〕「评审工具」分组：原型清单（三端站点地图）</t>
+（6）〔评审〕「评审工具」分组：原型清单（三端站点地图）
+（7）「0807 修订」品牌资产接入定稿：C 端登录落地页＝浅色底纯图标 logo（周边彩带环动画按反馈移除）；微信授权弹窗＝蓝底 app 图标版（贴近微信真实授权样式）；两后台登录页品牌区与侧栏品牌位＝横版 logo（图标＋中英文字，原「AI 问书」文字标题移除，侧栏折叠态切纯图标）；三种形态均 base64 内联（BRAND_LOGO / BRAND_LOGO_APP / BRAND_LOGO_FULL）三端共用、不随机构换肤
+（8）「0807 修订」会员状态在 C 端的呈现定稿为二分展示（运营四态语义只在后台）：用户卡会员标——有效会员 / 宽限期（权益仍在）显「会员」，已过期 / 未开通不显标；「会员中心」右值——已开通（有效 / 宽限期）/ 未开通（已过期 / 从未开通）；登录落地页〔演示〕环境切换新增「会员状态」四档（未开通/有效会员/宽限期/已过期），切换即联动上述展示点</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1322,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>（1）已购永享列表，按文件名模糊搜索 + 类型筛选（全部/图片/音频/视频）
 （2）网格卡片：封面 + 类型角标 + 名称 +「{类型} · 永久解锁」
@@ -1350,7 +1355,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>（1）展示用户所有线下扫码对应的知识 KP（不只首扫绑定的），含已解锁与未解锁
 （2）卡片：KP 封面 + KP 名（固定两行高）+「扫码解锁 · 时间」（钉在卡片底部对齐）；按 KP 名模糊搜索
@@ -1386,7 +1391,7 @@
           <t>扫一扫</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>（1）右上角「扫一扫」入口，点击调起手机相机扫码
 （2）0717 #1.3：扫码统一走「KP 前台入口 /kp/:kpId」判活——toast「已识别知识 KP 二维码」后进入入口页：已发布正常进入全新会话并绑定权益；已下架 / 已删除按入口页失效流程提示并跳转（原型演示按 已发布→已下架→已失效 轮换）。注意用词：兑换码的权益是会员，与 KP 绑定的是「知识 KP 二维码」</t>
@@ -1414,7 +1419,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>（1）由「我的」顶部头像/昵称/手机号区右侧箭头进入（不再有独立「个人资料」菜单）
 （2）「资料」列表：头像、昵称、性别、地区；微信环境由授权自动带回作初始填充，全字段均可修改</t>
@@ -1442,7 +1447,7 @@
           <t>头像上传+圆形裁剪</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>（1）点头像行调起手机相册，选图后弹全屏裁剪 overlay
 （2）可拖拽移动图片调整位置（无底部缩放条）；顶部标题与取消/确定按钮套用前台 AI 主视觉
@@ -1471,7 +1476,7 @@
           <t>昵称/性别/地区编辑</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>（1）昵称：居中弹窗输入框（限 20 字）+ 保存 → toast「已更新」
 （2）性别：弹窗仅「男/女」两项（去掉「保密」），选中即保存
@@ -1500,7 +1505,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>（1）「兑换会员权益 / 输入兑换码,或拍照自动识别」
 （2）输入框（自动转大写）+ 相机按钮（调起相机/相册 OCR 识别）
@@ -1522,20 +1527,19 @@
           <t>我的</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>我的订单</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D35" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>0722周三更新
-（1）「0722 修订」双维度筛选并存：顶部为「订单类型」Tab（全部 / 会员 / 永享 / 兑换码），其下「订单状态」chips 改为 全部 / 待支付 / 已支付 / 已失效 / 退款售后，两维度分层放置、过滤取交集——推翻 0716「支付成功才落库」口径：发起支付即落库为「待支付」；部分退款、全额退款、退款中统一归入「退款/售后」桶；兑换码核销单归入「已支付」分组（行内标签仍显「已核销」；切到「兑换码」Tab 时隐藏状态 chips 的规则不变）
+          <t>（1）「0722 修订」双维度筛选并存：顶部为「订单类型」Tab（全部 / 会员 / 永享 / 兑换码），其下「订单状态」chips 改为 全部 / 待支付 / 已支付 / 已失效 / 退款售后，两维度分层放置、过滤取交集——推翻 0716「支付成功才落库」口径：发起支付即落库为「待支付」；部分退款、全额退款、退款中统一归入「退款/售后」桶；兑换码核销单归入「已支付」分组（行内标签仍显「已核销」；切到「兑换码」Tab 时隐藏状态 chips 的规则不变）
 （2）列表按付款时间降序
 （3）「0722 修订」待支付订单卡显示「剩余支付时间」倒计时（下单起 30 分钟支付有效期）+「去支付」按钮，可重新调起微信支付；30 分钟未支付微信自动关单转「已失效」
 （4）「0722 修订」待支付 / 已失效订单无付款时间，卡片显示下单时间（其余订单仍显付款时间）
@@ -1559,20 +1563,19 @@
           <t>我的</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>订单详情</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D36" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>0722周三更新
-（1）按类型差异化呈现
+          <t>（1）按类型差异化呈现
 （2）会员：基础信息卡（订单编号/支付方式/续费方式 自动续费·手动支付/下单·付款时间）+ 会员权益卡（有效期）
 （3）永享：基础信息卡 + 永享内容卡（整行可点直接预览，无「点击封面预览」文字）
 （4）兑换码：页面标题为「详情」（非订单详情），仅展示 类型=兑换码核销/兑换码/兑换时间 + 兑换权益（权益名 + 会员时间区间），不展示订单编号/支付方式/下单付款时间/金额
@@ -1595,20 +1598,19 @@
           <t>我的</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" s="3" t="inlineStr">
         <is>
           <t>换绑手机号</t>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>0722周三更新
-（1）展示当前手机号（脱敏）+「换绑后用新号码登录」
+          <t>（1）展示当前手机号（脱敏）+「换绑后用新号码登录」
 （2）新手机号 + 验证码两输入框（校验同登录）+「获取验证码」
 （3）「确认换绑」（空值禁用）→ toast「换绑成功」→ 返回
 （4）仅需「新手机号 + 验证码」，不要求旧手机号双重校验
@@ -1637,7 +1639,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>（1）会员开通与永享买断统一走模拟微信支付收银台：标题区白底、AI 问书 logo 用会话同款电光靛紫色动画球
 （2）展示商户「AI 问书」+ 金额 + 商品名；商户/确认支付按钮沿用微信绿 + 模拟环境提示「不会产生真实扣款」
@@ -1667,7 +1669,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E39" s="6" t="inlineStr">
         <is>
           <t>（1）成功对勾用绿色/主题色 + 同心圆光环（避免被误解为未支付成功）
 （2）文案「已为你解锁权益，回到刚才的对话继续探索」
@@ -1696,7 +1698,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>（1）珊瑚红✕ +「支付失败」+「未扣款,可重新支付或稍后再试」
 （2）按钮：「重新支付」（重新发起微信支付）、「返回」（回会话）</t>
@@ -1724,7 +1726,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
         <is>
           <t>（1）两个独立入口并列，纯文本/Markdown 渲染
 （2）底部展示更新日期</t>
@@ -1752,7 +1754,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E42" s="6" t="inlineStr">
         <is>
           <t>（1）二维码本身作废时提示「二维码已失效」+「N 秒后自动跳转首页…」；KP 已下架 / 已删除的扫码改走「KP 前台入口 /kp/:kpId」判活流程（提示已下架/已失效并按跳转规则①处理），与二维码作废场景区分
 （2）3 秒倒计时自动跳首页，另提供「立即前往首页」按钮</t>
@@ -1780,7 +1782,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="E43" s="6" t="inlineStr">
         <is>
           <t>（1）展示机构后台配置的一个二维码（企微/个微）
 （2）下方电话、邮箱均非必填，有则展示无则隐藏并自动补位（不留空块）</t>
@@ -1808,7 +1810,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="E44" s="6" t="inlineStr">
         <is>
           <t>（1）〔评审〕原型清单：三端站点地图，列全站页面便于评审跳转，脱手机框全宽渲染
 （2）〔演示〕落地页演示环境开关：微信内/浏览器、Token 正常/超限，仅原型演示用、标注非上线功能</t>
@@ -1826,19 +1828,20 @@
           <t>登录与主控台</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C45" s="4" t="inlineStr">
         <is>
           <t>登录页</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>（1）左侧动态毛玻璃品牌区（浮动 blob + 旋转知识核）+ 标语「答案有出处 · 知识更可信」
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>0807周五更新
+（1）「0807 修订」左侧动态毛玻璃品牌区（浮动 blob + 横版真实品牌 LOGO（图标＋中英文字），替换原旋转知识核、原「AI 问书」网页字体标题移除）+ 标语「答案有出处 · 知识更可信」
 （2）右侧登录卡：账号（账号/手机号）、密码、图形验证码（4 位，字母表排除易混 0/O/1/I/L）
 （3）图形验证码点击「换一张」刷新
 （4）「登录遇到问题?」→ toast「请联系管理员」</t>
@@ -1856,25 +1859,30 @@
           <t>登录与主控台</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>主控台</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>（1）页头标题 + 右上「导出」；文件名规范「AI问书_{机构名}_主控台数据导出.xlsx」；拆分“实时总览/经营分析”两个 Sheet——实时 Sheet 标注实时统计时间、经营分析 Sheet 标注所选区间具体起止；头部统一注明导出时间与导出时刻的全部筛选条件
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>0807周五更新
+（1）页头标题 + 右上「导出」；文件名规范「AI问书_{机构名}_主控台数据导出.xlsx」；拆分“实时总览/经营分析”两个 Sheet——实时 Sheet 标注实时统计时间、经营分析 Sheet 标注所选区间具体起止；头部统一注明导出时间与导出时刻的全部筛选条件
 （2）0716 #3【全平台导出通用规则】：单次导出统一上限 10000 条（任一业务 Sheet 数据行超限即拦截，不下载），弹窗提示「本次筛选结果约 N 条，超过单次导出上限 10000 条，请缩小筛选范围后重试，或联系平台管理员导出完整数据」。规则集中在导出底座内拦截，两后台全部导出入口一致生效；导出进行中的提示统一为「正在导出」
 （3）导出指标全量不遗漏：实时总览含 累计GMV/累计退款/退款率/净GMV/当前会员数/累计注册用户；经营分析含各 KPI 及「较上一周期」环比列与趋势数据
 （4）当前生效订阅卡（机构侧只读）：KP 数、存储明确标“占用量/当前占用”，Token 明确标“消耗量/本周期消耗”；上限＝当前订阅基础额度+该订阅有效加油包，InfoDot 写明跨订阅、重置和降配阻断规则
 （5）实时总览（标「实时」，不随时间筛选变化）：累计 GMV、累计退款/退款率、净 GMV、当前会员数、累计注册用户，每卡带 InfoDot 口径说明
 （6）经营分析：今日/近7天/近30天；每个 KPI 的悬浮面板必须说明统计范围、去重方式、上一周期、差值单位和零基线处理；今日按小时趋势，7/30 天按日趋势
-（7）页脚数值单位规范说明</t>
+（7）页脚数值单位规范说明
+（8）「0807 新增」父机构视角：页头新增「机构」多选筛选（选项＝本机构（父机构）＋全部子机构，默认全选、支持跨机构任意组合勾选），实时总览与经营分析全部指标随所选机构集合联动——计数/金额类绝对量按集合聚合，率类指标为所选集合整体口径重算（非各机构简单相加）；子机构/独立机构视角无此筛选、保持现状
+（9）「0807 修订」机构多选交互定稿：选项行为自绘勾选框（选中靛蓝底白勾）＋「（父机构）」靛蓝标（与单选下拉同约定）、顶部「全部机构」快捷全选（分隔线隔开）；触发器回填所选机构名（全选显「全部机构」、部分选择顿号拼接、超宽省略号）；至少保留一家（取消最后一项 toast 拦截）
+（10）「0807 修订」导出 Sheet 结构对齐页面栏目：当前订阅（本机构配额，不随机构筛选）/ 实时总览 / 经营分析 三个 Sheet；父机构视角头部 scope 标「本机构（父机构）」并在筛选条件注明机构范围——导出数据随页面机构多选联动（多选＝合并口径、单选＝单机构），不单独产出分机构明细
+（11）「0807 修订」订阅套餐卡口径：订阅是机构级合同（各机构各自签、配额上限不同、聚合无意义）——父机构视角固定显示本机构订阅与配额、不随机构多选联动，卡右上角灰字注明「本机构订阅 · 不随机构筛选变化」；子机构订阅在平台后台对应机构详情查看</t>
         </is>
       </c>
     </row>
@@ -1889,26 +1897,28 @@
           <t>知识产品 KP</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>KP 列表</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>（1）卡片网格：封面色块 + KP 名 + 来源标签（自建/共享）+ 状态标签（草稿/已发布/已下架，0717 #2.4 两后台命名统一）+ 实时分享·分享方标（0717 二批 #4：接收方不再单独加标——「共享」来源标签已表达，避免标签堆叠）+ Agent 名 + 文件数/提问数；已删除（逻辑删除）的 KP 不在三端界面展示，数据库保留数据
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>0807周五更新
+（1）卡片网格：封面色块 + KP 名 + 来源标签（自建/共享）+ 状态标签（草稿/已发布/已下架，0717 #2.4 两后台命名统一）+ 实时分享·分享方标（0717 二批 #4：接收方不再单独加标——「共享」来源标签已表达，避免标签堆叠）+ Agent 名 + 文件数/提问数；已删除（逻辑删除）的 KP 不在三端界面展示，数据库保留数据
 （2）按 KP 名称模糊搜索；筛选 状态（全部/草稿/已发布/已下架）、来源（全部/自建/共享）——已删除 KP 不在列表与筛选中出现
 （3）0717 #2.3：列表与详情同一数据源（点开哪张卡，详情即那条数据：名称/状态/导入方式/业务关系一致）；演示数据覆盖每个状态各至少一条（草稿/已发布/已下架），并含实时分享双视角各一条——分享方（本机构分享出去）与接收方（实时同步导入、只读）
 （4）顶部右侧配额 chip：KP X/Y · 存储 X/Y GB（≥90% 红/≥70% 黄）+ 提示「达上限将无法新建/上传，请联系平台扩容」
 （5）新建阻断：KP 数达上限时点新建 → toast「已达 KP 数量上限（Y 个），请联系平台扩容」
 （6）点卡片进 KP 详情；空态「没有匹配的 KP」
 （7）「0718 修订」来源标签体系三分并在两后台统一：自建＝机构自己创建；分享导入·实时＝经实时同步导入（只读）；分享导入·快照＝经独立快照导入（可编辑）。来源标签统一使用灰色（原「自建」的靛蓝色取消），仅 KP 状态标签（草稿/已发布/已下架）随状态变色；「实时分享 · 分享方」角色标同步改灰。来源筛选选项改为 全部 / 自建 / 分享导入·实时 / 分享导入·快照
-（8）「0718 修订」状态标签颜色在列表与详情间统一：已发布＝玉绿、已下架＝琥珀、草稿＝灰描边（列表原「已发布」电光靛取消，与详情头 tag-s 同色）；平台 Agent 列表的「机构」类型标改用靛蓝类保持原观感，不受 KP 状态色统一影响</t>
+（8）「0718 修订」状态标签颜色在列表与详情间统一：已发布＝玉绿、已下架＝琥珀、草稿＝灰描边（列表原「已发布」电光靛取消，与详情头 tag-s 同色）；平台 Agent 列表的「机构」类型标改用靛蓝类保持原观感，不受 KP 状态色统一影响
+（9）「0807 新增」父子机构数据范围（父机构视角）：筛选区新增「机构」单选下拉——选项＝全部机构（默认）/ 本机构（带「父机构」标）/ 各子机构，单选联动下方卡片；卡片新增数据归属机构名称展示；归属为子机构的 KP 仅可查看详情，编辑/上下架等操作置灰并提示「仅可操作本机构数据」——机构后台角色的「可操作」权限仅针对本机构数据，父机构对子机构数据只有可见性、跨机构操作须走平台后台；子机构/独立机构视角无此筛选、界面保持现状。同规则适用于 Agent 人设 / C 端用户 / 订单管理 / 兑换码 / 答案反馈 五页；机构类型可在顶栏〔演示〕开关切换预览（见「评审工具 · 机构类型切换」）</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1943,7 @@
           <t>新建 KP</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E48" s="6" t="inlineStr">
         <is>
           <t>（1）弹窗：KP 名称（必填）+ 简介
 （2）确定 → toast「已创建 KP」</t>
@@ -1961,7 +1971,7 @@
           <t>导入分享 KP</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>（1）弹窗：分享链接（必填）+ 密码（必填）
 （2）弹窗底部提示改为灰色内容框内三条无序结构化条目：① 导入限制：仅支持导入外部机构分享，本机构分享不可导入 ② 实时同步：不占用接收方 KP 与存储，内容只读，Token 消耗归属接收方 ③ 独立快照：占用接收方 KP 与存储，支持编辑，Token 消耗归属接收方
@@ -1991,7 +2001,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
+      <c r="E50" s="6" t="inlineStr">
         <is>
           <t>（1）详情头：返回 + KP 名（与列表同源）+ 来源标签 + 状态标签（草稿/已发布/已下架，两后台命名统一）+ 右侧状态操作按钮——0717 #2.1/#2.2：草稿→「发布」、已发布→「下架」、已下架→「重新发布」；删除对草稿/已发布/已下架均可用；操作真实生效（原型内真实改状态，非仅提示）。0717 二批 #2/#4：来源标签统一「自建 / 共享」（详情不再用「共享导入」，与列表一致）；实时同步导入的详情头不再显示「实时同步 · 只读」附加标（顶部只读 banner 已说明）
 （2）「发布」同样走二次确认——弹窗说明「发布后前台立即可见：支持检索、购买、扫码与链接访问；发布需至少一份已向量化完成的知识内容」，确认后状态真实置为已发布并 toast「已发布」
@@ -2030,7 +2040,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="E51" s="6" t="inlineStr">
         <is>
           <t>（1）按文件名搜索 + 类型筛选（全部/文档/图片/音频/视频）
 （2）提示「上传即向量化，发布知识 KP 需至少一份已向量化完成的知识内容」
@@ -2065,7 +2075,7 @@
           <t>上传知识文件</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>（1）弹窗左右布局：左=拖拽/点击上传区（文档/图片/音频/视频多文件混传、批量、不支持文件夹）+ 单文件上限说明（文档≤100MB、图片≤20MB、音频≤300MB·120分钟、视频≤1GB·60分钟）
 （2）右=批量上传进度列表（每文件进度条 + 百分比 + 移除）
@@ -2094,7 +2104,7 @@
           <t>文件上下架/重试/删除</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
+      <c r="E53" s="6" t="inlineStr">
         <is>
           <t>（1）已向量化：下载 / 上架↔下架（toast「已上架,该内容可被检索」/「已下架,该内容停止被检索」）/ 删除
 （2）失败：下载 / 重试（确认「重新执行向量化」→ toast「已重新提交向量化」）/ 删除
@@ -2123,7 +2133,7 @@
           <t>设置 / 编辑永享价（图音视）</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
+      <c r="E54" s="6" t="inlineStr">
         <is>
           <t>（1）在知识库列表对图/音/视文件点「设置/编辑永享价」→ 弹窗：内容名 + 永享价（必填，元）
 （2）弹窗内含说明块（淡紫 / 淡珊瑚底）：「永享内容需单独付费，无论该 KP 是免费还是会员；免费用户无需先开通会员即可直接购买——免费/会员 与 永享 是两套独立的权益模型」
@@ -2153,7 +2163,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
+      <c r="E55" s="6" t="inlineStr">
         <is>
           <t>（1）此处设「基础权益」，决定本 KP 非永享内容的门槛：免费 / 会员 二选一互斥单选
 （2）免费：所有用户均可查看该 KP 全部非永享内容（文字/图片/音频/视频）
@@ -2184,7 +2194,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
+      <c r="E56" s="6" t="inlineStr">
         <is>
           <t>（1）按二维码包名称搜索 + 权益模式筛选（全部/首扫绑定后扫引导/无权益）
 （2）表格列：二维码包名称、权益模式、生成的二维码数量、扫描总量、首扫数量、后扫数量、操作（查看/下载 zip）
@@ -2214,7 +2224,7 @@
           <t>新建二维码包</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
+      <c r="E57" s="6" t="inlineStr">
         <is>
           <t>（1）弹窗：包名称（必填）+ 权益模式（下拉）+ 生成数量（必填）
 （2）确定 → toast「已生成二维码包」</t>
@@ -2242,7 +2252,7 @@
           <t>二维码明细抽屉</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
+      <c r="E58" s="6" t="inlineStr">
         <is>
           <t>（1）「查看」从右侧拉出抽屉：抽屉头显包名 +「包号 X · 权益模式 Y · 共 N 个二维码」
 （2）按 首扫账户名称/首扫手机号 模糊搜索
@@ -2271,7 +2281,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="E59" s="6" t="inlineStr">
         <is>
           <t>（1）筛选 模式（全部/实时同步/独立快照）、状态（全部/生效中/已作废）
 （2）表格列：链接/密码（点击复制 toast「已复制分享链接」）、模式、有效期（如还剩 N 天）、消费/上限、状态、操作
@@ -2300,7 +2310,7 @@
           <t>新建分享</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="E60" s="6" t="inlineStr">
         <is>
           <t>（1）弹窗：同步模式（实时同步/独立快照）+ 有效期（1天/7天/30天/永久）+ 导入次数上限
 （2）确定 → toast「已生成分享链接」</t>
@@ -2328,7 +2338,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
+      <c r="E61" s="6" t="inlineStr">
         <is>
           <t>（1）0717 #4：实时同步（接收方 / 消费者视角）只读升级——基础信息表单输入框全部禁用置灰（无光标、hover 显示 not-allowed 禁止态，样式同既有只读输入框先例）、关联 Agent 下拉禁用、定价与权益单选整体置灰不可选；仅「复制链接」可操作；其余操作按钮置灰、点击提示「无权限操作」；二维码、分享两 Tab 隐藏。顶部只读说明 banner 单行呈现，来源机构为动态变量：「本 KP 由「{分享机构名}」以「实时同步」分享导入：内容随源机构自动更新、仅可查看不可编辑；不占本机构 KP 数与存储、问答消耗本机构 Token；二维码与分享不可用。」0717 二批 #5：禁用置灰统一标准＝「前台访问地址」只读框样式（纸白底 + 实线浅边框 + 深灰文字），两后台一致，不再用虚线浅灰底
 （2）独立快照：五个 Tab 均可编辑；基础信息、知识库、定价数据在导入时复制，二维码与分享从消费机构自己的空数据开始
@@ -2347,22 +2357,24 @@
           <t>Agent 人设</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="C62" s="4" t="inlineStr">
         <is>
           <t>Agent 列表</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>（1）卡片网格：机器人封面 + 名称 + 类型标签（机构/普通）+「关联 KP · N」+ 音色（已设/默认）
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>0807周五更新
+（1）卡片网格：机器人封面 + 名称 + 类型标签（机构/普通）+「关联 KP · N」+ 音色（已设/默认）
 （2）按 Agent 名称模糊搜索
 （3）「新建 Agent」→ 进空白编辑页
-（4）点卡片进 Agent 详情</t>
+（4）点卡片进 Agent 详情
+（5）「0807 新增」父机构视角：新增「机构」单选筛选＋卡片新增数据归属机构名称，子机构 Agent 仅可查看不可编辑（父子机构数据范围规则同「知识产品 KP · KP 列表」）</t>
         </is>
       </c>
     </row>
@@ -2377,25 +2389,27 @@
           <t>Agent 人设</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>Agent 详情 / 编辑</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>（1）区分新建/编辑：头部名称 + 类型标签 + 右侧「创建」/「保存」
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>0807周五更新
+（1）区分新建/编辑：头部名称 + 类型标签 + 右侧「创建」/「保存」
 （2）左侧表单：头像（必填，上传 png/gif/jpg 走圆形裁剪）、名称（必填）、类型（不可更改，注「类型不可更改」）、TTS 参考音（必填，已上传显波形条 + 播放/暂停 + 时长 + 重新上传）、回答 Prompt
 （3）0716 #11：名称校验——机构内不允许重复（重名保存拦截 toast「该 Agent 名称在机构内已存在，请更换」），字段旁提示「名称在机构内不可重复」
 （4）0716 #11：TTS 参考音校验——仅支持 MP3 / WAV 格式、时长 3~10 秒；上传时真实读取音频元数据校验，超范围拦截并提示；字段旁提示「格式 MP3 / WAV · 时长 3~10 秒」
 （5）回答 Prompt 机构侧只读：灰底只读框 + 提示「受权限控制，若需编辑请联系平台管理员」（受角色权限「Agent 回答 Prompt 编辑」控制）
 （6）右侧「关联 KP」卡：列出关联 KP，点「前往 KP」跳对应 KP 详情
-（7）保存 → toast「已保存」；新建保存 → toast「已创建 Agent」回列表</t>
+（7）保存 → toast「已保存」；新建保存 → toast「已创建 Agent」回列表
+（8）「0807 新增」「TTS 参考音」下方新增字段「TTS 参考音文本」（必填）：即 TTS 参考音频内朗读的文本内容，用于 TTS 引擎将参考音与文本对齐；多行输入框，上限 100 字（按字符数计，不限制字符种类——中英文/数字/标点/符号均可），右下角实时字数「N / 100」、字段说明置输入框上方（文案「参考音频内朗读的文本内容・100 字以内，用于 TTS 引擎将参考音与文本对齐」）、名称字段的重复提示置输入框同行右侧；为空保存拦截 toast「请输入 TTS 参考音文本」，达 100 字后输入框拦截不可再输入；平台后台全域 Agent 详情同步生效（同一组件）</t>
         </is>
       </c>
     </row>
@@ -2410,22 +2424,25 @@
           <t>C 端用户</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="C64" s="4" t="inlineStr">
         <is>
           <t>用户列表</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>（1）表格列：用户昵称、手机号、微信号、地区、性别、会员状态、已购永享、累计 GMV、最新登录时间、注册时间、操作（详情）；「注册时间」列支持升 / 降序排序
-（2）按 手机号/微信号/昵称 三字段模糊搜索；筛选 会员状态（全部/会员/非会员）
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>0807周五更新
+（1）表格列：用户昵称、手机号、微信号、地区、性别、会员状态、已购永享、累计 GMV、最新登录时间、注册时间、操作（详情）；「注册时间」列支持升 / 降序排序
+（2）按 手机号/微信号/昵称 三字段模糊搜索；筛选 会员状态（全部/有效会员/宽限期（待续费）/会员已过期/未开通会员）
 （3）筛选行右侧「导出」：生成「AI问书_{机构名}_C端用户数据导出.xlsx」，严格沿用手机号/微信号/昵称搜索和会员状态筛选；文件头部注明导出时间与筛选条件
-（4）昵称规则：微信登录取微信昵称、手机号登录取「用户+后四位」；地区/性别为微信授权带回，非微信用户显「—」</t>
+（4）昵称规则：微信登录取微信昵称、手机号登录取「用户+后四位」；地区/性别为微信授权带回，非微信用户显「—」
+（5）「0807 修订」会员状态由「全部/会员/非会员」二分改为生命周期四态（三端及导出统一口径）：有效会员＝会员权益生效中（含连续包月期内）；宽限期（待续费）＝权益已到期、处于续费宽限窗口内，权益暂保留并引导续费（对应委托代扣扣款失败后的挽留窗口）；会员已过期＝权益终止且已出宽限窗口；未开通会员＝从未开通过会员。筛选五档＝全部＋四态；列表「会员状态」列改四色标签：有效会员＝玉绿、宽限期（待续费）＝琥珀、会员已过期＝赤陶、未开通会员＝灰描边；任一时刻四态互斥，判定与到期时间由后端下发
+（6）「0807 新增」父机构视角：新增「机构」单选筛选＋列表新增数据归属机构列（父子机构数据范围规则同「知识产品 KP · KP 列表」）</t>
         </is>
       </c>
     </row>
@@ -2440,21 +2457,23 @@
           <t>C 端用户</t>
         </is>
       </c>
-      <c r="C65" s="3" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>用户详情</t>
         </is>
       </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>（1）用户卡：头像 + 昵称 + 会员标签 + 手机号/微信号 + 地区/性别 + 活跃度（近 30 天提问次数 · 最近活跃时间）
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>0807周五更新
+（1）用户卡：头像 + 昵称 + 会员状态标签（四态）+ 手机号/微信号 + 地区/性别 + 活跃度（近 30 天提问次数 · 最近活跃时间）
 （2）「已购永享」卡：媒体项列表，点击进媒体预览弹窗
-（3）「全部订单」子表：订单号、类型、金额、支付方式、订单状态、退款状态、付款时间、操作（详情进订单详情）</t>
+（3）「全部订单」子表：订单号、类型、金额、支付方式、订单状态、退款状态、付款时间、操作（详情进订单详情）
+（4）「0807 修订」用户卡会员标签改四态（同列表口径与配色）；有效会员补充显示「有效期至 {日期}」、宽限期（待续费）显示「已于 {日期} 到期 · 宽限期内」；详情页随列表所点行真实渲染（原固定演示数据改为接通行级数据）</t>
         </is>
       </c>
     </row>
@@ -2469,26 +2488,27 @@
           <t>订单管理</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>订单列表</t>
         </is>
       </c>
-      <c r="D66" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>0722周三更新
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
+        <is>
+          <t>0807周五更新
 （1）仅显本机构订单，按付款时间降序
 （2）表格列：订单号、类型、关联知识产品、金额、支付方式、订单状态、退款状态、用户、下单时间、付款时间、兑换时间、操作（操作列固定右侧）
 （3）按 订单号/用户 搜索；筛选 类型、订单状态、退款状态（全部/未退款/退款中/部分退款/全额退款）
 （4）三个独立时间区间筛选（下单时间、支付时间、兑换时间）真实参与列表过滤（不限/近 7 天/30 天/自定义）
 （5）筛选行右侧「导出」：生成「AI问书_{机构名}_订单管理数据导出.xlsx」，严格沿用搜索、类型、状态、退款状态及三个时间区间筛选；文件头部注明导出时间与全部筛选条件
 （6）「0722 修订」订单状态筛选改为 全部 / 待支付 / 已支付 / 已核销 / 已失效（退款状态筛选维度不变）；状态色：待支付＝橙、已失效＝灰；付款时间为空（待支付 / 已失效）显「—」
-（7）「0722 修订」订单状态口径（三端统一，推翻 0716「支付成功才落库」）：用户发起支付即落库为「待支付」（微信 trade_state=NOTPAY），微信下单传 time_expire、30 分钟未支付微信自动关单（CLOSED）转「已失效」，无需自建定时器；网页支付（JSAPI/H5）不存在「支付失败」终态，用户余额不足、风控拦截等失败场景订单停留「待支付」可换方式重试；「已核销」为兑换码订单专属（无支付环节）；退款/售后走独立退款单与退款状态维度，与订单状态解耦；GMV、付费用户等营收指标仅计「已支付」订单（待支付 / 已失效不计入，相关指标 tooltip 注明）</t>
+（7）「0722 修订」订单状态口径（三端统一，推翻 0716「支付成功才落库」）：用户发起支付即落库为「待支付」（微信 trade_state=NOTPAY），微信下单传 time_expire、30 分钟未支付微信自动关单（CLOSED）转「已失效」，无需自建定时器；网页支付（JSAPI/H5）不存在「支付失败」终态，用户余额不足、风控拦截等失败场景订单停留「待支付」可换方式重试；「已核销」为兑换码订单专属（无支付环节）；退款/售后走独立退款单与退款状态维度，与订单状态解耦；GMV、付费用户等营收指标仅计「已支付」订单（待支付 / 已失效不计入，相关指标 tooltip 注明）
+（8）「0807 新增」父机构视角：新增「机构」单选筛选＋列表新增数据归属机构列（首列后），子机构订单仅可查看、退款操作置灰（父子机构数据范围规则同「知识产品 KP · KP 列表」）；「仅显本机构订单」在父机构视角放宽为「本机构＋全部子机构订单」</t>
         </is>
       </c>
     </row>
@@ -2503,20 +2523,19 @@
           <t>订单管理</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>订单列表</t>
         </is>
       </c>
-      <c r="D67" s="5" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>发起退款</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>0722周三更新
-（1）退款入口仅在可退款时显示（金额&gt;0 且退款状态不在「退款中/全额退款」）
+          <t>（1）退款入口仅在可退款时显示（金额&gt;0 且退款状态不在「退款中/全额退款」）
 （2）「0722 修订」退款操作仅对「已支付」订单出现：待支付、已失效、兑换码已核销订单无退款入口
 （3）退款金额弹窗：订单号 + 订单实付（已退&gt;0 时显「已退 ¥X · 可退 ¥Y」）+ 退款金额（默认填可退余额）+ 说明「支持部分退款 / 确认后原路退回，不可撤销」
 （4）校验：金额≤0 → toast「请输入退款金额」；超可退余额 → toast「退款金额不能超过可退余额 ¥X」
@@ -2547,7 +2566,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="E68" s="6" t="inlineStr">
         <is>
           <t>（1）头部标题（兑换码订单显「详情」，其余「订单详情」）+ 类型标签；订单不存在显空态
 （2）兑换码订单：基础卡（类型 兑换码核销/兑换码/兑换时间）+ 兑换权益卡（权益标题 + 会员时间区间）
@@ -2568,22 +2587,24 @@
           <t>兑换码</t>
         </is>
       </c>
-      <c r="C69" s="3" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
         <is>
           <t>兑换码批次列表</t>
         </is>
       </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>（1）副文案「每次生成为一个批次,点击批次查看该批次全部兑换码」
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>0807周五更新
+（1）副文案「每次生成为一个批次,点击批次查看该批次全部兑换码」
 （2）按批次名称搜索
 （3）表格列：批次名称、已兑换/生成、权益时长、可兑换时间、批次创建时间、操作（详情）；「可兑换时间」列支持升 / 降序排序（按有效开始时间）——兑换码均有明确周期，可按生效期排列
-（4）空态「还没有兑换码批次」+「点击『批量生成』创建第一个批次」</t>
+（4）空态「还没有兑换码批次」+「点击『批量生成』创建第一个批次」
+（5）「0807 新增」父机构视角：新增「机构」单选筛选＋列表新增数据归属机构列，子机构批次仅可查看、生成/导出等操作按本机构约束（父子机构数据范围规则同「知识产品 KP · KP 列表」）</t>
         </is>
       </c>
     </row>
@@ -2608,7 +2629,7 @@
           <t>批量生成</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="E70" s="6" t="inlineStr">
         <is>
           <t>（1）弹窗：批次名称（必填）+ 权益类型（固定会员）+ 会员时长（默认3个月，1–12）+ 可兑换时间（开始 / 结束）（必填且开始≤结束）+ 生成数量（默认500）
 （2）弹窗加宽，可兑换时间（开始 / 结束）在一行内完整展示；点击时间字段后日历面板完整弹出可直接选择，不被弹窗裁切、无需滚动
@@ -2637,7 +2658,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
+      <c r="E71" s="6" t="inlineStr">
         <is>
           <t>（1）「详情」从右侧拉出抽屉：抽屉头显批次名 +「已兑换 X/Y · 权益 会员 · Z · 批次创建 时间」
 （2）按兑换用户/手机号搜索 + 状态筛选；「导出」生成「AI问书_{机构名}_兑换码_{批次名}数据导出.xlsx」，含批次信息与兑换码明细（有效期、兑换人、兑换时间、权益到期时间）；头部注明导出时间与筛选条件
@@ -2656,20 +2677,49 @@
           <t>数据看板</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>机构筛选（父机构视角）</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
+        <is>
+          <t>0807周五新增
+（1）「0807 新增」父机构视角：页头「导出」左侧新增「机构」多选筛选（位置与主控台一致；选项＝本机构（父机构）＋全部子机构，默认全选、支持跨机构任意组合勾选，交互样式与主控台机构多选完全一致）；活跃概览、用户留存与四个主题 Tab 的全部指标随所选机构集合联动——绝对量按集合聚合、率类按集合整体口径重算；子机构/独立机构视角无此筛选、保持现状
+（2）「0807 修订」导出 Sheet 结构对齐页面栏目：活跃概览 / 用户留存 / 区间分析 三个 Sheet（与页面三区块一一对应）；「区间分析」将四个主题 Tab 合并为一个 Sheet、行首列标注主题 Tab 名（用户分析 / 提问分析 / 营收分析 / 热门 KP）；父机构视角头部注明机构范围——导出数据随机构多选联动，不单独产出分机构明细</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>机构后台 PC（机构运营）</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>数据看板</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>用户分析 Tab</t>
         </is>
       </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E72" s="6" t="inlineStr">
-        <is>
-          <t>0722周三更新
-（1）0717 二批 #8：页面自上而下——① 活跃概览（0724 修订：页级常驻，居用户留存上方，固定滚动窗口实时快照，见下）② 用户留存（页级常驻，一行三张等宽指标卡，卡片式回归、与平台整体风格一致）③ 区间分析条（轻量样式：左标题 + 右时间筛选，去掉白底 / 灰框容器）④ 四个主题 Tab（用户分析/提问分析/营收分析/热门 KP）。页头只保留「导出」，导出生成「AI问书_{机构名}_数据看板数据导出.xlsx」，七个 Sheet 全量覆盖页面内容（活跃概览按固定滚动窗口快照口径导出）；头部注明导出时间、所选区间起止与口径
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>0807周五更新
+（1）0717 二批 #8：页面自上而下——① 活跃概览（0724 修订：页级常驻，居用户留存上方，固定滚动窗口实时快照，见下）② 用户留存（页级常驻，一行三张等宽指标卡，卡片式回归、与平台整体风格一致）③ 区间分析条（轻量样式：左标题 + 右时间筛选，去掉白底 / 灰框容器）④ 四个主题 Tab（用户分析/提问分析/营收分析/热门 KP）。页头只保留「导出」，导出生成「AI问书_{机构名}_数据看板数据导出.xlsx」。「0807 修订」（补录 0807-3 导出定稿）导出 Sheet 结构对齐页面栏目：活跃概览 / 用户留存 / 区间分析 三个 Sheet（与页面三区块一一对应，「区间分析」将四个主题 Tab 合并为一个 Sheet、行首列标注 Tab 名，活跃概览按固定滚动窗口快照口径导出）；头部注明导出时间、所选区间起止与口径
 （2）时间口径收敛为两类：用户留存＝按注册时间（独立筛选、不受区间影响，活跃口径＝注册后第 N 天发生登录或提问行为，完整公式在卡面口径问号内）；其余指标＝随「区间分析」时间筛选联动并环比（活跃概览除外，0724 修订为固定滚动窗口实时快照）。0717 二批 #8.3：删除留存段底部「数据更新至 …」脚注，界面不再显示
 （3）0717 二批 #8.2/#8.4：活跃概览（日活 / 周活 / 月活）一行三卡，与对应对比窗口环比（KPI 卡同款 Delta + 对比窗口）；位置与统计口径按 0724 修订执行（页级常驻居用户留存上方、固定滚动窗口实时快照，见下）
 （4）② 用户留存（标「按注册时间」，页级常驻段，位于活跃概览下方）：口径即注册日，「注册批次」更名「注册时间」便于理解；口径问号 InfoDot 紧跟「用户留存」标题之后；常驻说明「观察注册用户在第 1 / 7 / 30 天是否仍然活跃，不受区间筛选影响」；右侧「注册时间：最新可统计 ▼」下拉（选项：最新可统计 / 自定义日期，0724 修订精简）；选「自定义日期」弹单日日历面板（视觉同区间选择器的自定义日历，但只选具体某一天，因留存按单个注册日观察）。0717 #8：选定具体日期后回显在下拉触发器上（如「注册时间：2026-06-30」），不再停留显示「自定义日期」字样
@@ -2692,28 +2742,28 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B73" s="3" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>数据看板</t>
         </is>
       </c>
-      <c r="C73" s="3" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>提问分析 Tab</t>
         </is>
       </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="inlineStr">
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
         <is>
           <t>（1）5 KPI：总提问、人均提问、平均会话轮次、答案点赞率、答案反馈率（InfoDot 指向答案反馈工作台）
 （2）提问量趋势面积折线图（区间联动 x 轴）
@@ -2722,31 +2772,30 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>数据看板</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>营收分析 Tab</t>
         </is>
       </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>0722周三更新
-（1）小节① 收入与转化（5 KPI）：区间 GMV、付费用户、付费转化率、ARPPU、续费率
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>（1）小节① 收入与转化（5 KPI）：区间 GMV、付费用户、付费转化率、ARPPU、续费率
 （2）小节② 退款（4 KPI）：退款金额、退款率、退款订单数、净 GMV（扣退款）
 （3）小节③ 转化漏斗（3 卡）：受限内容触发率、会员漏斗（看到会员页→点击购买→完成支付）、永享转化（触发永享墙→完成购买）
 （4）「0722 修订」小节①新增第 6 个 KPI「回流会员」（区间内开通会员、且开通时会员状态为已过期的用户数；不算新增、不算续费），KPI 行改为 3 列两行
@@ -2754,148 +2803,150 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>数据看板</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>热门 KP Tab</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
         <is>
           <t>（1）3 榜单（每榜 TOP10，数值按区间缩放、万进制）：被提问数 TOP10、付费转化贡献 TOP10、永享购买 TOP10
 （2）排名前 3 带奖牌样式；每行可点击下钻该 KP 详情</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>数据看板</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>数据看板 · 指标周期说明</t>
         </is>
       </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E76" s="6" t="inlineStr">
-        <is>
-          <t>0722周三更新
-（1）指标按统计口径分三类（0724 修订：日活 / 周活 / 月活为固定滚动窗口实时快照、各自与上一等长窗口环比，不归区间统计）：① 实时快照——累计 / 存量，如主控台累计 GMV、当前会员、KP 占用，截至当前的实时值、不参与环比；② 区间统计——随今日 / 7 日 / 30 日联动并与上一等长周期环比，如新增用户、区间 GMV、区间提问、付费转化；③ 成熟 cohort——留存率，独立队列口径、不跟随全局筛选。① 归「实时」分区、② 归「区间 / 经营分析」分区、③ 用独立队列筛选
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>（1）指标按统计口径分三类（0724 修订：日活 / 周活 / 月活为固定滚动窗口实时快照、各自与上一等长窗口环比，不归区间统计）：① 实时快照——累计 / 存量，如主控台累计 GMV、当前会员、KP 占用，截至当前的实时值、不参与环比；② 区间统计——随今日 / 7 日 / 30 日联动并与上一等长周期环比，如新增用户、区间 GMV、区间提问、付费转化；③ 成熟 cohort——留存率，独立队列口径、不跟随全局筛选。① 归「实时」分区、② 归「区间 / 经营分析」分区、③ 用独立队列筛选
 （2）每个指标悬浮面板统一写清：指标定义、分子/分母、去重主键、时区、统计周期、上一周期与差值单位；累计/快照指标明确标注“不参与环比”
-（3）今日 00:00–当前时刻对比昨日相同经过时长；近7/30天及自定义区间对比紧邻的上一等长区间；计数/金额用相对百分比，率类用百分点，时长用绝对差
+（3）今日 00:00–当前时刻对比昨日相同经过时长；近7/30天及自定义区间对比紧邻的上一等长区间；计数/金额用相对百分比，率类为绝对差、统一以「%」符号展示（0807 修订：原「N 个百分点」文案改为「N%」，与计数类视觉一致，差值口径在指标 tooltip 注明），时长用绝对差
 （4）上一周期为0时不计算无穷增幅，统一显示“上期为0，暂无可比增幅”；趋势按精确去重数据计算，不再使用0.62/0.42等估算系数；今日趋势按小时
 （5）「0722 修订」统一去重规则并全量落 tooltip：规模指标按用户去重——区间内按用户 ID 精确去重，同一用户跨天重复只计 1 人（活跃用户、新增 C 端、付费用户、提问用户等）；强度指标按人天——用户 × 自然日累加（日均活跃 DAU 均值、人均提问等）；两后台所有涉去重指标的悬浮口径均标注所属类别与去重口径。例：某用户 7 天区间内第 1、2 天活跃——「活跃用户」计 1 人，「日均活跃」贡献 2 个人天
 （6）「0724 修订」悬浮 tooltip 去重规则表述统一：去重规则不再混在指标定义句中，tooltip 内独立成条「· 去重：xxxx」；逐指标去重口径见附表一 / 附表二新增的「去重规则」列</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B77" s="3" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>答案反馈</t>
         </is>
       </c>
-      <c r="C77" s="3" t="inlineStr">
+      <c r="C78" s="4" t="inlineStr">
         <is>
           <t>答案反馈工作台</t>
         </is>
       </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>（1）副文案「前台答案点踩/反馈记录，供运营定位问题、迭代知识库」
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
+        <is>
+          <t>0807周五更新
+（1）副文案「前台答案点踩/反馈记录，供运营定位问题、迭代知识库」
 （2）表格列：问题、反馈标签、反馈人（昵称 + 会员标签）、提交时间、操作（详情）
 （3）按 问题/反馈人 搜索；筛选 反馈标签（全部/没有帮助/虚假信息/有害·不安全/其他）+ 提交时间区间
-（4）「导出」（按钮文案统一为「导出」，不再带 XLSX 字样）：生成「AI问书_{机构名}_答案反馈数据导出.xlsx」，仅含筛选后的问答文本与必要反馈元数据、不含媒体/溯源；头部注明导出时间与筛选条件</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+（4）「导出」（按钮文案统一为「导出」，不再带 XLSX 字样）：生成「AI问书_{机构名}_答案反馈数据导出.xlsx」，仅含筛选后的问答文本与必要反馈元数据、不含媒体/溯源；头部注明导出时间与筛选条件
+（5）「0807 修订」反馈人会员标签随四态口径：有效会员＝玉绿「有效会员」、宽限期（待续费）＝琥珀「宽限期」、会员已过期＝赤陶「已过期」、未开通不挂标（保持视觉克制）；详情弹窗元信息行同规则
+（6）「0807 新增」父机构视角：新增「机构」单选筛选＋列表新增数据归属机构列，子机构反馈仅可查看（父子机构数据范围规则同「知识产品 KP · KP 列表」）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>答案反馈</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>答案反馈详情弹窗</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>（1）顶部标签 + 反馈人（+会员标签）+ 时间，浅灰分隔线
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>（1）顶部标签 + 反馈人（+会员状态标签，四态口径）+ 时间，浅灰分隔线
 （2）仿前台 AI 会话气泡：用户问题（主题色气泡）+ AI 答案（白底气泡）
 （3）答案下「相关媒体资源」横向缩略图条（图/音/视图标 + 名，点击放大预览）</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>客服配置</t>
         </is>
       </c>
-      <c r="C79" s="3" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>客服配置</t>
         </is>
       </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
         <is>
           <t>（1）客服二维码（必填，上传企微/个微二维码）
 （2）客服电话（非必填，有则展示）
@@ -2904,28 +2955,28 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr">
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>系统配置</t>
         </is>
       </c>
-      <c r="C80" s="3" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>AI 会员价格</t>
         </is>
       </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
         <is>
           <t>（1）「0718 修订」价格配置按两种购买方式分组展示，向运营明示每档金额——① 连续包月（自动续费）：首月价格（首月特惠，默认 ¥9.9，仅首次开通的首月扣款）+ 次月起价格（默认 ¥19.9/月，第 2 个月起每月自动扣款）；② 单月（一次性购买 · 不自动续费）：单月价格（默认 ¥19.9/1 个月，一次性扣款、到期自动失效不再扣费）；每档附前台展示位置说明，与前台「开通会员」两档一一对应
 （2）续费规则只读：「按月自动续费，会员到期后 72 小时为服务缓冲期 · 暂不可编辑」
@@ -2938,28 +2989,28 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t>系统配置</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t>回答策略</t>
         </is>
       </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="4" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
         <is>
           <t>（1）副标题「知识库未检索到相关知识时」三选一
 （2）严谨模式：仅用知识库，未命中回「暂无相关资料」（医疗/合规场景）
@@ -2969,84 +3020,84 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>个人中心</t>
         </is>
       </c>
-      <c r="C82" s="3" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t>个人中心</t>
         </is>
       </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="inlineStr">
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
         <is>
           <t>（1）账户信息只读：账户名称、姓名、所属机构、上级机构、角色、手机号、账户状态；联系方式仅保留手机号
 （2）底部灰字「账户信息由平台统一管理，仅头像可自助更新；若需更改其他账户信息，请联系平台管理员」</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>个人中心</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>个人中心</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>更换头像（裁剪）</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
+      <c r="E84" s="6" t="inlineStr">
         <is>
           <t>（1）相册选图 → 圆形裁剪弹层（缩放滑块 + 拖拽定位）
 （2）确定按 canvas 输出 256px 头像，顶栏头像同步回显 → toast「头像已更新」</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>机构后台 PC（机构运营）</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr">
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t>个人中心</t>
         </is>
       </c>
-      <c r="C84" s="3" t="inlineStr">
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t>个人中心</t>
         </is>
       </c>
-      <c r="D84" s="3" t="inlineStr">
+      <c r="D85" s="3" t="inlineStr">
         <is>
           <t>修改登录密码</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
+      <c r="E85" s="6" t="inlineStr">
         <is>
           <t>（1）弹窗：旧密码（InfoDot「忘记请联系平台管理员重置」）+ 新密码 + 确认新密码
 （2）校验：旧密码非空、新密码 8~16 位且含字母+数字、两次一致
@@ -3054,117 +3105,152 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>机构后台 PC（机构运营）</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>评审工具</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t>原型清单</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>（1）〔评审〕三端通用站点地图，列全站页面便于评审跳转，同端内部导航</t>
-        </is>
-      </c>
-    </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>机构后台 PC（机构运营）</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>评审工具</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>原型清单</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>（1）〔评审〕三端通用站点地图，列全站页面便于评审跳转，同端内部导航</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>机构后台 PC（机构运营）</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>评审工具</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>机构类型切换</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>0807周五新增
+（1）「0807 新增」〔演示〕顶栏新增「机构类型」三态切换（父机构 / 子机构 / 独立机构，仅原型演示、非上线功能，上线后由登录账号所属机构在机构主数据中的父子关系决定）：用于预览三类机构在机构后台的界面差异，切换即时生效并本地持久化
+（2）概念定义：父机构＝本机构下辖 N 个机构；子机构＝有父机构的机构；独立机构＝无父无子的机构
+（3）父机构视角：知识产品 KP / Agent 人设 / C 端用户 / 订单管理 / 兑换码 / 答案反馈 六页出现「机构」单选筛选与数据归属机构展示；主控台 / 数据看板出现「机构」多选筛选联动全部指标
+（4）子机构视角：界面与现状一致（无机构筛选），个人中心显示上级机构；独立机构视角：界面与现状一致，个人中心无上级机构
+（5）数据权限口径（与平台侧角色权限说明一致）：机构后台角色的「可操作」权限仅针对本机构数据——父机构可见下属子机构数据（列表可筛、看板可汇总），但对子机构数据仅可查看、操作置灰并提示「仅可操作本机构数据」；平台后台角色的「可操作」权限可跨机构操作全平台数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B86" s="3" t="inlineStr">
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>登录与主控台</t>
         </is>
       </c>
-      <c r="C86" s="3" t="inlineStr">
+      <c r="C88" s="4" t="inlineStr">
         <is>
           <t>登录页</t>
         </is>
       </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>（1）左侧动态毛玻璃品牌区 + 标语「答案有出处 · 知识更可信」
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>0807周五更新
+（1）「0807 修订」左侧动态毛玻璃品牌区（浮动 blob + 横版真实品牌 LOGO（图标＋中英文字），与机构后台登录页同资产）+ 标语「答案有出处 · 知识更可信」
 （2）右侧登录卡：账号、密码、图形验证码（4 位，排除易混字符，可换一张）
 （3）「登录遇到问题?」→ toast「请联系管理员」</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B87" s="3" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>登录与主控台</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C89" s="4" t="inlineStr">
         <is>
           <t>主控台</t>
         </is>
       </c>
-      <c r="D87" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>0722周三更新
-（1）页头机构筛选覆盖全部机构（来自机构主数据，非固定名单）；父机构选项带「父机构」标签；选中父机构＝自动汇总该父机构自身及其全部子机构数据，并在页头下方标注「含子机构：A、B」，让看数人明确汇总范围
-（2）右侧「导出」：生成「AI问书_全域主控台数据导出.xlsx」，沿用当前机构范围与时间筛选；实时/经营分析两 Sheet 分别标注实时统计时间与区间起止，指标全量含环比
-（3）实时总览（标「实时」，不随时间变）：入驻机构数、累计用户、累计 GMV（资金 100% 进各机构账户）、净 GMV（扣退款，平台不参与分账）、提问总量，每卡带 InfoDot
-（4）经营分析周期与机构后台同口径；每个指标悬浮面板详细展示定义、周期、上一周期、差值单位、零基线处理和是否汇总下级机构
-（5）平台提问量趋势面积图 + 页脚单位规范
-（6）「0722 修订」经营分析新增「续费率」（区间内到期且完成续费的会员数 ÷ 同区间到期会员数）与「回流会员」（区间内开通会员、且开通时会员状态为已过期的用户数，不算新增不算续费），KPI 行改为 3 列两行；「新增会员」口径定稿＝区间内历史首次开通会员（续费、回流均不计入），新增 / 续费 / 回流三者互斥、与机构后台统一</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>0807周五更新
+（1）「0807 修订」页头「机构」筛选由单选升级为多选（覆盖全部机构、来自机构主数据非固定名单；默认全选＝全平台口径）：交互与机构后台主控台机构多选一致——选项行自绘勾选框、父机构选项带「父机构」标、顶部「全部机构」快捷全选（分隔线隔开），触发器回填所选机构名（全选显「全部机构」、部分选择顿号拼接、超宽省略号），至少保留一家；实时总览与经营分析全部指标随所选机构集合联动——计数/金额类绝对量按集合聚合、率类按集合整体口径重算（非各机构简单相加；父机构含其全部子机构、父子同选自动去重）；「入驻机构数」卡显示所选机构数量，区块副标题机构范围超 3 家收敛为「A、B、C 等 N 家」
+（2）「0807 删除」原「选中父机构＝自动汇总该父机构自身及其全部子机构数据，并在页头下方标注『含子机构：A、B』」的汇总口径说明行（紫色引用块）整体删除——机构范围已由多选筛选器直观表达，无需另行说明
+（3）「0807 修订」右侧「导出」：生成「AI问书_全域主控台数据导出.xlsx」，沿用当前机构多选集合与时间筛选（头部筛选条件注明机构范围）；实时/经营分析两 Sheet 分别标注实时统计时间与区间起止，指标全量含环比
+（4）实时总览（标「实时」，不随时间变）：入驻机构数、累计用户、累计 GMV（资金 100% 进各机构账户）、净 GMV（扣退款，平台不参与分账）、提问总量，每卡带 InfoDot
+（5）「0807 新增」实时总览第二行新增内容供给三卡（3 等分满行、与首行左右对齐）：① 知识产品 KP 总数（副行：已发布 / 草稿 / 已下架，数量＋占比）② 知识库文件总数（副行：文档 / 图片 / 音频 / 视频四类，数量＋占比）③ 知识库存储总量（TB，副行：文档与媒体资源的容量＋占比，两者互补 100%，与前两卡「数量＋占比」规则一致）；两行卡片行距 16px 与经营分析多行卡一致——平台运营能力＝机构规模 × 内容供给 × 用户消费 × 商业化，补齐「内容供给」存量视角；三卡均为实时快照、每卡带 InfoDot 口径，导出实时总览 Sheet 同步含此三指标（含副行分布明细）
+（6）经营分析周期与机构后台同口径；每个指标悬浮面板详细展示定义、周期、上一周期、差值单位、零基线处理和是否汇总下级机构
+（7）平台提问量趋势面积图 + 页脚单位规范
+（8）「0722 修订」经营分析新增「续费率」（区间内到期且完成续费的会员数 ÷ 同区间到期会员数）与「回流会员」（区间内开通会员、且开通时会员状态为已过期的用户数，不算新增不算续费），KPI 行改为 3 列两行；「新增会员」口径定稿＝区间内历史首次开通会员（续费、回流均不计入），新增 / 续费 / 回流三者互斥、与机构后台统一</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B88" s="3" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>机构管理</t>
         </is>
       </c>
-      <c r="C88" s="3" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>机构列表</t>
         </is>
       </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E88" s="4" t="inlineStr">
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
         <is>
           <t>（1）表格列改为“二级机构域名”，仅展示 test-aba，不展示根域名；机构名称后仅父机构显示“父机构”标签（子机构的从属由「上级机构」列体现、普通机构无从属，均不加标签）。KP/存储为当前占用，Token 为当前订阅周期消耗
 （2）按 机构名称/上级机构/ID 模糊搜索；筛选 机构状态（全部/正常/停用）、套餐（基础/专业/旗舰/定制）、上级机构
@@ -3174,56 +3260,56 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>机构管理</t>
         </is>
       </c>
-      <c r="C89" s="3" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>机构从属命名规范</t>
         </is>
       </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E89" s="4" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
         <is>
           <t>（1）「上级机构」＝关系字段（某机构的上级是谁），用于列头、详情字段与筛选；「父机构 / 子机构」＝角色标签（是否有下级 / 上级的身份），仅用于名称后标签与下拉选项后缀；两词分工不混用
 （2）数据归属列（订单 / 用户 / KP / 反馈属于哪个机构）在平台后台统一命名为「机构」，不再使用「归属机构」「所属机构」等变体</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr">
+      <c r="B92" s="3" t="inlineStr">
         <is>
           <t>机构管理</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="C92" s="3" t="inlineStr">
         <is>
           <t>机构列表</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>停用 / 恢复</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
+      <c r="E92" s="6" t="inlineStr">
         <is>
           <t>（1）操作列「停用/恢复」走二次确认
 （2）停用父机构只暂停父机构自身，不自动停用子机构，避免误伤独立经营主体；确认框列出仍在运营的子机构，如需停用须逐家确认并分别留痕
@@ -3232,28 +3318,28 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B91" s="3" t="inlineStr">
+      <c r="B93" s="3" t="inlineStr">
         <is>
           <t>机构管理</t>
         </is>
       </c>
-      <c r="C91" s="3" t="inlineStr">
+      <c r="C93" s="3" t="inlineStr">
         <is>
           <t>机构列表</t>
         </is>
       </c>
-      <c r="D91" s="3" t="inlineStr">
+      <c r="D93" s="3" t="inlineStr">
         <is>
           <t>新建机构</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
+      <c r="E93" s="6" t="inlineStr">
         <is>
           <t>（1）弹窗加宽；域名前缀与固定后缀同框同行展示，前缀可编辑、分隔线右侧“-aba.{当前环境根域名}”置灰只读；只允许小写字母、数字与中划线且全局唯一
 （2）上级机构下拉仅列出顶级机构（含“无（顶级机构）”）；不列出已有上级的子机构，保证只有父 / 子两层。选中某顶级机构后，本机构成为其子机构、该顶级机构成为父机构
@@ -3261,28 +3347,28 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B92" s="3" t="inlineStr">
+      <c r="B94" s="3" t="inlineStr">
         <is>
           <t>机构管理</t>
         </is>
       </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="C94" s="3" t="inlineStr">
         <is>
           <t>机构详情 · 基本资料</t>
         </is>
       </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E92" s="4" t="inlineStr">
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
         <is>
           <t>（1）表单含机构域名前缀：前缀与“-aba.{当前环境根域名}”同框同行、后缀置灰只读；保存前全局唯一校验，不再额外展示固定路由说明
 （2）页头状态后仅父机构显示“父机构”标签。上级机构字段按角色分三态——子机构不再只读：可直接改选其他顶级机构为新上级（二次确认后生效），并提供「取消关联，转为独立机构」操作（二次确认；解除后本机构变普通机构，原父机构若再无其他子机构则父机构身份同步解除）；父机构仍置灰并提示“已是父机构，不能再设上级机构（仅支持父 / 子两层）”；普通机构可选一个顶级机构作为上级。停用父机构默认不级联停用子机构
@@ -3291,28 +3377,28 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>机构管理</t>
         </is>
       </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="C95" s="3" t="inlineStr">
         <is>
           <t>机构详情 · 订阅配额</t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E93" s="4" t="inlineStr">
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
         <is>
           <t>（1）KP数与存储“已用”始终取机构当前实际占用，不按订阅订单拆分；Token“已用”仅取当前订阅周期消耗，新订阅生效时清零重新累计
 （2）新订阅生效即整体替换三项基础上限，不结转旧订阅剩余额度；加油包只在所属当前订阅内累加，到期不结转
@@ -3321,28 +3407,28 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr">
+      <c r="B96" s="3" t="inlineStr">
         <is>
           <t>机构管理</t>
         </is>
       </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="C96" s="3" t="inlineStr">
         <is>
           <t>机构详情 · 订阅配额</t>
         </is>
       </c>
-      <c r="D94" s="3" t="inlineStr">
+      <c r="D96" s="3" t="inlineStr">
         <is>
           <t>新建/复制订阅</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
+      <c r="E96" s="6" t="inlineStr">
         <is>
           <t>（1）弹窗：套餐六选一（体验/基础/专业/旗舰/定制/不限，3 列网格卡片，弹窗 780 宽内容全显不滑动）→ 自动带出 KP/存储/Token 三项额度（仅填数字）；改额度后自动匹配套餐：命中某预设则选中它、否则套餐自动变「定制版」（不再额外标 badge）
 （2）有效期（必填）、商务负责人（选填）、备注（选填）
@@ -3353,28 +3439,28 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B95" s="3" t="inlineStr">
+      <c r="B97" s="3" t="inlineStr">
         <is>
           <t>机构管理</t>
         </is>
       </c>
-      <c r="C95" s="3" t="inlineStr">
+      <c r="C97" s="3" t="inlineStr">
         <is>
           <t>机构详情 · 订阅配额</t>
         </is>
       </c>
-      <c r="D95" s="3" t="inlineStr">
+      <c r="D97" s="3" t="inlineStr">
         <is>
           <t>加油包抽屉</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
+      <c r="E97" s="6" t="inlineStr">
         <is>
           <t>（1）右侧抽屉，提示“即时生效，仅在当前订阅周期累加；有效期跟随该订阅至 {endDate}，不结转下一订阅”
 （2）新建加油包：KP/存储/Token 三项额度（至少一项 &gt;0，否则 toast「请至少为一项加量额度填写大于 0 的值」）+ 备注
@@ -3383,28 +3469,28 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B96" s="3" t="inlineStr">
+      <c r="B98" s="3" t="inlineStr">
         <is>
           <t>机构管理</t>
         </is>
       </c>
-      <c r="C96" s="3" t="inlineStr">
+      <c r="C98" s="3" t="inlineStr">
         <is>
           <t>机构详情 · 订阅配额</t>
         </is>
       </c>
-      <c r="D96" s="3" t="inlineStr">
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t>订阅详情/删除</t>
         </is>
       </c>
-      <c r="E96" s="4" t="inlineStr">
+      <c r="E98" s="6" t="inlineStr">
         <is>
           <t>（1）订阅详情弹窗：订阅 ID/套餐/额度/已用/有效期/商务负责人/状态/加油包数/创建时间/创建人/备注
 （2）删除规则（0714 与研发对齐，带护栏放开）：① 未生效订单——可直接删除，常规二次确认 ② 已生效订单——可删除，确认弹窗列明后果：连带删除其全部加油包、机构立即失去该订阅配额；若 KP/存储/Token 任一用量 &gt;0，追加红色强警告「该订阅已产生用量，删除将立即中断机构服务」 ③ 已过期订单——不可删除（商业单据审计留存，操作列不出删除入口）
@@ -3412,119 +3498,121 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B97" s="3" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t>机构管理</t>
         </is>
       </c>
-      <c r="C97" s="3" t="inlineStr">
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t>机构详情 · 机构配置</t>
         </is>
       </c>
-      <c r="D97" s="3" t="inlineStr">
+      <c r="D99" s="3" t="inlineStr">
         <is>
           <t>LLM 配置</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
+      <c r="E99" s="6" t="inlineStr">
         <is>
           <t>（1）单选：平台默认（使用平台统一模型与额度，选中）/ 自配厂商（机构自有 API Key 接入，暂未开放·灰禁）
 （2）「保存」→ toast「已保存」</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B98" s="3" t="inlineStr">
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t>机构管理</t>
         </is>
       </c>
-      <c r="C98" s="3" t="inlineStr">
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>机构详情 · 机构配置</t>
         </is>
       </c>
-      <c r="D98" s="3" t="inlineStr">
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t>联网配置</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
+      <c r="E100" s="6" t="inlineStr">
         <is>
           <t>（1）开关「允许联网检索」（默认开），点击 toast「已关闭/已开启联网检索」
 （2）注「开启后知识库未命中可联网补充检索（标注来源）· 开关即时生效」——此即 C 端会话「智能搜索」开关的机构级总开关</t>
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B99" s="3" t="inlineStr">
+      <c r="B101" s="3" t="inlineStr">
         <is>
           <t>机构管理</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
+      <c r="C101" s="4" t="inlineStr">
         <is>
           <t>机构详情 · 机构配置</t>
         </is>
       </c>
-      <c r="D99" s="5" t="inlineStr">
+      <c r="D101" s="4" t="inlineStr">
         <is>
           <t>微信配置</t>
         </is>
       </c>
-      <c r="E99" s="6" t="inlineStr">
-        <is>
-          <t>0722周三更新
+      <c r="E101" s="5" t="inlineStr">
+        <is>
+          <t>0807周五更新
 （1）微信公众号字段改为“网页授权回调地址”，微信开放平台字段改为“授权回调地址”；均填写完整 URL，并继续校验与微信后台配置一致
-（2）微信支付（必填，用于支付/退款/自动续费，未配置前台无法下单）：商户号 MchID、APIv3 密钥（掩码）、商户证书（上传 apiclient_cert.pem）；限制说明（商户号须与公众号 AppID 关联绑定/需上传证书且 APIv3 密钥在商户平台设置/退款·自动续费依赖支付能力）；保存 toast「已保存微信支付配置」
+（2）微信支付（必填，用于支付/退款/自动续费，未配置前台无法下单）：商户号 MchID、API v3 密钥（掩码）、商户证书（上传 apiclient_cert.pem）；限制说明（商户号须与公众号 AppID 关联绑定/需上传证书且 API v3 密钥在商户平台设置/退款·自动续费依赖支付能力）；保存 toast「已保存微信支付配置」
 （3）「0722 修订」微信公众号卡片新增「网页授权域名校验文件」上传（MP_verify_xxx.txt，公众号后台生成，需放置于网页授权域名根目录下）
 （4）「0722 修订」校验文件归属结论：域名校验文件属公众平台（公众号后台）要求，用于「网页授权域名 / JS 接口安全域名 / 业务域名」校验；微信开放平台的网站应用（扫码登录）不需要校验文件——故上传入口放「微信公众号」卡片，开放平台卡片不变
-（5）「0722 修订」微信支付卡片新增「商户 API 私钥」上传（apiclient_key.pem，与商户证书 apiclient_cert.pem 成对，调用微信支付 APIv3 接口签名必需）</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+（5）「0722 修订」微信支付卡片新增「商户 API 私钥」上传（apiclient_key.pem，与商户证书 apiclient_cert.pem 成对，调用微信支付 API v3 接口签名必需）
+（6）「0807 新增」微信支付卡片新增四项参数，字段顺序：商户号 → API v2 密钥 → API v3 密钥 → 商户证书 → 商户 API 私钥 → 支付公钥 ID → 支付公钥文件 → 委托代扣包月模板 ID（密钥按版本号升序、证书/验签/业务参数依次排列）：① API v2 密钥（掩码文本，置于 API v3 密钥之前）——微信支付 v2 版接口的签名密钥（32 位，商户平台「账户中心-API 安全」设置）；委托代扣（自动续费）的签约/扣款接口体系仍走 v2 签名，配置连续包月必需，与 API v3 密钥并存不互斥 ② 支付公钥 ID（文本，PUB_KEY_ID_ 开头，置于商户 API 私钥之后）——微信支付「公钥模式」验签标识，2024 年起新注册商户默认发放微信支付公钥（替代平台证书轮换机制），验签时按回调头 Wechatpay-Serial 匹配此 ID
+（7）「0807 修订」敏感配置项（公众号 / 开放平台 AppSecret、API v3 密钥、API v2 密钥）输入框增加显隐眼睛：默认脱敏（•••• + 尾 4 位、只读），点眼睛切明文（可编辑）、再点隐藏——便于核对配置又防误改与旁窥
+（8）「0807 新增」③ 支付公钥文件（上传 pub_key.pem，紧随支付公钥 ID）——与公钥 ID 配套的公钥文件，商户平台下载，用于验证微信支付应答与回调签名（新商户公钥验签、存量商户平台证书验签，按商户号实际发放形态二选一） ④ 委托代扣包月模板 ID（文本，置于卡片末尾业务参数位）——委托代扣「签约模板」经微信审核通过后分配的模板 ID（plan_id），C 端用户签约连续包月扣费时传入；卡片限制说明区同步补充四项参数用途一句话说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr">
+      <c r="B102" s="3" t="inlineStr">
         <is>
           <t>机构管理</t>
         </is>
       </c>
-      <c r="C100" s="5" t="inlineStr">
+      <c r="C102" s="3" t="inlineStr">
         <is>
           <t>机构详情 · 用量看板</t>
         </is>
       </c>
-      <c r="D100" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E100" s="6" t="inlineStr">
-        <is>
-          <t>0722周三更新
-（1）当前生效订阅卡置于时间筛选上方，归入“实时订阅与资源占用”；KP/存储显示占用量，Token 显示当前订阅周期消耗量，不随时间筛选变化
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>（1）当前生效订阅卡置于时间筛选上方，归入“实时订阅与资源占用”；KP/存储显示占用量，Token 显示当前订阅周期消耗量，不随时间筛选变化
 （2）页面明确拆分“实时存量”和“区间运营分析”；今日/近7天/近30天/自定义仅联动活跃、新增、提问、GMV、付费用户及 LLM 区间消耗
 （3）配额阈值预警条：「Token 已用 X%，已于 日期 向机构联系人（姓名·手机号）发送 70%/80% 预警短信；达 90%/95% 将再次提醒。配额可在『订阅配额』调整」
 （4）阈值预警短信触达规则与文案模版：触发档位＝本订阅周期 Token 消耗率达 70% / 80% / 90% / 95% 四档，每档首次达到时向机构联系人手机号各发一次，同一计费周期内同档不重复、进入下一周期归零重置；四档共用一条参数化模版，签名用平台方「【AI问书】」（区别于 C 端验证码短信用机构名签名）。文案：【AI问书】您的机构「${orgName}」本订阅周期 Token 用量已达 ${pct}%，达上限后 C 端问答将被暂停，请及时登录机构后台「订阅配额」扩容或联系客服。如已处理请忽略本短信。（${orgName}=机构名，${pct}=当前消耗率）
@@ -3536,28 +3624,28 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B101" s="3" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
         <is>
           <t>机构管理</t>
         </is>
       </c>
-      <c r="C101" s="3" t="inlineStr">
+      <c r="C103" s="3" t="inlineStr">
         <is>
           <t>机构详情 · 品牌外观</t>
         </is>
       </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr">
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
         <is>
           <t>（1）机构 Logo：上传 Logo 智能取色（自动读取像素主色/次色回填主辅色）→ toast「已上传 · 智能取色」
 （2）主视觉色 / 辅助视觉色取色器（含 mono 色值）
@@ -3566,28 +3654,61 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B102" s="3" t="inlineStr">
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>机构管理</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>机构详情 · 机构资料</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>0807周五新增
+（1）「0807 新增」机构详情新增第 6 个 Tab「机构资料」（置于品牌外观之后、Tab 栏末位；命名取「机构资料」而非「资源库」——避免与 KP「知识库」的库概念打架）：归档与机构相关的全部资料——ICP 授权函、微信网站应用登记表、产品截图、合作协议等
+（2）支持格式与单文件上限（单个文件上限，非单次合计）：图片 PNG / JPG / GIF ≤ 20MB；文档 DOC / DOCX / PDF ≤ 50MB；其余格式拦截（不支持 PPT——需求极少）
+（3）批量上传：复用知识产品 KP 知识库的上传弹窗组件（多选 + 拖拽入框、每个文件独立进度条、全部完成后方可确认），研发侧零新增组件；上传完成 toast「已上传 N 个文件」
+（4）文件列表：文件名（带类型彩色图标）、类型（图片/文档）、大小、上传时间（各列可排序）；按文件名模糊搜索 + 类型筛选
+（5）操作：下载（原型 toast 示意）、删除（二次确认「删除后不可恢复，确认删除「{文件名}」？」）
+（6）预置演示数据：ICP 授权函.pdf / 微信网站应用登记表.docx / 产品截图 ×2 / 平台合作协议.pdf / 合作备忘录.pdf / 品牌演示.gif</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>平台超管后台 PC</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
         <is>
           <t>机构账户</t>
         </is>
       </c>
-      <c r="C102" s="3" t="inlineStr">
+      <c r="C105" s="3" t="inlineStr">
         <is>
           <t>机构账户列表</t>
         </is>
       </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E102" s="4" t="inlineStr">
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
         <is>
           <t>（1）表格列：账户 ID、账户名、姓名、机构、上级机构、角色（管理员/运营/只读）、状态（正常/停用）、操作（操作列固定右侧）——「所属机构」列名统一为「机构」
 （2）按 账户名/姓名 搜索；筛选 机构、上级机构、角色、状态
@@ -3595,28 +3716,28 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B103" s="3" t="inlineStr">
+      <c r="B106" s="3" t="inlineStr">
         <is>
           <t>机构账户</t>
         </is>
       </c>
-      <c r="C103" s="3" t="inlineStr">
+      <c r="C106" s="3" t="inlineStr">
         <is>
           <t>机构账户列表</t>
         </is>
       </c>
-      <c r="D103" s="3" t="inlineStr">
+      <c r="D106" s="3" t="inlineStr">
         <is>
           <t>新建 / 编辑账户</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
+      <c r="E106" s="6" t="inlineStr">
         <is>
           <t>（1）新建/编辑共用弹窗：账户名称、姓名、机构、角色、联系手机号；账户名称创建后不可修改——编辑态该字段置灰并注「账户名称创建后不可修改」；平台后台列表、详情与弹窗均完整展示手机号，不脱敏
 （2）校验账户名+姓名非空（toast「请填写账户名称与姓名」）
@@ -3625,28 +3746,28 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B104" s="3" t="inlineStr">
+      <c r="B107" s="3" t="inlineStr">
         <is>
           <t>机构账户</t>
         </is>
       </c>
-      <c r="C104" s="3" t="inlineStr">
+      <c r="C107" s="3" t="inlineStr">
         <is>
           <t>机构账户列表</t>
         </is>
       </c>
-      <c r="D104" s="3" t="inlineStr">
+      <c r="D107" s="3" t="inlineStr">
         <is>
           <t>重置密码 / 停用恢复</t>
         </is>
       </c>
-      <c r="E104" s="4" t="inlineStr">
+      <c r="E107" s="6" t="inlineStr">
         <is>
           <t>（1）重置密码 → 弹凭证弹窗（账号 + 系统生成密码）+ toast「已重置密码」
 （2）停用/恢复二次确认：停用（danger）「停用账户「X」后将无法登录机构后台，提示『账户服务已暂停』，可随时恢复」
@@ -3654,28 +3775,28 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B105" s="3" t="inlineStr">
+      <c r="B108" s="3" t="inlineStr">
         <is>
           <t>订阅订单（全域 B 端）</t>
         </is>
       </c>
-      <c r="C105" s="3" t="inlineStr">
+      <c r="C108" s="3" t="inlineStr">
         <is>
           <t>全域订阅订单</t>
         </is>
       </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E105" s="4" t="inlineStr">
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
         <is>
           <t>（1）定位：B 端订阅（机构→平台），与 C 端「全域订单」两套体系；列表只展示「订阅」，加油包不入表
 （2）顶部 5 KPI（带 InfoDot）：订阅总数、生效、未生效、加油包、90 天内到期
@@ -3684,55 +3805,55 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B106" s="3" t="inlineStr">
+      <c r="B109" s="3" t="inlineStr">
         <is>
           <t>订阅订单（全域 B 端）</t>
         </is>
       </c>
-      <c r="C106" s="3" t="inlineStr">
+      <c r="C109" s="3" t="inlineStr">
         <is>
           <t>全域订阅订单</t>
         </is>
       </c>
-      <c r="D106" s="3" t="inlineStr">
+      <c r="D109" s="3" t="inlineStr">
         <is>
           <t>加油包抽屉</t>
         </is>
       </c>
-      <c r="E106" s="4" t="inlineStr">
+      <c r="E109" s="6" t="inlineStr">
         <is>
           <t>（1）同机构详情加油包抽屉：即时生效·额度累加·有效期跟随订阅；至少一项额度 &gt;0；列出加油包记录</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B107" s="3" t="inlineStr">
+      <c r="B110" s="3" t="inlineStr">
         <is>
           <t>全域知识产品 KP</t>
         </is>
       </c>
-      <c r="C107" s="3" t="inlineStr">
+      <c r="C110" s="3" t="inlineStr">
         <is>
           <t>全域 KP 列表</t>
         </is>
       </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="inlineStr">
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
         <is>
           <t>（1）卡片网格（复用机构后台 KP 卡视觉），平台只读监管
 （2）每卡：封面 + KP 名 +「机构 · {orgName}」（平台视角必显）+ 状态标签（已发布/草稿/已下架）+ 永享标
@@ -3744,28 +3865,28 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B108" s="3" t="inlineStr">
+      <c r="B111" s="3" t="inlineStr">
         <is>
           <t>全域知识产品 KP</t>
         </is>
       </c>
-      <c r="C108" s="3" t="inlineStr">
+      <c r="C111" s="3" t="inlineStr">
         <is>
           <t>全域 KP 详情（5 Tab，与机构后台同构）</t>
         </is>
       </c>
-      <c r="D108" s="3" t="inlineStr">
+      <c r="D111" s="3" t="inlineStr">
         <is>
           <t>基础信息</t>
         </is>
       </c>
-      <c r="E108" s="4" t="inlineStr">
+      <c r="E111" s="6" t="inlineStr">
         <is>
           <t>（1）与机构后台 KP 详情·基础信息一致：封面（裁剪）+ KP 名称（必填）/简介/纸书购买链接/关联 Agent（必填）+ 保存
 （2）前台访问地址：只读展示 + 「复制链接」一键复制 C 端前台访问地址（随当前环境自动生成，携带机构 + KP），同机构后台
@@ -3774,115 +3895,34 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B109" s="3" t="inlineStr">
+      <c r="B112" s="3" t="inlineStr">
         <is>
           <t>全域知识产品 KP</t>
         </is>
       </c>
-      <c r="C109" s="3" t="inlineStr">
+      <c r="C112" s="3" t="inlineStr">
         <is>
           <t>全域 KP 详情（5 Tab，与机构后台同构）</t>
         </is>
       </c>
-      <c r="D109" s="3" t="inlineStr">
+      <c r="D112" s="3" t="inlineStr">
         <is>
           <t>知识库</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
+      <c r="E112" s="6" t="inlineStr">
         <is>
           <t>（1）与机构后台一致：上传知识文件（左右布局、向量化状态机）、文件上下架/重试/删除、类型筛选、检索状态
 （2）与机构后台一致：原『永享』Tab 取消、并入知识库——图/音/视可设永享价 + 永享/非永享标签 + 预览；设价弹窗含独立权益说明块</t>
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>平台超管后台 PC</t>
-        </is>
-      </c>
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t>全域知识产品 KP</t>
-        </is>
-      </c>
-      <c r="C110" s="3" t="inlineStr">
-        <is>
-          <t>全域 KP 详情（5 Tab，与机构后台同构）</t>
-        </is>
-      </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>定价与权益</t>
-        </is>
-      </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>（1）与机构后台一致：免费/会员 二选一互斥（0717 #5 切换前二次确认）；永享与会员两套独立权益（设了永享价的资源会员也需单独购买）</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>平台超管后台 PC</t>
-        </is>
-      </c>
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t>全域知识产品 KP</t>
-        </is>
-      </c>
-      <c r="C111" s="3" t="inlineStr">
-        <is>
-          <t>全域 KP 详情（5 Tab，与机构后台同构）</t>
-        </is>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>二维码</t>
-        </is>
-      </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>（1）与机构后台一致：二维码包列表 + 新建包 + 明细抽屉 + 下载 zip</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
-        <is>
-          <t>平台超管后台 PC</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>全域知识产品 KP</t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="inlineStr">
-        <is>
-          <t>全域 KP 详情（5 Tab，与机构后台同构）</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>分享</t>
-        </is>
-      </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>（1）与机构后台一致：分享列表 + 新建分享 + 取消分享</t>
-        </is>
-      </c>
-    </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
@@ -3891,20 +3931,101 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
+          <t>全域知识产品 KP</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>全域 KP 详情（5 Tab，与机构后台同构）</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>定价与权益</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>（1）与机构后台一致：免费/会员 二选一互斥（0717 #5 切换前二次确认）；永享与会员两套独立权益（设了永享价的资源会员也需单独购买）</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>平台超管后台 PC</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>全域知识产品 KP</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>全域 KP 详情（5 Tab，与机构后台同构）</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>二维码</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>（1）与机构后台一致：二维码包列表 + 新建包 + 明细抽屉 + 下载 zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>平台超管后台 PC</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>全域知识产品 KP</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>全域 KP 详情（5 Tab，与机构后台同构）</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>分享</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>（1）与机构后台一致：分享列表 + 新建分享 + 取消分享</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>平台超管后台 PC</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
           <t>全域 Agent 人设</t>
         </is>
       </c>
-      <c r="C113" s="3" t="inlineStr">
+      <c r="C116" s="3" t="inlineStr">
         <is>
           <t>全域 Agent 列表</t>
         </is>
       </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E113" s="4" t="inlineStr">
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="inlineStr">
         <is>
           <t>（1）卡片网格：渐变封面 + Agent 名 +「机构 · {org}」+ 类型标签 +「关联 KP N 个」+ 音色（已设/默认）
 （2）按 Agent 名称搜索 + 机构筛选
@@ -3912,94 +4033,6 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>平台超管后台 PC</t>
-        </is>
-      </c>
-      <c r="B114" s="3" t="inlineStr">
-        <is>
-          <t>全域 Agent 人设</t>
-        </is>
-      </c>
-      <c r="C114" s="3" t="inlineStr">
-        <is>
-          <t>全域 Agent 详情（Prompt 平台可编辑）</t>
-        </is>
-      </c>
-      <c r="D114" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>（1）表单同机构后台 Agent 详情：头像（必填，圆形裁剪）、名称（必填）、类型（只读不可改）、TTS 参考音（必填）
-（2）回答 Prompt 平台超管可编辑：可编辑文本框 + 提示「平台超管可编辑全平台任意 Agent 的回答 Prompt，保存后即时生效」；保存 toast「已保存（含回答 Prompt）」
-（3）右侧「关联 KP」卡：点「前往 KP」跳全域 KP 详情</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>平台超管后台 PC</t>
-        </is>
-      </c>
-      <c r="B115" s="3" t="inlineStr">
-        <is>
-          <t>全域用户</t>
-        </is>
-      </c>
-      <c r="C115" s="3" t="inlineStr">
-        <is>
-          <t>全域用户列表</t>
-        </is>
-      </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>（1）表格列：用户昵称、微信号、手机号、机构、会员状态、已购永享、累计 GMV、最新登录时间、注册时间、操作（详情）——「归属机构」列名统一为「机构」；「注册时间」列支持升 / 降序排序
-（2）按 账户名/微信号/手机号 搜索；筛选 会员状态、机构
-（3）点「详情」携行数据进全域用户详情
-（4）「导出」按钮位于筛选行右侧（与筛选条件同行，不在页头）：生成「AI问书_全域C端用户数据导出.xlsx」，沿用机构、会员状态和搜索条件；头部注明导出时间与筛选条件；平台侧手机号完整展示，不脱敏</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>平台超管后台 PC</t>
-        </is>
-      </c>
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>全域用户</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="inlineStr">
-        <is>
-          <t>全域用户详情</t>
-        </is>
-      </c>
-      <c r="D116" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>（1）头部卡：头像 + 昵称 + 会员/非会员标签；副行「机构 · 手机号 · 微信号」；活跃度（近 30 天提问 · 累计 GMV · 最近活跃）
-（2）已购永享卡（点击查看具体内容，进媒体预览）
-（3）全部订单表：订单号、类型、金额、支付方式、订单状态、退款状态、付款时间、操作（详情进全域订单详情）</t>
-        </is>
-      </c>
-    </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
@@ -4008,23 +4041,116 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
+          <t>全域 Agent 人设</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>全域 Agent 详情（Prompt 平台可编辑）</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>0807周五更新
+（1）表单同机构后台 Agent 详情：头像（必填，圆形裁剪）、名称（必填）、类型（只读不可改）、TTS 参考音（必填）、TTS 参考音文本（必填）
+（2）回答 Prompt 平台超管可编辑：可编辑文本框 + 提示「平台超管可编辑全平台任意 Agent 的回答 Prompt，保存后即时生效」；保存 toast「已保存（含回答 Prompt）」
+（3）右侧「关联 KP」卡：点「前往 KP」跳全域 KP 详情
+（4）「0807 新增」新增「TTS 参考音文本」（必填，上限 100 字、不限字符种类，右下角实时字数）：TTS 参考音频内朗读的文本内容；位于 TTS 参考音之下，字段规格、校验与机构后台 Agent 详情一致（同一组件同步生效）</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>平台超管后台 PC</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>全域用户</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>全域用户列表</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>0807周五更新
+（1）表格列：用户昵称、微信号、手机号、机构、会员状态、已购永享、累计 GMV、最新登录时间、注册时间、操作（详情）——「归属机构」列名统一为「机构」；「注册时间」列支持升 / 降序排序
+（2）按 账户名/微信号/手机号 搜索；筛选 会员状态（全部/有效会员/宽限期（待续费）/会员已过期/未开通会员）、机构
+（3）点「详情」携行数据进全域用户详情
+（4）「导出」按钮位于筛选行右侧（与筛选条件同行，不在页头）：生成「AI问书_全域C端用户数据导出.xlsx」，沿用机构、会员状态和搜索条件；头部注明导出时间与筛选条件；平台侧手机号完整展示，不脱敏
+（5）「0807 修订」会员状态筛选由「全部/会员/非会员」改为五档：全部 / 有效会员 / 宽限期（待续费）/ 会员已过期 / 未开通会员；列表「会员状态」列改四色标签（有效会员＝玉绿、宽限期（待续费）＝琥珀、会员已过期＝赤陶、未开通会员＝灰描边）；四态定义与判定口径与机构后台 C 端用户完全一致（详见端二 · 4. C 端用户），导出同步新口径</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>平台超管后台 PC</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>全域用户</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>全域用户详情</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>0807周五更新
+（1）头部卡：头像 + 昵称 + 会员状态标签（四态）；副行「机构 · 手机号 · 微信号」；活跃度（近 30 天提问 · 累计 GMV · 最近活跃）
+（2）已购永享卡（点击查看具体内容，进媒体预览）
+（3）全部订单表：订单号、类型、金额、支付方式、订单状态、退款状态、付款时间、操作（详情进全域订单详情）
+（4）「0807 修订」头部卡会员标签由「会员/非会员」改为四态标签（同列表配色）；有效会员补充显示「有效期至 {日期}」、宽限期（待续费）显示「已于 {日期} 到期 · 宽限期内」</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>平台超管后台 PC</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
           <t>全域订单</t>
         </is>
       </c>
-      <c r="C117" s="5" t="inlineStr">
+      <c r="C120" s="3" t="inlineStr">
         <is>
           <t>全域订单列表</t>
         </is>
       </c>
-      <c r="D117" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E117" s="6" t="inlineStr">
-        <is>
-          <t>0722周三更新
-（1）C 端订单（终端用户→机构），复用订单字段，多「机构」列与筛选——「归属机构」列名统一为「机构」
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>（1）C 端订单（终端用户→机构），复用订单字段，多「机构」列与筛选——「归属机构」列名统一为「机构」
 （2）表格列：订单号、机构、类型、关联知识产品、金额、支付方式、订单状态、退款状态、用户、下单时间、付款时间、兑换时间、操作（详情）
 （3）按微信号/手机号/订单号搜索；平台侧用户手机号完整展示；筛选 机构/类型/订单状态/退款状态；时间筛选与机构后台订单一致——搜索与筛选行下方三个独立时间区间（下单/支付/兑换时间），真实参与过滤
 （4）「导出」按钮位于筛选行右侧（与筛选条件同行，不在页头）：生成「AI问书_全域订单数据导出.xlsx」，沿用全部筛选与三个时间区间；头部注明导出时间与筛选条件
@@ -4032,28 +4158,28 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B118" s="3" t="inlineStr">
+      <c r="B121" s="3" t="inlineStr">
         <is>
           <t>全域订单</t>
         </is>
       </c>
-      <c r="C118" s="3" t="inlineStr">
+      <c r="C121" s="3" t="inlineStr">
         <is>
           <t>全域订单详情</t>
         </is>
       </c>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E118" s="4" t="inlineStr">
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
         <is>
           <t>（1）结构同机构后台订单详情，额外显「机构」字段（原「归属机构」统一更名）
 （2）兑换码/会员/永享三类差异化；有退款记录时显退款信息卡 + 退款时间线
@@ -4061,59 +4187,61 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B119" s="3" t="inlineStr">
+      <c r="B122" s="3" t="inlineStr">
         <is>
           <t>全域答案反馈</t>
         </is>
       </c>
-      <c r="C119" s="3" t="inlineStr">
+      <c r="C122" s="4" t="inlineStr">
         <is>
           <t>全域答案反馈工作台</t>
         </is>
       </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>（1）副标题「全平台各机构 C 端答案点踩/反馈汇总，便于平台监管与质量分析」
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>0807周五更新
+（1）副标题「全平台各机构 C 端答案点踩/反馈汇总，便于平台监管与质量分析」
 （2）表格列：问题、机构、反馈标签、反馈人（昵称+会员标签）、提交时间、操作（详情）——「归属机构」列名统一为「机构」
 （3）按 问题/反馈人 搜索；筛选 机构/反馈标签 + 提交时间区间
 （4）「导出」（按钮文案统一为「导出」，不带 XLSX 字样）：生成「AI问书_全域答案反馈数据导出.xlsx」，沿用机构、标签、时间和搜索条件，长文本自动换行，仅含问答文本与必要反馈元数据、不含媒体/溯源；头部注明导出时间与筛选条件
-（5）详情弹窗（平台视角额外传机构）：标签 + 元信息行（机构·昵称·会员·时间）+ 问答气泡 + 相关媒体资源缩略图条</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+（5）详情弹窗（平台视角额外传机构）：标签 + 元信息行（机构·昵称·会员·时间）+ 问答气泡 + 相关媒体资源缩略图条
+（6）「0807 修订」反馈人会员标签随四态口径（同机构后台答案反馈）：有效会员＝玉绿「有效会员」、宽限期（待续费）＝琥珀「宽限期」、会员已过期＝赤陶「已过期」、未开通不挂标；详情弹窗元信息行同规则</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B120" s="3" t="inlineStr">
+      <c r="B123" s="3" t="inlineStr">
         <is>
           <t>全域模型用量</t>
         </is>
       </c>
-      <c r="C120" s="3" t="inlineStr">
+      <c r="C123" s="3" t="inlineStr">
         <is>
           <t>全域模型用量</t>
         </is>
       </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E120" s="4" t="inlineStr">
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
         <is>
           <t>（1）页头机构筛选覆盖全部机构，父机构带「父机构」标签；选中父机构＝自动汇总该父机构自身及其全部子机构数据，并在页面标注「含子机构：A、B」
 （2）右侧「导出」：生成「AI问书_全域模型用量数据导出.xlsx」，沿用机构范围与时间区间，实时/区间口径分别标注统计时间；头部注明导出时间与筛选条件
@@ -4123,28 +4251,28 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B121" s="3" t="inlineStr">
+      <c r="B124" s="3" t="inlineStr">
         <is>
           <t>平台账户</t>
         </is>
       </c>
-      <c r="C121" s="3" t="inlineStr">
+      <c r="C124" s="3" t="inlineStr">
         <is>
           <t>平台账户列表</t>
         </is>
       </c>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E121" s="4" t="inlineStr">
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
         <is>
           <t>（1）副标题强调与机构账户区分：平台方人员、平台级角色、无所属机构
 （2）表格列：账户名称、姓名、角色（平台超级管理员/平台运营/平台财务）、完整手机号、状态（启用/停用）、创建时间、操作；手机号不脱敏
@@ -4153,28 +4281,28 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B122" s="3" t="inlineStr">
+      <c r="B125" s="3" t="inlineStr">
         <is>
           <t>平台账户</t>
         </is>
       </c>
-      <c r="C122" s="3" t="inlineStr">
+      <c r="C125" s="3" t="inlineStr">
         <is>
           <t>平台账户列表</t>
         </is>
       </c>
-      <c r="D122" s="3" t="inlineStr">
+      <c r="D125" s="3" t="inlineStr">
         <is>
           <t>新建 / 重置密码 / 启停</t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr">
+      <c r="E125" s="6" t="inlineStr">
         <is>
           <t>（1）新建弹窗：账户名称（必填）、姓名（必填）、角色（必填，平台三角色）、联系方式（选填）；说明「平台账户无所属机构，仅用平台级角色 / 初始密码系统生成，创建后弹窗展示并支持复制」
 （2）校验账户名+姓名非空；新建成功弹凭证弹窗（机构标「平台（无所属机构）」）
@@ -4182,89 +4310,91 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B123" s="3" t="inlineStr">
+      <c r="B126" s="3" t="inlineStr">
         <is>
           <t>角色权限</t>
         </is>
       </c>
-      <c r="C123" s="3" t="inlineStr">
+      <c r="C126" s="4" t="inlineStr">
         <is>
           <t>角色权限（机构/平台双类型 · 三态）</t>
         </is>
       </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>（1）副标题「按角色类型分别管理机构角色与平台角色（权限点不同）；机构账户选机构角色、平台账户选平台角色」
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>0807周五更新
+（1）副标题「按角色类型分别管理机构角色与平台角色（权限点不同）；机构账户选机构角色、平台账户选平台角色」
 （2）顶部切换「机构角色 / 平台角色」
 （3）机构角色权限点分组：主控台 / 产品中心（0716 #7/#8.1：知识产品 KP 与 Agent 人设同一行左右两列，KP 在左列，其三态开关与「查看主控台」垂直对齐）/ 运营中心（C 端用户、订单管理、兑换码）/ 数据中心（数据看板）/ 系统设置（客服配置、系统配置）；「Agent 回答 Prompt 编辑」为功能权限（其余为菜单权限），加「功能权限」标签区分
 （4）0716 #8：「Agent 回答 Prompt 编辑」作为「Agent 人设」的嵌套子项——仅当「Agent 人设」= 可操作时才展开显示（无 / 只读时完全不显示，而非置灰锁定）；用缩进 + 灰色虚线连接线表达从属关系（0717 #6：去掉子项紫色背景块，仅保留缩进 + 虚线连接线）；「功能权限」标签移至权限 key 行（与标题行分离，保证右侧两态开关垂直居中对齐）；子项两态（只读 / 可操作）；「Agent 人设」降级为只读 / 无时子项自动收起
 （5）平台角色权限点分组：主控台 / 机构管理（机构管理、机构账户、订阅订单）/ 产品中心（全域 KP、全域 Agent）/ 运营中心（全域用户、全域订单）/ 数据中心（全域答案反馈、全域模型用量）/ 系统设置（平台账户、角色权限、默认 LLM）
 （6）左侧角色列表，右侧权限面板：菜单权限项 = 图标 + 名称 + 三态分段开关（无/只读/可操作）；功能权限「Agent 回答 Prompt 编辑」为两态（只读/可操作）——功能权限的「无」与「只读」语义相同（都表现为不可编辑），合并为「只读」
-（7）三态图例（InfoDot）：无＝看不见该菜单 / 只读＝可进入查看不能编辑（功能权限＝不可编辑）/ 可操作＝全部操作可用；「保存」→ toast「已保存权限」</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+（7）三态图例（InfoDot）：无＝看不见该菜单 / 只读＝可进入查看不能编辑（功能权限＝不可编辑）/ 可操作＝全部操作可用；「保存」→ toast「已保存权限」
+（8）「0807 修订」「可操作」的数据范围口径明确：平台角色的「可操作」＝可跨机构操作全平台数据；机构角色的「可操作」＝仅针对本机构数据——父机构账户虽可见下属子机构数据（列表可筛、看板可汇总），但对子机构数据仅可查看、不可操作（操作入口置灰并提示「仅可操作本机构数据」）；三态图例 InfoDot 同步补充本条说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B124" s="3" t="inlineStr">
+      <c r="B127" s="3" t="inlineStr">
         <is>
           <t>角色权限</t>
         </is>
       </c>
-      <c r="C124" s="3" t="inlineStr">
+      <c r="C127" s="3" t="inlineStr">
         <is>
           <t>角色权限（机构/平台双类型 · 三态）</t>
         </is>
       </c>
-      <c r="D124" s="3" t="inlineStr">
+      <c r="D127" s="3" t="inlineStr">
         <is>
           <t>新建角色</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr">
+      <c r="E127" s="6" t="inlineStr">
         <is>
           <t>（1）弹窗加宽，使角色类型一行完整展示不换行；角色类型继承当前“机构角色/平台角色”Tab并以置灰锁定显示，不可切换；删除解释文案「由创建入口页签决定，不可切换」（锁定态样式已自说明）；仅填写角色名称与备注
 （2）校验名称非空 + 同类型不重名；创建后入对应类型列表、空权限、自动切换选中 → toast「已创建角色，请在右侧逐项设置权限」</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B125" s="3" t="inlineStr">
+      <c r="B128" s="3" t="inlineStr">
         <is>
           <t>默认 LLM</t>
         </is>
       </c>
-      <c r="C125" s="3" t="inlineStr">
+      <c r="C128" s="3" t="inlineStr">
         <is>
           <t>默认 LLM 模型配置</t>
         </is>
       </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E125" s="4" t="inlineStr">
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="inlineStr">
         <is>
           <t>（1）副标题「仅『已上架』的模型可被设为所有机构底层的默认基模」
 （2）表格：模型名称、厂商、版本号、状态（已上架/未上架 + 默认标）、操作（编辑/上架·下架/设为默认）
@@ -4273,330 +4403,330 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B126" s="3" t="inlineStr">
+      <c r="B129" s="3" t="inlineStr">
         <is>
           <t>默认 LLM</t>
         </is>
       </c>
-      <c r="C126" s="3" t="inlineStr">
+      <c r="C129" s="3" t="inlineStr">
         <is>
           <t>默认 LLM 模型配置</t>
         </is>
       </c>
-      <c r="D126" s="3" t="inlineStr">
+      <c r="D129" s="3" t="inlineStr">
         <is>
           <t>新建 / 编辑模型</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
+      <c r="E129" s="6" t="inlineStr">
         <is>
           <t>（1）弹窗：模型名称（必填，唯一校验，重名实时红字 + toast「模型名称已存在」）、厂商（下拉 通义/DeepSeek/智谱/百川）、版本号（必填）、状态（编辑时只读，注「上下架请在列表操作列进行」）</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B127" s="3" t="inlineStr">
+      <c r="B130" s="3" t="inlineStr">
         <is>
           <t>个人中心</t>
         </is>
       </c>
-      <c r="C127" s="3" t="inlineStr">
+      <c r="C130" s="3" t="inlineStr">
         <is>
           <t>个人中心</t>
         </is>
       </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E127" s="4" t="inlineStr">
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="inlineStr">
         <is>
           <t>（1）账户信息只读：账户名称、姓名、角色、完整手机号、账户状态；两后台个人中心手机号均不脱敏，平台账户不显示所属机构/上级机构
 （2）平台超管不显示「账户信息由平台统一管理…」灰字提示</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B128" s="3" t="inlineStr">
+      <c r="B131" s="3" t="inlineStr">
         <is>
           <t>个人中心</t>
         </is>
       </c>
-      <c r="C128" s="3" t="inlineStr">
+      <c r="C131" s="3" t="inlineStr">
         <is>
           <t>个人中心</t>
         </is>
       </c>
-      <c r="D128" s="3" t="inlineStr">
+      <c r="D131" s="3" t="inlineStr">
         <is>
           <t>更换头像（裁剪）</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
+      <c r="E131" s="6" t="inlineStr">
         <is>
           <t>（1）相册选图 → 圆形裁剪（拖拽定位 + 缩放滑块）→ canvas 输出 256px 头像 → toast「头像已更新」</t>
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B129" s="3" t="inlineStr">
+      <c r="B132" s="3" t="inlineStr">
         <is>
           <t>个人中心</t>
         </is>
       </c>
-      <c r="C129" s="3" t="inlineStr">
+      <c r="C132" s="3" t="inlineStr">
         <is>
           <t>个人中心</t>
         </is>
       </c>
-      <c r="D129" s="3" t="inlineStr">
+      <c r="D132" s="3" t="inlineStr">
         <is>
           <t>修改登录密码</t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr">
+      <c r="E132" s="6" t="inlineStr">
         <is>
           <t>（1）弹窗：旧密码 + 新密码 + 确认新密码；校验 旧密码非空/新密码 8~16 位含字母+数字/两次一致 → toast「登录密码已修改」</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>平台超管后台 PC</t>
         </is>
       </c>
-      <c r="B130" s="3" t="inlineStr">
+      <c r="B133" s="3" t="inlineStr">
         <is>
           <t>评审工具</t>
         </is>
       </c>
-      <c r="C130" s="3" t="inlineStr">
+      <c r="C133" s="3" t="inlineStr">
         <is>
           <t>原型清单 / 微信对接清单下载</t>
         </is>
       </c>
-      <c r="D130" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E130" s="4" t="inlineStr">
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
         <is>
           <t>（1）〔评审〕原型清单：三端通用站点地图，列全站页面便于评审跳转
 （2）〔评审〕顶栏固定「新机构入驻微信对接清单」下载按钮（下载对接清单 docx）</t>
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>三端通用（全局交互）</t>
         </is>
       </c>
-      <c r="B131" s="3" t="inlineStr">
+      <c r="B134" s="3" t="inlineStr">
         <is>
           <t>通用状态规范</t>
         </is>
       </c>
-      <c r="C131" s="3" t="inlineStr">
+      <c r="C134" s="3" t="inlineStr">
         <is>
           <t>Toast 轻提示</t>
         </is>
       </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E131" s="4" t="inlineStr">
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
         <is>
           <t>（1）单条、统一位置弹出（移动端底部 / 后台顶部），默认数秒自动消失
 （2）用于操作结果反馈（已保存/已删除/已复制等），文案过长自动换行不超屏</t>
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>三端通用（全局交互）</t>
         </is>
       </c>
-      <c r="B132" s="3" t="inlineStr">
+      <c r="B135" s="3" t="inlineStr">
         <is>
           <t>通用状态规范</t>
         </is>
       </c>
-      <c r="C132" s="3" t="inlineStr">
+      <c r="C135" s="3" t="inlineStr">
         <is>
           <t>二次确认弹窗（ConfirmDialog）</t>
         </is>
       </c>
-      <c r="D132" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E132" s="4" t="inlineStr">
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
         <is>
           <t>（1）危险/不可逆操作（删除/下架/停用/退款/取消分享等）统一走二次确认
 （2）危险操作主按钮为 danger 红色，文案写清后果与是否可恢复</t>
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>三端通用（全局交互）</t>
         </is>
       </c>
-      <c r="B133" s="3" t="inlineStr">
+      <c r="B136" s="3" t="inlineStr">
         <is>
           <t>通用状态规范</t>
         </is>
       </c>
-      <c r="C133" s="3" t="inlineStr">
+      <c r="C136" s="3" t="inlineStr">
         <is>
           <t>加载骨架屏</t>
         </is>
       </c>
-      <c r="D133" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E133" s="4" t="inlineStr">
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
         <is>
           <t>（1）后台列表/详情挂载先显骨架屏占位，再渲染真实数据，避免白屏跳变</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>三端通用（全局交互）</t>
         </is>
       </c>
-      <c r="B134" s="3" t="inlineStr">
+      <c r="B137" s="3" t="inlineStr">
         <is>
           <t>通用状态规范</t>
         </is>
       </c>
-      <c r="C134" s="3" t="inlineStr">
+      <c r="C137" s="3" t="inlineStr">
         <is>
           <t>空态</t>
         </is>
       </c>
-      <c r="D134" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E134" s="4" t="inlineStr">
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E137" s="6" t="inlineStr">
         <is>
           <t>（1）列表/搜索/筛选无结果时显居中插画 + 标题 + 副文案（如「没有匹配的 X / 换个条件试试」）
 （2）部分空态内嵌主操作入口（如「新建 X」）</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>三端通用（全局交互）</t>
         </is>
       </c>
-      <c r="B135" s="3" t="inlineStr">
+      <c r="B138" s="3" t="inlineStr">
         <is>
           <t>通用状态规范</t>
         </is>
       </c>
-      <c r="C135" s="3" t="inlineStr">
+      <c r="C138" s="3" t="inlineStr">
         <is>
           <t>分页</t>
         </is>
       </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E135" s="4" t="inlineStr">
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E138" s="6" t="inlineStr">
         <is>
           <t>（1）后台列表默认每页 10 条，超过才分页；筛选/搜索变更后回到第 1 页；分页单位随实体变化（家/个/笔/条/单等）</t>
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>三端通用（全局交互）</t>
         </is>
       </c>
-      <c r="B136" s="3" t="inlineStr">
+      <c r="B139" s="3" t="inlineStr">
         <is>
           <t>通用状态规范</t>
         </is>
       </c>
-      <c r="C136" s="3" t="inlineStr">
+      <c r="C139" s="3" t="inlineStr">
         <is>
           <t>操作列固定</t>
         </is>
       </c>
-      <c r="D136" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E136" s="4" t="inlineStr">
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E139" s="6" t="inlineStr">
         <is>
           <t>（1）后台表格「操作」列固定在右侧（白底+左侧分隔线+阴影），横向滚动时常驻可见</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>三端通用（全局交互）</t>
         </is>
       </c>
-      <c r="B137" s="3" t="inlineStr">
+      <c r="B140" s="3" t="inlineStr">
         <is>
           <t>通用状态规范</t>
         </is>
       </c>
-      <c r="C137" s="3" t="inlineStr">
+      <c r="C140" s="3" t="inlineStr">
         <is>
           <t>数值单位规范</t>
         </is>
       </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E137" s="4" t="inlineStr">
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="inlineStr">
         <is>
           <t>（1）两后台数值统一中文进制缩写：&lt;1 万千分位；1 万~1 亿 → X.X 万；≥1 亿 → X.XX 亿；Token 统一以「亿」为单位
 （2）各看板页脚附统一单位规范说明
@@ -4607,28 +4737,28 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>三端通用（全局交互）</t>
         </is>
       </c>
-      <c r="B138" s="3" t="inlineStr">
+      <c r="B141" s="3" t="inlineStr">
         <is>
           <t>通用状态规范</t>
         </is>
       </c>
-      <c r="C138" s="3" t="inlineStr">
+      <c r="C141" s="3" t="inlineStr">
         <is>
           <t>登录态有效期</t>
         </is>
       </c>
-      <c r="D138" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E138" s="4" t="inlineStr">
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="inlineStr">
         <is>
           <t>（1）移动端采用滑动7天会话：每次经过认证的有效请求刷新最后活跃时间；连续7天无有效请求后失效并返回登录页
 （2）未登录不可进入业务内容；登录失效后的原目标地址可在重新登录成功后恢复跳转，但不自动补发任何未认证输入</t>
@@ -4646,7 +4776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4684,1134 +4814,1215 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>通用周期规则</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>累计 / 快照指标</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>截止当前时刻或区间末日快照；不展示上一周期比较</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>避免把存量规模误读为区间增长</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>通用周期规则</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>今日</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>本地时区今日 00:00 至当前时刻，对比昨日 00:00 至相同经过时长；趋势按小时</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>保证比较窗口等长</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>通用周期规则</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>近 7 天 / 近 30 天 / 自定义</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>含首尾日期；上一周期为紧邻的前一等长区间；趋势按日</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>统一环比边界</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>通用差值规则</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>计数 / 金额</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>(本期-上期)÷上期，显示相对百分比</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>衡量相对变化</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>通用差值规则</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>率类 / 时长</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>率类显示百分点差；时长显示绝对时长差</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>避免不同量纲混用</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>通用零基线</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>上一周期为 0</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>不计算无穷增幅，显示“上期为0，暂无可比增幅”</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>避免误导</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>通用差值规则</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>界面环比文案（0718 新增）</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>看板界面环比标签统一显示「↑x.x% 较上一周期」，不再出现「pp」字样；率类差值口径仍为百分点</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>避免用户对 pp 单位困惑</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>通用精确性</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>去重与估算</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>按指标指定主键精确 DISTINCT；禁止使用 0.62/0.42 等经验系数估算</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>可审计可复算</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>通用去重规则（0722 新增）</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>规模指标 / 强度指标</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>规模指标按用户去重：区间内按用户 ID 精确去重，同一用户跨天重复只计 1 人（活跃用户、新增 C 端、付费用户、提问用户等）；强度指标按人天：用户 × 自然日累加（日均活跃、人均提问等）；两后台涉去重指标 tooltip 全量标注所属类别</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>区分「多少人在用」与「用得有多勤」，口径可复算</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>主控台·实时总览</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>累计 GMV（实时）</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>SUM(已支付订单金额)</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
         <is>
           <t>不涉及（金额汇总）</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>总营收</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>主控台·实时总览</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>累计退款 / 退款率（实时）</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>SUM(退款成功额)；退款率 = 退款额 ÷ GMV</t>
         </is>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>不涉及（金额与比率）</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>售后与资金健康度</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>主控台·实时总览</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>净 GMV（累计扣退款）</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>累计 GMV − 累计退款</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
         <is>
           <t>不涉及（金额汇总）</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>实际到账净收入</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>主控台·实时总览</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>当前会员数（实时）</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>会员未到期的去重用户数</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr">
         <is>
           <t>按用户 ID 去重</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>商业化基本盘</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>主控台·实时总览</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>累计注册用户（实时）</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>COUNT(DISTINCT user_id)</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>按用户 ID 去重</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>用户规模</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>主控台·实时总览（平台）</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>知识产品 KP 总数（实时）（0807 新增）</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>COUNT(全平台 KP)；卡片副行按状态拆分：已发布 / 草稿 / 已下架（数量＋占比）</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（实体计数）</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>内容供给存量视角①：平台运营能力＝机构规模 × 内容供给 × 用户消费 × 商业化</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>主控台·实时总览（平台）</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>知识库文件总数（实时）（0807 新增）</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>COUNT(全平台知识库文件)；卡片副行按类型拆分：文档 / 图片 / 音频 / 视频 四类（数量＋占比）</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（实体计数）</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>内容供给存量视角②：知识库建设规模与内容结构</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>主控台·实时总览（平台）</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>知识库存储总量（实时）（0807 新增）</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>SUM(全平台知识库文件大小)，单位 TB；卡片副行：文档与媒体资源的容量＋占比（两者互补 100%）</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（容量汇总）</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>内容供给存量视角③：存储资源占用与结构（关联机构存储配额）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>主控台·经营分析</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>活跃用户 / 新增会员 / 区间 GMV / 区间提问数（区间）+ 趋势图</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>区间聚合；活跃用户＝规模指标·区间内按用户 ID 去重（0722 修订）；新增会员＝区间内历史首次开通会员的用户数，续费、回流均不计入（0722 口径定稿）；区间 GMV 仅计「已支付」订单（待支付 / 已失效不计）</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
         <is>
           <t>活跃用户、新增会员＝按用户 ID 去重（跨天只计 1 人）；区间 GMV、区间提问数＝不涉及</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>经营动态</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>主控台·经营分析（平台）</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>续费率 / 回流会员（区间）（0722 平台新增）</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>续费率＝区间内到期且完成续费的会员数 ÷ 同区间到期会员数；回流会员＝区间内开通会员、且开通时会员状态为已过期的用户数（不算新增、不算续费）；新增 / 续费 / 回流三者互斥，两后台统一</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>续费率＝分子分母均按会员去重；回流会员＝按用户 ID 去重</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>会员经营三分：拉新 / 留存 / 召回</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>活跃概览（页级常驻，居用户留存上方，0724 移出用户分析 Tab）</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>日活 / 周活 / 月活（实时滚动窗口快照）</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>（0724 修订，替换 0717「随区间联动」口径）固定滚动窗口实时快照、不随区间筛选联动：日活＝今日 00:00 至当前时刻的去重活跃用户（实时），环比对比昨日同时段；周活＝近 7 日滚动窗口去重活跃用户，环比上一个 7 日窗口；月活＝近 30 日滚动窗口去重活跃用户，环比上一个 30 日窗口</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>日活＝今日 00:00 至当前时刻按用户 ID 去重；周活 / 月活＝近 7 / 30 日滚动窗口内按用户 ID 去重（窗口内跨天只计 1 人）</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>粘性分层</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>用户分析</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>新增用户趋势（区间）</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>区间内按日/按小时的首次注册数序列</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr">
         <is>
           <t>按用户 ID 去重（注册仅计首次）</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>拉新节奏（新增用户卡右侧迷你折线）</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>用户分析</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>新增用户数（区间）</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>区间内首次注册数</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D23" s="6" t="inlineStr">
         <is>
           <t>按用户 ID 去重（注册仅计首次）</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>拉新效果</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>用户分析</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>次日 / 7 日 / 30 日留存率（独立 cohort）</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>分母=cohort 日注册去重用户；分子=第 N 日有有效行为用户；只纳入已满 N 日的成熟 cohort，显示样本量与成熟截止日，未成熟节点显示「尚未到统计时间」并给出预计可统计日期（注册日 + N）；单注册日批次三节点共用同一样本分母；（0724 修订）注册批次筛选精简为「最新可统计 / 自定义日期」两档</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>分子分母均按用户 ID 去重</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>产品价值是否站得住</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>用户分析</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>来源分布（区间）</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>扫码进入 vs 直接访问；图例含人数与占比；占比环比按百分点差计算、界面统一显示为「↑x.x% 较上一周期」</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>按用户 ID 去重（跨天只计 1 人）</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>渠道效果</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>用户分析</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>地区分布 / 性别分布（区间）</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>按地区·性别分组占比</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>按用户 ID 去重</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>用户画像与精细化运营</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>提问分析</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>总提问数（区间）</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>COUNT(提问)</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr">
         <is>
           <t>不涉及（逐条计数）</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>使用强度</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>提问分析</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>人均提问数（区间）</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>总提问数 / 活跃用户</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>按人天（用户×自然日）</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>单用户深度</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>提问分析</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>平均会话轮次（区间）</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>总提问数 / 总会话数</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>不涉及</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>对话沉浸度</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>提问分析</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>答案点赞率 / 答案反馈率（区间）</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>点赞数 ÷ 答案数；反馈数 ÷ 答案数</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>不涉及（按答案条数计）</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>答案质量摘要（明细在答案反馈菜单）</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>提问分析</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>提问量趋势（区间）</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>每日提问条数</t>
         </is>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr">
         <is>
           <t>不涉及（逐条计数）</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>提问走势</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>提问分析</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>按 Agent 提问分布（区间）</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>各 Agent 接收提问占比</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
         <is>
           <t>不涉及</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>Agent 配置 / 路由质量</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>提问分析</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>提问领域分布（区间）</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>按 KP / 领域聚合占比</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>不涉及</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>用户最关心的领域</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>提问分析</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>提问关键词云（区间）</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>高频关键词，hover 显示该词区间提问数</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>不涉及</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>运营 / 商业化分析</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>营收分析·收入与转化</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>区间 GMV（区间）</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>SUM(区间已支付金额)</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>不涉及（金额汇总）</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>区间营收</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>营收分析·收入与转化</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>付费用户数 / 付费转化率（区间）</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>区间付费用户 / 区间活跃用户</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>分子分母均按用户 ID 去重</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>商业化核心</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>营收分析·收入与转化</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>ARPPU（区间）</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>区间收入 / 区间付费用户数</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>分母付费用户按用户 ID 去重</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>单付费用户产值</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>营收分析·收入与转化</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>续费率（区间）</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>到期续费数 / 到期会员数</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>按会员去重</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>长期价值</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
         <is>
           <t>营收分析·收入与转化</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>回流会员（区间）（0722 新增）</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>区间内开通会员、且开通时会员状态为已过期的用户数（按用户去重）；不算新增、不算续费，三者互斥；两后台口径一致</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr">
         <is>
           <t>按用户 ID 去重（跨天只计 1 人）</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E39" s="6" t="inlineStr">
         <is>
           <t>流失召回效果</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>营收分析·退款</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>退款金额 / 退款率 / 退款订单数 / 净 GMV（区间）</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>见各指标</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D40" s="6" t="inlineStr">
         <is>
           <t>退款订单数＝按订单去重；退款金额、退款率、净 GMV＝不涉及</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>售后与净收入</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
         <is>
           <t>营收分析·转化漏斗</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>受限内容触发率（区间）</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>触发付费墙次数 / 总提问数</t>
         </is>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>不涉及（按次计数）</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
         <is>
           <t>付费墙强度（漏斗入口）</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
         <is>
           <t>营收分析·转化漏斗</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>会员漏斗（区间）</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>看到会员页 → 点击购买 → 完成支付（%）</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>各环节按用户 ID 去重</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E42" s="6" t="inlineStr">
         <is>
           <t>找漏斗瓶颈</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>营收分析·转化漏斗</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>永享转化（区间）</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>触发永享墙 → 完成购买（%）</t>
         </is>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>各环节按用户 ID 去重</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
+      <c r="E43" s="6" t="inlineStr">
         <is>
           <t>永享定价是否合理</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
         <is>
           <t>热门 KP</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>被提问数 TOP 10 KP（区间）</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>按 KP 维度统计提问</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr">
         <is>
           <t>不涉及（按 KP 维度计数）</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="E44" s="6" t="inlineStr">
         <is>
           <t>真正被使用的内容</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
         <is>
           <t>热门 KP</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>付费转化贡献 TOP 10 KP（区间）</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>通过该 KP 触发的会员 / 永享订单数</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>不涉及（按 KP 维度计数）</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E45" s="6" t="inlineStr">
         <is>
           <t>营销价值高的内容</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>热门 KP</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>永享购买 TOP 10 KP（区间）</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>按 KP 永享订单数</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>不涉及（按 KP 维度计数）</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
+      <c r="E46" s="6" t="inlineStr">
         <is>
           <t>永享潜力</t>
         </is>
@@ -5860,88 +6071,88 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>实时存量（不随时间筛选变化）</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>用户与营收存量（0722 由「用户存量」更名）</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>累计 C 端用户数（按用户 ID 去重）、当前会员数（含 72 小时缓冲期）、累计 GMV（0722 新增：机构开通至今全部已支付订单总额，含已产生退款的部分，不随区间筛选变化）</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>累计 C 端＝按用户 ID 去重；当前会员＝按用户 ID 去重；累计 GMV＝不涉及（金额汇总）</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>区间运营分析（随今日 / 近7天 / 近30天 / 自定义联动）</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>活跃与内容使用</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>活跃用户（登录或提问，区间内按用户 ID 去重）、新增 C 端用户数、区间提问数（含追问）</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>活跃用户、新增 C 端＝按用户 ID 去重（跨天只计 1 人）；区间提问数＝不涉及（逐条计数）</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>区间运营分析（随今日 / 近7天 / 近30天 / 自定义联动）</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>商业化（0722 由「商业化与 LLM 消耗」拆出，横跨整行）</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>区间 GMV（区间内「已支付」订单金额，待支付 / 已失效不计）、净 GMV（0722 新增：区间 GMV − 区间退款金额）、付费用户数（区间内完成支付的去重用户）、付费转化率（0722 新增：付费用户 ÷ 区间活跃用户）、永享订单（0722 新增：区间内已支付永享订单数）、退款金额（0722 新增：区间内退款成功金额）、退款率（0722 新增：退款金额 ÷ 区间 GMV）</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>付费用户＝按用户 ID 去重（跨天只计 1 人）；付费转化率＝分子分母均按用户 ID 去重；永享订单＝按订单去重；区间 GMV、净 GMV、退款金额、退款率＝不涉及</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>区间运营分析（随今日 / 近7天 / 近30天 / 自定义联动）</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>LLM 消耗（0722 由「商业化与 LLM 消耗」拆出）</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Token 消耗量、模型调用次数、平均响应时长</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>不涉及（累加与均值指标）</t>
         </is>

--- a/docs/feature-list.xlsx
+++ b/docs/feature-list.xlsx
@@ -3584,7 +3584,7 @@
 （4）「0722 修订」校验文件归属结论：域名校验文件属公众平台（公众号后台）要求，用于「网页授权域名 / JS 接口安全域名 / 业务域名」校验；微信开放平台的网站应用（扫码登录）不需要校验文件——故上传入口放「微信公众号」卡片，开放平台卡片不变
 （5）「0722 修订」微信支付卡片新增「商户 API 私钥」上传（apiclient_key.pem，与商户证书 apiclient_cert.pem 成对，调用微信支付 API v3 接口签名必需）
 （6）「0807 新增」微信支付卡片新增四项参数，字段顺序：商户号 → API v2 密钥 → API v3 密钥 → 商户证书 → 商户 API 私钥 → 支付公钥 ID → 支付公钥文件 → 委托代扣包月模板 ID（密钥按版本号升序、证书/验签/业务参数依次排列）：① API v2 密钥（掩码文本，置于 API v3 密钥之前）——微信支付 v2 版接口的签名密钥（32 位，商户平台「账户中心-API 安全」设置）；委托代扣（自动续费）的签约/扣款接口体系仍走 v2 签名，配置连续包月必需，与 API v3 密钥并存不互斥 ② 支付公钥 ID（文本，PUB_KEY_ID_ 开头，置于商户 API 私钥之后）——微信支付「公钥模式」验签标识，2024 年起新注册商户默认发放微信支付公钥（替代平台证书轮换机制），验签时按回调头 Wechatpay-Serial 匹配此 ID
-（7）「0807 修订」敏感配置项（公众号 / 开放平台 AppSecret、API v3 密钥、API v2 密钥）输入框增加显隐眼睛：默认脱敏（•••• + 尾 4 位、只读），点眼睛切明文（可编辑）、再点隐藏——便于核对配置又防误改与旁窥
+（7）「0807-2 修订」敏感项定稿「写后不回显」（推翻同批显隐眼睛方案）：九个敏感字段——公众号 AppSecret / 域名校验文件、开放平台 AppSecret、微信支付 API v2 密钥 / API v3 密钥 / 商户证书 / 商户 API 私钥 / 支付公钥 ID / 支付公钥文件——非空时仅显示「已配置 / 已上传」状态行（尾号 ****后 4 位或文件名 + 更新时间精确到秒），提供「更新」能力：点更新出空输入框（占位「输入新值 · 保存后不再回显」），点保存先弹二次确认（提醒整体覆盖原值、不可恢复、新值不再回显，请先核对输入无误），确认后回状态行、不回显新值；文件类「重新上传」同样先弹二次确认（提醒整体覆盖、原文件不可恢复、新文件同样不提供下载与回显）再选文件；显隐眼睛能力删除。密钥在数据库为加密存储（非明文），业务需要原值须联系技术发邮件申请（技术从微信后台获取或数据库解密提供），界面不提供明文查看与文件下载；卡片限制说明区同步注明。非敏感字段（AppID、回调地址、商户号、代扣模板 ID）保持可见可编辑
 （8）「0807 新增」③ 支付公钥文件（上传 pub_key.pem，紧随支付公钥 ID）——与公钥 ID 配套的公钥文件，商户平台下载，用于验证微信支付应答与回调签名（新商户公钥验签、存量商户平台证书验签，按商户号实际发放形态二选一） ④ 委托代扣包月模板 ID（文本，置于卡片末尾业务参数位）——委托代扣「签约模板」经微信审核通过后分配的模板 ID（plan_id），C 端用户签约连续包月扣费时传入；卡片限制说明区同步补充四项参数用途一句话说明</t>
         </is>
       </c>

--- a/docs/feature-list.xlsx
+++ b/docs/feature-list.xlsx
@@ -3577,15 +3577,16 @@
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>0807周五更新
+          <t>0810周一更新
 （1）微信公众号字段改为“网页授权回调地址”，微信开放平台字段改为“授权回调地址”；均填写完整 URL，并继续校验与微信后台配置一致
 （2）微信支付（必填，用于支付/退款/自动续费，未配置前台无法下单）：商户号 MchID、API v3 密钥（掩码）、商户证书（上传 apiclient_cert.pem）；限制说明（商户号须与公众号 AppID 关联绑定/需上传证书且 API v3 密钥在商户平台设置/退款·自动续费依赖支付能力）；保存 toast「已保存微信支付配置」
 （3）「0722 修订」微信公众号卡片新增「网页授权域名校验文件」上传（MP_verify_xxx.txt，公众号后台生成，需放置于网页授权域名根目录下）
 （4）「0722 修订」校验文件归属结论：域名校验文件属公众平台（公众号后台）要求，用于「网页授权域名 / JS 接口安全域名 / 业务域名」校验；微信开放平台的网站应用（扫码登录）不需要校验文件——故上传入口放「微信公众号」卡片，开放平台卡片不变
 （5）「0722 修订」微信支付卡片新增「商户 API 私钥」上传（apiclient_key.pem，与商户证书 apiclient_cert.pem 成对，调用微信支付 API v3 接口签名必需）
 （6）「0807 新增」微信支付卡片新增四项参数，字段顺序：商户号 → API v2 密钥 → API v3 密钥 → 商户证书 → 商户 API 私钥 → 支付公钥 ID → 支付公钥文件 → 委托代扣包月模板 ID（密钥按版本号升序、证书/验签/业务参数依次排列）：① API v2 密钥（掩码文本，置于 API v3 密钥之前）——微信支付 v2 版接口的签名密钥（32 位，商户平台「账户中心-API 安全」设置）；委托代扣（自动续费）的签约/扣款接口体系仍走 v2 签名，配置连续包月必需，与 API v3 密钥并存不互斥 ② 支付公钥 ID（文本，PUB_KEY_ID_ 开头，置于商户 API 私钥之后）——微信支付「公钥模式」验签标识，2024 年起新注册商户默认发放微信支付公钥（替代平台证书轮换机制），验签时按回调头 Wechatpay-Serial 匹配此 ID
-（7）「0807-2 修订」敏感项定稿「写后不回显」（推翻同批显隐眼睛方案）：九个敏感字段——公众号 AppSecret / 域名校验文件、开放平台 AppSecret、微信支付 API v2 密钥 / API v3 密钥 / 商户证书 / 商户 API 私钥 / 支付公钥 ID / 支付公钥文件——非空时仅显示「已配置 / 已上传」状态行（尾号 ****后 4 位或文件名 + 更新时间精确到秒），提供「更新」能力：点更新出空输入框（占位「输入新值 · 保存后不再回显」），点保存先弹二次确认（提醒整体覆盖原值、不可恢复、新值不再回显，请先核对输入无误），确认后回状态行、不回显新值；文件类「重新上传」同样先弹二次确认（提醒整体覆盖、原文件不可恢复、新文件同样不提供下载与回显）再选文件；显隐眼睛能力删除。密钥在数据库为加密存储（非明文），业务需要原值须联系技术发邮件申请（技术从微信后台获取或数据库解密提供），界面不提供明文查看与文件下载；卡片限制说明区同步注明。非敏感字段（AppID、回调地址、商户号、代扣模板 ID）保持可见可编辑
-（8）「0807 新增」③ 支付公钥文件（上传 pub_key.pem，紧随支付公钥 ID）——与公钥 ID 配套的公钥文件，商户平台下载，用于验证微信支付应答与回调签名（新商户公钥验签、存量商户平台证书验签，按商户号实际发放形态二选一） ④ 委托代扣包月模板 ID（文本，置于卡片末尾业务参数位）——委托代扣「签约模板」经微信审核通过后分配的模板 ID（plan_id），C 端用户签约连续包月扣费时传入；卡片限制说明区同步补充四项参数用途一句话说明</t>
+（7）「0807-2 修订」敏感项定稿「写后不回显」（推翻同批显隐眼睛方案）：九个敏感字段——公众号 AppSecret / 域名校验文件、开放平台 AppSecret、微信支付 API v2 密钥 / API v3 密钥 / 商户证书 / 商户 API 私钥 / 支付公钥 ID / 支付公钥文件——非空时仅显示「已配置 / 已上传」状态行，提供「更新」能力：点更新出空输入框（占位「输入新值 · 保存后不再回显」），点保存先弹二次确认（提醒整体覆盖原值、不可恢复、新值不再回显，请先核对输入无误），确认后回状态行、不回显新值；文件类「重新上传」同样先弹二次确认（提醒整体覆盖、原文件不可恢复、新文件同样不提供下载与回显）再选文件；显隐眼睛能力删除。密钥在数据库为加密存储（非明文），业务需要原值须联系技术发邮件申请（技术从微信后台获取或数据库解密提供），界面不提供明文查看与文件下载；卡片限制说明区同步注明。非敏感字段（AppID、回调地址、商户号、代扣模板 ID）保持可见可编辑
+（8）「0807 新增」③ 支付公钥文件（上传 pub_key.pem，紧随支付公钥 ID）——与公钥 ID 配套的公钥文件，商户平台下载，用于验证微信支付应答与回调签名（新商户公钥验签、存量商户平台证书验签，按商户号实际发放形态二选一） ④ 委托代扣包月模板 ID（文本，置于卡片末尾业务参数位）——委托代扣「签约模板」经微信审核通过后分配的模板 ID（plan_id），C 端用户签约连续包月扣费时传入；卡片限制说明区同步补充四项参数用途一句话说明
+（9）「0810 修订」敏感项状态行收敛为「状态 + 操作」两段（与技术确认后定稿）：九个敏感字段的「已配置 / 已上传」状态行不再展示 密钥尾号 ****后 4 位 / 文件名 与 更新时间，只保留状态字样与「更新 / 重新上传」操作（原 0807-2 的「尾号或文件名 + 更新时间精确到秒」展示取消）；二次确认弹窗文案同步去掉对尾号 / 文件名的引用，改为「整体覆盖当前值 / 当前文件」。更新覆写、写后不回显、二次确认、界面不提供明文查看与文件下载等规则均不变；未上传项的空态上传框保持原样</t>
         </is>
       </c>
     </row>

--- a/docs/feature-list.xlsx
+++ b/docs/feature-list.xlsx
@@ -1186,24 +1186,26 @@
           <t>付费墙与权益</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>开通会员</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>（1）0717 二批 #9：两档改为「购买方式即续费语义」，消除「按月自动续费」歧义——① 连续包月（默认选中，角标「首月特惠」）：首月 ¥9.9、次月起 ¥19.9/月 自动续费，卡内说明「自动续费，可随时退订」② 单月（¥19.9 / 1 个月）：一次性购买，卡内说明「到期自动失效，不自动续费不扣款」；选中即表达是否自动续费，不再靠一个含糊的全局勾选
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>0812周三更新
+（1）0717 二批 #9：两档改为「购买方式即续费语义」，消除「按月自动续费」歧义——① 连续包月（默认选中，角标「首月特惠」）：首月 ¥9.9、次月起 ¥19.9/月 自动续费，卡内说明「自动续费，可随时退订」② 单月（¥19.9 / 1 个月）：一次性购买，卡内说明「到期自动失效，不自动续费不扣款」；选中即表达是否自动续费，不再靠一个含糊的全局勾选
 （2）协议、按钮与底部说明随所选方式联动：连续包月→勾选《自动续费协议》+ 按钮「¥9.9 开通连续包月」+ 底部说明「次月起 ¥19.9/月 自动扣费 · 支持随时退订，到期赠 72 小时会员缓冲使用期」；单月→协议行换成《会员服务协议》（无自动续费协议）+ 按钮「¥19.9 购买单月会员」+ 底部说明「到期自动失效，不会自动扣费」；缓冲期不计入已付费会员时长
 （3）「立即开通」前校验手机号绑定（未绑先引导绑定再继续），通过后按所选方式进微信支付收银台
 （4）「0718 修订」开通会员页按「先权益、再套餐、后协议」重构交互：① 标题下新增三枚权益速览 chip（受限内容全解锁 / 图音视频精讲 / 电话问答·VIP 优先）；② 套餐卡信息层级重排——卡名 + 续费语义 pill（连续包月＝「自动续费 · 可随时取消」琥珀标；单月＝「一次性购买 · 不自动续费」灰标）+ 一行说明 + 右侧大价签；选中态改左侧对勾圆点（琥珀填充）+ 琥珀描边淡底，「首月特惠」角标改琥珀渐变；③ 协议勾选改为真实可点交互（未勾选点按钮 toast 引导先同意协议），连续包月需同意《会员服务协议》《自动续费协议》两份，单月仅《会员服务协议》；④ 按钮与底部说明随所选方式联动（语义与 0717 二批 #9 不变：连续包月＝首月 ¥9.9、次月起 ¥19.9/月 自动续费可退订；单月＝¥19.9 一次性、到期自动失效）
 （5）「0718 修订」删除开通按钮下方的补充说明文案（原「次月起 ¥19.9/月 自动扣费 · 支持随时退订，到期赠 72 小时会员缓冲使用期」/「一次性购买 · 到期自动失效，不会自动扣费」），续费规则由套餐卡内的续费语义 pill 与说明承载，不再页底重复
-（6）「0719 修订」协议勾选框改为**默认未勾选**，须用户主动勾选后方可开通（原默认已勾选）——连续包月场景含《自动续费协议》，默认代勾在国内合规口径下通常不被接受；同时与登录落地页「协议默认未勾选」的口径保持一致。未勾选时开通按钮呈置灰视觉，点击 toast「请先阅读并同意相关协议」并阻断，不进收银台</t>
+（6）「0719 修订」协议勾选框改为**默认未勾选**，须用户主动勾选后方可开通（原默认已勾选）——连续包月场景含《自动续费协议》，默认代勾在国内合规口径下通常不被接受；同时与登录落地页「协议默认未勾选」的口径保持一致。未勾选时开通按钮呈置灰视觉，点击 toast「请先阅读并同意相关协议」并阻断，不进收银台
+（7）「0812 新增」会员月度周期按「对日周期」计算：自开通当日起顺延至次月同日；若次月无对应日期，则顺延至当月最后一日，后续续费持续按该日期执行。示例：1 月 31 日开通，2 月无 31 日，当期有效期至 2 月 28 日，后续每月 28 日自动续费。扣费日＝到期日前 1 天（商户预约扣费节奏，详见 PRD 4.4.5）</t>
         </is>
       </c>
     </row>
@@ -1218,21 +1220,23 @@
           <t>付费墙与权益</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>会员中心</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>（1）会员卡：会员标识 + 有效期 + 续费状态（自动续费 / 到期不再续费）
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>0812周三更新
+（1）会员卡：会员标识 + 有效期 + 续费状态（自动续费 / 到期不再续费）
 （2）「免费 vs 会员」权益对比表（逐项 ✅/✗）：基础文字知识问答、图音视频深度知识精讲、VIP 极速优先通道、实时电话即时问答、永享名家典藏知识（永享标注为「单独购买」）
-（3）底部说明「自动续费将于到期前 3 天短信提醒，可随时取消」</t>
+（3）底部说明「自动续费将于扣费前 5 天短信提醒，可随时取消」
+（4）「0812 修订」自动续费提醒时点定版为「扣费前 5 天」（原「到期前 3 天」作废；扣费日＝到期日前 1 天）。续费提醒短信模版（签名固定【科技文献出版社】，非动态机构名）——标准版：「【科技文献出版社】您订购的AI问书会员将于${到期日}到期，${扣费日}我们将通过微信自动续费${金额}元。如需退订，请前往微信"我的-服务-钱包-支付设置-自动续费/免密支付"管理。」降价版（会员价下调时合并降价告知，一条短信一并通知）：「【科技文献出版社】您订购的AI问书会员将于${到期日}到期。会员价已由${原价}元调整为${新价}元，${扣费日}我们将通过微信按新价格${新价}元自动续费。如需退订，请前往微信"我的-服务-钱包-支付设置-自动续费/免密支付"管理。」</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1266,7 @@
           <t>（1）自动续费开启时显示「取消自动续费」入口（无手动续费按钮）
 （2）点取消 → 二次确认 sheet（挽留设计：主按钮「暂不取消」、弱化「确认取消」）
 （3）确认取消 → toast「已取消成功,会员有效期至 X 后将不再自动续费」
-（4）重新开启自动续费（经手机号绑定门槛）→ toast「已开启自动续费 · 将于到期前 3 天短信提醒」</t>
+（4）重新开启自动续费（经手机号绑定门槛）→ toast「已开启自动续费 · 将于扣费前 5 天短信提醒」（0812：提醒时点随上条同步为扣费前 5 天）</t>
         </is>
       </c>
     </row>
@@ -1527,28 +1531,30 @@
           <t>我的</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>我的订单</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>（1）「0722 修订」双维度筛选并存：顶部为「订单类型」Tab（全部 / 会员 / 永享 / 兑换码），其下「订单状态」chips 改为 全部 / 待支付 / 已支付 / 已失效 / 退款售后，两维度分层放置、过滤取交集——推翻 0716「支付成功才落库」口径：发起支付即落库为「待支付」；部分退款、全额退款、退款中统一归入「退款/售后」桶；兑换码核销单归入「已支付」分组（行内标签仍显「已核销」；切到「兑换码」Tab 时隐藏状态 chips 的规则不变）
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>0812周三更新
+（1）「0722 修订」双维度筛选并存：顶部为「订单类型」Tab（全部 / 会员 / 永享 / 兑换码），其下「订单状态」chips 改为 全部 / 待支付 / 已支付 / 已失效 / 退款售后，两维度分层放置、过滤取交集——推翻 0716「支付成功才落库」口径：发起支付即落库为「待支付」；部分退款、全额退款、退款中统一归入「退款/售后」桶；兑换码核销单归入「已支付」分组（行内标签仍显「已核销」；切到「兑换码」Tab 时隐藏状态 chips 的规则不变）
 （2）列表按付款时间降序
-（3）「0722 修订」待支付订单卡显示「剩余支付时间」倒计时（下单起 30 分钟支付有效期）+「去支付」按钮，可重新调起微信支付；30 分钟未支付微信自动关单转「已失效」
+（3）「0722 修订」待支付订单卡显示「剩余支付时间」倒计时（下单起 15 分钟支付有效期，0812-e 由 30 分钟统一收敛）+「去支付」按钮，可重新调起微信支付；15 分钟未支付微信自动关单转「已失效」
 （4）「0722 修订」待支付 / 已失效订单无付款时间，卡片显示下单时间（其余订单仍显付款时间）
 （5）每单展示类型标签 + 标题 + 金额 + 状态 + 时间；仅「永享」订单展示关联 KP + 媒体名
 （6）存在退款时，列表以浅灰退款内容条（奶白暖灰底，弱化不抢视觉）展示逐笔退款进度、金额与时间；单笔退款进度三色语义：退款成功=青绿、退款中=靛蓝、退款失败=珊瑚红
 （7）订单整单状态（部分退款 / 全额退款 / 已核销等）统一中性墨灰呈现，不再各配彩色——状态是信息不是行动点，同屏只保留一处彩色语义（单笔退款进度）
 （8）点击进订单详情
 （9）「0724 修订」订单状态筛选 chips 单行横向展示、不换行，超出宽度时横向滚动
-（10）「0724 修订」订单详情页待支付倒计时条 / 已失效说明条与基础信息面板同宽对齐</t>
+（10）「0724 修订」订单详情页待支付倒计时条 / 已失效说明条与基础信息面板同宽对齐
+（11）「0812 修订」状态筛选改双维谓词、一单可命中多个筛选（订单状态 × 退款状态双维解耦，与后台同模型；推翻 0722「退款态从已支付桶移出」的互斥分桶）：「已支付」＝付款曾成功——含 已支付 / 已核销 / 部分退款 / 全额退款 / 退款中（全额退款的订单不再从「已支付」消失，避免用户按"我付过钱"的记忆找不到订单）；「退款/售后」＝发生过退款动作——含 退款中 / 部分退款 / 全额退款；"钱已退"的事实由卡片退款标记与逐笔退款明细行传达，不靠从筛选里隐藏表达</t>
         </is>
       </c>
     </row>
@@ -1582,8 +1588,9 @@
 （5）会员/永享订单存在退款时展示退款记录卡（按时间倒序）；同一订单允许多笔部分退款，逐笔展示退款单号、金额、状态、申请与完成时间；卡片标题与首条记录之间不留空白带，退款状态配色与订单列表一致（成功=青绿、退款中=靛蓝、失败=珊瑚红）
 （6）退款权益说明（全额退款仅撤销由该订单单独产生的权益 / 部分退款及其他独立赠送、兑换权益不受影响）由红色警示框改为退款记录卡内底部浅灰小字注释——C 端合规文案弱化呈现，不抢主信息视觉
 （7）「0722 修订」待支付订单：详情顶部显「剩余支付时间」倒计时条 +「去支付」按钮，可重新调起微信支付
-（8）「0722 修订」已失效订单：显提示「订单超 30 分钟未支付已自动失效，如需购买请重新下单」
-（9）「0722 修订」未支付订单（待支付 / 已失效）付款时间显「—」，且不渲染会员权益卡（权益未生效不展示）</t>
+（8）「0812 新增」待支付订单详情按下单时支付通道差异化（订单新增 payChannel 字段：jsapi / native）：Native（非微信浏览器扫码）下单的待支付单，详情页在倒计时条下方内嵌「扫码支付」卡——支付二维码 +「保存二维码到相册」按钮 + 指引「微信扫一扫 · 点击相册选择二维码完成支付」+「等待支付中」轮询行与「我已完成支付」兜底，用户回到订单即可继续支付（最短路径），倒计时条不再放「去支付」；JSAPI（微信内）下单的待支付单保持现状（倒计时 +「去支付」回收银台）。演示数据：OD20260812090233（月度会员首月特惠 ¥9.9 · Native 待支付）
+（9）「0722 修订」已失效订单：显提示「订单超 15 分钟未支付已自动失效，如需购买请重新下单」（0812-e 同步 15 分钟口径）
+（10）「0722 修订」未支付订单（待支付 / 已失效）付款时间显「—」，且不渲染会员权益卡（权益未生效不展示）</t>
         </is>
       </c>
     </row>
@@ -1629,22 +1636,24 @@
           <t>支付</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>微信支付收银台</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>（1）会员开通与永享买断统一走模拟微信支付收银台：标题区白底、AI 问书 logo 用会话同款电光靛紫色动画球
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>0812周三更新
+（1）会员开通与永享买断统一走模拟微信支付收银台：标题区白底、AI 问书 logo 用会话同款电光靛紫色动画球
 （2）展示商户「AI 问书」+ 金额 + 商品名；商户/确认支付按钮沿用微信绿 + 模拟环境提示「不会产生真实扣款」
-（3）随落地页环境开关联动双场景：微信内 → JSAPI（公众号支付），零钱/快捷直接在微信内调起；微信外 → H5/MWEB 支付，提示「即将唤起微信完成支付」并模拟跳转回跳
-（4）确认支付 → 支付成功结果页</t>
+（3）随落地页环境开关联动双场景：微信内 → JSAPI（公众号支付），零钱/快捷直接在微信内调起；微信外 → 见 0812 修订（Native 扫码）
+（4）确认支付 → 支付成功结果页
+（5）「0812 修订」非微信浏览器通道由 H5/MWEB 改为 Native 扫码（H5 支付权限被微信审核拒绝且无申诉通道，不注册小程序前提下的定稿预案）。流程：识别非微信环境 → 生成支付二维码 → 保存 / 截图二维码 → 微信扫一扫、点击相册选图 → 支付。收银台非微信分支五点交互（设计原则：离开前不用想、离开时拿得走、回来时不用操作）：① 大尺寸二维码居中 + 金额与订单摘要就近展示 + 有效期提示「二维码 15 分钟内有效 · 过期可返回重新下单」（0812-e 定稿：**全平台支付倒计时统一 15 分钟**——微信内 JSAPI 与非微信 Native 扫码同口径，二维码与订单同生共死（下单传 time_expire，码随单失效）；不做「重新生成」，码过期即订单已失效、需重新下单）② 主按钮「保存二维码到相册」（canvas 触发下载；0812-b：不再展示「长按二维码保存 / 截图」兜底文案行）③ 三步引导紧贴二维码下方：保存二维码 →「微信扫一扫，点击相册」→ 选择二维码完成支付 ④ 页面持续轮询查单，支付成功自动跳转成功页（用户从微信切回时零操作），辅以「我已完成支付」手动查单兜底 +「等待支付中」状态 ⑤ PC 浏览器同一分支直接扫屏即付、无需下载步骤。0812-b：非微信分支不再显示「浏览器支付 · 微信扫码（Native）」环境标签（二维码形态自解释；微信内 JSAPI 标签保留）。通道矩阵定稿：微信内＝JSAPI（不变）、非微信浏览器（手机 + PC）＝Native 扫码；手机浏览器无法同机扫屏，故以「保存二维码 → 相册识别」为主路径</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1880,7 @@
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>0807周五更新
+          <t>0812周三更新
 （1）页头标题 + 右上「导出」；文件名规范「AI问书_{机构名}_主控台数据导出.xlsx」；拆分“实时总览/经营分析”两个 Sheet——实时 Sheet 标注实时统计时间、经营分析 Sheet 标注所选区间具体起止；头部统一注明导出时间与导出时刻的全部筛选条件
 （2）0716 #3【全平台导出通用规则】：单次导出统一上限 10000 条（任一业务 Sheet 数据行超限即拦截，不下载），弹窗提示「本次筛选结果约 N 条，超过单次导出上限 10000 条，请缩小筛选范围后重试，或联系平台管理员导出完整数据」。规则集中在导出底座内拦截，两后台全部导出入口一致生效；导出进行中的提示统一为「正在导出」
 （3）导出指标全量不遗漏：实时总览含 累计GMV/累计退款/退款率/净GMV/当前会员数/累计注册用户；经营分析含各 KPI 及「较上一周期」环比列与趋势数据
@@ -1882,7 +1891,8 @@
 （8）「0807 新增」父机构视角：页头新增「机构」多选筛选（选项＝本机构（父机构）＋全部子机构，默认全选、支持跨机构任意组合勾选），实时总览与经营分析全部指标随所选机构集合联动——计数/金额类绝对量按集合聚合，率类指标为所选集合整体口径重算（非各机构简单相加）；子机构/独立机构视角无此筛选、保持现状
 （9）「0807 修订」机构多选交互定稿：选项行为自绘勾选框（选中靛蓝底白勾）＋「（父机构）」靛蓝标（与单选下拉同约定）、顶部「全部机构」快捷全选（分隔线隔开）；触发器回填所选机构名（全选显「全部机构」、部分选择顿号拼接、超宽省略号）；至少保留一家（取消最后一项 toast 拦截）
 （10）「0807 修订」导出 Sheet 结构对齐页面栏目：当前订阅（本机构配额，不随机构筛选）/ 实时总览 / 经营分析 三个 Sheet；父机构视角头部 scope 标「本机构（父机构）」并在筛选条件注明机构范围——导出数据随页面机构多选联动（多选＝合并口径、单选＝单机构），不单独产出分机构明细
-（11）「0807 修订」订阅套餐卡口径：订阅是机构级合同（各机构各自签、配额上限不同、聚合无意义）——父机构视角固定显示本机构订阅与配额、不随机构多选联动，卡右上角灰字注明「本机构订阅 · 不随机构筛选变化」；子机构订阅在平台后台对应机构详情查看</t>
+（11）「0807 修订」订阅套餐卡口径：订阅是机构级合同（各机构各自签、配额上限不同、聚合无意义）——父机构视角固定显示本机构订阅与配额、不随机构多选联动，卡右上角灰字注明「本机构订阅 · 不随机构筛选变化」；子机构订阅在平台后台对应机构详情查看
+（12）「0812 新增」无生效套餐空态定版（原空态仅一行灰字）：机构无订阅或套餐全部过期时，订阅卡区分两态结构化展示——① 曾有套餐全部过期：卡头保留上一套餐名 +「已过期」状态标，正文「订阅套餐已全部过期」+「上一套餐「{套餐}」已于 {到期日} 到期：机构既有内容与数据完整保留，C 端问答与新建 / 上传暂停，续费后即时恢复」+ 引导行「如需开通或续费，请联系平台客服」② 从未开通：「暂未开通订阅套餐」+ 开通价值说明 + 同引导行。历史经营数据（GMV / 会员 / 注册等存量与区间指标）照常展示——数据是既成事实，不随套餐过期消失。页头新增〔演示〕「订阅状态」三态切换（正常 / 全部过期 / 未开通，0812-e 由两态扩为三态，仅原型演示预览空态、非上线功能）</t>
         </is>
       </c>
     </row>
@@ -1961,22 +1971,24 @@
           <t>知识产品 KP</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>KP 列表</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>导入分享 KP</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr">
-        <is>
-          <t>（1）弹窗：分享链接（必填）+ 密码（必填）
-（2）弹窗底部提示改为灰色内容框内三条无序结构化条目：① 导入限制：仅支持导入外部机构分享，本机构分享不可导入 ② 实时同步：不占用接收方 KP 与存储，内容只读，Token 消耗归属接收方 ③ 独立快照：占用接收方 KP 与存储，支持编辑，Token 消耗归属接收方
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>0812周三更新
+（1）弹窗：分享链接（必填）+ 密码（必填）
+（2）弹窗底部提示改为灰色内容框内三条无序结构化条目：① 导入限制：仅支持导入外部机构分享，本机构分享不可导入 ② 实时同步：占用接收方 KP、不占存储，内容只读，Token 消耗归属接收方 ③ 独立快照：占用接收方 KP 与存储，支持编辑，Token 消耗归属接收方
 （3）禁止导入本机构自己生成的分享链接，命中时阻断并提示「不能导入本机构分享的知识产品」
-（4）确定 → toast「已导入分享 KP」</t>
+（4）确定 → toast「已导入分享 KP」
+（5）「0812 修订」实时分享计量口径变更：实时同步导入的 KP 改为「计入」接收方（消费机构）KP 数配额（原不占用），存储空间仍不占用（文件实体在源机构）、Token 仍计接收方——即 实时共享＝计 KP、不计存储、计 Token；快照共享＝计 KP、计存储、计 Token（不变）。导入弹窗三条规则、接收方只读 banner、新建分享弹窗规则说明与订阅配额口径文案同步更新（规则单一真源 sharePolicy 已同步）</t>
         </is>
       </c>
     </row>
@@ -2328,21 +2340,23 @@
           <t>知识产品 KP</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>共享 KP 权限矩阵</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>（1）0717 #4：实时同步（接收方 / 消费者视角）只读升级——基础信息表单输入框全部禁用置灰（无光标、hover 显示 not-allowed 禁止态，样式同既有只读输入框先例）、关联 Agent 下拉禁用、定价与权益单选整体置灰不可选；仅「复制链接」可操作；其余操作按钮置灰、点击提示「无权限操作」；二维码、分享两 Tab 隐藏。顶部只读说明 banner 单行呈现，来源机构为动态变量：「本 KP 由「{分享机构名}」以「实时同步」分享导入：内容随源机构自动更新、仅可查看不可编辑；不占本机构 KP 数与存储、问答消耗本机构 Token；二维码与分享不可用。」0717 二批 #5：禁用置灰统一标准＝「前台访问地址」只读框样式（纸白底 + 实线浅边框 + 深灰文字），两后台一致，不再用虚线浅灰底
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>0812周三更新
+（1）0717 #4：实时同步（接收方 / 消费者视角）只读升级——基础信息表单输入框全部禁用置灰（无光标、hover 显示 not-allowed 禁止态，样式同既有只读输入框先例）、关联 Agent 下拉禁用、定价与权益单选整体置灰不可选；仅「复制链接」可操作；其余操作按钮置灰、点击提示「无权限操作」；二维码、分享两 Tab 隐藏。顶部只读说明 banner 单行呈现，来源机构为动态变量：「本 KP 由「{分享机构名}」以「实时同步」分享导入：内容随源机构自动更新、仅可查看不可编辑；不占本机构 KP 数与存储、问答消耗本机构 Token；二维码与分享不可用。」0717 二批 #5：禁用置灰统一标准＝「前台访问地址」只读框样式（纸白底 + 实线浅边框 + 深灰文字），两后台一致，不再用虚线浅灰底
 （2）独立快照：五个 Tab 均可编辑；基础信息、知识库、定价数据在导入时复制，二维码与分享从消费机构自己的空数据开始
-（3）「0718 修订」实现对齐：实时同步只读表单的禁用输入框底色/边框/文字色已统一为「前台访问地址」只读框同款（纸白 --paper 底 + --line-2 实线浅边框 + --ink-2 深灰文字），修复此前禁用框使用另一套灰底（--surface-warm）造成的两灰并存</t>
+（3）「0718 修订」实现对齐：实时同步只读表单的禁用输入框底色/边框/文字色已统一为「前台访问地址」只读框同款（纸白 --paper 底 + --line-2 实线浅边框 + --ink-2 深灰文字），修复此前禁用框使用另一套灰底（--surface-warm）造成的两灰并存
+（4）「0812 修订」接收方只读 banner 文案随实时分享计量口径变更同步：「……占本机构 KP 数、不占存储、问答消耗本机构 Token；二维码与分享不可用。」（原「不占本机构 KP 数与存储」作废，见 KP 列表 · 导入分享 KP 0812 修订）</t>
         </is>
       </c>
     </row>
@@ -2401,15 +2415,17 @@
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>0807周五更新
+          <t>0812周三更新
 （1）区分新建/编辑：头部名称 + 类型标签 + 右侧「创建」/「保存」
-（2）左侧表单：头像（必填，上传 png/gif/jpg 走圆形裁剪）、名称（必填）、类型（不可更改，注「类型不可更改」）、TTS 参考音（必填，已上传显波形条 + 播放/暂停 + 时长 + 重新上传）、回答 Prompt
+（2）左侧表单：头像（必填，上传 png/gif/jpg 走圆形裁剪）、名称（必填）、类型（不可更改，注「类型不可更改」）、TTS 参考音（必填，已上传显波形条 + 播放/暂停 + 时长 + 重新上传）、人设风格（必填，0812 由「回答 Prompt」更名；0812-f 标红星必填——预设或自定义二选一，不可为空）
 （3）0716 #11：名称校验——机构内不允许重复（重名保存拦截 toast「该 Agent 名称在机构内已存在，请更换」），字段旁提示「名称在机构内不可重复」
 （4）0716 #11：TTS 参考音校验——仅支持 MP3 / WAV 格式、时长 3~10 秒；上传时真实读取音频元数据校验，超范围拦截并提示；字段旁提示「格式 MP3 / WAV · 时长 3~10 秒」
-（5）回答 Prompt 机构侧只读：灰底只读框 + 提示「受权限控制，若需编辑请联系平台管理员」（受角色权限「Agent 回答 Prompt 编辑」控制）
-（6）右侧「关联 KP」卡：列出关联 KP，点「前往 KP」跳对应 KP 详情
-（7）保存 → toast「已保存」；新建保存 → toast「已创建 Agent」回列表
-（8）「0807 新增」「TTS 参考音」下方新增字段「TTS 参考音文本」（必填）：即 TTS 参考音频内朗读的文本内容，用于 TTS 引擎将参考音与文本对齐；多行输入框，上限 100 字（按字符数计，不限制字符种类——中英文/数字/标点/符号均可），右下角实时字数「N / 100」、字段说明置输入框上方（文案「参考音频内朗读的文本内容・100 字以内，用于 TTS 引擎将参考音与文本对齐」）、名称字段的重复提示置输入框同行右侧；为空保存拦截 toast「请输入 TTS 参考音文本」，达 100 字后输入框拦截不可再输入；平台后台全域 Agent 详情同步生效（同一组件）</t>
+（5）人设风格（原「回答 Prompt」）机构侧（0812-e 改造）：预设 chip 可切换并保存，「自定义」chip 按角色权限「人设风格-自定义」开关——无权限时锁定态（虚线灰底 + 锁图标）、正文只读，但仍可切回查看本 Agent 已保存的自定义文案；说明行「此处只定义身份与语气，事实与安全规则由系统统一控制；可切换平台预设，「自定义」需平台授权」
+（6）「0812-f 新增」人设风格保存校验（不区分权限，「自定义」态正文为空一律拦截——人设风格是必填的生效配置，空文案会让 Agent 回落到无人设状态）：① 有自定义权限且正文为空 → toast「自定义人设风格不能为空，可先选择一个预设作起点」② 无自定义权限且正文为空（如原自定义文案被清空后权限被回收）→ toast「人设风格不能为空，请选择一个平台预设后保存」（按其可行动路径引导去选预设，而非提示改文本框）③ 其余情况（选中任一预设、或自定义正文非空）→ 正常保存 toast「已保存」。〔演示〕Agent 详情页头新增「自定义权限 有 / 无」两态切换，便于评审对比两种权限下的表现（上线后由登录账号的角色权限决定，非用户可切换项）
+（7）「0812 修订」字段「回答 Prompt」更名「人设风格」（机构后台、平台后台、角色权限项全链路统一；权限 key agent.prompt.edit 不变，避免存量角色数据迁移），并由裸文本框升级「预设 + 自定义」：文本区上方一排人设风格 chip 单选——专业友好（默认）/ 严谨学者 / 讲书人 / 极简效率 / 教练引导 / 行业顾问 / 少儿科普 七档平台预设 + 「自定义」。选预设＝正文只读展示该预设 prompt 全文（可见不黑盒，预设文案平台统一维护、升级后全平台生效；0812-e 删除正文下方「预设文案由平台统一维护…请切换到「自定义」」提示行——只读态本身已表达，无需文字重复）；选自定义＝正文可编辑，预填切换前文本作起点（降低从零编写门槛）。预设 chip 悬浮显示各档适用场景（如「严谨学者：医学、法律、财税、标准规范类机构」），采用平台通用深色浮层规格（同 InfoDot），帮机构选型。0812-e 权限语义定稿（与权限项定名「人设风格-自定义」对齐）：**预设人人可切**——机构后台不再整块只读，机构可自行在七档预设间切换并保存；**仅「自定义」受权限控制**——无「人设风格-自定义」权限时该 chip 呈锁定态（虚线灰底 + 锁图标），正文只读不可编辑。**锁的是「编辑」不是「查看」**：无权限机构切到预设后仍可切回「自定义」查看本 Agent 已保存的自定义文案（只读、且切回时自动恢复原文），避免一次切换就把原文案永久换掉而无权限写回、造成不可逆的数据丢失；该 Agent 从未存过自定义文案时（如新建），点「自定义」提示「需平台管理员授权（权限项：人设风格-自定义）」。说明文案合并为一行置于输入区上方（讲清「此处只定义身份与语气，事实与安全规则由系统统一控制」的分层边界 + 预设/自定义用法），输入框高度收窄（可手动拉高）研发口径（最小改动）：后端仅新增 preset_key 字段，选预设存 key、选自定义（preset_key=custom）才存 prompt 全文；存量 Agent 数据默认视为自定义、无迁移。新建 Agent 默认「专业友好」预设。0812-e：七档预设文案取自《AI问书-Agent人设-Prompt模板库.md》，统一为「身份陈述 + 风格 + 避免」三段结构化格式（每档 200 字上下）——人设段只管身份与语气；检索范围、溯源、事实约束、安全边界、拒答口径由平台底座的回答策略 Prompt 统一控制，人设段不重复也不覆盖（分层治理：机构可编辑的只有身份与语气描述，否则机构顺手写入的「要热情推荐相关书籍」之类会与策略段打架）；各档「避免」清单不可删——模型腔集中在开场寒暄、「希望对你有帮助」式收尾、过度共情三处，正面描述压不住、只有明确禁止才有效
+（8）右侧「关联 KP」卡：列出关联 KP，点「前往 KP」跳对应 KP 详情
+（9）保存 → toast「已保存」；新建保存 → toast「已创建 Agent」回列表
+（10）「0807 新增」「TTS 参考音」下方新增字段「TTS 参考音文本」（必填）：即 TTS 参考音频内朗读的文本内容，用于 TTS 引擎将参考音与文本对齐；多行输入框，上限 100 字（按字符数计，不限制字符种类——中英文/数字/标点/符号均可），右下角实时字数「N / 100」、字段说明置输入框上方（文案「参考音频内朗读的文本内容・100 字以内，用于 TTS 引擎将参考音与文本对齐」）、名称字段的重复提示置输入框同行右侧；为空保存拦截 toast「请输入 TTS 参考音文本」，达 100 字后输入框拦截不可再输入；平台后台全域 Agent 详情同步生效（同一组件）</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2523,7 @@
 （4）三个独立时间区间筛选（下单时间、支付时间、兑换时间）真实参与列表过滤（不限/近 7 天/30 天/自定义）
 （5）筛选行右侧「导出」：生成「AI问书_{机构名}_订单管理数据导出.xlsx」，严格沿用搜索、类型、状态、退款状态及三个时间区间筛选；文件头部注明导出时间与全部筛选条件
 （6）「0722 修订」订单状态筛选改为 全部 / 待支付 / 已支付 / 已核销 / 已失效（退款状态筛选维度不变）；状态色：待支付＝橙、已失效＝灰；付款时间为空（待支付 / 已失效）显「—」
-（7）「0722 修订」订单状态口径（三端统一，推翻 0716「支付成功才落库」）：用户发起支付即落库为「待支付」（微信 trade_state=NOTPAY），微信下单传 time_expire、30 分钟未支付微信自动关单（CLOSED）转「已失效」，无需自建定时器；网页支付（JSAPI/H5）不存在「支付失败」终态，用户余额不足、风控拦截等失败场景订单停留「待支付」可换方式重试；「已核销」为兑换码订单专属（无支付环节）；退款/售后走独立退款单与退款状态维度，与订单状态解耦；GMV、付费用户等营收指标仅计「已支付」订单（待支付 / 已失效不计入，相关指标 tooltip 注明）
+（7）「0722 修订」订单状态口径（三端统一，推翻 0716「支付成功才落库」）：用户发起支付即落库为「待支付」（微信 trade_state=NOTPAY），微信下单传 time_expire、15 分钟未支付微信自动关单（CLOSED）转「已失效」（0812-e：支付有效期由 30 分钟统一收敛为 15 分钟），无需自建定时器；网页支付（JSAPI/H5）不存在「支付失败」终态，用户余额不足、风控拦截等失败场景订单停留「待支付」可换方式重试；「已核销」为兑换码订单专属（无支付环节）；退款/售后走独立退款单与退款状态维度，与订单状态解耦；GMV、付费用户等营收指标仅计「已支付」订单（待支付 / 已失效不计入，相关指标 tooltip 注明）
 （8）「0807 新增」父机构视角：新增「机构」单选筛选＋列表新增数据归属机构列（首列后），子机构订单仅可查看、退款操作置灰（父子机构数据范围规则同「知识产品 KP · KP 列表」）；「仅显本机构订单」在父机构视角放宽为「本机构＋全部子机构订单」</t>
         </is>
       </c>
@@ -2966,26 +2982,28 @@
           <t>系统配置</t>
         </is>
       </c>
-      <c r="C81" s="3" t="inlineStr">
+      <c r="C81" s="4" t="inlineStr">
         <is>
           <t>AI 会员价格</t>
         </is>
       </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
-        <is>
-          <t>（1）「0718 修订」价格配置按两种购买方式分组展示，向运营明示每档金额——① 连续包月（自动续费）：首月价格（首月特惠，默认 ¥9.9，仅首次开通的首月扣款）+ 次月起价格（默认 ¥19.9/月，第 2 个月起每月自动扣款）；② 单月（一次性购买 · 不自动续费）：单月价格（默认 ¥19.9/1 个月，一次性扣款、到期自动失效不再扣费）；每档附前台展示位置说明，与前台「开通会员」两档一一对应
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>0812周三更新
+（1）「0718 修订」价格配置按两种购买方式分组展示，向运营明示每档金额——① 连续包月（自动续费）：首月价格（首月特惠，默认 ¥9.9，仅首次开通的首月扣款）+ 次月起价格（默认 ¥19.9/月，第 2 个月起每月自动扣款）；② 单月（一次性购买 · 不自动续费）：单月价格（默认 ¥19.9/1 个月，一次性扣款、到期自动失效不再扣费）；每档附前台展示位置说明，与前台「开通会员」两档一一对应
 （2）续费规则只读：「按月自动续费，会员到期后 72 小时为服务缓冲期 · 暂不可编辑」
 （3）0717 #7：「调价须知」标题与文案同一行、以「：」衔接——「调价须知：会员价一经确定，非必要请勿修改；已开通自动续费的用户，下一扣费周期将按修改后的价格扣款。」（amber 淡底左边线警示块）
 （4）「保存」→ toast「已保存价格」
 （5）「0718 修订」「调价须知」警示块移到「保存」按钮右侧（同一行，原在按钮之前独占一行），并去掉左侧 amber 色条、仅保留灰色内容块，页面动线变为：两组价格 → 续费规则 → 保存＋调价须知
 （6）「0718 修订」①「调价须知：」标题去掉加粗（与正文同字重）；②「保存」价格增加二次确认弹窗（说明影响范围：新开通按新价、已开通自动续费的用户下一扣费周期按新价扣款，确认后才生效并 toast「已保存价格」）
 （7）「0718 修订」价格配置视觉清洗：两组价格改为并排两枚子面板（连续包月＝「自动续费」琥珀语义标 / 单月＝「一次性购买 · 不自动续费」灰标，与前台「开通会员」套餐卡的续费语义标一致）；每档为「标签＋输入框＋一行说明」；续费规则由禁用输入框改为静态文本＋「暂不可编辑」小标（只读信息不再伪装成表单控件）
-（8）「0718 修订」续费规则与调价须知合并为同一灰色说明块（与上方两枚价格面板同宽、左对齐，不再缩进表单标签列；两行：续费规则 / 调价须知，纯文字呈现——去掉「暂不可编辑」小标与两行间分隔线），保存按钮单独一行、同样左对齐</t>
+（8）「0718 修订」续费规则与调价须知合并为同一灰色说明块（与上方两枚价格面板同宽、左对齐，不再缩进表单标签列；两行：续费规则 / 调价须知，纯文字呈现——去掉「暂不可编辑」小标与两行间分隔线），保存按钮单独一行、同样左对齐
+（9）「0812 修订」调价后的自动扣费口径定版「就低不就高」（自动扣费价 = min(签约价, 当前售价)，推翻 0717「下一扣费周期按修改后价格扣款」的单一口径）：① 降价——已开通自动续费的存量用户按最新（更低）价格扣款，且须在扣费前告知（并入扣费前 5 天的续费提醒短信，用降价版模版一并通知，见 C 端会员中心 0812 修订）② 涨价——存量用户仍按其签约价格扣款（保护存量用户，符合委托代扣「不高于」型签约模板约束），仅新签约用户按新价格执行 ③ 新用户始终按最新价格签约。说明块由两行扩为四行（续费规则 / 调价须知 / 降价 / 涨价），保存二次确认弹窗文案同步改为就低不就高口径</t>
         </is>
       </c>
     </row>
@@ -3358,22 +3376,24 @@
           <t>机构管理</t>
         </is>
       </c>
-      <c r="C94" s="3" t="inlineStr">
+      <c r="C94" s="4" t="inlineStr">
         <is>
           <t>机构详情 · 基本资料</t>
         </is>
       </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E94" s="6" t="inlineStr">
-        <is>
-          <t>（1）表单含机构域名前缀：前缀与“-aba.{当前环境根域名}”同框同行、后缀置灰只读；保存前全局唯一校验，不再额外展示固定路由说明
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
+        <is>
+          <t>0812周三更新
+（1）表单含机构域名前缀：前缀与“-aba.{当前环境根域名}”同框同行、后缀置灰只读；保存前全局唯一校验，不再额外展示固定路由说明
 （2）页头状态后仅父机构显示“父机构”标签。上级机构字段按角色分三态——子机构不再只读：可直接改选其他顶级机构为新上级（二次确认后生效），并提供「取消关联，转为独立机构」操作（二次确认；解除后本机构变普通机构，原父机构若再无其他子机构则父机构身份同步解除）；父机构仍置灰并提示“已是父机构，不能再设上级机构（仅支持父 / 子两层）”；普通机构可选一个顶级机构作为上级。停用父机构默认不级联停用子机构
 （3）联系人仅保留姓名与手机号；状态只读
-（4）仅本 Tab 时头部显「保存」→ toast「已保存」</t>
+（4）仅本 Tab 时头部显「保存」→ toast「已保存」
+（5）「0812 新增」机构名称之后新增字段「机构主体全称」（营业执照名称，必填、可重复——同一主体可运营多个机构）：作为变量注入 C 端《用户协议》《隐私政策》《会员服务协议》《自动续费（扣费）协议》四份协议文本中的机构主体名称；字段旁小问号说明用途，输入框右侧灰字「同步至协议文本」</t>
         </is>
       </c>
     </row>
@@ -3388,22 +3408,24 @@
           <t>机构管理</t>
         </is>
       </c>
-      <c r="C95" s="3" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>机构详情 · 订阅配额</t>
         </is>
       </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>（1）KP数与存储“已用”始终取机构当前实际占用，不按订阅订单拆分；Token“已用”仅取当前订阅周期消耗，新订阅生效时清零重新累计
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>0812周三更新
+（1）KP数与存储“已用”始终取机构当前实际占用，不按订阅订单拆分；Token“已用”仅取当前订阅周期消耗，新订阅生效时清零重新累计
 （2）新订阅生效即整体替换三项基础上限，不结转旧订阅剩余额度；加油包只在所属当前订阅内累加，到期不结转
-（3）降配后若KP/存储当前占用超过新上限，保留既有内容但阻断新建、上传和快照导入，直至占用回落；实时共享不计KP/存储但计消费机构Token
-（4）订阅列表筛选调整：商务负责人由下拉改为模糊搜索输入框，置于套餐筛选之前；其后依次为套餐、状态筛选</t>
+（3）降配后若KP/存储当前占用超过新上限，保留既有内容但阻断新建、上传和快照导入，直至占用回落；实时共享计KP、不计存储、计消费机构Token（0812 修订，原「实时共享不计KP/存储」作废）
+（4）订阅列表筛选调整：商务负责人由下拉改为模糊搜索输入框，置于套餐筛选之前；其后依次为套餐、状态筛选
+（5）「0812 新增」无生效套餐空态（与机构后台主控台同一组件同规则）：机构无订阅或套餐全部过期时，当前订阅卡区分「全部过期」（保留上一套餐名与到期日 + 影响说明）与「从未开通」两态，引导行为「可点击右上角「新建订阅」为机构开通或续费」；预置两家演示机构：「EE 美术出版」（订阅记录全部已过期，演示「全部过期」态）、「AA 少儿分社」（无任何订阅记录，演示「从未开通」态）</t>
         </is>
       </c>
     </row>
@@ -3577,7 +3599,7 @@
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>0810周一更新
+          <t>0812周三更新
 （1）微信公众号字段改为“网页授权回调地址”，微信开放平台字段改为“授权回调地址”；均填写完整 URL，并继续校验与微信后台配置一致
 （2）微信支付（必填，用于支付/退款/自动续费，未配置前台无法下单）：商户号 MchID、API v3 密钥（掩码）、商户证书（上传 apiclient_cert.pem）；限制说明（商户号须与公众号 AppID 关联绑定/需上传证书且 API v3 密钥在商户平台设置/退款·自动续费依赖支付能力）；保存 toast「已保存微信支付配置」
 （3）「0722 修订」微信公众号卡片新增「网页授权域名校验文件」上传（MP_verify_xxx.txt，公众号后台生成，需放置于网页授权域名根目录下）
@@ -3586,7 +3608,8 @@
 （6）「0807 新增」微信支付卡片新增四项参数，字段顺序：商户号 → API v2 密钥 → API v3 密钥 → 商户证书 → 商户 API 私钥 → 支付公钥 ID → 支付公钥文件 → 委托代扣包月模板 ID（密钥按版本号升序、证书/验签/业务参数依次排列）：① API v2 密钥（掩码文本，置于 API v3 密钥之前）——微信支付 v2 版接口的签名密钥（32 位，商户平台「账户中心-API 安全」设置）；委托代扣（自动续费）的签约/扣款接口体系仍走 v2 签名，配置连续包月必需，与 API v3 密钥并存不互斥 ② 支付公钥 ID（文本，PUB_KEY_ID_ 开头，置于商户 API 私钥之后）——微信支付「公钥模式」验签标识，2024 年起新注册商户默认发放微信支付公钥（替代平台证书轮换机制），验签时按回调头 Wechatpay-Serial 匹配此 ID
 （7）「0807-2 修订」敏感项定稿「写后不回显」（推翻同批显隐眼睛方案）：九个敏感字段——公众号 AppSecret / 域名校验文件、开放平台 AppSecret、微信支付 API v2 密钥 / API v3 密钥 / 商户证书 / 商户 API 私钥 / 支付公钥 ID / 支付公钥文件——非空时仅显示「已配置 / 已上传」状态行，提供「更新」能力：点更新出空输入框（占位「输入新值 · 保存后不再回显」），点保存先弹二次确认（提醒整体覆盖原值、不可恢复、新值不再回显，请先核对输入无误），确认后回状态行、不回显新值；文件类「重新上传」同样先弹二次确认（提醒整体覆盖、原文件不可恢复、新文件同样不提供下载与回显）再选文件；显隐眼睛能力删除。密钥在数据库为加密存储（非明文），业务需要原值须联系技术发邮件申请（技术从微信后台获取或数据库解密提供），界面不提供明文查看与文件下载；卡片限制说明区同步注明。非敏感字段（AppID、回调地址、商户号、代扣模板 ID）保持可见可编辑
 （8）「0807 新增」③ 支付公钥文件（上传 pub_key.pem，紧随支付公钥 ID）——与公钥 ID 配套的公钥文件，商户平台下载，用于验证微信支付应答与回调签名（新商户公钥验签、存量商户平台证书验签，按商户号实际发放形态二选一） ④ 委托代扣包月模板 ID（文本，置于卡片末尾业务参数位）——委托代扣「签约模板」经微信审核通过后分配的模板 ID（plan_id），C 端用户签约连续包月扣费时传入；卡片限制说明区同步补充四项参数用途一句话说明
-（9）「0810 修订」敏感项状态行收敛为「状态 + 操作」两段（与技术确认后定稿）：九个敏感字段的「已配置 / 已上传」状态行不再展示 密钥尾号 ****后 4 位 / 文件名 与 更新时间，只保留状态字样与「更新 / 重新上传」操作（原 0807-2 的「尾号或文件名 + 更新时间精确到秒」展示取消）；二次确认弹窗文案同步去掉对尾号 / 文件名的引用，改为「整体覆盖当前值 / 当前文件」。更新覆写、写后不回显、二次确认、界面不提供明文查看与文件下载等规则均不变；未上传项的空态上传框保持原样</t>
+（9）「0810 修订」敏感项状态行收敛为「状态 + 操作」两段（与技术确认后定稿）：九个敏感字段的「已配置 / 已上传」状态行不再展示 密钥尾号 ****后 4 位 / 文件名 与 更新时间，只保留状态字样与「更新 / 重新上传」操作（原 0807-2 的「尾号或文件名 + 更新时间精确到秒」展示取消）；二次确认弹窗文案同步去掉对尾号 / 文件名的引用，改为「整体覆盖当前值 / 当前文件」。更新覆写、写后不回显、二次确认、界面不提供明文查看与文件下载等规则均不变；未上传项的空态上传框保持原样
+（10）「0812 新增」微信公众号卡片新增两字段：① 微信公众号名称（文本，必填，置于公众号 AppID 之前）——公众号后台展示的账号名称 ② 备注（文本，选填，0812-e 定稿置于卡片末位「域名校验文件」之下——备注是整卡的补充说明，不插在接入参数序列中间）。两字段均为非敏感项，正常回显可编辑，不走「写后不回显」通道</t>
         </is>
       </c>
     </row>
@@ -3601,19 +3624,20 @@
           <t>机构管理</t>
         </is>
       </c>
-      <c r="C102" s="3" t="inlineStr">
+      <c r="C102" s="4" t="inlineStr">
         <is>
           <t>机构详情 · 用量看板</t>
         </is>
       </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E102" s="6" t="inlineStr">
-        <is>
-          <t>（1）当前生效订阅卡置于时间筛选上方，归入“实时订阅与资源占用”；KP/存储显示占用量，Token 显示当前订阅周期消耗量，不随时间筛选变化
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>0812周三更新
+（1）当前生效订阅卡置于时间筛选上方，归入“实时订阅与资源占用”；KP/存储显示占用量，Token 显示当前订阅周期消耗量，不随时间筛选变化
 （2）页面明确拆分“实时存量”和“区间运营分析”；今日/近7天/近30天/自定义仅联动活跃、新增、提问、GMV、付费用户及 LLM 区间消耗
 （3）配额阈值预警条：「Token 已用 X%，已于 日期 向机构联系人（姓名·手机号）发送 70%/80% 预警短信；达 90%/95% 将再次提醒。配额可在『订阅配额』调整」
 （4）阈值预警短信触达规则与文案模版：触发档位＝本订阅周期 Token 消耗率达 70% / 80% / 90% / 95% 四档，每档首次达到时向机构联系人手机号各发一次，同一计费周期内同档不重复、进入下一周期归零重置；四档共用一条参数化模版，签名用平台方「【AI问书】」（区别于 C 端验证码短信用机构名签名）。文案：【AI问书】您的机构「${orgName}」本订阅周期 Token 用量已达 ${pct}%，达上限后 C 端问答将被暂停，请及时登录机构后台「订阅配额」扩容或联系客服。如已处理请忽略本短信。（${orgName}=机构名，${pct}=当前消耗率）
@@ -3621,7 +3645,8 @@
 （6）「0724 修订」内容存量板块（KP 当前占用 / KP 状态分布 已发布·草稿·已下架 / 存储当前占用）整体从用量看板移除；【实时存量】仅保留「用户与营收存量」一张卡，KP 与存储占用在页面顶部「当前生效订阅卡」查看
 （7）「0722 修订」「累计 GMV」＝机构开通至今全部已支付订单总额（含已产生退款的部分），存量口径、不随区间筛选变化，故放实时板块；放置原则：区间板块放「流量」指标（该时间段内发生的量，随时间筛选联动），实时板块放「存量」指标（当前 / 累计快照）——避免「选了近 7 天却显示累计值」的口径混乱；指标口径与机构后台数据看板、附表二三方一致
 （8）0716 #13：UsageCard 指标数值与后面的对比周期时间（如「对比 07-03~07-09」）之间增加水平间距，避免过于紧凑
-（9）「用户与营收存量」卡片标题不带括号「实时快照」字样——实时口径已由所在「实时订阅与资源占用」分区标题统一说明，不逐卡重复</t>
+（9）「用户与营收存量」卡片标题不带括号「实时快照」字样——实时口径已由所在「实时订阅与资源占用」分区标题统一说明，不逐卡重复
+（10）「0812 新增」无生效套餐空态：机构无订阅或套餐全部过期时，当前订阅卡走空态（同订阅配额 Tab 0812 规则，引导行「可切换到「订阅配额」Tab 新建订阅为机构开通或续费；历史用量数据仍按下方板块正常展示」）；配额阈值预警条（Token 已达 X%）随之隐藏——无生效周期即无「本周期消耗」，不可再渲染预警；「用户与营收存量」等历史用量卡照常展示（数据是既成事实，不随套餐过期消失）</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4072,7 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>全域 Agent 详情（Prompt 平台可编辑）</t>
+          <t>全域 Agent 详情（人设风格平台可编辑）</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -4057,11 +4082,12 @@
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>0807周五更新
+          <t>0812周三更新
 （1）表单同机构后台 Agent 详情：头像（必填，圆形裁剪）、名称（必填）、类型（只读不可改）、TTS 参考音（必填）、TTS 参考音文本（必填）
-（2）回答 Prompt 平台超管可编辑：可编辑文本框 + 提示「平台超管可编辑全平台任意 Agent 的回答 Prompt，保存后即时生效」；保存 toast「已保存（含回答 Prompt）」
+（2）人设风格（原「回答 Prompt」）平台超管可编辑：预设 chip + 文本区 + 说明行「此处只定义身份与语气，事实与安全规则由系统统一控制；选预设即用即生效，「自定义」可自由改写」；保存 toast「已保存」；自定义为空保存拦截 toast「自定义人设风格不能为空，可先选择一个预设作起点」
 （3）右侧「关联 KP」卡：点「前往 KP」跳全域 KP 详情
-（4）「0807 新增」新增「TTS 参考音文本」（必填，上限 100 字、不限字符种类，右下角实时字数）：TTS 参考音频内朗读的文本内容；位于 TTS 参考音之下，字段规格、校验与机构后台 Agent 详情一致（同一组件同步生效）</t>
+（4）「0807 新增」新增「TTS 参考音文本」（必填，上限 100 字、不限字符种类，右下角实时字数）：TTS 参考音频内朗读的文本内容；位于 TTS 参考音之下，字段规格、校验与机构后台 Agent 详情一致（同一组件同步生效）
+（5）「0812 修订」「回答 Prompt」更名「人设风格」并升级「七档平台预设 + 自定义」（规格、交互与机构后台 Agent 详情 0812 修订一致，同一组件同步生效；预设文案平台统一维护）：专业友好（默认）/ 严谨学者 / 讲书人 / 极简效率 / 教练引导 / 行业顾问 / 少儿科普；选预设正文只读展示全文并注明「预设文案由平台统一维护、升级后全平台生效；如需在此基础上修改，请切换到「自定义」」</t>
         </is>
       </c>
     </row>
@@ -4337,10 +4363,10 @@
           <t>0807周五更新
 （1）副标题「按角色类型分别管理机构角色与平台角色（权限点不同）；机构账户选机构角色、平台账户选平台角色」
 （2）顶部切换「机构角色 / 平台角色」
-（3）机构角色权限点分组：主控台 / 产品中心（0716 #7/#8.1：知识产品 KP 与 Agent 人设同一行左右两列，KP 在左列，其三态开关与「查看主控台」垂直对齐）/ 运营中心（C 端用户、订单管理、兑换码）/ 数据中心（数据看板）/ 系统设置（客服配置、系统配置）；「Agent 回答 Prompt 编辑」为功能权限（其余为菜单权限），加「功能权限」标签区分
-（4）0716 #8：「Agent 回答 Prompt 编辑」作为「Agent 人设」的嵌套子项——仅当「Agent 人设」= 可操作时才展开显示（无 / 只读时完全不显示，而非置灰锁定）；用缩进 + 灰色虚线连接线表达从属关系（0717 #6：去掉子项紫色背景块，仅保留缩进 + 虚线连接线）；「功能权限」标签移至权限 key 行（与标题行分离，保证右侧两态开关垂直居中对齐）；子项两态（只读 / 可操作）；「Agent 人设」降级为只读 / 无时子项自动收起
+（3）机构角色权限点分组：主控台 / 产品中心（0716 #7/#8.1：知识产品 KP 与 Agent 人设同一行左右两列，KP 在左列，其三态开关与「查看主控台」垂直对齐）/ 运营中心（C 端用户、订单管理、兑换码）/ 数据中心（数据看板）/ 系统设置（客服配置、系统配置）；「人设风格-自定义」（0812 由「Agent 回答 Prompt 编辑」更名为「Agent 人设风格编辑」，0812-e 再定名「人设风格-自定义」；权限 key agent.prompt.edit 始终不变，无存量角色数据迁移）为功能权限（其余为菜单权限），加「功能权限」标签区分
+（4）0716 #8：「人设风格-自定义」（0812-e 定名）作为「Agent 人设」的嵌套子项——仅当「Agent 人设」= 可操作时才展开显示（无 / 只读时完全不显示，而非置灰锁定）；用缩进 + 灰色虚线连接线表达从属关系（0717 #6：去掉子项紫色背景块，仅保留缩进 + 虚线连接线）；「功能权限」标签移至权限 key 行（与标题行分离，保证右侧两态开关垂直居中对齐）；子项两态（只读 / 可操作）；「Agent 人设」降级为只读 / 无时子项自动收起
 （5）平台角色权限点分组：主控台 / 机构管理（机构管理、机构账户、订阅订单）/ 产品中心（全域 KP、全域 Agent）/ 运营中心（全域用户、全域订单）/ 数据中心（全域答案反馈、全域模型用量）/ 系统设置（平台账户、角色权限、默认 LLM）
-（6）左侧角色列表，右侧权限面板：菜单权限项 = 图标 + 名称 + 三态分段开关（无/只读/可操作）；功能权限「Agent 回答 Prompt 编辑」为两态（只读/可操作）——功能权限的「无」与「只读」语义相同（都表现为不可编辑），合并为「只读」
+（6）左侧角色列表，右侧权限面板：菜单权限项 = 图标 + 名称 + 三态分段开关（无/只读/可操作）；功能权限「人设风格-自定义」为两态（只读/可操作）——功能权限的「无」与「只读」语义相同（都表现为不可编辑），合并为「只读」
 （7）三态图例（InfoDot）：无＝看不见该菜单 / 只读＝可进入查看不能编辑（功能权限＝不可编辑）/ 可操作＝全部操作可用；「保存」→ toast「已保存权限」
 （8）「0807 修订」「可操作」的数据范围口径明确：平台角色的「可操作」＝可跨机构操作全平台数据；机构角色的「可操作」＝仅针对本机构数据——父机构账户虽可见下属子机构数据（列表可筛、看板可汇总），但对子机构数据仅可查看、不可操作（操作入口置灰并提示「仅可操作本机构数据」）；三态图例 InfoDot 同步补充本条说明</t>
         </is>

--- a/docs/feature-list.xlsx
+++ b/docs/feature-list.xlsx
@@ -1892,7 +1892,7 @@
 （9）「0807 修订」机构多选交互定稿：选项行为自绘勾选框（选中靛蓝底白勾）＋「（父机构）」靛蓝标（与单选下拉同约定）、顶部「全部机构」快捷全选（分隔线隔开）；触发器回填所选机构名（全选显「全部机构」、部分选择顿号拼接、超宽省略号）；至少保留一家（取消最后一项 toast 拦截）
 （10）「0807 修订」导出 Sheet 结构对齐页面栏目：当前订阅（本机构配额，不随机构筛选）/ 实时总览 / 经营分析 三个 Sheet；父机构视角头部 scope 标「本机构（父机构）」并在筛选条件注明机构范围——导出数据随页面机构多选联动（多选＝合并口径、单选＝单机构），不单独产出分机构明细
 （11）「0807 修订」订阅套餐卡口径：订阅是机构级合同（各机构各自签、配额上限不同、聚合无意义）——父机构视角固定显示本机构订阅与配额、不随机构多选联动，卡右上角灰字注明「本机构订阅 · 不随机构筛选变化」；子机构订阅在平台后台对应机构详情查看
-（12）「0812 新增」无生效套餐空态定版（原空态仅一行灰字）：机构无订阅或套餐全部过期时，订阅卡区分两态结构化展示——① 曾有套餐全部过期：卡头保留上一套餐名 +「已过期」状态标，正文「订阅套餐已全部过期」+「上一套餐「{套餐}」已于 {到期日} 到期：机构既有内容与数据完整保留，C 端问答与新建 / 上传暂停，续费后即时恢复」+ 引导行「如需开通或续费，请联系平台客服」② 从未开通：「暂未开通订阅套餐」+ 开通价值说明 + 同引导行。历史经营数据（GMV / 会员 / 注册等存量与区间指标）照常展示——数据是既成事实，不随套餐过期消失。页头新增〔演示〕「订阅状态」三态切换（正常 / 全部过期 / 未开通，0812-e 由两态扩为三态，仅原型演示预览空态、非上线功能）</t>
+（12）「0812 新增」无生效套餐空态定版（原空态仅一行灰字）：机构无订阅或套餐全部过期时，订阅卡区分两态结构化展示——① 曾有套餐全部过期：卡头保留上一套餐名 +「已过期」状态标，正文「订阅套餐已全部过期」+「上一套餐「{套餐}」已于 {到期日} 到期：机构既有内容与数据完整保留，C 端问答与新建 / 上传暂停，续费后即时恢复」+ 引导行「如需开通或续费，请联系平台客服」② 从未开通：「暂未开通订阅套餐」+ 开通价值说明 + 同引导行。历史经营数据（GMV / 会员 / 注册等存量与区间指标）照常展示——数据是既成事实，不随套餐过期消失。页头新增〔演示〕「订阅状态」四态切换（正常 / 不限 / 全部过期 / 未开通，0812-g 补「不限」态，仅原型演示、非上线功能）</t>
         </is>
       </c>
     </row>
@@ -3425,7 +3425,8 @@
 （2）新订阅生效即整体替换三项基础上限，不结转旧订阅剩余额度；加油包只在所属当前订阅内累加，到期不结转
 （3）降配后若KP/存储当前占用超过新上限，保留既有内容但阻断新建、上传和快照导入，直至占用回落；实时共享计KP、不计存储、计消费机构Token（0812 修订，原「实时共享不计KP/存储」作废）
 （4）订阅列表筛选调整：商务负责人由下拉改为模糊搜索输入框，置于套餐筛选之前；其后依次为套餐、状态筛选
-（5）「0812 新增」无生效套餐空态（与机构后台主控台同一组件同规则）：机构无订阅或套餐全部过期时，当前订阅卡区分「全部过期」（保留上一套餐名与到期日 + 影响说明）与「从未开通」两态，引导行为「可点击右上角「新建订阅」为机构开通或续费」；预置两家演示机构：「EE 美术出版」（订阅记录全部已过期，演示「全部过期」态）、「AA 少儿分社」（无任何订阅记录，演示「从未开通」态）</t>
+（5）「0812-g 新增」额度「不限」的展示规则（不限版套餐三项均不限；定制版可只设某一项不限，故按行判定）：额度值显示「不限」而非数字，**不画百分比进度条**——无上限则「还剩多少 / 快满了吗」不成立，画一条恒 0% 的进度条会被误读为「几乎没用」或数据异常；进度条位置改为满宽的电光靛渐隐轨道、右端淡出不封口 + 一层慢速流光扫过（0813 视觉定版，表达「延伸出去、没有终点」，与有上限的实心条一眼可辨），右侧百分比位置显示「不限」（电光靛）。保留「当前占用 / 本周期消耗」的绝对值——这是不限额度下唯一有意义的信息（了解规模与成本）。配套规则：不限项不做超限阻断；加油包对不限项无意义；Token 不限时用量看板的阈值预警条隐藏（无上限即无 70/80/90/95% 阈值）。演示：机构后台主控台〔演示〕订阅状态「不限」态、平台后台演示机构「BB 数字出版」
+（6）「0812 新增」无生效套餐空态（与机构后台主控台同一组件同规则）：机构无订阅或套餐全部过期时，当前订阅卡区分「全部过期」（保留上一套餐名与到期日 + 影响说明）与「从未开通」两态，引导行为「可点击右上角「新建订阅」为机构开通或续费」；预置两家演示机构：「EE 美术出版」（订阅记录全部已过期，演示「全部过期」态）、「AA 少儿分社」（无任何订阅记录，演示「从未开通」态）</t>
         </is>
       </c>
     </row>

--- a/docs/feature-list.xlsx
+++ b/docs/feature-list.xlsx
@@ -2873,9 +2873,12 @@
           <t>（1）指标按统计口径分三类（0724 修订：日活 / 周活 / 月活为固定滚动窗口实时快照、各自与上一等长窗口环比，不归区间统计）：① 实时快照——累计 / 存量，如主控台累计 GMV、当前会员、KP 占用，截至当前的实时值、不参与环比；② 区间统计——随今日 / 7 日 / 30 日联动并与上一等长周期环比，如新增用户、区间 GMV、区间提问、付费转化；③ 成熟 cohort——留存率，独立队列口径、不跟随全局筛选。① 归「实时」分区、② 归「区间 / 经营分析」分区、③ 用独立队列筛选
 （2）每个指标悬浮面板统一写清：指标定义、分子/分母、去重主键、时区、统计周期、上一周期与差值单位；累计/快照指标明确标注“不参与环比”
 （3）今日 00:00–当前时刻对比昨日相同经过时长；近7/30天及自定义区间对比紧邻的上一等长区间；计数/金额用相对百分比，率类为绝对差、统一以「%」符号展示（0807 修订：原「N 个百分点」文案改为「N%」，与计数类视觉一致，差值口径在指标 tooltip 注明），时长用绝对差
-（4）上一周期为0时不计算无穷增幅，统一显示“上期为0，暂无可比增幅”；趋势按精确去重数据计算，不再使用0.62/0.42等估算系数；今日趋势按小时
-（5）「0722 修订」统一去重规则并全量落 tooltip：规模指标按用户去重——区间内按用户 ID 精确去重，同一用户跨天重复只计 1 人（活跃用户、新增 C 端、付费用户、提问用户等）；强度指标按人天——用户 × 自然日累加（日均活跃 DAU 均值、人均提问等）；两后台所有涉去重指标的悬浮口径均标注所属类别与去重口径。例：某用户 7 天区间内第 1、2 天活跃——「活跃用户」计 1 人，「日均活跃」贡献 2 个人天
-（6）「0724 修订」悬浮 tooltip 去重规则表述统一：去重规则不再混在指标定义句中，tooltip 内独立成条「· 去重：xxxx」；逐指标去重口径见附表一 / 附表二新增的「去重规则」列</t>
+（4）「0813周四 修订」区间统计口径定版为「完整自然日、不含今日」：近 7 天＝截至昨日 24:00 往前 7 个完整自然日（如今天 08-13 则为 08-06—08-12），对比区间为再往前 7 个完整自然日（07-30—08-05）；近 30 天与自定义同规则。原口径把区间终点取到「今天 23:59」，而对比区间是完整日，等于拿未过完的半天去比整天，环比系统性偏负、同一天早晚看到的数还不一样。「今日」档不变（00:00 至当前时刻 vs 昨日同已过时长），是唯一的实时口径。四处区间区块（机构主控台经营分析 / 数据看板区间分析 / 平台主控台经营分析 / 机构详情区间运营分析）副标题统一标注「统计截至昨日 24:00（不含今日），今日数据见「今日」档」
+（5）「0813周四 修订」自定义区间日历加可选边界：结束日最晚为昨日（今天及未来日期置灰不可选），起始日最早为近 3 年（超出置灰）；面板底部固定脚注说明口径与可选范围。数据看板「自定义」原先只回传 label、落不到三档字典上，会静默回落成 7 日数据与 7 日环比（用户无感），本次改为按真实天数就近取档并显式标注实际落用档位，环比按真实天数计算
+（6）「0813周四 修订」日活 / 周活 / 月活三卡为「含今日」的实时滚动窗口，与区间档的「截至昨日完整自然日」口径不同，两者数值不可直接对齐（一个问活跃规模的实时脉搏、一个问一段时间的经营结果）。周活 / 月活 tooltip 末尾显式注明该差异，避免误读为数据不一致
+（7）上一周期为0时不计算无穷增幅，统一显示“上期为0，暂无可比增幅”；趋势按精确去重数据计算，不再使用0.62/0.42等估算系数；今日趋势按小时
+（8）「0722 修订」统一去重规则并全量落 tooltip：规模指标按用户去重——区间内按用户 ID 精确去重，同一用户跨天重复只计 1 人（活跃用户、新增 C 端、付费用户、提问用户等）；强度指标按人天——用户 × 自然日累加（日均活跃 DAU 均值、人均提问等）；两后台所有涉去重指标的悬浮口径均标注所属类别与去重口径。例：某用户 7 天区间内第 1、2 天活跃——「活跃用户」计 1 人，「日均活跃」贡献 2 个人天
+（9）「0724 修订」悬浮 tooltip 去重规则表述统一：去重规则不再混在指标定义句中，tooltip 内独立成条「· 去重：xxxx」；逐指标去重口径见附表一 / 附表二新增的「去重规则」列</t>
         </is>
       </c>
     </row>
@@ -3258,23 +3261,25 @@
           <t>机构管理</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="C90" s="4" t="inlineStr">
         <is>
           <t>机构列表</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E90" s="6" t="inlineStr">
-        <is>
-          <t>（1）表格列改为“二级机构域名”，仅展示 test-aba，不展示根域名；机构名称后仅父机构显示“父机构”标签（子机构的从属由「上级机构」列体现、普通机构无从属，均不加标签）。KP/存储为当前占用，Token 为当前订阅周期消耗
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>0813周四更新
+（1）表格列改为“二级机构域名”，仅展示 test-aba，不展示根域名；机构名称后仅父机构显示“父机构”标签（子机构的从属由「上级机构」列体现、普通机构无从属，均不加标签）。KP/存储为当前占用，Token 为当前订阅周期消耗
 （2）按 机构名称/上级机构/ID 模糊搜索；筛选 机构状态（全部/正常/停用）、套餐（基础/专业/旗舰/定制）、上级机构
 （3）筛选行右侧新增「导出」：生成「AI问书_全域机构管理数据导出.xlsx」，沿用搜索与状态/套餐/上级机构筛选，列含机构ID/名称/二级机构域名/状态/上级机构/套餐/三项配额已用与上限；头部注明导出时间与筛选条件
 （4）配额套餐预设（6 档，弹窗内 3 列网格、不限版排在定制版后）：体验版 KP3/存储5GB/Token0.1亿（付费前试用）；基础版 10/20/0.5亿；专业版 50/100/2亿；旗舰版 200/500/10亿；定制版 三额度自定义填数字；不限版 三额度均不限（深度合作机构）
-（5）点「详情」进机构详情</t>
+（5）点「详情」进机构详情
+（6）「0813周四 删除」列表「微信配置」列不再展示（原显示已配置 / 未配置状态标签）——配置状态在机构详情 · 机构配置 · 微信配置内查看即可，列表层面收窄为机构身份、套餐与配额三类信息</t>
         </is>
       </c>
     </row>
@@ -3347,21 +3352,23 @@
           <t>机构管理</t>
         </is>
       </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr">
         <is>
           <t>机构列表</t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr">
+      <c r="D93" s="4" t="inlineStr">
         <is>
           <t>新建机构</t>
         </is>
       </c>
-      <c r="E93" s="6" t="inlineStr">
-        <is>
-          <t>（1）弹窗加宽；域名前缀与固定后缀同框同行展示，前缀可编辑、分隔线右侧“-aba.{当前环境根域名}”置灰只读；只允许小写字母、数字与中划线且全局唯一
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>0813周四更新
+（1）弹窗加宽；域名前缀与固定后缀同框同行展示，前缀可编辑、分隔线右侧“-aba.{当前环境根域名}”置灰只读；只允许小写字母、数字与中划线且全局唯一
 （2）上级机构下拉仅列出顶级机构（含“无（顶级机构）”）；不列出已有上级的子机构，保证只有父 / 子两层。选中某顶级机构后，本机构成为其子机构、该顶级机构成为父机构
-（3）套餐不在此设（在机构详情订阅配额设）</t>
+（3）套餐不在此设（在机构详情订阅配额设）
+（4）「0813周四 新增」创建表单在「机构名称」之后增加字段「机构主体全称」（营业执照名称，**必填**，未填时「创建」按钮禁用；可与其他机构重复——同一主体可运营多个机构）：与机构详情 · 基本资料为同一字段、同一规则，作为变量注入 C 端《用户协议》《隐私政策》《会员服务协议》《自动续费（扣费）协议》四份协议文本的机构主体名称；字段旁小问号说明用途，输入框右侧灰字「同步至协议文本」。放在创建环节而非只在详情补录，是为避免机构建完即有一份主体为空的协议文本挂在 C 端</t>
         </is>
       </c>
     </row>
@@ -3424,9 +3431,13 @@
 （1）KP数与存储“已用”始终取机构当前实际占用，不按订阅订单拆分；Token“已用”仅取当前订阅周期消耗，新订阅生效时清零重新累计
 （2）新订阅生效即整体替换三项基础上限，不结转旧订阅剩余额度；加油包只在所属当前订阅内累加，到期不结转
 （3）降配后若KP/存储当前占用超过新上限，保留既有内容但阻断新建、上传和快照导入，直至占用回落；实时共享计KP、不计存储、计消费机构Token（0812 修订，原「实时共享不计KP/存储」作废）
-（4）订阅列表筛选调整：商务负责人由下拉改为模糊搜索输入框，置于套餐筛选之前；其后依次为套餐、状态筛选
-（5）「0812-g 新增」额度「不限」的展示规则（不限版套餐三项均不限；定制版可只设某一项不限，故按行判定）：额度值显示「不限」而非数字，**不画百分比进度条**——无上限则「还剩多少 / 快满了吗」不成立，画一条恒 0% 的进度条会被误读为「几乎没用」或数据异常；进度条位置改为满宽的电光靛渐隐轨道、右端淡出不封口 + 一层慢速流光扫过（0813 视觉定版，表达「延伸出去、没有终点」，与有上限的实心条一眼可辨），右侧百分比位置显示「不限」（电光靛）。保留「当前占用 / 本周期消耗」的绝对值——这是不限额度下唯一有意义的信息（了解规模与成本）。配套规则：不限项不做超限阻断；加油包对不限项无意义；Token 不限时用量看板的阈值预警条隐藏（无上限即无 70/80/90/95% 阈值）。演示：机构后台主控台〔演示〕订阅状态「不限」态、平台后台演示机构「BB 数字出版」
-（6）「0812 新增」无生效套餐空态（与机构后台主控台同一组件同规则）：机构无订阅或套餐全部过期时，当前订阅卡区分「全部过期」（保留上一套餐名与到期日 + 影响说明）与「从未开通」两态，引导行为「可点击右上角「新建订阅」为机构开通或续费」；预置两家演示机构：「EE 美术出版」（订阅记录全部已过期，演示「全部过期」态）、「AA 少儿分社」（无任何订阅记录，演示「从未开通」态）</t>
+（4）「0813周四 定版」三项额度性质不同，超额处理不能同一套（这是本条规则的推导前提）：① KP 数——占用型，超额不产生额外硬成本（它只是商务分档标尺，超出的 KP 摊的仍是新套餐的 Token 与存储，只会用得更快、更早触发扩容），故只需冻结增量；② 存储——占用型，且超额是平台在持续掏钱（对象存储 + 向量索引），故除冻结增量外还要求降档留痕并让平台侧可见可催收；③ Token——消耗型，每期归零，不存在超额存量，沿用现有阈值预警。
+（5）「0813周四 定版」降档超额沿用「既存不适格」原则（取自城市规划的 legal nonconforming use：容积率调低后不拆既有楼）三条：① **既有存量永久有效**——已有 KP 与文件完整保留、正常服务，C 端读者问答与已购权益完全无感，**平台永不自动删除机构数据**；② **超额期间冻结增量**——KP 数超额冻结「新建 KP / 导入分享 KP」，存储超额冻结「上传知识文件」，保证超额量只减不增；③ **棘轮**——判定用「已用 &gt;= 上限」而非「&gt;」，即 12 个 KP 降到 5 个额度后，删到 6 个仍继续阻断，必须回落到 4 个才能再建到 5，**删一个不等于能建一个**。不设宽限期、不做自动下架、不收超额费。KP 额度基数＝该机构所有未删除的 KP（草稿 / 已发布 / 已下架都占，只有删除释放）
+（6）「0813周四 定版」机构侧超额呈现：当前订阅卡的占用型额度行在 已用 &gt; 上限 时进度条封顶转赤陶斜纹，数值仍显示真实的「12 / 5」**不截断到 100%**（截断是撒谎，管理员必须看到真实超出多少才知道要清理多少），右侧百分比位改显「超额 N 个 / N GB」（超过 100% 的百分比没有信息量，「还要清理多少」才是唯一要行动的数字）；KP 列表页头配额 chip 同步显示超额量，页内常驻超额告警条，写明三件事——既有内容不受影响（安抚）、当前冻结了什么（后果）、怎么解除（删除至额度内 / 联系平台扩容两条路，不再是「请联系平台扩容」这种死路）
+（7）「0813周四 新增」平台侧超额可见性：机构列表的「KP 用量」「存储空间」两列在已用 &gt; 上限时整格标红并挂「超额」标签（hover 说明影响与处理方式），Token 列不参与；机构详情订阅记录表的降档订阅挂「降档」标签（hover 看说明全文）、总额度列标红。演示机构「DD 考试中心」（上一期基础版 10 个 KP + 加油包 2 个用满 12 个，本期降到 5 个 KP / 5 GB，超 7 个 KP、5 GB）；机构后台主控台〔演示〕订阅状态新增第五态「降档超额」，与 KP 列表、KP 详情联动
+（8）订阅列表筛选调整：商务负责人由下拉改为模糊搜索输入框，置于套餐筛选之前；其后依次为套餐、状态筛选
+（9）「0812-g 新增」额度「不限」的展示规则（不限版套餐三项均不限；定制版可只设某一项不限，故按行判定）：额度值显示「不限」而非数字，**不画百分比进度条**——无上限则「还剩多少 / 快满了吗」不成立，画一条恒 0% 的进度条会被误读为「几乎没用」或数据异常；进度条位置改为满宽的电光靛渐隐轨道、右端淡出不封口 + 一层慢速流光扫过（0813 视觉定版，表达「延伸出去、没有终点」，与有上限的实心条一眼可辨），右侧百分比位置显示「不限」（电光靛）。保留「当前占用 / 本周期消耗」的绝对值——这是不限额度下唯一有意义的信息（了解规模与成本）。配套规则：不限项不做超限阻断；加油包对不限项无意义；Token 不限时用量看板的阈值预警条隐藏（无上限即无 70/80/90/95% 阈值）。演示：机构后台主控台〔演示〕订阅状态「不限」态、平台后台演示机构「BB 数字出版」
+（10）「0812 新增」无生效套餐空态（与机构后台主控台同一组件同规则）：机构无订阅或套餐全部过期时，当前订阅卡区分「全部过期」（保留上一套餐名与到期日 + 影响说明）与「从未开通」两态，引导行为「可点击右上角「新建订阅」为机构开通或续费」；预置两家演示机构：「EE 美术出版」（订阅记录全部已过期，演示「全部过期」态）、「AA 少儿分社」（无任何订阅记录，演示「从未开通」态）</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3469,10 @@
 （3）额度三项以三张横排指标卡呈现（图标 + 指标名 + 占用量/消耗量标签 + 步进器）：KP 数、存储为「占用量」型（随内容删除可释放）；Token 为「消耗量」型（只增不退、订阅周期结束清零重计）；每卡数值用「− 数字 +」步进器编辑，「不限」态禁用步进器显静态「不限」；改数值即自动匹配套餐（命中预设选中、否则转定制版）。加油包加量额度同款卡片布局。0716 #6：额度卡默认不高亮（普通描边），仅鼠标悬浮或聚焦到输入框时高亮（靛边框 + 淡靛底，与套餐卡选中态一致）；加油包新建表单底色由淡紫改为浅灰白（与下方历史列表区分）
 （4）「复制」带原订阅数据进表单，有效期取衔接默认避免重叠
 （5）校验：① 已有 1 期未生效订阅时拦截「最多只能预建一期续约」② 有效期不可与任一现有订阅重叠 ③ 起始&gt;今天自动置「未生效」（到生效日自动转生效）
-（6）说明「同一时间段只能有一个生效订阅 / 有生效订阅时最多再预建 1 期未生效 / 不可重叠 / 自动转生效」</t>
+（6）说明「同一时间段只能有一个生效订阅 / 有生效订阅时最多再预建 1 期未生效 / 不可重叠 / 自动转生效」
+（7）「0813周四 新增」降档实时预警：当所选套餐 / 所调额度的 KP 数或存储低于该机构当前实际占用时（Token 为消耗型、每期归零，**不触发**），额度卡下方实时展开赤陶预警块，分「现状 → 影响 → 建议下一步」三段。现状：该机构当前占用与新额度及分项超出量；**不受影响**：既有 KP / 文件 / 数据完整保留，C 端读者问答与已购权益完全无感，平台不会删除任何机构数据；**会受限**：按实际降档项动态列出（只降 KP 则只说无法新建 KP，降存储才加「无法上传知识库文件」），直到占用回落到新额度以内
+（8）「0813周四 新增」降档预警的「建议下一步」（只报告问题不给下一步等于没说，故给两条明确路径并各自讲清代价）：① **优先**——先与机构商定清理范围（删除不再运营的 KP 与知识库文件），待占用回落到新额度以内后再签本单，机构签约即可正常使用、也不产生超额成本；若机构确实需要这些容量，改为按实际占用调高本单额度、或先签本单再补加油包。② **或**——按此额度签约：降存储时写「超出的 N GB 存储将暂由平台承担，建议后续与机构沟通清理，或在下次续费时按实际占用调整额度」，仅降 KP 时（无平台硬成本）改写「机构在清理到额度内之前无法新建 KP，可能影响其正常上新」；两种情况均引导至下方「套餐降档说明」简要填写降档原因
+（9）「0813周四 新增」字段「套餐降档说明」——与通用「备注」是**两个独立字段、不混用**，仅在降档触发时出现且**必填**（未填时「确认创建」拦截并 toast「本次为套餐降档，请先填写「套餐降档说明」」，字段脚注转赤陶）。**只收降档原因**（placeholder「简要填写本次降档原因，如客户预算调整、业务收缩等」）——清理时限、责任归属属于线下商务约定，不塞进这个字段。设为必填的理由：降档会让机构超出额度、超出的存储由平台承担，这件事需要在单据上留下缘由可查。**它不阻碍创建订阅订单**——降档是正常商业行为（客户预算变了是常态），硬阻断只会卡住签约丢单、并逼商务去催客户删数据；平台只提醒、只留痕，绝不自动删除机构数据。该说明随订阅记录永久留存，在订阅详情弹窗中独立成行展示（不与备注混排）、列表挂「降档」标签 hover 可查</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3529,7 @@
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>（1）订阅详情弹窗：订阅 ID/套餐/额度/已用/有效期/商务负责人/状态/加油包数/创建时间/创建人/备注
+          <t>（1）订阅详情弹窗：订阅 ID/套餐/额度/已用/有效期/商务负责人/状态/加油包数/创建时间/创建人/备注；降档订阅追加「套餐降档说明」独立行（多行完整展示不截断）
 （2）删除规则（0714 与研发对齐，带护栏放开）：① 未生效订单——可直接删除，常规二次确认 ② 已生效订单——可删除，确认弹窗列明后果：连带删除其全部加油包、机构立即失去该订阅配额；若 KP/存储/Token 任一用量 &gt;0，追加红色强警告「该订阅已产生用量，删除将立即中断机构服务」 ③ 已过期订单——不可删除（商业单据审计留存，操作列不出删除入口）
 （3）删除≠退款：删除只移除订阅记录与配额，不产生退款单；如涉退费走线下商务流程</t>
         </is>
@@ -3600,7 +3614,7 @@
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>0812周三更新
+          <t>0813周四更新
 （1）微信公众号字段改为“网页授权回调地址”，微信开放平台字段改为“授权回调地址”；均填写完整 URL，并继续校验与微信后台配置一致
 （2）微信支付（必填，用于支付/退款/自动续费，未配置前台无法下单）：商户号 MchID、API v3 密钥（掩码）、商户证书（上传 apiclient_cert.pem）；限制说明（商户号须与公众号 AppID 关联绑定/需上传证书且 API v3 密钥在商户平台设置/退款·自动续费依赖支付能力）；保存 toast「已保存微信支付配置」
 （3）「0722 修订」微信公众号卡片新增「网页授权域名校验文件」上传（MP_verify_xxx.txt，公众号后台生成，需放置于网页授权域名根目录下）
@@ -3610,7 +3624,8 @@
 （7）「0807-2 修订」敏感项定稿「写后不回显」（推翻同批显隐眼睛方案）：九个敏感字段——公众号 AppSecret / 域名校验文件、开放平台 AppSecret、微信支付 API v2 密钥 / API v3 密钥 / 商户证书 / 商户 API 私钥 / 支付公钥 ID / 支付公钥文件——非空时仅显示「已配置 / 已上传」状态行，提供「更新」能力：点更新出空输入框（占位「输入新值 · 保存后不再回显」），点保存先弹二次确认（提醒整体覆盖原值、不可恢复、新值不再回显，请先核对输入无误），确认后回状态行、不回显新值；文件类「重新上传」同样先弹二次确认（提醒整体覆盖、原文件不可恢复、新文件同样不提供下载与回显）再选文件；显隐眼睛能力删除。密钥在数据库为加密存储（非明文），业务需要原值须联系技术发邮件申请（技术从微信后台获取或数据库解密提供），界面不提供明文查看与文件下载；卡片限制说明区同步注明。非敏感字段（AppID、回调地址、商户号、代扣模板 ID）保持可见可编辑
 （8）「0807 新增」③ 支付公钥文件（上传 pub_key.pem，紧随支付公钥 ID）——与公钥 ID 配套的公钥文件，商户平台下载，用于验证微信支付应答与回调签名（新商户公钥验签、存量商户平台证书验签，按商户号实际发放形态二选一） ④ 委托代扣包月模板 ID（文本，置于卡片末尾业务参数位）——委托代扣「签约模板」经微信审核通过后分配的模板 ID（plan_id），C 端用户签约连续包月扣费时传入；卡片限制说明区同步补充四项参数用途一句话说明
 （9）「0810 修订」敏感项状态行收敛为「状态 + 操作」两段（与技术确认后定稿）：九个敏感字段的「已配置 / 已上传」状态行不再展示 密钥尾号 ****后 4 位 / 文件名 与 更新时间，只保留状态字样与「更新 / 重新上传」操作（原 0807-2 的「尾号或文件名 + 更新时间精确到秒」展示取消）；二次确认弹窗文案同步去掉对尾号 / 文件名的引用，改为「整体覆盖当前值 / 当前文件」。更新覆写、写后不回显、二次确认、界面不提供明文查看与文件下载等规则均不变；未上传项的空态上传框保持原样
-（10）「0812 新增」微信公众号卡片新增两字段：① 微信公众号名称（文本，必填，置于公众号 AppID 之前）——公众号后台展示的账号名称 ② 备注（文本，选填，0812-e 定稿置于卡片末位「域名校验文件」之下——备注是整卡的补充说明，不插在接入参数序列中间）。两字段均为非敏感项，正常回显可编辑，不走「写后不回显」通道</t>
+（10）「0812 新增」微信公众号卡片新增两字段：① 微信公众号名称（文本，必填，置于公众号 AppID 之前）——公众号后台展示的账号名称 ② 备注（文本，选填，0812-e 定稿置于卡片末位「域名校验文件」之下——备注是整卡的补充说明，不插在接入参数序列中间）。两字段均为非敏感项，正常回显可编辑，不走「写后不回显」通道
+（11）「0813周四 删除」三个版块（微信公众号 / 微信开放平台 / 微信支付）标题行右侧的版块级「已配置」状态标签统一删除——各敏感字段自身已有「已配置 / 已上传」状态行，版块级标签既重复、又会在「版块内部分字段未配置」时与字段状态自相矛盾。版块标题、必填星号与用途说明灰字均保留；字段级状态行与更新 / 重新上传能力不变</t>
         </is>
       </c>
     </row>
@@ -4804,7 +4819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4908,7 +4923,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>含首尾日期；上一周期为紧邻的前一等长区间；趋势按日</t>
+          <t>按完整自然日统计，截至昨日 24:00、不含今日（今天 08-13 则近 7 天＝08-06—08-12）；上一周期为紧邻的前一等长完整日区间（07-30—08-05）；趋势按日</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -4918,24 +4933,24 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>统一环比边界</t>
+          <t>等长且等完整度——含未过完的今日会拿半天比整天，环比系统性偏负</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>通用差值规则</t>
+          <t>通用周期规则</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>计数 / 金额</t>
+          <t>自定义区间可选范围</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>(本期-上期)÷上期，显示相对百分比</t>
+          <t>结束日最晚昨日（今天及未来置灰）；起始日最早近 3 年（超出置灰）</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -4945,51 +4960,51 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>衡量相对变化</t>
+          <t>杜绝不完整日入统，同时限制无意义的超远期查询</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>通用差值规则</t>
+          <t>通用周期规则</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>率类 / 时长</t>
+          <t>日活 / 周活 / 月活</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>率类显示百分点差；时长显示绝对时长差</t>
+          <t>含今日的实时滚动窗口（DAU＝今日 00:00 至当前时刻；WAU/MAU＝截至今日的近 7 / 30 日滚动窗口），各自对比上一等长窗口，不随区间筛选联动</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>窗口内按用户 ID 去重</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>避免不同量纲混用</t>
+          <t>与区间档口径不同、数值不可直接对齐——一个问活跃规模的实时脉搏，一个问一段时间的经营结果</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>通用零基线</t>
+          <t>通用差值规则</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>上一周期为 0</t>
+          <t>计数 / 金额</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>不计算无穷增幅，显示“上期为0，暂无可比增幅”</t>
+          <t>(本期-上期)÷上期，显示相对百分比</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -4999,7 +5014,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>避免误导</t>
+          <t>衡量相对变化</t>
         </is>
       </c>
     </row>
@@ -5011,12 +5026,12 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>界面环比文案（0718 新增）</t>
+          <t>率类 / 时长</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>看板界面环比标签统一显示「↑x.x% 较上一周期」，不再出现「pp」字样；率类差值口径仍为百分点</t>
+          <t>率类显示百分点差；时长显示绝对时长差</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -5026,24 +5041,24 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>避免用户对 pp 单位困惑</t>
+          <t>避免不同量纲混用</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>通用精确性</t>
+          <t>通用零基线</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>去重与估算</t>
+          <t>上一周期为 0</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>按指标指定主键精确 DISTINCT；禁止使用 0.62/0.42 等经验系数估算</t>
+          <t>不计算无穷增幅，显示“上期为0，暂无可比增幅”</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -5053,24 +5068,24 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>可审计可复算</t>
+          <t>避免误导</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>通用去重规则（0722 新增）</t>
+          <t>通用差值规则</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>规模指标 / 强度指标</t>
+          <t>界面环比文案（0718 新增）</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>规模指标按用户去重：区间内按用户 ID 精确去重，同一用户跨天重复只计 1 人（活跃用户、新增 C 端、付费用户、提问用户等）；强度指标按人天：用户 × 自然日累加（日均活跃、人均提问等）；两后台涉去重指标 tooltip 全量标注所属类别</t>
+          <t>看板界面环比标签统一显示「↑x.x% 较上一周期」，不再出现「pp」字样；率类差值口径仍为百分点</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -5080,61 +5095,61 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>区分「多少人在用」与「用得有多勤」，口径可复算</t>
+          <t>避免用户对 pp 单位困惑</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>主控台·实时总览</t>
+          <t>通用精确性</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>累计 GMV（实时）</t>
+          <t>去重与估算</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>SUM(已支付订单金额)</t>
+          <t>按指标指定主键精确 DISTINCT；禁止使用 0.62/0.42 等经验系数估算</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>不涉及（金额汇总）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>总营收</t>
+          <t>可审计可复算</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>主控台·实时总览</t>
+          <t>通用去重规则（0722 新增）</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>累计退款 / 退款率（实时）</t>
+          <t>规模指标 / 强度指标</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>SUM(退款成功额)；退款率 = 退款额 ÷ GMV</t>
+          <t>规模指标按用户去重：区间内按用户 ID 精确去重，同一用户跨天重复只计 1 人（活跃用户、新增 C 端、付费用户、提问用户等）；强度指标按人天：用户 × 自然日累加（日均活跃、人均提问等）；两后台涉去重指标 tooltip 全量标注所属类别</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>不涉及（金额与比率）</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>售后与资金健康度</t>
+          <t>区分「多少人在用」与「用得有多勤」，口径可复算</t>
         </is>
       </c>
     </row>
@@ -5146,12 +5161,12 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>净 GMV（累计扣退款）</t>
+          <t>累计 GMV（实时）</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>累计 GMV − 累计退款</t>
+          <t>SUM(已支付订单金额)</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -5161,7 +5176,7 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>实际到账净收入</t>
+          <t>总营收</t>
         </is>
       </c>
     </row>
@@ -5173,22 +5188,22 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>当前会员数（实时）</t>
+          <t>累计退款 / 退款率（实时）</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>会员未到期的去重用户数</t>
+          <t>SUM(退款成功额)；退款率 = 退款额 ÷ GMV</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>按用户 ID 去重</t>
+          <t>不涉及（金额与比率）</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>商业化基本盘</t>
+          <t>售后与资金健康度</t>
         </is>
       </c>
     </row>
@@ -5200,76 +5215,76 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>累计注册用户（实时）</t>
+          <t>净 GMV（累计扣退款）</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>COUNT(DISTINCT user_id)</t>
+          <t>累计 GMV − 累计退款</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>按用户 ID 去重</t>
+          <t>不涉及（金额汇总）</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>用户规模</t>
+          <t>实际到账净收入</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>主控台·实时总览（平台）</t>
+          <t>主控台·实时总览</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>知识产品 KP 总数（实时）（0807 新增）</t>
+          <t>当前会员数（实时）</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>COUNT(全平台 KP)；卡片副行按状态拆分：已发布 / 草稿 / 已下架（数量＋占比）</t>
+          <t>会员未到期的去重用户数</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>不涉及（实体计数）</t>
+          <t>按用户 ID 去重</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>内容供给存量视角①：平台运营能力＝机构规模 × 内容供给 × 用户消费 × 商业化</t>
+          <t>商业化基本盘</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>主控台·实时总览（平台）</t>
+          <t>主控台·实时总览</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>知识库文件总数（实时）（0807 新增）</t>
+          <t>累计注册用户（实时）</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>COUNT(全平台知识库文件)；卡片副行按类型拆分：文档 / 图片 / 音频 / 视频 四类（数量＋占比）</t>
+          <t>COUNT(DISTINCT user_id)</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>不涉及（实体计数）</t>
+          <t>按用户 ID 去重</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>内容供给存量视角②：知识库建设规模与内容结构</t>
+          <t>用户规模</t>
         </is>
       </c>
     </row>
@@ -5281,157 +5296,157 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>知识库存储总量（实时）（0807 新增）</t>
+          <t>知识产品 KP 总数（实时）（0807 新增）</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>SUM(全平台知识库文件大小)，单位 TB；卡片副行：文档与媒体资源的容量＋占比（两者互补 100%）</t>
+          <t>COUNT(全平台 KP)；卡片副行按状态拆分：已发布 / 草稿 / 已下架（数量＋占比）</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>不涉及（容量汇总）</t>
+          <t>不涉及（实体计数）</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>内容供给存量视角③：存储资源占用与结构（关联机构存储配额）</t>
+          <t>内容供给存量视角①：平台运营能力＝机构规模 × 内容供给 × 用户消费 × 商业化</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>主控台·经营分析</t>
+          <t>主控台·实时总览（平台）</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>活跃用户 / 新增会员 / 区间 GMV / 区间提问数（区间）+ 趋势图</t>
+          <t>知识库文件总数（实时）（0807 新增）</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>区间聚合；活跃用户＝规模指标·区间内按用户 ID 去重（0722 修订）；新增会员＝区间内历史首次开通会员的用户数，续费、回流均不计入（0722 口径定稿）；区间 GMV 仅计「已支付」订单（待支付 / 已失效不计）</t>
+          <t>COUNT(全平台知识库文件)；卡片副行按类型拆分：文档 / 图片 / 音频 / 视频 四类（数量＋占比）</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>活跃用户、新增会员＝按用户 ID 去重（跨天只计 1 人）；区间 GMV、区间提问数＝不涉及</t>
+          <t>不涉及（实体计数）</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>经营动态</t>
+          <t>内容供给存量视角②：知识库建设规模与内容结构</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>主控台·经营分析（平台）</t>
+          <t>主控台·实时总览（平台）</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>续费率 / 回流会员（区间）（0722 平台新增）</t>
+          <t>知识库存储总量（实时）（0807 新增）</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>续费率＝区间内到期且完成续费的会员数 ÷ 同区间到期会员数；回流会员＝区间内开通会员、且开通时会员状态为已过期的用户数（不算新增、不算续费）；新增 / 续费 / 回流三者互斥，两后台统一</t>
+          <t>SUM(全平台知识库文件大小)，单位 TB；卡片副行：文档与媒体资源的容量＋占比（两者互补 100%）</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>续费率＝分子分母均按会员去重；回流会员＝按用户 ID 去重</t>
+          <t>不涉及（容量汇总）</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>会员经营三分：拉新 / 留存 / 召回</t>
+          <t>内容供给存量视角③：存储资源占用与结构（关联机构存储配额）</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>活跃概览（页级常驻，居用户留存上方，0724 移出用户分析 Tab）</t>
+          <t>主控台·经营分析</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>日活 / 周活 / 月活（实时滚动窗口快照）</t>
+          <t>活跃用户 / 新增会员 / 区间 GMV / 区间提问数（区间）+ 趋势图</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>（0724 修订，替换 0717「随区间联动」口径）固定滚动窗口实时快照、不随区间筛选联动：日活＝今日 00:00 至当前时刻的去重活跃用户（实时），环比对比昨日同时段；周活＝近 7 日滚动窗口去重活跃用户，环比上一个 7 日窗口；月活＝近 30 日滚动窗口去重活跃用户，环比上一个 30 日窗口</t>
+          <t>区间聚合；活跃用户＝规模指标·区间内按用户 ID 去重（0722 修订）；新增会员＝区间内历史首次开通会员的用户数，续费、回流均不计入（0722 口径定稿）；区间 GMV 仅计「已支付」订单（待支付 / 已失效不计）</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>日活＝今日 00:00 至当前时刻按用户 ID 去重；周活 / 月活＝近 7 / 30 日滚动窗口内按用户 ID 去重（窗口内跨天只计 1 人）</t>
+          <t>活跃用户、新增会员＝按用户 ID 去重（跨天只计 1 人）；区间 GMV、区间提问数＝不涉及</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>粘性分层</t>
+          <t>经营动态</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>用户分析</t>
+          <t>主控台·经营分析（平台）</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>新增用户趋势（区间）</t>
+          <t>续费率 / 回流会员（区间）（0722 平台新增）</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>区间内按日/按小时的首次注册数序列</t>
+          <t>续费率＝区间内到期且完成续费的会员数 ÷ 同区间到期会员数；回流会员＝区间内开通会员、且开通时会员状态为已过期的用户数（不算新增、不算续费）；新增 / 续费 / 回流三者互斥，两后台统一</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>按用户 ID 去重（注册仅计首次）</t>
+          <t>续费率＝分子分母均按会员去重；回流会员＝按用户 ID 去重</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>拉新节奏（新增用户卡右侧迷你折线）</t>
+          <t>会员经营三分：拉新 / 留存 / 召回</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>用户分析</t>
+          <t>活跃概览（页级常驻，居用户留存上方，0724 移出用户分析 Tab）</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>新增用户数（区间）</t>
+          <t>日活 / 周活 / 月活（实时滚动窗口快照）</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>区间内首次注册数</t>
+          <t>（0724 修订，替换 0717「随区间联动」口径）固定滚动窗口实时快照、不随区间筛选联动：日活＝今日 00:00 至当前时刻的去重活跃用户（实时），环比对比昨日同时段；周活＝近 7 日滚动窗口去重活跃用户，环比上一个 7 日窗口；月活＝近 30 日滚动窗口去重活跃用户，环比上一个 30 日窗口</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>按用户 ID 去重（注册仅计首次）</t>
+          <t>日活＝今日 00:00 至当前时刻按用户 ID 去重；周活 / 月活＝近 7 / 30 日滚动窗口内按用户 ID 去重（窗口内跨天只计 1 人）</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>拉新效果</t>
+          <t>粘性分层</t>
         </is>
       </c>
     </row>
@@ -5443,22 +5458,22 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>次日 / 7 日 / 30 日留存率（独立 cohort）</t>
+          <t>新增用户趋势（区间）</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>分母=cohort 日注册去重用户；分子=第 N 日有有效行为用户；只纳入已满 N 日的成熟 cohort，显示样本量与成熟截止日，未成熟节点显示「尚未到统计时间」并给出预计可统计日期（注册日 + N）；单注册日批次三节点共用同一样本分母；（0724 修订）注册批次筛选精简为「最新可统计 / 自定义日期」两档</t>
+          <t>区间内按日/按小时的首次注册数序列</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>分子分母均按用户 ID 去重</t>
+          <t>按用户 ID 去重（注册仅计首次）</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>产品价值是否站得住</t>
+          <t>拉新节奏（新增用户卡右侧迷你折线）</t>
         </is>
       </c>
     </row>
@@ -5470,22 +5485,22 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>来源分布（区间）</t>
+          <t>新增用户数（区间）</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>扫码进入 vs 直接访问；图例含人数与占比；占比环比按百分点差计算、界面统一显示为「↑x.x% 较上一周期」</t>
+          <t>区间内首次注册数</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>按用户 ID 去重（跨天只计 1 人）</t>
+          <t>按用户 ID 去重（注册仅计首次）</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>渠道效果</t>
+          <t>拉新效果</t>
         </is>
       </c>
     </row>
@@ -5497,76 +5512,76 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>地区分布 / 性别分布（区间）</t>
+          <t>次日 / 7 日 / 30 日留存率（独立 cohort）</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>按地区·性别分组占比</t>
+          <t>分母=cohort 日注册去重用户；分子=第 N 日有有效行为用户；只纳入已满 N 日的成熟 cohort，显示样本量与成熟截止日，未成熟节点显示「尚未到统计时间」并给出预计可统计日期（注册日 + N）；单注册日批次三节点共用同一样本分母；（0724 修订）注册批次筛选精简为「最新可统计 / 自定义日期」两档</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>按用户 ID 去重</t>
+          <t>分子分母均按用户 ID 去重</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>用户画像与精细化运营</t>
+          <t>产品价值是否站得住</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>提问分析</t>
+          <t>用户分析</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>总提问数（区间）</t>
+          <t>来源分布（区间）</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>COUNT(提问)</t>
+          <t>扫码进入 vs 直接访问；图例含人数与占比；占比环比按百分点差计算、界面统一显示为「↑x.x% 较上一周期」</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>不涉及（逐条计数）</t>
+          <t>按用户 ID 去重（跨天只计 1 人）</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>使用强度</t>
+          <t>渠道效果</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>提问分析</t>
+          <t>用户分析</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>人均提问数（区间）</t>
+          <t>地区分布 / 性别分布（区间）</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>总提问数 / 活跃用户</t>
+          <t>按地区·性别分组占比</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>按人天（用户×自然日）</t>
+          <t>按用户 ID 去重</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>单用户深度</t>
+          <t>用户画像与精细化运营</t>
         </is>
       </c>
     </row>
@@ -5578,22 +5593,22 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>平均会话轮次（区间）</t>
+          <t>总提问数（区间）</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>总提问数 / 总会话数</t>
+          <t>COUNT(提问)</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>不涉及（逐条计数）</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>对话沉浸度</t>
+          <t>使用强度</t>
         </is>
       </c>
     </row>
@@ -5605,22 +5620,22 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>答案点赞率 / 答案反馈率（区间）</t>
+          <t>人均提问数（区间）</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>点赞数 ÷ 答案数；反馈数 ÷ 答案数</t>
+          <t>总提问数 / 活跃用户</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>不涉及（按答案条数计）</t>
+          <t>按人天（用户×自然日）</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>答案质量摘要（明细在答案反馈菜单）</t>
+          <t>单用户深度</t>
         </is>
       </c>
     </row>
@@ -5632,22 +5647,22 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>提问量趋势（区间）</t>
+          <t>平均会话轮次（区间）</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>每日提问条数</t>
+          <t>总提问数 / 总会话数</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>不涉及（逐条计数）</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>提问走势</t>
+          <t>对话沉浸度</t>
         </is>
       </c>
     </row>
@@ -5659,22 +5674,22 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>按 Agent 提问分布（区间）</t>
+          <t>答案点赞率 / 答案反馈率（区间）</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>各 Agent 接收提问占比</t>
+          <t>点赞数 ÷ 答案数；反馈数 ÷ 答案数</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>不涉及（按答案条数计）</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Agent 配置 / 路由质量</t>
+          <t>答案质量摘要（明细在答案反馈菜单）</t>
         </is>
       </c>
     </row>
@@ -5686,22 +5701,22 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>提问领域分布（区间）</t>
+          <t>提问量趋势（区间）</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>按 KP / 领域聚合占比</t>
+          <t>每日提问条数</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>不涉及（逐条计数）</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>用户最关心的领域</t>
+          <t>提问走势</t>
         </is>
       </c>
     </row>
@@ -5713,12 +5728,12 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>提问关键词云（区间）</t>
+          <t>按 Agent 提问分布（区间）</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>高频关键词，hover 显示该词区间提问数</t>
+          <t>各 Agent 接收提问占比</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -5728,61 +5743,61 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>运营 / 商业化分析</t>
+          <t>Agent 配置 / 路由质量</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>营收分析·收入与转化</t>
+          <t>提问分析</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>区间 GMV（区间）</t>
+          <t>提问领域分布（区间）</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>SUM(区间已支付金额)</t>
+          <t>按 KP / 领域聚合占比</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>不涉及（金额汇总）</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>区间营收</t>
+          <t>用户最关心的领域</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>营收分析·收入与转化</t>
+          <t>提问分析</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>付费用户数 / 付费转化率（区间）</t>
+          <t>提问关键词云（区间）</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>区间付费用户 / 区间活跃用户</t>
+          <t>高频关键词，hover 显示该词区间提问数</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>分子分母均按用户 ID 去重</t>
+          <t>不涉及</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>商业化核心</t>
+          <t>运营 / 商业化分析</t>
         </is>
       </c>
     </row>
@@ -5794,22 +5809,22 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>ARPPU（区间）</t>
+          <t>区间 GMV（区间）</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>区间收入 / 区间付费用户数</t>
+          <t>SUM(区间已支付金额)</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>分母付费用户按用户 ID 去重</t>
+          <t>不涉及（金额汇总）</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>单付费用户产值</t>
+          <t>区间营收</t>
         </is>
       </c>
     </row>
@@ -5821,22 +5836,22 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>续费率（区间）</t>
+          <t>付费用户数 / 付费转化率（区间）</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>到期续费数 / 到期会员数</t>
+          <t>区间付费用户 / 区间活跃用户</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>按会员去重</t>
+          <t>分子分母均按用户 ID 去重</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>长期价值</t>
+          <t>商业化核心</t>
         </is>
       </c>
     </row>
@@ -5848,103 +5863,103 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>回流会员（区间）（0722 新增）</t>
+          <t>ARPPU（区间）</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>区间内开通会员、且开通时会员状态为已过期的用户数（按用户去重）；不算新增、不算续费，三者互斥；两后台口径一致</t>
+          <t>区间收入 / 区间付费用户数</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>按用户 ID 去重（跨天只计 1 人）</t>
+          <t>分母付费用户按用户 ID 去重</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>流失召回效果</t>
+          <t>单付费用户产值</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>营收分析·退款</t>
+          <t>营收分析·收入与转化</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>退款金额 / 退款率 / 退款订单数 / 净 GMV（区间）</t>
+          <t>续费率（区间）</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>见各指标</t>
+          <t>到期续费数 / 到期会员数</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>退款订单数＝按订单去重；退款金额、退款率、净 GMV＝不涉及</t>
+          <t>按会员去重</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>售后与净收入</t>
+          <t>长期价值</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>营收分析·转化漏斗</t>
+          <t>营收分析·收入与转化</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>受限内容触发率（区间）</t>
+          <t>回流会员（区间）（0722 新增）</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>触发付费墙次数 / 总提问数</t>
+          <t>区间内开通会员、且开通时会员状态为已过期的用户数（按用户去重）；不算新增、不算续费，三者互斥；两后台口径一致</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>不涉及（按次计数）</t>
+          <t>按用户 ID 去重（跨天只计 1 人）</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>付费墙强度（漏斗入口）</t>
+          <t>流失召回效果</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>营收分析·转化漏斗</t>
+          <t>营收分析·退款</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>会员漏斗（区间）</t>
+          <t>退款金额 / 退款率 / 退款订单数 / 净 GMV（区间）</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>看到会员页 → 点击购买 → 完成支付（%）</t>
+          <t>见各指标</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>各环节按用户 ID 去重</t>
+          <t>退款订单数＝按订单去重；退款金额、退款率、净 GMV＝不涉及</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>找漏斗瓶颈</t>
+          <t>售后与净收入</t>
         </is>
       </c>
     </row>
@@ -5956,76 +5971,76 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>永享转化（区间）</t>
+          <t>受限内容触发率（区间）</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>触发永享墙 → 完成购买（%）</t>
+          <t>触发付费墙次数 / 总提问数</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>各环节按用户 ID 去重</t>
+          <t>不涉及（按次计数）</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>永享定价是否合理</t>
+          <t>付费墙强度（漏斗入口）</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>热门 KP</t>
+          <t>营收分析·转化漏斗</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>被提问数 TOP 10 KP（区间）</t>
+          <t>会员漏斗（区间）</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>按 KP 维度统计提问</t>
+          <t>看到会员页 → 点击购买 → 完成支付（%）</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>不涉及（按 KP 维度计数）</t>
+          <t>各环节按用户 ID 去重</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>真正被使用的内容</t>
+          <t>找漏斗瓶颈</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>热门 KP</t>
+          <t>营收分析·转化漏斗</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>付费转化贡献 TOP 10 KP（区间）</t>
+          <t>永享转化（区间）</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>通过该 KP 触发的会员 / 永享订单数</t>
+          <t>触发永享墙 → 完成购买（%）</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>不涉及（按 KP 维度计数）</t>
+          <t>各环节按用户 ID 去重</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>营销价值高的内容</t>
+          <t>永享定价是否合理</t>
         </is>
       </c>
     </row>
@@ -6037,20 +6052,74 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
+          <t>被提问数 TOP 10 KP（区间）</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>按 KP 维度统计提问</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（按 KP 维度计数）</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>真正被使用的内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>热门 KP</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>付费转化贡献 TOP 10 KP（区间）</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>通过该 KP 触发的会员 / 永享订单数</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（按 KP 维度计数）</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>营销价值高的内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>热门 KP</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
           <t>永享购买 TOP 10 KP（区间）</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>按 KP 永享订单数</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t>不涉及（按 KP 维度计数）</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E48" s="6" t="inlineStr">
         <is>
           <t>永享潜力</t>
         </is>

--- a/docs/feature-list.xlsx
+++ b/docs/feature-list.xlsx
@@ -8,8 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="功能清单" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="数据看板指标" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="用量看板指标" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="指标口径" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4819,1439 +4818,3150 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:F98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="78" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>看板 / 段</t>
+          <t>端</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>指标（实时 / 区间）</t>
+          <t>模块</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>公式 / 取数</t>
+          <t>分区</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>去重规则（0724 新增列）</t>
+          <t>指标</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>业务意义</t>
+          <t>统计规则</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>去重规则</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>通用周期规则</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
+          <t>周期与差值规则</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>周期口径</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
           <t>累计 / 快照指标</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>截止当前时刻或区间末日快照；不展示上一周期比较</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>避免把存量规模误读为区间增长</t>
+          <t>1）定义：截至当前时刻的存量值。2）统计区间：不随时间筛选变化。3）环比：不展示上一周期比较。</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>通用周期规则</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
+          <t>周期与差值规则</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>周期口径</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
           <t>今日</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>本地时区今日 00:00 至当前时刻，对比昨日 00:00 至相同经过时长；趋势按小时</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>保证比较窗口等长</t>
+          <t>1）定义：本地时区今日 00:00 至当前时刻。2）环比对象：昨日 00:00 至相同已过时长。3）趋势粒度：按小时。4）说明：全站唯一含今日的实时口径。</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>通用周期规则</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
+          <t>周期与差值规则</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>周期口径</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
           <t>近 7 天 / 近 30 天 / 自定义</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>按完整自然日统计，截至昨日 24:00、不含今日（今天 08-13 则近 7 天＝08-06—08-12）；上一周期为紧邻的前一等长完整日区间（07-30—08-05）；趋势按日</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>等长且等完整度——含未过完的今日会拿半天比整天，环比系统性偏负</t>
+          <t>1）定义：按完整自然日统计，截至昨日 24:00，不含今日。2）示例：今天 08-14，则近 7 天＝08-07—08-13。3）环比对象：紧邻此前的等长完整日区间（07-31—08-06）。4）趋势粒度：按自然日。</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>通用周期规则</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
+          <t>周期与差值规则</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>周期口径</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
           <t>自定义区间可选范围</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>结束日最晚昨日（今天及未来置灰）；起始日最早近 3 年（超出置灰）</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>杜绝不完整日入统，同时限制无意义的超远期查询</t>
+          <t>1）结束日最晚昨日，今日及未来日期置灰不可选。2）起始日最早近 3 年，超出置灰。3）日历面板底部常驻口径脚注。</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>通用周期规则</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>日活 / 周活 / 月活</t>
+          <t>周期与差值规则</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>含今日的实时滚动窗口（DAU＝今日 00:00 至当前时刻；WAU/MAU＝截至今日的近 7 / 30 日滚动窗口），各自对比上一等长窗口，不随区间筛选联动</t>
+          <t>周期口径</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>窗口内按用户 ID 去重</t>
+          <t>日活 / 周活 / 月活的窗口口径（0814 修订）</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>与区间档口径不同、数值不可直接对齐——一个问活跃规模的实时脉搏，一个问一段时间的经营结果</t>
+          <t>1）日活＝今日 00:00 至当前时刻，实时统计，环比昨日同已过时长。2）周活 / 月活＝截至昨日 24:00 的 7 / 30 个完整自然日，不含今日，环比紧邻此前的等长完整日区间。3）三者均为页级常驻，不随区间筛选联动。4）周活与区间档「近 7 天活跃用户」口径完全一致、数值重合，属预期结果而非重复统计。</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>窗口内按用户 ID 去重，跨天重复只计 1 人</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>通用差值规则</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>计数 / 金额</t>
+          <t>周期与差值规则</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>(本期-上期)÷上期，显示相对百分比</t>
+          <t>差值与零基线</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>计数 / 金额类差值</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>衡量相对变化</t>
+          <t>1）计算式：（本期 − 上期）÷ 上期。2）展示：相对百分比。</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>通用差值规则</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>率类 / 时长</t>
+          <t>周期与差值规则</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>率类显示百分点差；时长显示绝对时长差</t>
+          <t>差值与零基线</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>率类 / 时长类差值</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>避免不同量纲混用</t>
+          <t>1）率类：绝对差，百分点语义，界面统一以「%」符号展示。2）时长类：绝对时长差。</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>通用零基线</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
+          <t>周期与差值规则</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>差值与零基线</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
           <t>上一周期为 0</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>不计算无穷增幅，显示“上期为0，暂无可比增幅”</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>避免误导</t>
+          <t>1）不计算无穷增幅。2）显示「上期为0，暂无可比增幅」。</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>通用差值规则</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>界面环比文案（0718 新增）</t>
+          <t>周期与差值规则</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>看板界面环比标签统一显示「↑x.x% 较上一周期」，不再出现「pp」字样；率类差值口径仍为百分点</t>
+          <t>差值与零基线</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>界面环比文案</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>避免用户对 pp 单位困惑</t>
+          <t>1）统一显示「↑x.x% 较上一周期」，其后灰字给出上一周期的具体起止日期。2）不出现「pp」字样，率类差值口径在各指标 tooltip 内注明。</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>通用精确性</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
+          <t>周期与差值规则</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>去重口径</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
           <t>去重与估算</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>按指标指定主键精确 DISTINCT；禁止使用 0.62/0.42 等经验系数估算</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>可审计可复算</t>
+          <t>1）按指标指定主键做精确 DISTINCT。2）禁止使用 0.62 / 0.42 等经验系数估算。</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>通用去重规则（0722 新增）</t>
+          <t>通用</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>规模指标 / 强度指标</t>
+          <t>周期与差值规则</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>规模指标按用户去重：区间内按用户 ID 精确去重，同一用户跨天重复只计 1 人（活跃用户、新增 C 端、付费用户、提问用户等）；强度指标按人天：用户 × 自然日累加（日均活跃、人均提问等）；两后台涉去重指标 tooltip 全量标注所属类别</t>
+          <t>去重口径</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>规模指标 / 强度指标两分类</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>区分「多少人在用」与「用得有多勤」，口径可复算</t>
+          <t>1）规模指标按用户去重：区间内按用户 ID 精确去重，同一用户跨天重复只计 1 人（活跃用户、新增 C 端、付费用户等）。2）强度指标按人天：用户 × 自然日累加（人均提问等）。3）两后台所有涉及去重的指标 tooltip 均标注所属类别。</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>主控台·实时总览</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>累计 GMV（实时）</t>
+          <t>主控台</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>SUM(已支付订单金额)</t>
+          <t>实时总览（不随时间筛选）</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
+          <t>累计 GMV</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：历史累计已支付订单的实付金额合计（会员 + 永享）。2）待支付、已失效订单不计入。3）兑换码订单金额计 0，不计入。4）统计区间：截至当前的实时快照，不展示环比。</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
           <t>不涉及（金额汇总）</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>总营收</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>主控台·实时总览</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>累计退款 / 退款率（实时）</t>
+          <t>主控台</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>SUM(退款成功额)；退款率 = 退款额 ÷ GMV</t>
+          <t>实时总览（不随时间筛选）</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
+          <t>累计退款 / 退款率</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>1）累计退款＝历史累计成功退款金额。2）退款率＝累计退款金额 ÷ 累计 GMV。3）实时快照，不展示环比。</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
           <t>不涉及（金额与比率）</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>售后与资金健康度</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>主控台·实时总览</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>净 GMV（累计扣退款）</t>
+          <t>主控台</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>累计 GMV − 累计退款</t>
+          <t>实时总览（不随时间筛选）</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
+          <t>净 GMV</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>1）计算式：累计 GMV − 累计退款金额。2）实时快照，不展示环比。</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
           <t>不涉及（金额汇总）</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>实际到账净收入</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>主控台·实时总览</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>当前会员数（实时）</t>
+          <t>主控台</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>会员未到期的去重用户数</t>
+          <t>实时总览（不随时间筛选）</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
+          <t>当前会员数</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：当前处于付费期或赠送 72 小时缓冲使用期的会员人数。2）缓冲期（会员四态中的「宽限期（待续费）」）内权益仍生效，故计入。3）实时快照，不展示环比。4）与平台后台机构详情 · 用量看板的「当前会员数」同口径，两端数值必须一致。</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
           <t>按用户 ID 去重</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>商业化基本盘</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>主控台·实时总览</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>累计注册用户（实时）</t>
+          <t>主控台</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>COUNT(DISTINCT user_id)</t>
+          <t>实时总览（不随时间筛选）</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
+          <t>累计注册用户</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：本机构 C 端注册用户数。2）实时快照，不展示环比。</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
           <t>按用户 ID 去重</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>用户规模</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>主控台·实时总览（平台）</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>知识产品 KP 总数（实时）（0807 新增）</t>
+          <t>主控台</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>COUNT(全平台 KP)；卡片副行按状态拆分：已发布 / 草稿 / 已下架（数量＋占比）</t>
+          <t>经营分析（随区间联动）</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>不涉及（实体计数）</t>
+          <t>活跃用户</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>内容供给存量视角①：平台运营能力＝机构规模 × 内容供给 × 用户消费 × 商业化</t>
+          <t>1）定义：所选区间内有登录或提问行为的用户数。2）统计区间：随今日 / 近 7 天 / 近 30 天 / 自定义联动。3）今日档为截至当前时刻。4）环比对象：紧邻此前的等长区间。</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>按用户 ID 去重，跨天重复只计 1 人</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>主控台·实时总览（平台）</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>知识库文件总数（实时）（0807 新增）</t>
+          <t>主控台</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>COUNT(全平台知识库文件)；卡片副行按类型拆分：文档 / 图片 / 音频 / 视频 四类（数量＋占比）</t>
+          <t>经营分析（随区间联动）</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>不涉及（实体计数）</t>
+          <t>新增会员</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>内容供给存量视角②：知识库建设规模与内容结构</t>
+          <t>1）定义：所选区间内历史首次开通会员的用户数。2）续费、回流均不计入。3）随区间联动并展示环比。</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>按用户 ID 去重</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>主控台·实时总览（平台）</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>知识库存储总量（实时）（0807 新增）</t>
+          <t>主控台</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>SUM(全平台知识库文件大小)，单位 TB；卡片副行：文档与媒体资源的容量＋占比（两者互补 100%）</t>
+          <t>经营分析（随区间联动）</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>不涉及（容量汇总）</t>
+          <t>区间 GMV</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>内容供给存量视角③：存储资源占用与结构（关联机构存储配额）</t>
+          <t>1）定义：所选区间内已支付订单的实付金额合计（会员 + 永享）。2）待支付、已失效订单不计入。3）随区间联动并展示环比。</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（金额汇总）</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>主控台·经营分析</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>活跃用户 / 新增会员 / 区间 GMV / 区间提问数（区间）+ 趋势图</t>
+          <t>主控台</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>区间聚合；活跃用户＝规模指标·区间内按用户 ID 去重（0722 修订）；新增会员＝区间内历史首次开通会员的用户数，续费、回流均不计入（0722 口径定稿）；区间 GMV 仅计「已支付」订单（待支付 / 已失效不计）</t>
+          <t>经营分析（随区间联动）</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>活跃用户、新增会员＝按用户 ID 去重（跨天只计 1 人）；区间 GMV、区间提问数＝不涉及</t>
+          <t>区间提问数</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>经营动态</t>
+          <t>1）定义：所选区间内 C 端新增提问条数，包含追问。2）随区间联动并展示环比。</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（逐条计数）</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>主控台·经营分析（平台）</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>续费率 / 回流会员（区间）（0722 平台新增）</t>
+          <t>数据看板</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>续费率＝区间内到期且完成续费的会员数 ÷ 同区间到期会员数；回流会员＝区间内开通会员、且开通时会员状态为已过期的用户数（不算新增、不算续费）；新增 / 续费 / 回流三者互斥，两后台统一</t>
+          <t>活跃概览（页级常驻）</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>续费率＝分子分母均按会员去重；回流会员＝按用户 ID 去重</t>
+          <t>日活（DAU）</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>会员经营三分：拉新 / 留存 / 召回</t>
+          <t>1）定义：今日 00:00 至当前时刻的活跃用户数，实时统计。2）环比对象：昨日同已过时长。3）不随下方时间筛选联动。4）本卡是三卡中唯一含今日的实时口径。</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>单日内按用户 ID 去重</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>活跃概览（页级常驻，居用户留存上方，0724 移出用户分析 Tab）</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>日活 / 周活 / 月活（实时滚动窗口快照）</t>
+          <t>数据看板</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>（0724 修订，替换 0717「随区间联动」口径）固定滚动窗口实时快照、不随区间筛选联动：日活＝今日 00:00 至当前时刻的去重活跃用户（实时），环比对比昨日同时段；周活＝近 7 日滚动窗口去重活跃用户，环比上一个 7 日窗口；月活＝近 30 日滚动窗口去重活跃用户，环比上一个 30 日窗口</t>
+          <t>活跃概览（页级常驻）</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>日活＝今日 00:00 至当前时刻按用户 ID 去重；周活 / 月活＝近 7 / 30 日滚动窗口内按用户 ID 去重（窗口内跨天只计 1 人）</t>
+          <t>周活（WAU）</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>粘性分层</t>
+          <t>1）定义：截至昨日 24:00 的 7 个完整自然日内的活跃用户数，不含今日。2）环比对象：紧邻此前的 7 个完整自然日。3）不随下方时间筛选联动。4）与区间档「近 7 天活跃用户」同口径、数值重合。</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>窗口内按用户 ID 去重，跨天重复只计 1 人</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>用户分析</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>新增用户趋势（区间）</t>
+          <t>数据看板</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>区间内按日/按小时的首次注册数序列</t>
+          <t>活跃概览（页级常驻）</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>按用户 ID 去重（注册仅计首次）</t>
+          <t>月活（MAU）</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>拉新节奏（新增用户卡右侧迷你折线）</t>
+          <t>1）定义：截至昨日 24:00 的 30 个完整自然日内的活跃用户数，不含今日。2）环比对象：紧邻此前的 30 个完整自然日。3）不随下方时间筛选联动。4）与区间档「近 30 天活跃用户」同口径、数值重合。</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>窗口内按用户 ID 去重，跨天重复只计 1 人</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>用户分析</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>新增用户数（区间）</t>
+          <t>数据看板</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>区间内首次注册数</t>
+          <t>用户留存（cohort，独立口径）</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>按用户 ID 去重（注册仅计首次）</t>
+          <t>次日 / 7 日 / 30 日留存率</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>拉新效果</t>
+          <t>1）定义：某注册批次的用户中，注册后第 N 天仍发生登录或提问的用户占比。2）计算式：第 N 日有有效行为用户数 ÷ 该批次注册用户总数。3）统计区间：按注册时间独立成队列，不随「区间分析」时间筛选变化。4）成熟度：只纳入已满 N 日的成熟节点，未成熟节点不显示 0%，改显示「尚未到统计时间」并给出预计可统计日期（注册日 + N）。5）卡底显示样本量与统计截止日。</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>分子分母均按用户 ID 去重（同批注册用户）</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>用户分析</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>次日 / 7 日 / 30 日留存率（独立 cohort）</t>
+          <t>数据看板</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>分母=cohort 日注册去重用户；分子=第 N 日有有效行为用户；只纳入已满 N 日的成熟 cohort，显示样本量与成熟截止日，未成熟节点显示「尚未到统计时间」并给出预计可统计日期（注册日 + N）；单注册日批次三节点共用同一样本分母；（0724 修订）注册批次筛选精简为「最新可统计 / 自定义日期」两档</t>
+          <t>用户留存（cohort，独立口径）</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>分子分母均按用户 ID 去重</t>
+          <t>注册批次筛选（两档）</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>产品价值是否站得住</t>
+          <t>1）档位：最新可统计 / 自定义日期，两档。2）自定义单注册日：次日 / 7 日 / 30 日三个节点共用同一样本人数，分母完全相同，节点间只差「是否已满观察期」。3）最新可统计：各节点成熟截止日不同（截止日＝今天 − N），对应不同注册日，三卡样本各不相同。</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>按用户 ID 去重</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>用户分析</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>来源分布（区间）</t>
+          <t>数据看板</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>扫码进入 vs 直接访问；图例含人数与占比；占比环比按百分点差计算、界面统一显示为「↑x.x% 较上一周期」</t>
+          <t>用户分析（随区间联动）</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>按用户 ID 去重（跨天只计 1 人）</t>
+          <t>新增用户数（含趋势）</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>渠道效果</t>
+          <t>1）定义：所选区间内首次注册的用户数。2）随区间联动并展示环比。3）趋势：卡片右侧迷你折线，为区间内按自然日（今日档按小时）的首次注册数序列，与大数字共用同一个口径问号。</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>按用户 ID 去重（注册仅计首次）</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>用户分析</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>地区分布 / 性别分布（区间）</t>
+          <t>数据看板</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>按地区·性别分组占比</t>
+          <t>用户分析（随区间联动）</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>按用户 ID 去重</t>
+          <t>来源分布</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>用户画像与精细化运营</t>
+          <t>1）定义：C 端用户进入渠道占比。2）分类：扫码进入＝链接带 KP 二维码参数；直接访问＝直链或无码进入。3）呈现：图例含人数与占比。4）占比环比按百分点差计算，界面统一显示为「↑x.x% 较上一周期」。</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>按用户 ID 去重，跨天重复只计 1 人</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>提问分析</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>总提问数（区间）</t>
+          <t>数据看板</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>COUNT(提问)</t>
+          <t>用户分析（随区间联动）</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>不涉及（逐条计数）</t>
+          <t>地区分布</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>使用强度</t>
+          <t>1）定义：C 端用户按地区（省 / 市）分组的占比。2）数据来源：微信授权带回，未授权归「未知」。</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>按用户 ID 去重</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>提问分析</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>人均提问数（区间）</t>
+          <t>数据看板</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>总提问数 / 活跃用户</t>
+          <t>用户分析（随区间联动）</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>按人天（用户×自然日）</t>
+          <t>性别分布</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>单用户深度</t>
+          <t>1）定义：C 端用户按性别分组的占比。2）数据来源：微信授权带回，未授权归「未知」。</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>按用户 ID 去重</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>提问分析</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>平均会话轮次（区间）</t>
+          <t>数据看板</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>总提问数 / 总会话数</t>
+          <t>提问分析（随区间联动）</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>总提问数</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>对话沉浸度</t>
+          <t>1）定义：所选区间内 C 端提问条数，含追问。2）随区间联动并展示环比。</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（按条累计，不去重）</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>提问分析</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>答案点赞率 / 答案反馈率（区间）</t>
+          <t>数据看板</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>点赞数 ÷ 答案数；反馈数 ÷ 答案数</t>
+          <t>提问分析（随区间联动）</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>不涉及（按答案条数计）</t>
+          <t>人均提问数</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>答案质量摘要（明细在答案反馈菜单）</t>
+          <t>1）计算式：所选区间总提问数 ÷ 同区间活跃用户数。2）随区间联动并展示环比。</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>分母活跃用户按用户 ID 去重（跨天只计 1 人）；本指标整体属强度指标（人天口径）</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>提问分析</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>提问量趋势（区间）</t>
+          <t>数据看板</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>每日提问条数</t>
+          <t>提问分析（随区间联动）</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>不涉及（逐条计数）</t>
+          <t>平均会话轮次</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>提问走势</t>
+          <t>1）计算式：所选区间总提问数 ÷ 同区间总会话数。2）随区间联动并展示环比。</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>不涉及</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>提问分析</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>按 Agent 提问分布（区间）</t>
+          <t>数据看板</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>各 Agent 接收提问占比</t>
+          <t>提问分析（随区间联动）</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>答案点赞率</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Agent 配置 / 路由质量</t>
+          <t>1）计算式：所选区间点赞答案数 ÷ 已完成答案数。2）明细见「答案反馈」菜单。3）随区间联动，差值为百分点。</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（按答案条数计）</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>提问分析</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>提问领域分布（区间）</t>
+          <t>数据看板</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>按 KP / 领域聚合占比</t>
+          <t>提问分析（随区间联动）</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>答案反馈率</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>用户最关心的领域</t>
+          <t>1）计算式：所选区间收到用户反馈（点踩 / 举报 / 建议）的答案数 ÷ 已完成答案数。2）明细见「答案反馈」工作台。3）随区间联动，差值为百分点。</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（按答案条数计）</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>提问分析</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>提问关键词云（区间）</t>
+          <t>数据看板</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>高频关键词，hover 显示该词区间提问数</t>
+          <t>提问分析（随区间联动）</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>不涉及</t>
+          <t>提问量趋势</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>运营 / 商业化分析</t>
+          <t>1）定义：区间内每日（今日档按小时）提问条数序列。</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（逐条计数）</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>营收分析·收入与转化</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>区间 GMV（区间）</t>
+          <t>数据看板</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>SUM(区间已支付金额)</t>
+          <t>提问分析（随区间联动）</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>不涉及（金额汇总）</t>
+          <t>按 Agent 提问分布</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>区间营收</t>
+          <t>1）计算式：各 Agent 承接提问数 ÷ 总提问数。2）随区间联动。</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>不涉及</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>营收分析·收入与转化</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>付费用户数 / 付费转化率（区间）</t>
+          <t>数据看板</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>区间付费用户 / 区间活跃用户</t>
+          <t>提问分析（随区间联动）</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>分子分母均按用户 ID 去重</t>
+          <t>提问领域分布</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>商业化核心</t>
+          <t>1）计算式：按 KP / 领域聚合的提问数 ÷ 总提问数。2）随区间联动。</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>不涉及</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>营收分析·收入与转化</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>ARPPU（区间）</t>
+          <t>数据看板</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>区间收入 / 区间付费用户数</t>
+          <t>提问分析（随区间联动）</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>分母付费用户按用户 ID 去重</t>
+          <t>提问关键词云</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>单付费用户产值</t>
+          <t>1）定义：区间内高频关键词，字号与色深随频次变化。2）交互：hover 显示该词的区间提问数。</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>不涉及</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
+          <t>机构后台</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>数据看板</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
           <t>营收分析·收入与转化</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>续费率（区间）</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>到期续费数 / 到期会员数</t>
-        </is>
-      </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>按会员去重</t>
+          <t>区间 GMV</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>长期价值</t>
+          <t>1）定义：所选区间内已支付订单的实付金额合计（会员 + 永享）。2）待支付、已失效订单不计入。3）随区间联动并展示环比。</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（金额汇总）</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
+          <t>机构后台</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>数据看板</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
           <t>营收分析·收入与转化</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>回流会员（区间）（0722 新增）</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>区间内开通会员、且开通时会员状态为已过期的用户数（按用户去重）；不算新增、不算续费，三者互斥；两后台口径一致</t>
-        </is>
-      </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>按用户 ID 去重（跨天只计 1 人）</t>
+          <t>付费用户数</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>流失召回效果</t>
+          <t>1）定义：所选区间内产生有效支付（已支付且金额 &gt; 0）的用户数。2）随区间联动并展示环比。</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>按用户 ID 去重，跨天重复只计 1 人</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>营收分析·退款</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>退款金额 / 退款率 / 退款订单数 / 净 GMV（区间）</t>
+          <t>数据看板</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>见各指标</t>
+          <t>营收分析·收入与转化</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>退款订单数＝按订单去重；退款金额、退款率、净 GMV＝不涉及</t>
+          <t>付费转化率</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>售后与净收入</t>
+          <t>1）计算式：区间付费用户数 ÷ 同区间活跃用户数。2）分母是区间活跃用户，不是累计注册用户。3）随区间联动，差值为百分点。</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>分子分母均按用户 ID 去重</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>营收分析·转化漏斗</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>受限内容触发率（区间）</t>
+          <t>数据看板</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>触发付费墙次数 / 总提问数</t>
+          <t>营收分析·收入与转化</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>不涉及（按次计数）</t>
+          <t>ARPPU（每付费用户均收入）</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>付费墙强度（漏斗入口）</t>
+          <t>1）计算式：区间支付收入 ÷ 同区间付费用户数。2）随区间联动并展示环比。</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>分母付费用户按用户 ID 去重</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>营收分析·转化漏斗</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>会员漏斗（区间）</t>
+          <t>数据看板</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>看到会员页 → 点击购买 → 完成支付（%）</t>
+          <t>营收分析·收入与转化</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>各环节按用户 ID 去重</t>
+          <t>续费率</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>找漏斗瓶颈</t>
+          <t>1）计算式：所选区间内到期且完成续费的会员数 ÷ 同区间到期会员数。2）随区间联动，差值为百分点。</t>
+        </is>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>分子分母均按会员（用户 ID）去重</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>营收分析·转化漏斗</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>永享转化（区间）</t>
+          <t>数据看板</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>触发永享墙 → 完成购买（%）</t>
+          <t>营收分析·收入与转化</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>各环节按用户 ID 去重</t>
+          <t>回流会员</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>永享定价是否合理</t>
+          <t>1）定义：所选区间内开通会员、且开通时会员状态为已过期的用户数。2）不计入新增会员，也不计入续费率。3）新增 / 续费 / 回流三者互斥，任一次开通行为只落入一类。4）随区间联动并展示环比。</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>按用户 ID 去重，跨天重复只计 1 人</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>热门 KP</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>被提问数 TOP 10 KP（区间）</t>
+          <t>数据看板</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>按 KP 维度统计提问</t>
+          <t>营收分析·退款</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>不涉及（按 KP 维度计数）</t>
+          <t>退款金额</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>真正被使用的内容</t>
+          <t>1）定义：所选区间内成功退款的金额合计，含部分退款。2）随区间联动并展示环比。</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（金额汇总）</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>热门 KP</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>付费转化贡献 TOP 10 KP（区间）</t>
+          <t>数据看板</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>通过该 KP 触发的会员 / 永享订单数</t>
+          <t>营收分析·退款</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>不涉及（按 KP 维度计数）</t>
+          <t>退款率</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>营销价值高的内容</t>
+          <t>1）计算式：所选区间退款金额 ÷ 同区间 GMV。2）随区间联动，差值为百分点。</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（比率）</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>热门 KP</t>
+          <t>机构后台</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>永享购买 TOP 10 KP（区间）</t>
+          <t>数据看板</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>按 KP 永享订单数</t>
+          <t>营收分析·退款</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
+          <t>退款订单数</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：所选区间内发生成功退款（含部分退款）的订单数。2）随区间联动并展示环比。</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>按订单去重</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>机构后台</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>数据看板</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>营收分析·退款</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>净 GMV（扣退款）</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>1）计算式：所选区间 GMV − 同区间成功退款金额。2）随区间联动并展示环比。</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（金额汇总）</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>机构后台</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>数据看板</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>营收分析·转化漏斗</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>受限内容触发率</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>1）计算式：区间内触发付费墙次数 ÷ 总提问数。2）定位：会员与永享转化的漏斗入口。3）随区间联动。</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（按次计数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>机构后台</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>数据看板</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>营收分析·转化漏斗</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>会员漏斗</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>1）三步：看到会员页 → 点击购买 → 完成支付。2）各步展示去重人数及转化率。3）随区间联动。</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>各环节按用户 ID 去重</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>机构后台</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>数据看板</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>营收分析·转化漏斗</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>永享转化</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>1）两步：触发永享付费墙 → 完成永享购买。2）计算式：完成购买数 ÷ 触发数。3）随区间联动。</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>各环节按用户 ID 去重</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>机构后台</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>数据看板</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>热门 KP（随区间联动）</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>被提问数 TOP 10 KP</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：按 KP 维度统计被命中的提问条数并排序取前 10。2）随区间联动。3）交互：点击行下钻进 KP 详情。</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
           <t>不涉及（按 KP 维度计数）</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>永享潜力</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>分区</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>维度</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>指标</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>去重规则（0724 新增列）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>实时存量（不随时间筛选变化）</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>用户与营收存量（0722 由「用户存量」更名）</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>累计 C 端用户数（按用户 ID 去重）、当前会员数（含 72 小时缓冲期）、累计 GMV（0722 新增：机构开通至今全部已支付订单总额，含已产生退款的部分，不随区间筛选变化）</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>累计 C 端＝按用户 ID 去重；当前会员＝按用户 ID 去重；累计 GMV＝不涉及（金额汇总）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>区间运营分析（随今日 / 近7天 / 近30天 / 自定义联动）</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>活跃与内容使用</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>活跃用户（登录或提问，区间内按用户 ID 去重）、新增 C 端用户数、区间提问数（含追问）</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>活跃用户、新增 C 端＝按用户 ID 去重（跨天只计 1 人）；区间提问数＝不涉及（逐条计数）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>区间运营分析（随今日 / 近7天 / 近30天 / 自定义联动）</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>商业化（0722 由「商业化与 LLM 消耗」拆出，横跨整行）</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>区间 GMV（区间内「已支付」订单金额，待支付 / 已失效不计）、净 GMV（0722 新增：区间 GMV − 区间退款金额）、付费用户数（区间内完成支付的去重用户）、付费转化率（0722 新增：付费用户 ÷ 区间活跃用户）、永享订单（0722 新增：区间内已支付永享订单数）、退款金额（0722 新增：区间内退款成功金额）、退款率（0722 新增：退款金额 ÷ 区间 GMV）</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>付费用户＝按用户 ID 去重（跨天只计 1 人）；付费转化率＝分子分母均按用户 ID 去重；永享订单＝按订单去重；区间 GMV、净 GMV、退款金额、退款率＝不涉及</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>区间运营分析（随今日 / 近7天 / 近30天 / 自定义联动）</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>LLM 消耗（0722 由「商业化与 LLM 消耗」拆出）</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Token 消耗量、模型调用次数、平均响应时长</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>不涉及（累加与均值指标）</t>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>机构后台</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>数据看板</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>热门 KP（随区间联动）</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>付费转化贡献 TOP 10 KP</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：按经由该 KP 触发并完成的会员 / 永享订单贡献排序取前 10。2）随区间联动。</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（按 KP 维度计数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>机构后台</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>数据看板</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>热门 KP（随区间联动）</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>永享购买 TOP 10 KP</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：按该 KP 下永享买断已支付订单数排序取前 10。2）随区间联动。</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（按 KP 维度计数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>主控台</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>实时总览（不随时间筛选）</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>入驻机构数</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：平台已创建且未删除的机构总数。2）机构筛选生效时显示所选机构数量，父机构含其子机构。3）实时快照，不展示环比。</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（实体计数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>主控台</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>实时总览（不随时间筛选）</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>累计用户</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：全平台各机构 C 端注册用户数合计。2）实时快照，不展示环比。</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>按用户 ID 去重</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>主控台</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>实时总览（不随时间筛选）</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>累计 GMV</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：全平台各机构已支付订单金额合计。2）资金 100% 进入各机构账户，平台不参与分账。3）实时快照，不展示环比。</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（金额汇总）</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>主控台</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>实时总览（不随时间筛选）</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>净 GMV（0814 补入文档）</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>1）计算式：全平台累计 GMV − 累计成功退款金额，即各机构净收入合计。2）平台不参与分账。3）实时快照，不展示环比。</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（金额汇总）</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>主控台</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>实时总览（不随时间筛选）</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>提问总量</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：全平台 C 端历史累计提问条数合计。2）实时快照，不展示环比。</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（逐条计数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>主控台</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>实时总览（不随时间筛选）</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>知识产品 KP 总数</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：全平台各机构创建且未删除的知识产品总数，含草稿与已下架。2）卡片副行按状态拆分：已发布 / 草稿 / 已下架，各显示数量与占比。3）实时快照。</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（实体计数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>主控台</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>实时总览（不随时间筛选）</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>知识库文件总数</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：全平台各机构 KP 知识库内的文件总数，不含已删除。2）卡片副行按类型拆分：文档 / 图片 / 音频 / 视频，各显示数量与占比。3）实时快照。</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（实体计数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>主控台</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>实时总览（不随时间筛选）</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>知识库存储总量</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：全平台知识库文件占用的存储空间合计，单位 TB。2）只计原始文件，不含向量索引。3）卡片副行：文档与媒体资源的容量及占比，两者互补 100%。4）实时快照。</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（容量汇总）</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>主控台</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>经营分析（随区间联动）</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>活跃用户</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：所选区间内全平台有登录或提问行为的用户数。2）今日档为截至当前时刻。3）随区间联动并展示环比。4）口径与机构后台一致，仅统计范围为全平台汇总。</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>按用户 ID 去重，跨天重复只计 1 人</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>主控台</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>经营分析（随区间联动）</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>新增会员</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：所选区间内全平台历史首次开通会员的用户数。2）续费、回流均不计入。3）随区间联动并展示环比。</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>按用户 ID 去重</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>主控台</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>经营分析（随区间联动）</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>续费率</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>1）计算式：所选区间内到期且完成续费的会员数 ÷ 同区间到期会员数。2）与机构后台同口径。3）随区间联动，差值为百分点。</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>分子分母均按会员（用户 ID）去重</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>主控台</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>经营分析（随区间联动）</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>回流会员</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：所选区间内开通会员、且开通时会员状态为已过期的用户数。2）不计入新增会员与续费率，三者互斥。3）与机构后台同口径。4）随区间联动并展示环比。</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>按用户 ID 去重</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>主控台</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>经营分析（随区间联动）</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>区间 GMV</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：所选区间内全平台已支付订单金额合计。2）待支付、已失效订单不计入。3）随区间联动并展示环比。</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（金额汇总）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>主控台</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>经营分析（随区间联动）</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>区间提问数</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：所选区间内全平台 C 端新增提问条数，包含追问。2）随区间联动并展示环比。</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（逐条计数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>模型用量（平台默认 LLM）</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>实时快照</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>累计 tokens</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：平台默认 LLM 自开通至今消耗的输入与输出 token 总数。2）实时快照，不展示环比。3）单位以「亿」为基准，与机构配额 Token 口径一致。</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（累加）</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>模型用量（平台默认 LLM）</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>实时快照</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>累计调用次数</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：平台默认 LLM 自开通至今被请求的总次数。2）实时快照，不展示环比。</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（累加）</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>模型用量（平台默认 LLM）</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>区间统计（随区间与机构筛选联动）</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>区间 tokens</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：平台默认 LLM 在所选机构与区间内消耗的输入与输出 token 总数。2）随机构筛选与时间区间联动并展示环比。</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（累加）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>模型用量（平台默认 LLM）</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>区间统计（随区间与机构筛选联动）</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>区间调用次数</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：平台默认 LLM 在所选机构与区间内被请求的次数。2）随机构筛选与时间区间联动并展示环比。</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（累加）</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>模型用量（平台默认 LLM）</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>区间统计（随区间与机构筛选联动）</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>平均响应</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：所选机构与区间内，单次模型调用从请求到首字返回的平均耗时。2）随筛选联动，差值显示绝对时长差。</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（均值指标）</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>机构详情 · 用量看板</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>实时存量与配额（不随时间筛选）</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>累计 C 端用户数</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：该机构开通至今的注册用户总数。2）实时快照，不参与环比。</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>按用户 ID 去重</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>机构详情 · 用量看板</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>实时存量与配额（不随时间筛选）</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>当前会员数</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：当前处于付费期或赠送 72 小时缓冲使用期的会员人数。2）缓冲期内权益仍生效，故计入。3）实时快照，不参与环比。4）与机构后台主控台的「当前会员数」同口径，两端数值必须一致。</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>按用户 ID 去重</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>机构详情 · 用量看板</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>实时存量与配额（不随时间筛选）</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>累计 GMV</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：该机构开通至今已支付订单总金额，含已产生退款的部分。2）属累计存量，故置于实时板块而非区间板块，避免「选了近 7 天却显示累计值」的口径混乱。3）不随时间筛选变化。</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（金额汇总）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>机构详情 · 用量看板</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>实时存量与配额（不随时间筛选）</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>KP 数占用量</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>1）展示：占用量（当前占用 / 上限）。2）上限＝当前生效订阅基础额度 + 该订阅有效加油包；当前占用按机构真实内容实时统计并跨订阅延续，删除可释放。3）进度条着色：＜70% 青 / 70%~90% 橙 / ≥90% 珊瑚红。4）已用 ≥ 上限时冻结新建与导入 KP，既有存量永久有效、C 端读者完全无感；回落到上限以内即自动恢复。</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（实体计数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>机构详情 · 用量看板</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>实时存量与配额（不随时间筛选）</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>存储空间占用量</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>1）展示：占用量（当前占用 / 上限）。2）上限口径同 KP 数。3）进度条着色规则同上。4）已用 ≥ 上限时冻结知识文件上传，既有文件永久保留、C 端读者完全无感；回落到上限以内即自动恢复。</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（容量汇总）</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>机构详情 · 用量看板</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>实时存量与配额（不随时间筛选）</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>Token 消耗量</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>1）展示：消耗量（本订阅周期消耗 / 额度），措辞不得与「占用量」混用；本周期消耗绑定当前订阅周期且不可回收，新订阅生效时归零、旧额度不结转。2）性质：消耗型，每计费周期归零重置，不存在超额存量。3）进度条着色规则同占用型。4）阈值预警：本周期消耗率达 70% / 80% / 90% / 95% 各向机构联系人发一次短信，同周期同阈值不重复。5）看板顶部预警条仅当 ≥ 70% 时出现并常驻；达上限后 C 端问答被拦截，需扩容或等下一周期归零。</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（累加）</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>机构详情 · 用量看板</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>区间 · 商业化</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>区间 GMV</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：所选区间内已支付的会员与永享订单金额。2）待支付、已失效订单不计入。3）随区间联动。4）环比对象：紧邻此前的等长区间，卡内显示「↑x.x% 较上一周期」与对比区间日期。</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（金额汇总）</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>机构详情 · 用量看板</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>区间 · 商业化</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>净 GMV（扣退款）</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>1）计算式：所选区间 GMV − 同区间成功退款金额。2）随区间联动。3）环比对象：紧邻此前的等长区间。</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（金额汇总）</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>机构详情 · 用量看板</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>区间 · 商业化</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>付费用户</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：所选区间内产生有效支付的用户数。2）随区间联动。3）环比对象：紧邻此前的等长区间。</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>按用户 ID 去重，跨天重复只计 1 人</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>机构详情 · 用量看板</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>区间 · 商业化</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>付费转化率</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>1）计算式：所选区间付费用户 ÷ 同区间活跃用户。2）随区间联动。3）环比对象：紧邻此前的等长区间，差值为百分点、界面统一以「%」展示。</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>分子分母均按用户 ID 去重</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>机构详情 · 用量看板</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>区间 · 商业化</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>永享订单</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：所选区间内已支付的单本永享订单数。2）随区间联动。3）环比对象：紧邻此前的等长区间。</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>按订单去重</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>机构详情 · 用量看板</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>区间 · 商业化</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>退款金额</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：所选区间内退款成功的金额，含部分退款。2）随区间联动。3）环比对象：紧邻此前的等长区间；退款为负面指标，下降时环比显示为负值（配色只反映方向、不反映好坏）。</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（金额汇总）</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>机构详情 · 用量看板</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>区间 · 商业化</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>退款率</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>1）计算式：所选区间退款成功金额 ÷ 同区间区间 GMV。2）随区间联动。3）环比对象：紧邻此前的等长区间，差值为百分点；负面指标同退款金额。</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（比率）</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>机构详情 · 用量看板</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>区间 · 活跃与内容使用</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>活跃用户</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：所选区间内登录或提问的用户数。2）随区间联动。3）环比对象：紧邻此前的等长区间。4）区别于机构后台数据看板页首的页级常驻三卡。</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>按用户 ID 去重，跨天重复只计 1 人</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>机构详情 · 用量看板</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>区间 · 活跃与内容使用</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>新增 C 端</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：所选区间内首次注册的用户数。2）随区间联动。3）环比对象：紧邻此前的等长区间。</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>按用户 ID 去重（注册仅计首次）</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>机构详情 · 用量看板</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>区间 · 活跃与内容使用</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>区间提问</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：所选区间内新增提问条数，包含追问。2）随区间联动。3）环比对象：紧邻此前的等长区间。</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（逐条计数）</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>机构详情 · 用量看板</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>区间 · LLM 消耗</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>Token 消耗量</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：所选区间内平台默认 LLM 的输入与输出 token 消耗。2）属不可回收消耗量。3）随区间联动。4）环比对象：紧邻此前的等长区间。</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（累加）</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>机构详情 · 用量看板</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>区间 · LLM 消耗</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>调用次数</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：所选区间内模型请求次数。2）随区间联动。3）环比对象：紧邻此前的等长区间。</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（累加）</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>机构详情 · 用量看板</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>区间 · LLM 消耗</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>平均响应</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：所选区间内从请求到首字返回的平均耗时。2）随区间联动。3）环比对象：紧邻此前的等长区间；时长类差值显示绝对时长差（如「缩短 0.2 秒」），不显示百分比。</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>不涉及（均值指标）</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>订阅订单</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>实时汇总（不随时间筛选）</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>订阅总数</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：平台全部机构的「订阅」订单总数。2）不含加油包，加油包单列统计。3）统计区间：开通至今，实时快照。</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>按订阅订单去重</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>订阅订单</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>实时汇总（不随时间筛选）</t>
+        </is>
+      </c>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>生效</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：当前处于「生效」状态（生效日 ≤ 今天 ≤ 到期日）的订阅数。2）同一机构同时仅一笔生效订阅。3）该订阅与生效加油包共同决定机构当前可用额度。</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>按订阅订单去重</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>订阅订单</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>实时汇总（不随时间筛选）</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>未生效</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：已创建但今天 &lt; 生效日的订阅数，如提前预建的下一期续约。2）到生效日自动转生效。3）暂不计入当前可用额度。4）三种状态（未生效 / 生效 / 已过期）均由有效期自动判定，非人工置位。</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>按订阅订单去重</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>订阅订单</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>实时汇总（不随时间筛选）</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>加油包</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：全部机构的加油包总数。2）性质：期中加量，即时生效，额度累加到机构当前可用额度，不改变套餐。</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>按加油包订单去重</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>平台后台</t>
+        </is>
+      </c>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>订阅订单</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>实时汇总（不随时间筛选）</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>90 天内到期</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>1）定义：生效中且距到期日不足 90 天的订阅数。2）计算式：到期日 − 今天 ∈ (0, 90] 天。</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>按订阅订单去重</t>
         </is>
       </c>
     </row>

--- a/docs/feature-list.xlsx
+++ b/docs/feature-list.xlsx
@@ -1197,14 +1197,17 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>0812周三更新
+          <t>0814周五更新
 （1）0717 二批 #9：两档改为「购买方式即续费语义」，消除「按月自动续费」歧义——① 连续包月（默认选中，角标「首月特惠」）：首月 ¥9.9、次月起 ¥19.9/月 自动续费，卡内说明「自动续费，可随时退订」② 单月（¥19.9 / 1 个月）：一次性购买，卡内说明「到期自动失效，不自动续费不扣款」；选中即表达是否自动续费，不再靠一个含糊的全局勾选
 （2）协议、按钮与底部说明随所选方式联动：连续包月→勾选《自动续费协议》+ 按钮「¥9.9 开通连续包月」+ 底部说明「次月起 ¥19.9/月 自动扣费 · 支持随时退订，到期赠 72 小时会员缓冲使用期」；单月→协议行换成《会员服务协议》（无自动续费协议）+ 按钮「¥19.9 购买单月会员」+ 底部说明「到期自动失效，不会自动扣费」；缓冲期不计入已付费会员时长
 （3）「立即开通」前校验手机号绑定（未绑先引导绑定再继续），通过后按所选方式进微信支付收银台
 （4）「0718 修订」开通会员页按「先权益、再套餐、后协议」重构交互：① 标题下新增三枚权益速览 chip（受限内容全解锁 / 图音视频精讲 / 电话问答·VIP 优先）；② 套餐卡信息层级重排——卡名 + 续费语义 pill（连续包月＝「自动续费 · 可随时取消」琥珀标；单月＝「一次性购买 · 不自动续费」灰标）+ 一行说明 + 右侧大价签；选中态改左侧对勾圆点（琥珀填充）+ 琥珀描边淡底，「首月特惠」角标改琥珀渐变；③ 协议勾选改为真实可点交互（未勾选点按钮 toast 引导先同意协议），连续包月需同意《会员服务协议》《自动续费协议》两份，单月仅《会员服务协议》；④ 按钮与底部说明随所选方式联动（语义与 0717 二批 #9 不变：连续包月＝首月 ¥9.9、次月起 ¥19.9/月 自动续费可退订；单月＝¥19.9 一次性、到期自动失效）
 （5）「0718 修订」删除开通按钮下方的补充说明文案（原「次月起 ¥19.9/月 自动扣费 · 支持随时退订，到期赠 72 小时会员缓冲使用期」/「一次性购买 · 到期自动失效，不会自动扣费」），续费规则由套餐卡内的续费语义 pill 与说明承载，不再页底重复
 （6）「0719 修订」协议勾选框改为**默认未勾选**，须用户主动勾选后方可开通（原默认已勾选）——连续包月场景含《自动续费协议》，默认代勾在国内合规口径下通常不被接受；同时与登录落地页「协议默认未勾选」的口径保持一致。未勾选时开通按钮呈置灰视觉，点击 toast「请先阅读并同意相关协议」并阻断，不进收银台
-（7）「0812 新增」会员月度周期按「对日周期」计算：自开通当日起顺延至次月同日；若次月无对应日期，则顺延至当月最后一日，后续续费持续按该日期执行。示例：1 月 31 日开通，2 月无 31 日，当期有效期至 2 月 28 日，后续每月 28 日自动续费。扣费日＝到期日前 1 天（商户预约扣费节奏，详见 PRD 4.4.5）</t>
+（7）「0812 新增」会员月度周期按「对日周期」计算：自开通当日起顺延至次月同日；若次月无对应日期，则顺延至当月最后一日，后续续费持续按该日期执行。示例：1 月 31 日开通，2 月无 31 日，当期有效期至 2 月 28 日，后续每月 28 日自动续费。扣费日＝到期日前 1 天（商户预约扣费节奏，详见 PRD 4.4.5）
+（8）「0814-2 新增」套餐卡与协议之间新增「缓冲期安心提示」常驻一行：「会员到期附赠 72 小时 缓冲期，权益持续可用，缓冲期不计会员时长。」——原 72 小时缓冲期只在《会员服务协议》正文与到期后的界面里出现，用户在付费决策时看不到；该承诺是降低「怕买了到期就断」焦虑的兜底项，须在付费前完成告知。视觉上刻意不并入顶部权益速览 chip：缓冲期是兜底承诺不是卖点，用中性灰底细条 + 玉绿盾形图标，不与琥珀套餐卡抢注意力
+（9）「0814-2 修订」连续包月卡内说明中的「次月起 ¥19.9/月」加粗加深（原与整行同字重）：首月 ¥9.9 是拉新钩子，次月价才是用户长期实际支付的金额，不应被淹没在一行小字里——付费前把真实长期成本讲清楚，减少后续因「不知道会涨价」产生的退订与投诉
+（10）「0814-2 修订」单月会员卡说明由「¥19.9 / 1 个月，到期自动失效不扣款，适合先体验一个月」改为「¥19.9 / 1 个月，到期不扣款、不自动续期，适合先体验一个月」——原「到期自动失效」与「到期赠 72 小时缓冲」直接矛盾。口径定版：缓冲期的目的是防止服务突然中断伤害体验，与是否开通自动续费无关，连续包月与单月两档一视同仁均赠 72 小时缓冲；「不扣款」表达的是计费语义，与权益是否立即终止解耦</t>
         </is>
       </c>
     </row>
@@ -1231,11 +1234,17 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>0812周三更新
+          <t>0814周五更新
 （1）会员卡：会员标识 + 有效期 + 续费状态（自动续费 / 到期不再续费）
 （2）「免费 vs 会员」权益对比表（逐项 ✅/✗）：基础文字知识问答、图音视频深度知识精讲、VIP 极速优先通道、实时电话即时问答、永享名家典藏知识（永享标注为「单独购买」）
 （3）底部说明「自动续费将于扣费前 5 天短信提醒，可随时取消」
-（4）「0812 修订」自动续费提醒时点定版为「扣费前 5 天」（原「到期前 3 天」作废；扣费日＝到期日前 1 天）。续费提醒短信模版（签名固定【科技文献出版社】，非动态机构名）——标准版：「【科技文献出版社】您订购的AI问书会员将于${到期日}到期，${扣费日}我们将通过微信自动续费${金额}元。如需退订，请前往微信"我的-服务-钱包-支付设置-自动续费/免密支付"管理。」降价版（会员价下调时合并降价告知，一条短信一并通知）：「【科技文献出版社】您订购的AI问书会员将于${到期日}到期。会员价已由${原价}元调整为${新价}元，${扣费日}我们将通过微信按新价格${新价}元自动续费。如需退订，请前往微信"我的-服务-钱包-支付设置-自动续费/免密支付"管理。」</t>
+（4）「0812 修订」自动续费提醒时点定版为「扣费前 5 天」（原「到期前 3 天」作废；扣费日＝到期日前 1 天）。续费提醒短信模版（签名固定【科技文献出版社】，非动态机构名）——标准版：「【科技文献出版社】您订购的AI问书会员将于${到期日}到期，${扣费日}我们将通过微信自动续费${金额}元。如需退订，请前往微信"我的-服务-钱包-支付设置-自动续费/免密支付"管理。」降价版（会员价下调时合并降价告知，一条短信一并通知）：「【科技文献出版社】您订购的AI问书会员将于${到期日}到期。会员价已由${原价}元调整为${新价}元，${扣费日}我们将通过微信按新价格${新价}元自动续费。如需退订，请前往微信"我的-服务-钱包-支付设置-自动续费/免密支付"管理。」
+（5）「0814-2 新增」会员中心改为按会员四态渲染（原页面只有「有效会员」一种形态，且有效期硬编码，宽限期 / 已过期 / 未开通用户进入均看到一张有效会员卡——属错误展示，本次一并修正）。四态卡面：① 有效会员＝靛紫卡，「有效期至 {日期}」+ 续费状态「按月自动续费 / 到期不再续费」+ 按钮「取消自动续费 / 自动续费」；② 宽限期＝琥珀卡（详见下条）；③ 会员已过期＝灰卡 + 角标「已失效」+「会员已到期 {日期}」+「权益已暂停」+ 按钮「重新开通会员」（无底部说明）；④ 未开通＝灰卡 + 角标「未开通」+「尚未开通 / —」+「开通后即刻生效」+ 按钮「开通会员」+ 底部说明「开通后受限内容即刻解锁；到期额外赠送 72 小时缓冲使用期」。「免费 vs 会员」权益对比表四态均保留（对已流失用户即价值召回）
+（6）「0814-2 新增」宽限期（到期后 72 小时缓冲使用期）C 端展示定版。信息优先级按「用户此刻真正关心什么」排序：① 我还能用吗 → ② 还剩多久 → ③ 我该做什么。卡面：保持会员卡形态不降级为空态（缓冲期内权益仍生效，降级成空态等于告诉用户他不是会员），仅换琥珀色调；「会员」字样右侧加角标「已到期」；主信息位 lab 改「权益还可使用」、大字改倒计时「剩 {N} 小时」（琥珀强调色），到期日退为次要信息「已于 {日期} 到期」；卡内不放任何机制说明（详见下条）；主按钮唯一动作「立即续费 · 恢复会员」→ 开通会员页；无底部说明
+（7）「0814-3 修复」会员卡显式左对齐（原继承页面 text-align:center）。原先看不出问题，是因为卡内每个盒子的宽度恰好等于自身文字宽度，居中没有可见效果；本批给宽限期加了「已到期」角标、并把倒计时字号调大后，mc-brand / mc-valid 被撑宽，同列较窄的「AI 问书」「权益还可使用」开始居中偏移，表现为左边空一块、且只在部分会员状态下出现。修法不是逐个状态调间距，而是给卡片补 text-align:left——四态一致，且后续再加任何角标或改字号都不会复发
+（8）「0814-3 修订」宽限期卡面「不变脸」＋机制说明改按需展开（推翻 0814-2 初稿的「整卡转琥珀 + 卡内常驻说明段落」）。① 卡底仍用有效会员的靛紫，不整卡转暖——宽限期内权益一样都没少，整卡变色等于暗示身份降级，不准确；且暖卡配靛紫知识球必然撞色。警示色只给真正需要行动的那一个元素＝倒计时（外加「已到期」琥珀角标），「会员」二字保持品牌渐变不染警示色。由此形成三档卡面语言：有效＝靛紫 / 宽限期＝靛紫＋琥珀警示元素 / 已过期＝灰，宽限期在视觉上正好落在两者之间，与其语义一致。② 卡内那段「会员到期附赠 72 小时缓冲期……」整段删除——卡片是身份凭证不是条款栏，且卡上「已到期」+「权益还可使用 剩 N 小时」两个标签已把「到期了 / 还能用 / 还剩多久」说完，该段是同一件事说第二遍。③ 机制说明改为卡外一行可点链接「为什么到期了还能用？」→ 半屏 sheet「关于到期缓冲期」，主按钮「知道了」。三段文案定版：「会员到期享 72 小时缓冲期，全部会员权益正常可用。」「缓冲时长不计会员有效期，缓冲期续费，新时长从缴费当日起算。」「缓冲期满权益暂停，续费后即可立即恢复使用。」链接文案直接用用户的原始疑问，不出现「缓冲期」这一机制名词（与本批 C 端不出现「宽限期」的原则一致）
+（9）「0814-2 口径」缓冲期内续费的有效期起算时点＝实际缴费时刻，不是上一期的到期日。沿用既有顺延规则「会员时长自 max（当前时间, 当前已付费会员到期时间）起顺延累加」——缓冲期内当前时间已晚于到期时间，故取当前时间，用户不会为缓冲期这段时间二次付费。（本条为对既有规则的显式重申：0814-2 初稿曾在宽限期底部写「续费后有效期自 {到期日} 顺延」，与该规则冲突，已随底部说明一并删除）
+（10）「0814-2 口径」宽限期展示的三条定版原则：① C 端不出现「宽限期」这一状态名词——运营四态语义（有效会员 / 宽限期（待续费）/ 会员已过期 / 未开通会员）只在两个后台使用；C 端不让用户先理解一个状态名再自行推断后果，直接讲他能感知的事实「还能用多久」。② 倒计时全程用小时制，向上取整，剩余 ≤1 小时显示「不足 1 小时」，出窗口显示「缓冲期已结束」——72 小时尺度下换算成「2 天 23 小时」会被读成「还早」，反而削弱紧迫感。③ 用琥珀不用赤陶——赤陶＝已失效，琥珀＝还能用但需行动，与两个后台四态标签色（玉绿/琥珀/赤陶/灰）同源。宽限期不区分成因（自动续费扣款失败 / 未开自动续费自然到期）展示同一套文案，CTA 统一为「立即续费」</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1301,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>0807周五更新
+          <t>0814周五更新
 （1）顶部用户卡（点击进个人资料）：头像 + 昵称（无则「未设置昵称」）+ 会员标 + 手机号（未绑显「未绑定手机号」）
 （2）「会员」分组：会员中心（右值 已开通/未开通）
 （3）「我的」分组：我的永享、我的纸书、我的订单、兑换码
@@ -1300,7 +1309,8 @@
 （5）退出登录 → toast「已退出登录」→ 回落地页
 （6）〔评审〕「评审工具」分组：原型清单（三端站点地图）
 （7）「0807 修订」品牌资产接入定稿：C 端登录落地页＝浅色底纯图标 logo（周边彩带环动画按反馈移除）；微信授权弹窗＝蓝底 app 图标版（贴近微信真实授权样式）；两后台登录页品牌区与侧栏品牌位＝横版 logo（图标＋中英文字，原「AI 问书」文字标题移除，侧栏折叠态切纯图标）；三种形态均 base64 内联（BRAND_LOGO / BRAND_LOGO_APP / BRAND_LOGO_FULL）三端共用、不随机构换肤
-（8）「0807 修订」会员状态在 C 端的呈现定稿为二分展示（运营四态语义只在后台）：用户卡会员标——有效会员 / 宽限期（权益仍在）显「会员」，已过期 / 未开通不显标；「会员中心」右值——已开通（有效 / 宽限期）/ 未开通（已过期 / 从未开通）；登录落地页〔演示〕环境切换新增「会员状态」四档（未开通/有效会员/宽限期/已过期），切换即联动上述展示点</t>
+（8）「0807 修订」会员状态在 C 端的呈现定稿为二分展示（运营四态语义只在后台）：用户卡会员标——有效会员 / 宽限期（权益仍在）显「会员」，已过期 / 未开通不显标；「会员中心」右值——已开通（有效 / 宽限期）/ 未开通（已过期 / 从未开通）；登录落地页〔演示〕环境切换新增「会员状态」四档（未开通/有效会员/宽限期/已过期），切换即联动上述展示点
+（9）「0814-2 修订」部分推翻 0807 的二分口径：用户卡会员标维持二分不变（宽限期内权益确实还在，标「会员」不算失实）；但「会员中心」右值在宽限期下由「已开通」改为琥珀色倒计时「剩 {N} 小时」。原因：72 小时窗口极短，用户若不主动进会员中心就完全不知情，而「已开通」三个字等于对用户隐瞒即将断服——入口本身必须承担告知责任。本批触达范围只到「我的」页入口与会员中心两层，不做会话页顶部条幅（打扰度高于收益，如后续实测转化不足再评估）</t>
         </is>
       </c>
     </row>
@@ -2999,7 +3009,7 @@
           <t>0812周三更新
 （1）「0718 修订」价格配置按两种购买方式分组展示，向运营明示每档金额——① 连续包月（自动续费）：首月价格（首月特惠，默认 ¥9.9，仅首次开通的首月扣款）+ 次月起价格（默认 ¥19.9/月，第 2 个月起每月自动扣款）；② 单月（一次性购买 · 不自动续费）：单月价格（默认 ¥19.9/1 个月，一次性扣款、到期自动失效不再扣费）；每档附前台展示位置说明，与前台「开通会员」两档一一对应
 （2）续费规则只读：「按月自动续费，会员到期后 72 小时为服务缓冲期 · 暂不可编辑」
-（3）0717 #7：「调价须知」标题与文案同一行、以「：」衔接——「调价须知：会员价一经确定，非必要请勿修改；已开通自动续费的用户，下一扣费周期将按修改后的价格扣款。」（amber 淡底左边线警示块）
+（3）0717 #7：「调价须知」标题与文案同一行、以「：」衔接——「调价须知：会员价一经确定，非必要请勿修改；已开通自动续费的用户，下一扣费周期将按修改后的价格扣款。」（amber 淡底左边线警示块）【0814-2 收口：本条后半句「下一扣费周期将按修改后的价格扣款」已被本功能点末条 0812 定版的「就低不就高」推翻，此处仅保留警示块的版式沿革记录，扣费口径一律以末条为准】
 （4）「保存」→ toast「已保存价格」
 （5）「0718 修订」「调价须知」警示块移到「保存」按钮右侧（同一行，原在按钮之前独占一行），并去掉左侧 amber 色条、仅保留灰色内容块，页面动线变为：两组价格 → 续费规则 → 保存＋调价须知
 （6）「0718 修订」①「调价须知：」标题去掉加粗（与正文同字重）；②「保存」价格增加二次确认弹窗（说明影响范围：新开通按新价、已开通自动续费的用户下一扣费周期按新价扣款，确认后才生效并 toast「已保存价格」）
@@ -3239,13 +3249,14 @@
         <is>
           <t>0807周五更新
 （1）「0807 修订」页头「机构」筛选由单选升级为多选（覆盖全部机构、来自机构主数据非固定名单；默认全选＝全平台口径）：交互与机构后台主控台机构多选一致——选项行自绘勾选框、父机构选项带「父机构」标、顶部「全部机构」快捷全选（分隔线隔开），触发器回填所选机构名（全选显「全部机构」、部分选择顿号拼接、超宽省略号），至少保留一家；实时总览与经营分析全部指标随所选机构集合联动——计数/金额类绝对量按集合聚合、率类按集合整体口径重算（非各机构简单相加；父机构含其全部子机构、父子同选自动去重）；「入驻机构数」卡显示所选机构数量，区块副标题机构范围超 3 家收敛为「A、B、C 等 N 家」
-（2）「0807 删除」原「选中父机构＝自动汇总该父机构自身及其全部子机构数据，并在页头下方标注『含子机构：A、B』」的汇总口径说明行（紫色引用块）整体删除——机构范围已由多选筛选器直观表达，无需另行说明
-（3）「0807 修订」右侧「导出」：生成「AI问书_全域主控台数据导出.xlsx」，沿用当前机构多选集合与时间筛选（头部筛选条件注明机构范围）；实时/经营分析两 Sheet 分别标注实时统计时间与区间起止，指标全量含环比
-（4）实时总览（标「实时」，不随时间变）：入驻机构数、累计用户、累计 GMV（资金 100% 进各机构账户）、净 GMV（扣退款，平台不参与分账）、提问总量，每卡带 InfoDot
-（5）「0807 新增」实时总览第二行新增内容供给三卡（3 等分满行、与首行左右对齐）：① 知识产品 KP 总数（副行：已发布 / 草稿 / 已下架，数量＋占比）② 知识库文件总数（副行：文档 / 图片 / 音频 / 视频四类，数量＋占比）③ 知识库存储总量（TB，副行：文档与媒体资源的容量＋占比，两者互补 100%，与前两卡「数量＋占比」规则一致）；两行卡片行距 16px 与经营分析多行卡一致——平台运营能力＝机构规模 × 内容供给 × 用户消费 × 商业化，补齐「内容供给」存量视角；三卡均为实时快照、每卡带 InfoDot 口径，导出实时总览 Sheet 同步含此三指标（含副行分布明细）
-（6）经营分析周期与机构后台同口径；每个指标悬浮面板详细展示定义、周期、上一周期、差值单位、零基线处理和是否汇总下级机构
-（7）平台提问量趋势面积图 + 页脚单位规范
-（8）「0722 修订」经营分析新增「续费率」（区间内到期且完成续费的会员数 ÷ 同区间到期会员数）与「回流会员」（区间内开通会员、且开通时会员状态为已过期的用户数，不算新增不算续费），KPI 行改为 3 列两行；「新增会员」口径定稿＝区间内历史首次开通会员（续费、回流均不计入），新增 / 续费 / 回流三者互斥、与机构后台统一</t>
+（2）「0814-4 修订」机构多选升级为层级（树状）多选：选项按 父机构 → 缩进子机构 分组渲染，子机构缩进一级并带归属竖线，一眼可见隶属关系（原为父子视觉平级的平铺列表，用户看不出勾了父机构等于已含子机构，重复勾选子机构时数字不变会被误认为界面失灵）。交互三条：① 勾父＝父自身与其全部子机构一并勾上；② 子机构可单独勾选（此时父呈半选态＝靛蓝描边加一横，区别于全选的实心勾）；③ 由此支持「只看父机构本部」——勾父后取消其全部子机构即可，此前的平铺 + 自动展开口径下这个诉求表达不出来。因机构树深度恒为 2 层、共 13 家，不做展开 / 收起：全展开的滚动成本远低于折叠后找不到某家分社的成本。配套口径变更：联动系数由「按所选集合做父→子展开后求和」改为按选中集合精确求和——界面既然已显式勾选子机构，再做展开会把用户刚取消的子机构强行加回来，令「只看本部」失效。机构后台（主控台 / 数据看板）维持原平铺多选不变
+（3）「0807 删除」原「选中父机构＝自动汇总该父机构自身及其全部子机构数据，并在页头下方标注『含子机构：A、B』」的汇总口径说明行（紫色引用块）整体删除——机构范围已由多选筛选器直观表达，无需另行说明
+（4）「0807 修订」右侧「导出」：生成「AI问书_全域主控台数据导出.xlsx」，沿用当前机构多选集合与时间筛选（头部筛选条件注明机构范围）；实时/经营分析两 Sheet 分别标注实时统计时间与区间起止，指标全量含环比
+（5）实时总览（标「实时」，不随时间变）：入驻机构数、累计用户、累计 GMV（资金 100% 进各机构账户）、净 GMV（扣退款，平台不参与分账）、提问总量，每卡带 InfoDot
+（6）「0807 新增」实时总览第二行新增内容供给三卡（3 等分满行、与首行左右对齐）：① 知识产品 KP 总数（副行：已发布 / 草稿 / 已下架，数量＋占比）② 知识库文件总数（副行：文档 / 图片 / 音频 / 视频四类，数量＋占比）③ 知识库存储总量（TB，副行：文档与媒体资源的容量＋占比，两者互补 100%，与前两卡「数量＋占比」规则一致）；两行卡片行距 16px 与经营分析多行卡一致——平台运营能力＝机构规模 × 内容供给 × 用户消费 × 商业化，补齐「内容供给」存量视角；三卡均为实时快照、每卡带 InfoDot 口径，导出实时总览 Sheet 同步含此三指标（含副行分布明细）
+（7）经营分析周期与机构后台同口径；每个指标悬浮面板详细展示定义、周期、上一周期、差值单位、零基线处理和是否汇总下级机构
+（8）平台提问量趋势面积图 + 页脚单位规范
+（9）「0722 修订」经营分析新增「续费率」（区间内到期且完成续费的会员数 ÷ 同区间到期会员数）与「回流会员」（区间内开通会员、且开通时会员状态为已过期的用户数，不算新增不算续费），KPI 行改为 3 列两行；「新增会员」口径定稿＝区间内历史首次开通会员（续费、回流均不计入），新增 / 续费 / 回流三者互斥、与机构后台统一</t>
         </is>
       </c>
     </row>
@@ -4285,11 +4296,12 @@
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>（1）页头机构筛选覆盖全部机构，父机构带「父机构」标签；选中父机构＝自动汇总该父机构自身及其全部子机构数据，并在页面标注「含子机构：A、B」
+          <t>（1）页头机构筛选覆盖全部机构，父机构带「父机构」标签；选中父机构＝自动汇总该父机构自身及其全部子机构数据
 （2）右侧「导出」：生成「AI问书_全域模型用量数据导出.xlsx」，沿用机构范围与时间区间，实时/区间口径分别标注统计时间；头部注明导出时间与筛选条件
 （3）实时总览（累计，不随时间变）：累计 tokens、累计调用次数（各带 InfoDot）
 （4）经营分析周期与通用指标规则一致；tokens、调用次数用相对百分比，平均响应用绝对时长差，上一周期为0时显示暂无可比增幅。0716：区间 tokens / 区间调用次数 / 平均响应 的环比行去掉重复的 JSX 箭头图标，仅保留数据串内嵌的方向箭头（↑ 上升 / ↓ 缩短），避免双箭头；三张卡数值行与环比行结构一致，卡片高度对齐
-（5）图表：全部机构 → 全平台总量趋势面积图 + Top 机构 token 排行横条；选中单机构 → 该机构趋势</t>
+（5）「0814-2 修订」机构筛选由单选改多选，口径与平台主控台完全一致（原单选下拉「全部 / 单个机构」作废）：默认全选＝全平台口径，回填「全部机构」；部分选中按顿号拼接回填、超宽省略；至少保留一家。多选即累加。「0814-4 修订」升级为层级多选（同平台主控台）：父机构成组、子机构缩进一级并带归属竖线；勾父＝父自身与其全部子机构一并勾上，子机构也可单独勾选（此时父呈半选态＝靛蓝描边加一横）；因只有 2 层、13 家机构，不做展开 / 收起——全展开的滚动成本远低于折叠后找不到某家分社的成本。缩放规则同主控台：绝对量指标（累计 tokens、累计调用次数、区间 tokens、区间调用次数）按所选机构占比累加缩放；均值类指标（平均响应）不累加。实时总览与经营分析两个区段标题均回显当前机构范围（超过 3 家收敛为「A、B、C 等 N 家」）。原「选中父机构时在页面标注『含子机构：A、B』」的汇总说明行删除——与主控台 0806-4 的处理一致，多选回填本身已表达范围
+（6）「0814-2 修订」图表随多选联动：总量趋势恒为「所选机构累加」（不再按全选/单选切换两套布局），标题回显机构范围；Top 机构 token 排行按展开后的所选机构过滤，条形占比相对当前榜首重算；若所选机构均不在榜（榜单为空）则整卡隐藏、趋势图独占整行</t>
         </is>
       </c>
     </row>

--- a/docs/feature-list.xlsx
+++ b/docs/feature-list.xlsx
@@ -2808,23 +2808,30 @@
           <t>数据看板</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C75" s="4" t="inlineStr">
         <is>
           <t>营收分析 Tab</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="inlineStr">
-        <is>
-          <t>（1）小节① 收入与转化（5 KPI）：区间 GMV、付费用户、付费转化率、ARPPU、续费率
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>0819周三更新
+（1）小节① 收入与转化（5 KPI）：区间 GMV、付费用户、付费转化率、ARPPU、续费率
 （2）小节② 退款（4 KPI）：退款金额、退款率、退款订单数、净 GMV（扣退款）
-（3）小节③ 转化漏斗（3 卡）：受限内容触发率、会员漏斗（看到会员页→点击购买→完成支付）、永享转化（触发永享墙→完成购买）
+（3）小节③ 转化漏斗（3 卡）：受限内容触发率、会员漏斗、永享转化
 （4）「0722 修订」小节①新增第 6 个 KPI「回流会员」（区间内开通会员、且开通时会员状态为已过期的用户数；不算新增、不算续费），KPI 行改为 3 列两行
-（5）「0722 修订」「新增会员」口径定稿＝区间内历史首次开通会员的用户数（续费、回流均不计入），两后台统一；新增 / 续费 / 回流三者互斥，任一次开通行为只落入其中一类</t>
+（5）「0722 修订」「新增会员」口径定稿＝区间内历史首次开通会员的用户数（续费、回流均不计入），两后台统一；新增 / 续费 / 回流三者互斥，任一次开通行为只落入其中一类
+（6）「0819 重构」会员漏斗由三步改四步，起点前移至「可转化用户」：可转化用户 → 看到会员页 → 点击购买 → 完成支付。原起点「看到会员页」默认曝光已发生，把「多数可转化用户根本没打开过会员页」这一最大漏点排除在漏斗之外，导致优化资源被导向错误环节
+（7）「0819 重构」会员漏斗分母排除「区间内全程处于有效状态」的会员——他们没有「要不要开通」的决策可做，计入只会稀释转化率，且机构会员占比越高被污染越重、形成反向激励。「有效状态」含到期后 72 小时宽限期（宽限期内权益仍生效，与「当前会员数」口径一致）；判定关键在「全程」，区间内到期且宽限期已走完的会员计入分母
+（8）「0819 重构」永享转化由两步改三步（补入中间的「点击购买」，原「完成购买」更名「完成支付」与订单口径对齐），统计单元由「用户」改「用户 × KP 对」——永享按 KP 单本买断，按用户去重会把「撞 3 本墙只买 1 本」整个记成转化成功（66.7%），真实成交为 6 次机会成交 2 次（33.3%），且用户越重度高估越严重
+（9）「0819 新增」每步同时展示步间转化率（本步 ÷ 上一步，深色主视觉，用于定位是哪一环在漏人）与累计转化率（本步 ÷ 第一步，灰色副信息，用于与历史周期比大盘）；卡底给整体转化率，永享另给人维度副指标（触发人数 / 购买人数 / 人均购买）。两个百分比的分母差异在指标悬浮面板内分条写明
+（10）「0819 新增」漏斗区绝对量一律精确千分位、不走页脚万进制——万进制会把 10,100 舍成「1万」，用户按 2,970 ÷ 1万 = 29.7% 自行验算与卡面标注的 29.4% 对不上，会被当成数据 bug
+（11）「0819 新增」受限内容触发率卡补出分子分母绝对值（触发付费墙 N 次 / 总提问 N 条），并在悬浮面板注明本指标按「次」计、同排两个漏斗按「人」与「用户 × KP 对」计，三卡同属转化主题但单位不同、不可首尾相接读成一条链</t>
         </is>
       </c>
     </row>
@@ -6432,12 +6439,12 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>1）计算式：区间内触发付费墙次数 ÷ 总提问数。2）定位：会员与永享转化的漏斗入口。3）随区间联动。</t>
+          <t>1）计算式：区间内触发付费墙次数 ÷ 同区间总提问数。2）定位：衡量内容付费策略的强度——受限内容铺得够不够、拦得是不是地方。3）「0819 修订」卡内同时给出分子分母绝对值（触发付费墙 N 次 / 总提问 N 条），与同排两个漏斗一致可自行验算。4）「0819 修订」本指标按「次」计（同一用户多次触发计多次），同排会员漏斗按「人」、永享漏斗按「用户 × KP 对」计；三卡同属转化主题但统计单位不同，不可首尾相接读成一条链，悬浮面板已注明。5）随区间联动。</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>不涉及（按次计数）</t>
+          <t>不去重（按次计数）：分母「总提问数」按提问条数计，分子须同单位，故同一用户多次触发计多次；若分子去重到人则比值变成「人 ÷ 条」无意义，需连分母一并换成提问人数——那是另一个指标（受限内容触达率，衡量覆盖面而非策略强度）。「多少人撞过墙」的信息已由永享漏斗「触发人数」与会员漏斗「看到会员页」承载，此卡不重复</t>
         </is>
       </c>
     </row>
@@ -6464,12 +6471,12 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>1）三步：看到会员页 → 点击购买 → 完成支付。2）各步展示去重人数及转化率。3）随区间联动。</t>
+          <t>1）「0819 定版」四步闭合漏斗：可转化用户 → 看到会员页 → 点击购买 → 完成支付（原三步，起点由「看到会员页」前移）。2）各步事件定义：① 可转化用户＝区间内有过提问行为的活跃用户；② 看到会员页＝打开开通会员页（入口为会话内会员付费墙「开通会员」按钮、我的-会员中心两处）；③ 点击购买＝点会员页内开通按钮进收银台；④ 完成支付＝会员订单支付成功，含新增 / 续费 / 回流三类开通。3）「0819 定版」分母口径：可转化用户 = 区间内活跃用户 − 区间内**全程处于有效状态**的会员。「有效状态」含到期后 72 小时宽限期——宽限期内权益仍生效，故宽限期会员计入有效会员、不计入可转化用户，与「当前会员数」两端口径一致（见 0814 / 0814-2）。判定关键在「全程」：只要区间内存在任一时刻该用户已掉出有效状态（付费期结束且宽限期亦结束），即计入可转化用户；因此区间内到期且宽限期已走完的会员计入分母，而区间结束时仍在宽限期内的会员不计入。排除全程有效会员的理由：他们没有「要不要开通」的决策可做，计入只会稀释转化率，且机构会员占比越高被污染越重、形成反向激励。4）「0819 定版」每步同时给两个百分比：步间转化率＝本步 ÷ 上一步（主视觉，用于定位是哪一环在漏人）、累计转化率＝本步 ÷ 可转化用户（副信息，用于与历史周期比大盘）；卡底整体转化率＝完成支付 ÷ 可转化用户。5）闭合漏斗：后一步人群是前一步的严格子集，故各步人数逐级单调不增、永不出现 &gt;100%；未经会员页直达支付的不计入本漏斗（同区间内闭合，跨区间的后续购买不计入本区间）。6）一致性断言：完成支付人数应恒等于同区间「新增会员 + 续费 + 回流」之和（三者互斥，见 0722 口径），不等则说明埋点有缺失。7）随区间联动。</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>各环节按用户 ID 去重</t>
+          <t>各环节按用户 ID 去重（会员为账号级唯一权益，一个用户一个区间只计 1 次）</t>
         </is>
       </c>
     </row>
@@ -6496,12 +6503,12 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>1）两步：触发永享付费墙 → 完成永享购买。2）计算式：完成购买数 ÷ 触发数。3）随区间联动。</t>
+          <t>1）「0819 定版」三步闭合漏斗：触发永享墙 → 点击购买 → 完成支付（原两步「触发 → 完成购买」补入中间的点击环节，「完成购买」更名「完成支付」与订单口径对齐）。2）各步事件定义：① 触发永享墙＝会话内点击永享角标媒体、或大图预览翻页至永享内容时弹出的永享付费墙曝光（该浮层组件按资源门槛 tier 分流：forever 进本漏斗、member 跳开通会员页进会员漏斗，两者视觉几乎一致，埋点必须带 tier 参数，否则两条漏斗数据混淆）；② 点击购买＝点「永久解锁此内容」进收银台（永享无独立商品详情页，点击直达收银台）；③ 完成支付＝该 KP 永享订单支付成功。3）「0819 定版」统计单元为「用户 × KP」对、非用户：永享按 KP 单本买断，一个用户撞 3 本墙只买 1 本时，按用户去重会把他整个记成转化成功（66.7%），而真实成交是 6 次机会成交 2 次（33.3%），且用户越重度、撞墙越多高估越严重；与会员漏斗按用户去重的差异源于售卖单元不同（会员＝账号级订阅、永享＝单本买断），不是口径不统一。4）计算式：永享转化率＝完成支付对数 ÷ 触发永享墙对数；每步同时给步间转化率（÷ 上一步）与累计转化率（÷ 触发永享墙）。5）卡底副指标：触发人数 / 购买人数（人维度覆盖面）、人均购买＝完成支付对数 ÷ 购买人数（复购深度）。6）随区间联动。</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>各环节按用户 ID 去重</t>
+          <t>各环节按「用户 ID + KP ID」对去重（同一用户对同一 KP 重复触发只计 1 对，不同 KP 分别计对）；副指标触发人数 / 购买人数按用户 ID 去重</t>
         </is>
       </c>
     </row>

--- a/docs/feature-list.xlsx
+++ b/docs/feature-list.xlsx
@@ -2829,7 +2829,7 @@
 （6）「0819 重构」会员漏斗由三步改四步，起点前移至「可转化用户」：可转化用户 → 看到会员页 → 点击购买 → 完成支付。原起点「看到会员页」默认曝光已发生，把「多数可转化用户根本没打开过会员页」这一最大漏点排除在漏斗之外，导致优化资源被导向错误环节
 （7）「0819 重构」会员漏斗分母排除「区间内全程处于有效状态」的会员——他们没有「要不要开通」的决策可做，计入只会稀释转化率，且机构会员占比越高被污染越重、形成反向激励。「有效状态」含到期后 72 小时宽限期（宽限期内权益仍生效，与「当前会员数」口径一致）；判定关键在「全程」，区间内到期且宽限期已走完的会员计入分母
 （8）「0819 重构」永享转化由两步改三步（补入中间的「点击购买」，原「完成购买」更名「完成支付」与订单口径对齐），统计单元由「用户」改「用户 × KP 对」——永享按 KP 单本买断，按用户去重会把「撞 3 本墙只买 1 本」整个记成转化成功（66.7%），真实成交为 6 次机会成交 2 次（33.3%），且用户越重度高估越严重
-（9）「0819 新增」每步同时展示步间转化率（本步 ÷ 上一步，深色主视觉，用于定位是哪一环在漏人）与累计转化率（本步 ÷ 第一步，灰色副信息，用于与历史周期比大盘）；卡底给整体转化率，永享另给人维度副指标（触发人数 / 购买人数 / 人均购买）。两个百分比的分母差异在指标悬浮面板内分条写明
+（9）「0819 新增」每步同时展示步间转化率（本步 ÷ 上一步，深色主视觉，用于定位是哪一环在漏人）与累计转化率（本步 ÷ 第一步，灰色副信息，用于与历史周期比大盘）；卡底给整体转化率，永享另给人维度副指标（触发人数 / 购买人数）。两个百分比的分母差异在指标悬浮面板内分条写明
 （10）「0819 新增」漏斗区绝对量一律精确千分位、不走页脚万进制——万进制会把 10,100 舍成「1万」，用户按 2,970 ÷ 1万 = 29.7% 自行验算与卡面标注的 29.4% 对不上，会被当成数据 bug
 （11）「0819 新增」受限内容触发率卡补出分子分母绝对值（触发付费墙 N 次 / 总提问 N 条），并在悬浮面板注明本指标按「次」计、同排两个漏斗按「人」与「用户 × KP 对」计，三卡同属转化主题但单位不同、不可首尾相接读成一条链</t>
         </is>
@@ -6503,7 +6503,7 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>1）「0819 定版」三步闭合漏斗：触发永享墙 → 点击购买 → 完成支付（原两步「触发 → 完成购买」补入中间的点击环节，「完成购买」更名「完成支付」与订单口径对齐）。2）各步事件定义：① 触发永享墙＝会话内点击永享角标媒体、或大图预览翻页至永享内容时弹出的永享付费墙曝光（该浮层组件按资源门槛 tier 分流：forever 进本漏斗、member 跳开通会员页进会员漏斗，两者视觉几乎一致，埋点必须带 tier 参数，否则两条漏斗数据混淆）；② 点击购买＝点「永久解锁此内容」进收银台（永享无独立商品详情页，点击直达收银台）；③ 完成支付＝该 KP 永享订单支付成功。3）「0819 定版」统计单元为「用户 × KP」对、非用户：永享按 KP 单本买断，一个用户撞 3 本墙只买 1 本时，按用户去重会把他整个记成转化成功（66.7%），而真实成交是 6 次机会成交 2 次（33.3%），且用户越重度、撞墙越多高估越严重；与会员漏斗按用户去重的差异源于售卖单元不同（会员＝账号级订阅、永享＝单本买断），不是口径不统一。4）计算式：永享转化率＝完成支付对数 ÷ 触发永享墙对数；每步同时给步间转化率（÷ 上一步）与累计转化率（÷ 触发永享墙）。5）卡底副指标：触发人数 / 购买人数（人维度覆盖面）、人均购买＝完成支付对数 ÷ 购买人数（复购深度）。6）随区间联动。</t>
+          <t>1）「0819 定版」三步闭合漏斗：触发永享墙 → 点击购买 → 完成支付（原两步「触发 → 完成购买」补入中间的点击环节，「完成购买」更名「完成支付」与订单口径对齐）。2）各步事件定义：① 触发永享墙＝会话内点击永享角标媒体、或大图预览翻页至永享内容时弹出的永享付费墙曝光（该浮层组件按资源门槛 tier 分流：forever 进本漏斗、member 跳开通会员页进会员漏斗，两者视觉几乎一致，埋点必须带 tier 参数，否则两条漏斗数据混淆）；② 点击购买＝点「永久解锁此内容」进收银台（永享无独立商品详情页，点击直达收银台）；③ 完成支付＝该 KP 永享订单支付成功。3）「0819 定版」统计单元为「用户 × KP」对、非用户：永享按 KP 单本买断，一个用户撞 3 本墙只买 1 本时，按用户去重会把他整个记成转化成功（66.7%），而真实成交是 6 次机会成交 2 次（33.3%），且用户越重度、撞墙越多高估越严重；与会员漏斗按用户去重的差异源于售卖单元不同（会员＝账号级订阅、永享＝单本买断），不是口径不统一。4）计算式：永享转化率＝完成支付对数 ÷ 触发永享墙对数；每步同时给步间转化率（÷ 上一步）与累计转化率（÷ 触发永享墙）。5）卡底副指标：触发人数 / 购买人数（人维度覆盖面，均按用户 ID 去重）。6）随区间联动。</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
